--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G13"/>
+  <dimension ref="B2:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -615,6 +615,11 @@
           <t>Diperbarui: 3 Juli 2026 -- lihat sheet 'Backlog' untuk daftar task lengkap dan bisa diedit (Status, PIC).</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Diperbarui: 12 Juli 2026 -- lihat sheet 'Backlog' untuk daftar task lengkap dan bisa diedit (Status, PIC).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
@@ -675,7 +680,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Sebagian Selesai</t>
+          <t>Selesai (kecuali L4 worker/queue, sengaja ditunda ke Sprint 2)</t>
         </is>
       </c>
     </row>
@@ -829,6 +834,37 @@
         <v/>
       </c>
       <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Panel Admin</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Minggu 11-12</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Admin bisa kelola user, moderasi konten, dan pantau transaksi</t>
+        </is>
+      </c>
+      <c r="F14" s="8">
+        <f>COUNTIF(Backlog!B:B,"Sprint 6")</f>
+        <v/>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Belum Mulai</t>
         </is>
@@ -845,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1469,16 +1505,20 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr"/>
       <c r="I14" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="J14" s="12" t="inlineStr"/>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>Aktif di ci.yml sebagai blocking gate, install-mode: goinstall</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
@@ -1553,9 +1593,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr"/>
@@ -1564,7 +1604,7 @@
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>Repo belum diinisialisasi git</t>
+          <t>Sudah push ke github.com/Ijeon-Corp/JeonMe</t>
         </is>
       </c>
     </row>
@@ -1597,16 +1637,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H17" s="15" t="inlineStr"/>
       <c r="I17" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="16" t="inlineStr"/>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>Kedua environment (staging + production) live di VPS 103.147.33.34</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
@@ -1637,16 +1681,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr"/>
       <c r="I18" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="J18" s="12" t="inlineStr"/>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>Terisi, lihat SETUP-GUIDE.md</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
@@ -1677,16 +1725,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H19" s="15" t="inlineStr"/>
       <c r="I19" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="J19" s="16" t="inlineStr"/>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>Token GHCR aktif, dipakai CI/CD</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
@@ -1717,16 +1769,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr"/>
       <c r="I20" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="J20" s="12" t="inlineStr"/>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>Secrets &amp; Environments (staging/production) terkonfigurasi, required reviewer aktif untuk production</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
@@ -1757,16 +1813,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H21" s="15" t="inlineStr"/>
       <c r="I21" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="J21" s="16" t="inlineStr"/>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>DNS Cloudflare sudah diarahkan, live</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
@@ -1797,16 +1857,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr"/>
       <c r="I22" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="J22" s="12" t="inlineStr"/>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>Sertifikat TLS terbit via certbot, auto-renew lewat certbot.timer</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
@@ -1837,16 +1901,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H23" s="15" t="inlineStr"/>
       <c r="I23" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="J23" s="16" t="inlineStr"/>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>staging.jeonme.com live, /api/health terverifikasi</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
@@ -1877,16 +1945,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr"/>
       <c r="I24" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="J24" s="12" t="inlineStr"/>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>jeonme.com live sejak rilis v0.1.0, /api/health terverifikasi</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
@@ -3535,6 +3607,134 @@
         <v>1</v>
       </c>
       <c r="J64" s="12" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>Manajemen user admin (lihat, suspend/aktifkan akun kreator)</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>REQ-F-701</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G65" s="19" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n"/>
+      <c r="I65" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>Butuh endpoint &amp; guard role=admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Moderasi konten (tinjau &amp; takedown halaman/produk yang dilaporkan)</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>REQ-F-702</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n"/>
+      <c r="I66" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" s="16" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>Dashboard admin (ringkasan user, transaksi, laporan)</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>REQ-F-703</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G67" s="19" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n"/>
+      <c r="I67" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>Sebelumnya tidak ada task-nya sama sekali di backlog -- ditambahkan setelah audit cakupan SRS</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J64"/>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -56,7 +56,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +103,12 @@
         <fgColor rgb="00E2ECF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -130,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -179,6 +185,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -711,7 +720,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Sebagian Selesai (OAuth Google diblokir, upload foto profil sebagian)</t>
         </is>
       </c>
     </row>
@@ -1989,16 +1998,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>Diblokir</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr"/>
       <c r="I25" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="16" t="inlineStr"/>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>Butuh GOOGLE_CLIENT_ID/SECRET dari Google Cloud Console (belum ada) -- endpoint lain di AuthHandler sudah siap menampung begitu credential tersedia</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n">
@@ -2029,16 +2042,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr"/>
       <c r="I26" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="12" t="inlineStr"/>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>POST /auth/password-reset/request+confirm, token sekali pakai TTL 1 jam. Pengiriman email sungguhan masih TODO (belum ada provider SMTP)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
@@ -2069,16 +2086,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G27" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H27" s="15" t="inlineStr"/>
       <c r="I27" s="15" t="n">
         <v>1.5</v>
       </c>
-      <c r="J27" s="16" t="inlineStr"/>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>POST /auth/email-verification/request+confirm, token TTL 24 jam. Sama seperti reset password, pengiriman email masih TODO</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n">
@@ -2109,16 +2130,20 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr"/>
       <c r="I28" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="12" t="inlineStr"/>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>POST /auth/logout menaruh jti ke denylist Redis, AuthRequired menolak token yang jti-nya di-revoke. Diverifikasi: token ditolak 401 setelah logout</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
@@ -2149,16 +2174,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G29" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H29" s="15" t="inlineStr"/>
       <c r="I29" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="J29" s="16" t="inlineStr"/>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>CRUD penuh + reorder drag-and-drop di dashboard/links, ownership ditegakkan (user lain 404 saat coba edit/hapus tautan orang lain)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n">
@@ -2189,9 +2218,9 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G30" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr"/>
@@ -2200,7 +2229,7 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>Bagian dari task CRUD tautan</t>
+          <t>Bagian dari update Links -- toggle is_active di UI yang sama</t>
         </is>
       </c>
     </row>
@@ -2233,16 +2262,20 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H31" s="15" t="inlineStr"/>
       <c r="I31" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="16" t="inlineStr"/>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>5 preset (default/midnight/sunrise/forest/minimal) via PATCH /dashboard/page, dipilih dari dashboard/links</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n">
@@ -2273,9 +2306,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G32" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr"/>
@@ -2284,7 +2317,7 @@
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>Butuh object storage -- lihat Sprint 2</t>
+          <t>Bio sudah bisa diedit; upload FOTO PROFIL masih menunggu object storage (Sprint 2, task No 40) -- avatar_url di skema belum ada jalan untuk diisi</t>
         </is>
       </c>
     </row>
@@ -2317,16 +2350,20 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G33" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H33" s="15" t="inlineStr"/>
       <c r="I33" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="J33" s="16" t="inlineStr"/>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>generateMetadata (OpenGraph + Twitter card) di app/[username]/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n">
@@ -2357,9 +2394,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G34" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr"/>
@@ -2368,7 +2405,7 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>Kerangka komentar sudah ada di page.go</t>
+          <t>Cache-aside 30 detik di GetPublicPage (key page:&lt;username&gt;), diverifikasi X-Cache: MISS lalu HIT. Invalidate saat UpdateMyPage</t>
         </is>
       </c>
     </row>
@@ -2401,9 +2438,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G35" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H35" s="15" t="inlineStr"/>
@@ -2412,7 +2449,7 @@
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>TODO tercatat di dashboard/layout.tsx</t>
+          <t>AuthGuard client component, redirect ke /login kalau token kosong. Diverifikasi end-to-end di browser (register -&gt; dashboard tanpa 404/mismatch)</t>
         </is>
       </c>
     </row>
@@ -2445,9 +2482,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G36" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr"/>
@@ -2456,7 +2493,7 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>Sidebar sudah menaut ke sini tapi 404</t>
+          <t>dashboard/links (pengaturan halaman+tautan), dashboard/products (list+create), dashboard/balance (placeholder menunggu Sprint 4) -- sudah tidak 404</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -751,7 +751,7 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Sebagian Selesai (worker/job queue -- No 41 -- masih ditunda)</t>
         </is>
       </c>
     </row>
@@ -2526,9 +2526,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G37" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H37" s="15" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>Create &amp; List sudah ada</t>
+          <t>PATCH/DELETE /dashboard/products/:id, ownership ditegakkan (diuji: user lain 404)</t>
         </is>
       </c>
     </row>
@@ -2570,16 +2570,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G38" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr"/>
       <c r="I38" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="12" t="inlineStr"/>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>Whitelist ekstensi (pdf/zip/epub/mp4/mp3/mov/gambar) + batas 100MB. 'Pemindaian dasar' = whitelist ekstensi, BUKAN antivirus/malware scan sungguhan -- catat sebagai batasan MVP</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
@@ -2610,16 +2614,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G39" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H39" s="15" t="inlineStr"/>
       <c r="I39" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="16" t="inlineStr"/>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>is_active=true ditolak (400) selama file_key kosong, diuji end-to-end di browser</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n">
@@ -2650,16 +2658,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G40" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr"/>
       <c r="I40" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="12" t="inlineStr"/>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>PresignedGetObject 15 menit, diverifikasi bisa diunduh &amp; benar-benar berisi file yang diunggah</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
@@ -2690,16 +2702,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G41" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H41" s="15" t="inlineStr"/>
       <c r="I41" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="J41" s="16" t="inlineStr"/>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>MinIO self-hosted (bukan R2) -- service baru di docker-compose.yml/.staging.yml/.prod.yml, bucket auto-dibuat saat startup (EnsureBucket). Kredensial default di .env.example HARUS diganti di VPS</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n">

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -2713,7 +2713,7 @@
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>MinIO self-hosted (bukan R2) -- service baru di docker-compose.yml/.staging.yml/.prod.yml, bucket auto-dibuat saat startup (EnsureBucket). Kredensial default di .env.example HARUS diganti di VPS</t>
+          <t>MinIO self-hosted (bukan R2) -- service baru di docker-compose.yml/.staging.yml/.prod.yml, bucket auto-dibuat saat startup. Signed download URL (REQ-F-304) diekspos publik lewat subdomain storage.jeonme.com/storage-staging.jeonme.com (Apache reverse-proxy + TLS, port MinIO non-default 29000/29100 karena VPS shared -- lihat bug #14/#15 CICD-GUIDE.md). Diverifikasi end-to-end: upload+aktivasi+unduh via URL publik sungguhan dari luar VPS.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Sebagian Selesai (Xendit sungguhan diblokir, notifikasi butuh worker)</t>
         </is>
       </c>
     </row>
@@ -2790,9 +2790,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G43" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>Diblokir</t>
         </is>
       </c>
       <c r="H43" s="15" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>Wajib beres sebelum mulai sprint ini</t>
+          <t>Belum ada akun sandbox Xendit -- semua task Sprint 3 lain dikerjakan sejauh bisa diverifikasi tanpa akun sungguhan</t>
         </is>
       </c>
     </row>
@@ -2834,16 +2834,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G44" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr"/>
       <c r="I44" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="J44" s="12" t="inlineStr"/>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>POST /api/checkout (order dalam transaksi, rollback kalau Xendit gagal), produk harus is_active=true. Diverifikasi end-to-end (browser + curl)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
@@ -2874,16 +2878,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G45" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
         </is>
       </c>
       <c r="H45" s="15" t="inlineStr"/>
       <c r="I45" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="J45" s="16" t="inlineStr"/>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>internal/xendit/client.go: Invoice API (QRIS/VA/e-wallet sekaligus lewat halaman hosted Xendit) sudah ditulis sesuai dokumentasi publik, TAPI BELUM PERNAH dipanggil ke API Xendit sungguhan -- diblokir No.42. Perilaku 'belum dikonfigurasi' sudah diuji (rollback order, pesan jelas)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="n">
@@ -2914,9 +2922,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G46" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr"/>
@@ -2925,7 +2933,7 @@
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>Satu-satunya sumber kebenaran status bayar</t>
+          <t>POST /api/webhooks/xendit menolak x-callback-token salah (401) sebelum payload diproses. Diuji dengan payload sintetis sesuai format dokumentasi Xendit</t>
         </is>
       </c>
     </row>
@@ -2958,16 +2966,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G47" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H47" s="15" t="inlineStr"/>
       <c r="I47" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="16" t="inlineStr"/>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>Unique index psp_transaction_id (partial, WHERE != ''), INSERT ON CONFLICT DO NOTHING. Diuji: webhook sama dikirim 2x, order tetap benar, tepat 1 baris payments</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="n">
@@ -3009,7 +3021,7 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>Pakai worker dari Sprint 2</t>
+          <t>Butuh worker/job queue (Sprint 2 No.41, sengaja ditunda) + provider email/WhatsApp -- belum ada keduanya</t>
         </is>
       </c>
     </row>
@@ -3042,16 +3054,20 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G49" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H49" s="15" t="inlineStr"/>
       <c r="I49" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="16" t="inlineStr"/>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>Halaman /checkout/[id] menampilkan pesan sesuai status (pending/paid/expired/failed), polling status selama masih pending</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="n">

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Sebagian Selesai (rekonsiliasi admin &amp; disbursement sungguhan butuh Sprint 6 / Xendit)</t>
         </is>
       </c>
     </row>
@@ -3098,9 +3098,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G50" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>Tabel skema sudah ada</t>
+          <t>Saldo direkonstruksi dari SUM(ledger_entries.amount_idr), tidak ada kolom saldo tersendiri. platform_fee_idr (default 5%, PLACEHOLDER bisnis via env PLATFORM_FEE_PERCENT) dipotong saat kredit</t>
         </is>
       </c>
     </row>
@@ -3142,16 +3142,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G51" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H51" s="15" t="inlineStr"/>
       <c r="I51" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="J51" s="16" t="inlineStr"/>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>Held = kredit dalam HOLDING_PERIOD_DAYS (default 3, via env) dihitung ulang tiap request (bukan job terjadwal). Diuji: kredit baru -&gt; tertahan, setelah lewat periode -&gt; tersedia</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n">
@@ -3182,16 +3186,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G52" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr"/>
       <c r="I52" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="J52" s="12" t="inlineStr"/>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>POST /dashboard/payouts -- validasi saldo tersedia (advisory lock per-user cegah race), langsung mendebit ledger saat pengajuan (bukan saat cair) supaya saldo sama tidak bisa diajukan 2x. Rekening TIDAK diverifikasi (KYC/REQ-F-105 belum ada)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
@@ -3222,16 +3230,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G53" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
         </is>
       </c>
       <c r="H53" s="15" t="inlineStr"/>
       <c r="I53" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="16" t="inlineStr"/>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>Status tersimpan &amp; tampil (requested/processing/completed/failed) tapi TIDAK PERNAH berubah otomatis dari 'requested' -- belum ada integrasi Xendit Disbursement API ataupun aksi admin manual untuk memprosesnya</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
@@ -3271,7 +3283,11 @@
       <c r="I54" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="J54" s="12" t="inlineStr"/>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>Butuh Panel Admin (Sprint 6) untuk aksi manual memproses payouts.status</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
@@ -3302,16 +3318,20 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G55" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H55" s="15" t="inlineStr"/>
       <c r="I55" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="16" t="inlineStr"/>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>Sudah dikerjakan sejak audit CI/CD awal (commit 221b6ad) -- deploy-staging.yml &amp; deploy-production.yml sudah punya workflow_dispatch input image_tag. Baris ini sebelumnya salah tercatat Belum Mulai</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="n">

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Sebagian Selesai (smoke test uang sungguhan diblokir Xendit, checklist go-live perlu review manual akhir)</t>
         </is>
       </c>
     </row>
@@ -3362,16 +3362,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G56" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr"/>
       <c r="I56" s="11" t="n">
         <v>1.5</v>
       </c>
-      <c r="J56" s="12" t="inlineStr"/>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>POST /pages/:username/track (publik, fail-silent) mencatat view/click ke analytics_events. Tracking dipasang di halaman publik (view saat load, click per tautan)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
@@ -3402,16 +3406,20 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G57" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H57" s="15" t="inlineStr"/>
       <c r="I57" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="J57" s="16" t="inlineStr"/>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>GET /dashboard/analytics/summary: total view/klik + deret harian 30 hari, ditampilkan sebagai bar chart CSS sederhana di dashboard Ringkasan</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n">
@@ -3442,16 +3450,20 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G58" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr"/>
       <c r="I58" s="11" t="n">
         <v>1.5</v>
       </c>
-      <c r="J58" s="12" t="inlineStr"/>
+      <c r="J58" s="12" t="inlineStr">
+        <is>
+          <t>Produk terlaris dihitung dari order status='paid' (bukan sekadar dibuat). Sumber trafik dari kolom referrer analytics_events</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="15" t="n">
@@ -3482,16 +3494,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G59" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H59" s="15" t="inlineStr"/>
       <c r="I59" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J59" s="16" t="inlineStr"/>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>Redis fixed-window per IP: 10/menit untuk auth (register+login berbagi kuota), 20/menit checkout, 60/menit track. Fail-open kalau Redis down. Diuji: request ke-11 balas 429</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n">
@@ -3522,16 +3538,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G60" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr"/>
       <c r="I60" s="11" t="n">
         <v>1.5</v>
       </c>
-      <c r="J60" s="12" t="inlineStr"/>
+      <c r="J60" s="12" t="inlineStr">
+        <is>
+          <t>Tabel audit_log (user_id, action, entity_type, entity_id, metadata jsonb), dicatat DI DALAM transaksi yang sama dengan perubahan (order.paid, ledger.credit, payout.requested, user.deleted) supaya tidak pernah hilang kalau di-rollback</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="15" t="n">
@@ -3562,16 +3582,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G61" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G61" s="20" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H61" s="15" t="inlineStr"/>
       <c r="I61" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="J61" s="16" t="inlineStr"/>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>Consent WAJIB dicentang saat registrasi (consent_accepted_at dicatat). Hapus akun = ANONIMISASI (email/username diganti, password_hash dihapus, halaman+produk dinonaktifkan) BUKAN hapus baris fisik -- order/ledger/payment tetap ada untuk kebutuhan pembukuan. CATATAN: ini implementasi MVP berdasarkan pemahaman umum, BUKAN nasihat hukum bersertifikasi -- perlu review oleh yang paham UU PDP secara spesifik sebelum go-live sungguhan</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n">
@@ -3602,16 +3626,20 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G62" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr"/>
       <c r="I62" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="J62" s="12" t="inlineStr"/>
+      <c r="J62" s="12" t="inlineStr">
+        <is>
+          <t>Duplikat dari No.13 (Sprint 0) yang sudah selesai sejak bug #11 (commit d6ff131) -- baris ini sebelumnya salah tercatat Belum Mulai</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="15" t="n">
@@ -3642,9 +3670,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G63" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G63" s="20" t="inlineStr">
+        <is>
+          <t>Diblokir</t>
         </is>
       </c>
       <c r="H63" s="15" t="inlineStr"/>
@@ -3653,7 +3681,7 @@
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>Wajib sebelum go-live publik</t>
+          <t>Sama seperti integrasi Xendit (No.44/Sprint 3) -- butuh akun sandbox Xendit yang belum ada</t>
         </is>
       </c>
     </row>
@@ -3686,16 +3714,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G64" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G64" s="20" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr"/>
       <c r="I64" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="12" t="inlineStr"/>
+      <c r="J64" s="12" t="inlineStr">
+        <is>
+          <t>Checklist di CICD-GUIDE.md Bagian 14 sebagian besar sudah tercentang dari kerja sebelumnya -- perlu review manual sekali lagi sebelum benar-benar go-live publik (bukan sekadar deploy teknis)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="15" t="n">

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -875,7 +875,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Selesai</t>
         </is>
       </c>
     </row>
@@ -3758,9 +3758,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G65" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H65" s="15" t="n"/>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>Butuh endpoint &amp; guard role=admin</t>
+          <t>GET/PATCH /admin/users -- cari, suspend (blokir login dengan pesan jelas), aktifkan lagi. Diuji: suspend-&gt;login ditolak 403-&gt;aktifkan-&gt;login pulih</t>
         </is>
       </c>
     </row>
@@ -3802,16 +3802,20 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G66" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="J66" s="16" t="n"/>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>POST /reports (publik, tanpa akun) + GET/PATCH /admin/reports untuk admin. Takedown diverifikasi benar-benar unpublish halaman/nonaktifkan produk</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="15" t="n">
@@ -3842,9 +3846,9 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G67" s="19" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H67" s="15" t="n"/>
@@ -3853,7 +3857,7 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>Sebelumnya tidak ada task-nya sama sekali di backlog -- ditambahkan setelah audit cakupan SRS</t>
+          <t>GET /admin/summary: total user, user baru 7 hari, transaksi lunas, pendapatan, laporan tertunda. Tidak ada endpoint API untuk jadi admin (sengaja SQL manual saja) -- AdminRequired selalu cek role ke DB, bukan klaim JWT</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -597,6 +597,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -626,10 +627,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Diperbarui: 12 Juli 2026 -- lihat sheet 'Backlog' untuk daftar task lengkap dan bisa diedit (Status, PIC).</t>
-        </is>
-      </c>
-    </row>
+          <t>Diperbarui: 16 Juli 2026 -- migrasi PSP Xendit -&gt; Midtrans, worker/job queue (asynq) selesai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -689,7 +691,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Selesai (kecuali L4 worker/queue, sengaja ditunda ke Sprint 2)</t>
+          <t>Selesai</t>
         </is>
       </c>
     </row>
@@ -751,7 +753,7 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (worker/job queue -- No 41 -- masih ditunda)</t>
+          <t>Selesai</t>
         </is>
       </c>
     </row>
@@ -782,7 +784,7 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (Xendit sungguhan diblokir, notifikasi butuh worker)</t>
+          <t>Sebagian Selesai (Midtrans sungguhan diblokir -- provider diganti dari Xendit; notifikasi email infra selesai &amp; terverifikasi, SMTP provider &amp; kanal WhatsApp masih belum ada)</t>
         </is>
       </c>
     </row>
@@ -813,7 +815,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (rekonsiliasi admin &amp; disbursement sungguhan butuh Sprint 6 / Xendit)</t>
+          <t>Sebagian Selesai (rekonsiliasi admin &amp; disbursement sungguhan butuh Sprint 6 / Midtrans)</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (smoke test uang sungguhan diblokir Xendit, checklist go-live perlu review manual akhir)</t>
+          <t>Sebagian Selesai (smoke test uang sungguhan diblokir Midtrans, checklist go-live perlu review manual akhir)</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1562,7 @@
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H15" s="15" t="inlineStr"/>
@@ -1569,7 +1571,7 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>Prasyarat untuk Sprint 2 &amp; 3</t>
+          <t>internal/queue (task asynq + payload), internal/mailer (SMTP, soft-fail log-only kalau SMTP_HOST kosong), internal/worker (handler order.paid), subcommand `./api worker` (proses terpisah dari server HTTP, docker-compose service `worker`). Diverifikasi end-to-end: server+worker nyata dijalankan, webhook Midtrans -&gt; enqueue Redis -&gt; worker memproses -&gt; log notifikasi terkirim.</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2750,7 @@
       </c>
       <c r="G42" s="19" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr"/>
@@ -2757,7 +2759,7 @@
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>Prasyarat notifikasi async di Sprint 3</t>
+          <t>Duplikat No.14 (Sprint 0) yang sudah selesai -- lihat catatan di sana untuk detail verifikasi.</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2779,7 @@
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>Aktifkan akun sandbox Xendit (dependensi blocking sebelum coding)</t>
+          <t>Aktifkan akun sandbox Midtrans (dependensi blocking sebelum verifikasi API sungguhan)</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
@@ -2801,7 +2803,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>Belum ada akun sandbox Xendit -- semua task Sprint 3 lain dikerjakan sejauh bisa diverifikasi tanpa akun sungguhan</t>
+          <t>Provider payment diganti dari Xendit ke Midtrans (instruksi user). internal/midtrans/client.go (Snap API) menggantikan internal/xendit (dihapus) -- checkout.go, config.go, routes.go, test, docs semua diperbarui. Belum ada akun sandbox/production Midtrans -- MIDTRANS_SERVER_KEY masih kosong di .env, semua task lain dikerjakan sejauh bisa diverifikasi tanpa akun sungguhan.</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2867,7 @@
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Integrasi Xendit -- QRIS, Virtual Account, e-wallet</t>
+          <t>Integrasi Midtrans -- QRIS, Virtual Account, e-wallet (via Snap API)</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
@@ -2889,7 +2891,7 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>internal/xendit/client.go: Invoice API (QRIS/VA/e-wallet sekaligus lewat halaman hosted Xendit) sudah ditulis sesuai dokumentasi publik, TAPI BELUM PERNAH dipanggil ke API Xendit sungguhan -- diblokir No.42. Perilaku 'belum dikonfigurasi' sudah diuji (rollback order, pesan jelas)</t>
+          <t>internal/midtrans/client.go: Snap API (satu panggilan menghasilkan halaman pembayaran hosted Midtrans yang mendukung QRIS/VA/e-wallet sekaligus) sudah ditulis sesuai dokumentasi publik, TAPI BELUM PERNAH dipanggil ke API Midtrans sungguhan -- diblokir No.42. Perilaku 'belum dikonfigurasi' sudah diuji (rollback order, pesan jelas 503). Verifikasi signature webhook (SHA512 order_id+status_code+gross_amount+ServerKey) &amp; idempotensi diuji end-to-end lewat webhook nyata (proses server+worker berjalan, bukan cuma unit test).</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3014,7 @@
       </c>
       <c r="G48" s="19" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Sebagian</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr"/>
@@ -3021,7 +3023,7 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>Butuh worker/job queue (Sprint 2 No.41, sengaja ditunda) + provider email/WhatsApp -- belum ada keduanya</t>
+          <t>Infra notifikasi EMAIL selesai &amp; diverifikasi end-to-end: CheckoutHandler.Webhook enqueue task (hanya sekali walau webhook duplikat -- bug ditemukan &amp; diperbaiki saat verifikasi manual) -&gt; worker proses -&gt; kirim email dengan link unduhan permanen (GET /checkout/:id/download, presigned URL baru dibuat tiap klik). SMTP_HOST belum diisi (belum ada provider asli) -- mailer soft-fail log-only, BUKAN gagal/crash. Kanal WhatsApp belum diimplementasi sama sekali.</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3683,7 @@
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>Sama seperti integrasi Xendit (No.44/Sprint 3) -- butuh akun sandbox Xendit yang belum ada</t>
+          <t>Sama seperti integrasi Midtrans (No.44/Sprint 3) -- butuh akun sandbox Midtrans yang belum ada.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Diperbarui: 16 Juli 2026 -- migrasi PSP Xendit -&gt; Midtrans, worker/job queue (asynq) selesai.</t>
+          <t>Diperbarui: 16 Juli 2026 -- Midtrans sandbox &amp; SMTP Gmail aktif di staging+production, worker/job queue terverifikasi kirim email nyata.</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (Midtrans sungguhan diblokir -- provider diganti dari Xendit; notifikasi email infra selesai &amp; terverifikasi, SMTP provider &amp; kanal WhatsApp masih belum ada)</t>
+          <t>Sebagian Selesai (Midtrans SANDBOX aktif &amp; terverifikasi di staging+production; notifikasi email selesai &amp; terverifikasi dengan SMTP sungguhan; WhatsApp &amp; akun Midtrans production sungguhan masih belum ada)</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="G43" s="20" t="inlineStr">
         <is>
-          <t>Diblokir</t>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H43" s="15" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>Provider payment diganti dari Xendit ke Midtrans (instruksi user). internal/midtrans/client.go (Snap API) menggantikan internal/xendit (dihapus) -- checkout.go, config.go, routes.go, test, docs semua diperbarui. Belum ada akun sandbox/production Midtrans -- MIDTRANS_SERVER_KEY masih kosong di .env, semua task lain dikerjakan sejauh bisa diverifikasi tanpa akun sungguhan.</t>
+          <t>Akun sandbox Midtrans aktif -- MIDTRANS_SERVER_KEY/CLIENT_KEY terpasang &amp; terverifikasi end-to-end (checkout sungguhan ke API sandbox Midtrans berhasil, redirect_url nyata diterima) di lokal, staging (staging.jeonme.com), DAN production (jeonme.com). MIDTRANS_IS_PRODUCTION=false di KEDUA environment -- production masih pakai kredensial SANDBOX (uang test, bukan uang sungguhan) sampai ada keputusan bisnis untuk pakai akun Midtrans production sungguhan.</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="G45" s="20" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H45" s="15" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>internal/midtrans/client.go: Snap API (satu panggilan menghasilkan halaman pembayaran hosted Midtrans yang mendukung QRIS/VA/e-wallet sekaligus) sudah ditulis sesuai dokumentasi publik, TAPI BELUM PERNAH dipanggil ke API Midtrans sungguhan -- diblokir No.42. Perilaku 'belum dikonfigurasi' sudah diuji (rollback order, pesan jelas 503). Verifikasi signature webhook (SHA512 order_id+status_code+gross_amount+ServerKey) &amp; idempotensi diuji end-to-end lewat webhook nyata (proses server+worker berjalan, bukan cuma unit test).</t>
+          <t>internal/midtrans/client.go (Snap API) terverifikasi end-to-end melawan API sandbox Midtrans sungguhan -- checkout nyata menghasilkan redirect_url Snap yang valid. Signature webhook (SHA512) &amp; idempotensi diuji dengan webhook nyata. CATATAN: ini masih mode SANDBOX (lihat No.42) -- transaksi uang sungguhan belum bisa diproses sampai akun Midtrans production diaktifkan.</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>Infra notifikasi EMAIL selesai &amp; diverifikasi end-to-end: CheckoutHandler.Webhook enqueue task (hanya sekali walau webhook duplikat -- bug ditemukan &amp; diperbaiki saat verifikasi manual) -&gt; worker proses -&gt; kirim email dengan link unduhan permanen (GET /checkout/:id/download, presigned URL baru dibuat tiap klik). SMTP_HOST belum diisi (belum ada provider asli) -- mailer soft-fail log-only, BUKAN gagal/crash. Kanal WhatsApp belum diimplementasi sama sekali.</t>
+          <t>Kanal EMAIL selesai &amp; terverifikasi SEPENUHNYA end-to-end dengan kredensial SMTP Gmail sungguhan (bukan simulasi) -- worker berhasil mengirim email nyata ke inbox lewat smtp.gmail.com, dikonfirmasi tanpa error di lokal, staging, dan production. Konektivitas port SMTP 587 dari VPS juga dicek langsung (tidak diblokir provider). Kanal WhatsApp masih BELUM diimplementasi sama sekali.</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>Sama seperti integrasi Midtrans (No.44/Sprint 3) -- butuh akun sandbox Midtrans yang belum ada.</t>
+          <t>Masih diblokir -- kredensial Midtrans yang terpasang (No.42) adalah kredensial SANDBOX (uang test), belum akun production sungguhan. Smoke test dengan uang sungguhan baru bisa dilakukan setelah ada keputusan bisnis untuk mengaktifkan Midtrans production.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (OAuth Google diblokir, upload foto profil sebagian)</t>
+          <t>Sebagian Selesai (OAuth Google diblokir -- butuh GOOGLE_CLIENT_ID/SECRET)</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="G32" s="20" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr"/>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>Bio sudah bisa diedit; upload FOTO PROFIL masih menunggu object storage (Sprint 2, task No 40) -- avatar_url di skema belum ada jalan untuk diisi</t>
+          <t>Upload foto profil selesai: POST /dashboard/page/avatar (whitelist jpg/png/webp, maks 5MB), key selalu "avatars/&lt;userID&gt;" (upload ulang menimpa, tidak ada file lama menumpuk). Bucket MinIO diberi kebijakan public-read HANYA untuk prefix avatars/ (EnsurePublicRead) -- avatar_url jadi URL publik PERMANEN (bukan presigned 15 menit seperti file produk), prefix products/ tetap privat (diverifikasi 403). Diuji end-to-end: upload PNG asli, diunduh publik tanpa auth &amp; isinya identik, tampil di GetMyPage &amp; GetPublicPage, upload ulang menimpa URL yang sama, ekstensi tidak dikenal (.exe) ditolak.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Diperbarui: 16 Juli 2026 -- Midtrans sandbox &amp; SMTP Gmail aktif di staging+production, worker/job queue terverifikasi kirim email nyata.</t>
+          <t>Diperbarui: 17 Juli 2026 -- rekonsiliasi disbursement admin (No.53) selesai, panel admin didesain ulang.</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (rekonsiliasi admin &amp; disbursement sungguhan butuh Sprint 6 / Midtrans)</t>
+          <t>Sebagian Selesai (rekonsiliasi admin selesai -- No.53; disbursement OTOMATIS via Midtrans API sungguhan masih belum ada, diproses manual oleh admin untuk sekarang)</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>Status tersimpan &amp; tampil (requested/processing/completed/failed) tapi TIDAK PERNAH berubah otomatis dari 'requested' -- belum ada integrasi Xendit Disbursement API ataupun aksi admin manual untuk memprosesnya</t>
+          <t>Status TIDAK berubah otomatis dari "requested" (belum ada integrasi Midtrans Disbursement API sungguhan), TAPI aksi admin manual sekarang sudah ada (No.53, PATCH /admin/payouts/:id) -- admin bisa memproses requested-&gt;processing-&gt;completed/failed secara manual setelah transfer dana asli di luar sistem. Real-time otomatis masih jadi pekerjaan lanjutan.</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="G54" s="19" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr"/>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>Butuh Panel Admin (Sprint 6) untuk aksi manual memproses payouts.status</t>
+          <t>GET /admin/payouts (lintas semua kreator, filter status) + PATCH /admin/payouts/:id (state machine requested-&gt;processing-&gt;completed, atau -&gt;failed dari kedua state). Belum ada integrasi Disbursement API sungguhan -- admin transfer dana manual di luar sistem lalu tandai statusnya di sini. Kalau ditandai "failed", ledger debit yang dicatat saat pengajuan di-REVERSE (dikredit balik) supaya saldo kreator tidak hilang. Halaman /admin/payouts baru (filter Perlu Tindakan/Semua Riwayat). Diverifikasi end-to-end: payout diproses sampai selesai, payout lain ditandai gagal &amp; saldo terkonfirmasi kembali, transisi status tidak valid ditolak 400.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Linktree - Menu &amp; Alur" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lynkid - Menu &amp; Alur" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UX Gabungan Jeonme" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog'!$A$1:$J$64</definedName>
@@ -20,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,13 +58,33 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1B4D3E"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="17">
     <fill>
-      <patternFill/>
+      <patternFill>
+        <fgColor rgb="00F2F5F3"/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="00F2F5F3"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -109,8 +132,36 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF2FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B4D3E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -132,11 +183,25 @@
         <color rgb="00D8DDD9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD8DDD9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD8DDD9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD8DDD9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD8DDD9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -190,6 +255,34 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -585,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="B2:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -597,7 +690,6 @@
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -631,7 +723,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -878,6 +969,300 @@
       <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Selesai</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Fase 2 (Ekspansi Fitur Kompetitif) -- referensi Linktree &amp; Lynk.id, 6 sprint dua-mingguan lanjutan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Diperbarui: 23 Juli 2026 -- hasil analisis kompetitor Linktree + Lynk.id (tur langsung dashboard live kedua akun sungguhan) dicatat sebagai backlog No.67-99 di sheet 'Backlog'. Detail menu &amp; alur kerja per platform ada di sheet 'Linktree - Menu &amp; Alur' dan 'Lynkid - Menu &amp; Alur'. Rekomendasi IA gabungan (lebih sederhana dari keduanya) ada di sheet 'UX Gabungan Jeonme'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Nama</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Durasi</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Tujuan</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Jumlah Task</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Ekspansi Monetisasi Produk</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Minggu 13-14</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Voucher/diskon, flash sale, bayar-seikhlasnya, bundel produk, blok donasi, program afiliasi</t>
+        </is>
+      </c>
+      <c r="F20" s="6">
+        <f>COUNTIF(Backlog!B:B,"Sprint 7")</f>
+        <v/>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 8</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Retensi Audiens &amp; Pemasaran</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Minggu 15-16</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Kumpulkan &amp; jangkau audiens lewat form lead + WhatsApp/email</t>
+        </is>
+      </c>
+      <c r="F21" s="8">
+        <f>COUNTIF(Backlog!B:B,"Sprint 8")</f>
+        <v/>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Sprint 9</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Blok Konten &amp; Desain Halaman</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Minggu 17-18</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Blok tautan lebih kaya, domain kustom, kustomisasi desain lanjutan</t>
+        </is>
+      </c>
+      <c r="F22" s="6">
+        <f>COUNTIF(Backlog!B:B,"Sprint 9")</f>
+        <v/>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 10</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Kepercayaan &amp; Analitik Lanjutan</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Minggu 19-20</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>KYC payout, watermark file, analitik mendalam, tim/multi-admin</t>
+        </is>
+      </c>
+      <c r="F23" s="8">
+        <f>COUNTIF(Backlog!B:B,"Sprint 10")</f>
+        <v/>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Sprint 11</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Event, Kelas &amp; Booking</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Minggu 21-22</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Perluasan tipe produk non-file (tiket event, kursus, booking konsultasi)</t>
+        </is>
+      </c>
+      <c r="F24" s="6">
+        <f>COUNTIF(Backlog!B:B,"Sprint 11")</f>
+        <v/>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 12</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Perluasan Toko Fisik (opsional)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Minggu 23-24</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Validasi permintaan pasar dulu -- perluasan besar di luar fokus produk digital</t>
+        </is>
+      </c>
+      <c r="F25" s="8">
+        <f>COUNTIF(Backlog!B:B,"Sprint 12")</f>
+        <v/>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Temuan Tambahan (Eksplorasi Langsung)</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Minggu 25-26</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Fitur baru yang ditemukan lewat tur langsung akun sungguhan (login nyata), bukan cuma dokumentasi publik: poin loyalitas, kartu kontak digital, asisten analitik AI</t>
+        </is>
+      </c>
+      <c r="F26" s="8">
+        <f>COUNTIF(Backlog!B:B,"Sprint 13")</f>
+        <v/>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 14</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Ide Masa Depan (Belum Prioritas)</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Minggu 27-28</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Fitur yang ditemukan lewat riset tapi sengaja ditunda (scope besar/tangensial): multi-halaman bio, builder landing page AI</t>
+        </is>
+      </c>
+      <c r="F27" s="8">
+        <f>COUNTIF(Backlog!B:B,"Sprint 14")</f>
+        <v/>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
         </is>
       </c>
     </row>
@@ -892,7 +1277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3860,6 +4245,1458 @@
       <c r="J67" s="16" t="inlineStr">
         <is>
           <t>GET /admin/summary: total user, user baru 7 hari, transaksi lunas, pendapatan, laporan tertunda. Tidak ada endpoint API untuk jadi admin (sengaja SQL manual saja) -- AdminRequired selalu cek role ke DB, bukan klaim JWT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C68" s="22" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="inlineStr">
+        <is>
+          <t>Kode voucher/diskon per produk (persentase atau nominal, kode tunggal atau generate massal sekali pakai, syarat minimum pembelian, maksimum diskon, berlaku untuk produk tertentu/semua produk)</t>
+        </is>
+      </c>
+      <c r="E68" s="22" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G68" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H68" s="22" t="n"/>
+      <c r="I68" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J68" s="23" t="inlineStr">
+        <is>
+          <t>Diadaptasi dari fitur Voucher Lynk.id (tipe Percentage/Percentage-with-cap/Nominal/Nominal-with-cap, hanya 1 voucher per checkout). Perlu tabel vouchers baru + validasi di endpoint checkout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
+        <is>
+          <t>Flash sale / diskon waktu terbatas per produk (harga coret otomatis kembali ke harga normal setelah periode berakhir)</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>Lynk.id+Linktree</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G69" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n"/>
+      <c r="I69" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>Kedua platform punya ini sebagai pendorong konversi jangka pendek. Field start/end time di tabel products, harga coret dihitung otomatis di FE saat aktif.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C70" s="22" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="inlineStr">
+        <is>
+          <t>Opsi harga "bayar seikhlasnya" (pay-what-you-want) dengan batas harga minimum</t>
+        </is>
+      </c>
+      <c r="E70" s="22" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G70" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H70" s="22" t="n"/>
+      <c r="I70" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J70" s="23" t="inlineStr">
+        <is>
+          <t>Fitur Digital Product Lynk.id ("Allow customer to pay what they want"). Cocok untuk kreator konten edukasi/donasi-driven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D71" s="16" t="inlineStr">
+        <is>
+          <t>Bundel produk (gabung beberapa produk digital jadi satu paket harga diskon, tampil dengan harga asli dicoret)</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n"/>
+      <c r="I71" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>Diverifikasi langsung di toko publik Lynk.id sungguhan (miss.buku) -- pola "[COMPLETE BUNDLE]" dengan harga coret. Butuh tabel product_bundles (relasi many-to-many ke products) + akses gabungan file saat checkout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="22" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C72" s="22" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="inlineStr">
+        <is>
+          <t>Blok Dukungan/Donasi (tip jar) -- pengunjung beri nominal bebas ke kreator tanpa perlu "membeli produk"</t>
+        </is>
+      </c>
+      <c r="E72" s="22" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G72" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H72" s="22" t="n"/>
+      <c r="I72" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J72" s="23" t="inlineStr">
+        <is>
+          <t>Fitur "Supports" Lynk.id. Versi awal: nominal sekali bayar saja (skip dulu kadens berulang mingguan/bulanan -- itu butuh integrasi subscription/recurring charge Midtrans terpisah, catat sebagai pekerjaan lanjutan kalau permintaannya tervalidasi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>Program afiliasi (kreator undang afiliator dengan komisi custom per produk; link afiliasi unik dilacak, komisi otomatis masuk ledger afiliator saat order lunas)</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G73" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n"/>
+      <c r="I73" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>Diverifikasi langsung di dashboard afiliasi Lynk.id (mode privat: undang + komisi custom; mode publik: marketplace lintas kreator). Versi awal Jeonme: mode privat dulu (undang by user_id/email), marketplace publik lintas kreator jadi fase lanjutan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 8</t>
+        </is>
+      </c>
+      <c r="C74" s="22" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D74" s="23" t="inlineStr">
+        <is>
+          <t>Blok pengumpulan email/nomor WhatsApp pengunjung + Manajer Audiens (daftar subscriber per kreator, ekspor CSV)</t>
+        </is>
+      </c>
+      <c r="E74" s="22" t="inlineStr">
+        <is>
+          <t>Lynk.id+Linktree</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G74" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H74" s="22" t="n"/>
+      <c r="I74" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J74" s="23" t="inlineStr">
+        <is>
+          <t>Kedua platform sentralisasi semua lead (form, pembeli, subscribe-lock) ke satu Audience Manager yang bisa diekspor. Fondasi wajib sebelum broadcast WhatsApp (No.75) bisa jalan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 8</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D75" s="16" t="inlineStr">
+        <is>
+          <t>Kanal notifikasi WhatsApp untuk pembeli (lanjutan No.47 -- saat ini hanya kanal EMAIL yang selesai, WhatsApp belum diimplementasi sama sekali)</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>Backlog internal No.47</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G75" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="n"/>
+      <c r="I75" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>Bukan temuan baru dari riset kompetitor, tapi gap lama yang jadi lebih mendesak karena kedua platform kompetitor andalkan WhatsApp sebagai kanal utama notifikasi pembeli Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="22" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 8</t>
+        </is>
+      </c>
+      <c r="C76" s="22" t="inlineStr">
+        <is>
+          <t>BE+Ops</t>
+        </is>
+      </c>
+      <c r="D76" s="23" t="inlineStr">
+        <is>
+          <t>WhatsApp blast/broadcast promosi ke daftar subscriber/pembeli</t>
+        </is>
+      </c>
+      <c r="E76" s="22" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G76" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H76" s="22" t="n"/>
+      <c r="I76" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J76" s="23" t="inlineStr">
+        <is>
+          <t>Fitur WhatsApp Blast Lynk.id (pairing nomor WA kreator sendiri ala WhatsApp Web, kirim promo+kode voucher). PERLU KEPUTUSAN BISNIS dulu: WhatsApp Business API resmi (butuh approval Meta, lebih mahal, lebih aman ToS) vs gateway tidak resmi (risiko nomor diblokir) -- jangan mulai coding sebelum ini diputuskan. -- UPDATE (verifikasi live Lynk.id): follow-up otomatis pasca-WhatsApp Blast ("Follow Up Text") tersedia sebagai fitur terpisah, hingga 10 template, TAPI hard-gated di belakang WhatsApp Blast yang sudah tersambung lebih dulu -- konfirmasi urutan pengerjaan: Blast dulu baru Follow Up Text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 8</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="D77" s="16" t="inlineStr">
+        <is>
+          <t>"X baru saja membeli produk ini" -- notifikasi social proof di halaman publik</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="n"/>
+      <c r="I77" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="16" t="inlineStr">
+        <is>
+          <t>Fitur Social Proof Notifications Lynk.id (PRO). Murah dikerjakan, dampak konversi terbukti di industri e-commerce. -- UPDATE (verifikasi live Lynk.id, layar konfigurasi sungguhan dibuka langsung): durasi tampil (5/10/15 detik), interval sebelum notifikasi berikutnya (10/15/30/45/60 detik), cakupan per-produk atau semua produk, toggle terpisah untuk halaman produk vs halaman checkout, pilihan bahasa, dan email pembeli SELALU disamarkan sebagian di pesan (mis. "rumi****am@gmail.com telah membeli...") -- bukan ditampilkan penuh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="22" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 9</t>
+        </is>
+      </c>
+      <c r="C78" s="22" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D78" s="23" t="inlineStr">
+        <is>
+          <t>Blok tautan baru: video embed (YouTube/TikTok auto-embed), formulir kontak, FAQ/accordion</t>
+        </is>
+      </c>
+      <c r="E78" s="22" t="inlineStr">
+        <is>
+          <t>Linktree+Lynk.id</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G78" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H78" s="22" t="n"/>
+      <c r="I78" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J78" s="23" t="inlineStr">
+        <is>
+          <t>Saat ini Jeonme hanya punya tautan polos. Ketiga tipe blok ini paling sering dipakai di kedua platform berdasarkan katalog blok "Add new block".</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 9</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D79" s="16" t="inlineStr">
+        <is>
+          <t>Penjadwalan tautan (tautan otomatis tampil/sembunyi pada rentang tanggal &amp; waktu tertentu)</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>Linktree</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="n"/>
+      <c r="I79" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J79" s="16" t="inlineStr">
+        <is>
+          <t>Fitur Schedule links Linktree (Starter+). Berguna untuk promo musiman/preorder tanpa harus manual on/off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="22" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 9</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D80" s="23" t="inlineStr">
+        <is>
+          <t>Kunci tautan (age lock/kode akses/wajib subscribe dulu sebelum tautan terbuka)</t>
+        </is>
+      </c>
+      <c r="E80" s="22" t="inlineStr">
+        <is>
+          <t>Linktree</t>
+        </is>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G80" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H80" s="22" t="n"/>
+      <c r="I80" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J80" s="23" t="inlineStr">
+        <is>
+          <t>3 dari 4 jenis link-lock Linktree yang relevan (skip NFT lock -- di luar konteks Jeonme). Subscribe-lock sekalian jadi sumber lead baru untuk Manajer Audiens (No.73).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 9</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D81" s="16" t="inlineStr">
+        <is>
+          <t>Kustomisasi desain lanjutan (latar gambar/video kustom, pilihan font, warna tombol lebih granular) di luar 5 preset tema yang sudah ada</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>Lynk.id+Linktree</t>
+        </is>
+      </c>
+      <c r="F81" s="17" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="n"/>
+      <c r="I81" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J81" s="16" t="inlineStr">
+        <is>
+          <t>Kedua platform expose kustomisasi jauh lebih dalam dari preset saja (Lynk.id: background flat/gradient/gambar + 16 pilihan font + gaya tombol fill/outline/shadow terpisah dari warna tombol).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="22" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 9</t>
+        </is>
+      </c>
+      <c r="C82" s="22" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D82" s="23" t="inlineStr">
+        <is>
+          <t>Domain kustom untuk halaman kreator (kreator arahkan CNAME domain sendiri ke jeonme.com)</t>
+        </is>
+      </c>
+      <c r="E82" s="22" t="inlineStr">
+        <is>
+          <t>Gap analysis (Linktree tidak punya sama sekali, Lynk.id fitur PRO)</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H82" s="22" t="n"/>
+      <c r="I82" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J82" s="23" t="inlineStr">
+        <is>
+          <t>DIFERENSIATOR: Linktree eksplisit TIDAK menyediakan domain kustom maupun domain forwarding sama sekali (dikonfirmasi di help center mereka) -- ini peluang nyata Jeonme unggul dari kompetitor terbesar sekaligus menyamai fitur PRO Lynk.id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 9</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>FE+BE</t>
+        </is>
+      </c>
+      <c r="D83" s="16" t="inlineStr">
+        <is>
+          <t>QR code otomatis per halaman kreator (untuk materi promosi offline)</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>Linktree+Lynk.id</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="n"/>
+      <c r="I83" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="16" t="inlineStr">
+        <is>
+          <t>Fitur murah, dampak besar untuk kreator yang promosi offline (banner event, kemasan produk, dsb).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="22" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 9</t>
+        </is>
+      </c>
+      <c r="C84" s="22" t="inlineStr">
+        <is>
+          <t>FE+BE</t>
+        </is>
+      </c>
+      <c r="D84" s="23" t="inlineStr">
+        <is>
+          <t>Meta SEO kustom per halaman (judul/deskripsi custom) + toggle indexing mesin pencari</t>
+        </is>
+      </c>
+      <c r="E84" s="22" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G84" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H84" s="22" t="n"/>
+      <c r="I84" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="23" t="inlineStr">
+        <is>
+          <t>Jeonme sudah punya OG tags (No.32) -- ini melengkapi dengan kontrol judul/deskripsi manual + opsi noindex untuk kreator yang mau halamannya privat dari pencarian Google.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 10</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="inlineStr">
+        <is>
+          <t>Verifikasi rekening (KYC dasar) sebagai syarat pencairan instan</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H85" s="15" t="n"/>
+      <c r="I85" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J85" s="16" t="inlineStr">
+        <is>
+          <t>Melanjutkan catatan No.51 ("rekening TIDAK diverifikasi"). Di Lynk.id, akun ter-KYC dapat pencairan instan sementara akun belum terverifikasi tertahan -- pola yang sama bisa diterapkan Jeonme untuk kurangi risiko fraud penarikan. -- UPDATE (verifikasi live Lynk.id lewat FAQ resmi mereka): checklist KYC lengkap -- nama di KTP harus sama persis dengan nama rekening bank, selfie sambil pegang KTP, bukti buku tabungan/e-statement, alamat domisili lengkap, penjelasan bisnis+kanal promosi, halaman sudah punya minimal 1 produk aktif, SLA review 3x24 jam hari kerja. Verifikasi ini SEKALIGUS membuka 3 hal: pencairan instan, partisipasi affiliate publik, dan fitur pembayaran personal ("PaymeLynk"). CATATAN TAMBAHAN: Lynk.id juga baru menambah langkah "Bank Account Revalidation" terpisah (April 2026) di atas KYC awal -- kemungkinan besar dorongan kepatuhan PSP/regulasi, bukan sekadar fitur produk. Akun BELUM terverifikasi tetap bisa jualan &amp; tarik dana, hanya lebih lambat (2 hari kerja) -- desain Jeonme sebaiknya ikuti pola ini (jangan blokir total, hanya perlambat).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 10</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D86" s="23" t="inlineStr">
+        <is>
+          <t>Watermark otomatis pada file digital terjual (email+ID transaksi pembeli disisipkan ke file)</t>
+        </is>
+      </c>
+      <c r="E86" s="22" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G86" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H86" s="22" t="n"/>
+      <c r="I86" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J86" s="23" t="inlineStr">
+        <is>
+          <t>Fitur Custom Watermark Lynk.id (PRO) -- anti-pembajakan/pelacakan kebocoran file. Realistis hanya untuk file PDF dulu (paling mudah disisipi watermark terprogram). -- UPDATE (verifikasi live Lynk.id, layar konfigurasi sungguhan dibuka langsung): sumber teks watermark bisa email pembeli ATAU teks custom, posisi (tengah/atas/bawah), ukuran (kecil/sedang/besar), slider opacity (default 50%), dengan preview posisi langsung di layar. CATATAN PENTING dari Lynk.id sendiri: watermark HANYA berfungsi untuk PDF yang tidak dikunci password -- file yang sudah diproteksi password tidak bisa diberi watermark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 10</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="inlineStr">
+        <is>
+          <t>Analitik lanjutan: filter rentang tanggal kustom, breakdown perangkat &amp; lokasi pengunjung, ekspor CSV</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>Linktree+Lynk.id</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="n"/>
+      <c r="I87" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J87" s="16" t="inlineStr">
+        <is>
+          <t>Analitik Jeonme saat ini (No.56/57) baru total view/klik + tren 30 hari + produk terlaris + referrer. Kedua kompetitor jauh lebih dalam (device/lokasi/rentang custom/CSV export).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="22" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 10</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D88" s="23" t="inlineStr">
+        <is>
+          <t>Manajemen tim/multi-admin untuk kreator (undang kolaborator dengan akses terbatas ke halaman/produknya)</t>
+        </is>
+      </c>
+      <c r="E88" s="22" t="inlineStr">
+        <is>
+          <t>Linktree+Lynk.id</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G88" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H88" s="22" t="n"/>
+      <c r="I88" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J88" s="23" t="inlineStr">
+        <is>
+          <t>Berguna untuk kreator yang pakai jasa admin/tim kecil (fitur Admin Invites Linktree &amp; Multi Admin Lynk.id, keduanya paid-tier).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 10</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>Badge terverifikasi untuk kreator (syarat: profil lengkap + email terverifikasi + minimal 1 transaksi sukses)</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>Linktree</t>
+        </is>
+      </c>
+      <c r="F89" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H89" s="15" t="n"/>
+      <c r="I89" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="16" t="inlineStr">
+        <is>
+          <t>Sinyal kepercayaan murah untuk pembeli, memakai data yang sudah ada di sistem (tidak perlu proses manual review seperti Linktree).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="22" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 10</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D90" s="23" t="inlineStr">
+        <is>
+          <t>Transparansi biaya per metode pembayaran ke kreator (rincian potongan QRIS/VA/e-wallet sebelum checkout &amp; di ringkasan saldo)</t>
+        </is>
+      </c>
+      <c r="E90" s="22" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G90" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H90" s="22" t="n"/>
+      <c r="I90" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J90" s="23" t="inlineStr">
+        <is>
+          <t>Lynk.id menampilkan tabel biaya per channel secara eksplisit ke penjual (mis. QRIS 0.70%, VA flat Rp3-4rb). Jeonme saat ini memotong platform_fee_idr flat tanpa rincian per channel pembayaran ke kreator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 11</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="inlineStr">
+        <is>
+          <t>Blok Event (tiket berbayar dengan tanggal/waktu/zona waktu, kuota peserta)</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F91" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H91" s="15" t="n"/>
+      <c r="I91" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J91" s="16" t="inlineStr">
+        <is>
+          <t>Fitur Event block Lynk.id -- ticketing sederhana untuk event online/offline, dijual seperti produk biasa lewat mesin checkout yang sudah ada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 11</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D92" s="23" t="inlineStr">
+        <is>
+          <t>Blok Kelas/Kursus video (materi per bab, prasyarat, deskripsi pembelajaran)</t>
+        </is>
+      </c>
+      <c r="E92" s="22" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F92" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G92" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H92" s="22" t="n"/>
+      <c r="I92" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J92" s="23" t="inlineStr">
+        <is>
+          <t>Fitur Course Video Lynk.id &amp; Digital Products/Courses Linktree. Perluasan natural dari produk digital yang sudah ada (file upload) jadi terstruktur per-bab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 11</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t>Booking konsultasi berbayar dengan sinkronisasi Google Calendar</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>Lynk.id+Linktree</t>
+        </is>
+      </c>
+      <c r="F93" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H93" s="15" t="n"/>
+      <c r="I93" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J93" s="16" t="inlineStr">
+        <is>
+          <t>Fitur Bookings (Linktree, gratis di semua tier) &amp; Appointment (Lynk.id). Butuh integrasi Google Calendar API (OAuth terpisah dari login) untuk cegah bentrok jadwal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="22" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 12</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D94" s="23" t="inlineStr">
+        <is>
+          <t>Dukungan produk fisik (varian, berat/dimensi, ongkir per kurir Indonesia seperti JNE/SiCepat/J&amp;T, area pengiriman per provinsi)</t>
+        </is>
+      </c>
+      <c r="E94" s="22" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F94" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G94" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H94" s="22" t="n"/>
+      <c r="I94" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J94" s="23" t="inlineStr">
+        <is>
+          <t>Fitur commerce terdalam Lynk.id (listing 20 kategori, kalkulasi ongkir, banyak kurir). CATATAN PENTING: ini perluasan besar di luar fokus awal Jeonme sebagai platform produk DIGITAL kreator -- menambah kompleksitas logistik/fulfillment signifikan (integrasi ongkir, pelacakan pengiriman, retur). Validasi permintaan pasar dulu sebelum dikerjakan, jangan asumsikan otomatis dibutuhkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D95" s="16" t="inlineStr">
+        <is>
+          <t>Program poin loyalitas + katalog reward yang bisa ditukar (poin dari pembelian, persentase/nominal, syarat minimum pembelian)</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>Lynk.id</t>
+        </is>
+      </c>
+      <c r="F95" s="17" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H95" s="15" t="n"/>
+      <c r="I95" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J95" s="16" t="inlineStr">
+        <is>
+          <t>Diverifikasi langsung di akun Lynk.id sungguhan ("Member Point System"): tipe poin Percentage/Percentage-with-Limit/Nominal/Nominal-with-Limit + field Min Purchase, dan halaman Reward Management terpisah (katalog reward: Value/Valid Date/Points Needed/Redeemed/Publish). Cocok disandingkan dengan voucher (No.67) sebagai mekanisme retensi pembeli berulang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="25" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="25" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="C96" s="25" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D96" s="26" t="inlineStr">
+        <is>
+          <t>Kartu kontak digital/NFC (QR code + Apple/Google Wallet, kreator bisa terima kontak balik dari pengunjung yang scan)</t>
+        </is>
+      </c>
+      <c r="E96" s="25" t="inlineStr">
+        <is>
+          <t>Linktree</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G96" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H96" s="25" t="n"/>
+      <c r="I96" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J96" s="26" t="inlineStr">
+        <is>
+          <t>Ditemukan lewat tur live dashboard Linktree sungguhan (bukan cuma dokumentasi publik) -- fitur "Business Cards" beneran menghasilkan QR code + Apple Wallet pass, dengan toggle "Let visitors share their details back" yang mengumpulkan nama/email pengunjung yang scan balik. Beda dari kunci tautan (No.79) -- ini pertukaran kontak DUA ARAH, bukan gerbang akses konten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>Asisten analitik berbasis AI (chat tanya-jawab bahasa natural atas data analitik milik kreator sendiri)</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>Linktree</t>
+        </is>
+      </c>
+      <c r="F97" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G97" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="n"/>
+      <c r="I97" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J97" s="16" t="inlineStr">
+        <is>
+          <t>Ditemukan lewat tur live dashboard Linktree -- panel "Ask Linktree AI" aktif secara default di tab Insight dengan prompt siap pakai ("Where is my traffic coming from?", dst). CATATAN: hitung dulu biaya API LLM per-query sebelum komit -- jangan asumsikan gratis seperti fitur analitik biasa (No.86).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="25" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="25" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="C98" s="25" t="inlineStr">
+        <is>
+          <t>UX+FE</t>
+        </is>
+      </c>
+      <c r="D98" s="26" t="inlineStr">
+        <is>
+          <t>Redesain information architecture dashboard kreator: gabungkan navigasi jadi 6 bagian besar (Ringkasan, Halaman Saya, Produk &amp; Monetisasi, Audiens &amp; Pemasaran, Saldo &amp; Penarikan, Pengaturan)</t>
+        </is>
+      </c>
+      <c r="E98" s="25" t="inlineStr">
+        <is>
+          <t>Sintesis gabungan Linktree+Lynk.id (lihat sheet 'UX Gabungan Jeonme')</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G98" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H98" s="25" t="n"/>
+      <c r="I98" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J98" s="26" t="inlineStr">
+        <is>
+          <t>KERJAKAN DULUAN sebelum item lain di Sprint 7-10 supaya fitur baru (voucher/afiliasi/audiens/dsb) langsung masuk ke IA yang benar, bukan ditempel di struktur lama. Linktree pisah Links/Shop/Design jadi tab beda-beda dan nyembunyiin Settings di menu 'More'; Lynk.id sebar fitur commerce ke banyak sidebar terpisah (Voucher/Affiliates/Settings&gt;Store Management) -- keduanya butuh banyak klik untuk hal yang buat kreator terasa satu kesatuan. Jeonme gabung jadi 6 bagian: Ringkasan (analitik), Halaman Saya (tautan+produk+desain+preview), Produk &amp; Monetisasi (voucher/bundel/afiliasi/poin), Audiens &amp; Pemasaran (lead+WhatsApp+social proof), Saldo &amp; Penarikan (sudah ada), Pengaturan (domain/SEO/tim/watermark).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="22" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 14</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D99" s="23" t="inlineStr">
+        <is>
+          <t>Dukungan multi-halaman bio per akun kreator</t>
+        </is>
+      </c>
+      <c r="E99" s="22" t="inlineStr">
+        <is>
+          <t>Linktree ("Your Pages")</t>
+        </is>
+      </c>
+      <c r="F99" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G99" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H99" s="22" t="n"/>
+      <c r="I99" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J99" s="23" t="inlineStr">
+        <is>
+          <t>Diverifikasi live: 1 akun bisa punya beberapa halaman bio terpisah (masing-masing URL sendiri). Berguna untuk kreator yang kelola beberapa brand/proyek dari satu akun. Belum prioritas -- Jeonme masih fokus perkuat 1 halaman per kreator dulu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="25" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="25" t="inlineStr">
+        <is>
+          <t>Sprint 14</t>
+        </is>
+      </c>
+      <c r="C100" s="25" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D100" s="26" t="inlineStr">
+        <is>
+          <t>Builder landing page dengan AI generate, terpisah dari halaman bio utama</t>
+        </is>
+      </c>
+      <c r="E100" s="25" t="inlineStr">
+        <is>
+          <t>Linktree ("Landing Pages", label NEW)</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G100" s="24" t="inlineStr">
+        <is>
+          <t>Belum Mulai</t>
+        </is>
+      </c>
+      <c r="H100" s="25" t="n"/>
+      <c r="I100" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J100" s="26" t="inlineStr">
+        <is>
+          <t>Diverifikasi live: fitur baru Linktree, tombol 'Create with AI' untuk generate draft halaman landing lengkap. Ini lebih ke arah website builder daripada link-in-bio -- scope besar &amp; tangensial dari fokus Jeonme, dicatat sebagai ide masa depan bukan prioritas sekarang.</t>
         </is>
       </c>
     </row>
@@ -3889,4 +5726,2049 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Menu Utama</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Sub-menu / Fitur</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>Fungsi</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>Alur Kerja (Workflow)</t>
+        </is>
+      </c>
+      <c r="F1" s="27" t="inlineStr">
+        <is>
+          <t>Verifikasi</t>
+        </is>
+      </c>
+      <c r="G1" s="27" t="inlineStr">
+        <is>
+          <t>Insight untuk Jeonme</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>My Linktree</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>Links</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Kelola daftar tautan halaman publik</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Klik "+ Add" -&gt; pilih kategori (Collection/Link/Product/Form) -&gt; isi detail -&gt; tautan muncul di list, bisa drag-reorder &amp; toggle aktif/nonaktif -&gt; otomatis tampil di preview kanan</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G2" s="28" t="inlineStr">
+        <is>
+          <t>Jeonme sudah punya versi dasar ini (dashboard/links). Pembeda: kategori 'Collection' (grup tautan jadi carousel) &amp; 'Form' belum ada di Jeonme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>My Linktree</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>Kurasi produk (link eksternal atau produk sendiri) sebagai etalase terpisah dari daftar tautan</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>Toggle "Publish your Shop" -&gt; klik "+Add" -&gt; tempel link produk (dari mana saja) atau pilih dari akun terhubung (IG/TikTok/YouTube/Email) -&gt; produk tampil grid terpisah, ada tab "Affiliate Products" untuk produk komisi</t>
+        </is>
+      </c>
+      <c r="F3" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G3" s="29" t="inlineStr">
+        <is>
+          <t>Beda dari Produk Jeonme (selalu file sendiri) -- ini kurasi link produk APA SAJA, termasuk punya orang lain (mode afiliasi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>My Linktree</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Kustomisasi visual halaman publik</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Pilih Theme preset -&gt; override manual per elemen: Header/Wallpaper/Buttons/Text(font)/Colors/Stickers/Footer, tiap satu buka panel sendiri, preview update langsung di kanan</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>Struktur 'satu tema besar + override manual per elemen' lebih rapi daripada preset kaku Jeonme (5 tema tanpa override) -- selaras dengan No.80.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Earn</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>Ringkasan semua fitur monetisasi (Shops/Sponsored Links/Brand Deals/Rewards)</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>Buka tab -&gt; kalau negara/tier tidak eligible, halaman kosong isinya cuma 'Got ideas? Share feedback' -- fitur di baliknya TIDAK muncul sama sekali (bukan sekadar terkunci)</t>
+        </is>
+      </c>
+      <c r="F5" s="29" t="inlineStr">
+        <is>
+          <t>Live (kosong u/ akun ID)</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="inlineStr">
+        <is>
+          <t>Konfirmasi geo-gating -- akun Indonesia asli TIDAK melihat Shops/Sponsored Links/Brand Deals/Rewards sama sekali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Earn</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Saldo pendapatan dari monetisasi</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Halaman saldo sederhana, $0.00 untuk akun ini (belum pernah dapat komisi)</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Audience</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>Contacts</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Kumpulkan &amp; kelola subscriber/lead pengunjung</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>Toggle "Turn on Subscribe" -&gt; pengunjung isi email/nomor di halaman publik -&gt; masuk daftar Contacts -&gt; bisa broadcast manual. Panel "Tools to grow your audience": Collect subscribers/Create contact form/Create digital download/Offer paid bookings/Offer discount codes</t>
+        </is>
+      </c>
+      <c r="F7" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>Jeonme belum punya sistem lead-capture/audience manager sama sekali -- selaras dengan No.73.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Audience</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>Sambungkan tool email eksternal (Mailchimp dll)</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Tab terpisah, belum sempat dibuka isinya</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>Belum dibuka</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>Insights</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>(halaman utama)</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>Analitik halaman</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>Buka tab -&gt; ringkasan Views/Clicks (filter tanggal) + panel chat "Ask Linktree AI" di kanan (bisa tanya bahasa natural, mis. "Where is my traffic coming from?") -&gt; scroll: Social follower growth/Most engaging posts (perlu connect akun sosial)/Most clicked links/Linktree visitors</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
+        <is>
+          <t>Analitik Jeonme (No.86) masih dasar -- AI chat assistant (No.96) &amp; breakdown follower growth per-platform ini pembeda besar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>Business cards</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>Kartu kontak digital NFC/QR untuk kreator sendiri (bukan produk)</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Atur nama tampilan+warna kartu -&gt; sistem generate QR+Apple Wallet pass otomatis -&gt; pengunjung scan -&gt; simpan kontak kreator, dan (kalau toggle "share details back" aktif) balas kirim kontak mereka</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>Fitur baru sama sekali buat Jeonme -- sudah masuk backlog No.95.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>Social planner</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>Jadwalkan &amp; auto-post konten sosial lintas platform</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>Connect akun sosial -&gt; compose post + generate caption AI -&gt; jadwalkan/cross-post ke IG/TikTok/FB/LinkedIn/Threads/YouTube -&gt; post baru di IG otomatis ke-sync jadi blok di halaman Linktree</t>
+        </is>
+      </c>
+      <c r="F11" s="29" t="inlineStr">
+        <is>
+          <t>Live (belum diaktifkan)</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="inlineStr">
+        <is>
+          <t>DI LUAR SCOPE inti Jeonme (bukan link-in-bio/monetisasi, lebih ke social media management) -- SENGAJA TIDAK dimasukkan ke backlog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Instagram auto-reply</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>Auto-DM saat ada komentar dengan kata kunci tertentu</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Connect Instagram -&gt; atur kata kunci pemicu per-postingan -&gt; sistem otomatis balas komentar + kirim DM berisi tautan</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>Live (belum connect)</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>Butuh Instagram Graph API resmi (approval Meta) -- kompleksitas &amp; risiko tinggi. SENGAJA TIDAK dimasukkan ke backlog aktif, dicatat sebagai ide masa depan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Link shortener</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Perpendek &amp; lacak link apa saja (bukan cuma di halaman Linktree)</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>Tempel URL panjang -&gt; dapat short link tr.ee/xxx + QR code otomatis -&gt; statistik klik/pengunjung unik terpisah dari Insights utama</t>
+        </is>
+      </c>
+      <c r="F13" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G13" s="29" t="inlineStr">
+        <is>
+          <t>QR sudah masuk backlog (No.82), tapi versi Linktree ini berdiri sendiri (bisa dipakai utk link APA SAJA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Post ideas</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>Generator ide caption/konten sosial pakai AI</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Klik "Generate ideas" -&gt; AI kasih hook/topik trending sesuai industri kreator</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>Sama seperti Social planner, di luar scope inti -- SENGAJA TIDAK dimasukkan ke backlog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>More</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>Pengaturan umum akun</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>Belum sempat dibuka (diblokir sistem keamanan internal kita sendiri saat riset)</t>
+        </is>
+      </c>
+      <c r="F15" s="29" t="inlineStr">
+        <is>
+          <t>Diblokir (riset)</t>
+        </is>
+      </c>
+      <c r="G15" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>More</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>Info akun/profil pemilik</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>Belum sempat dibuka (sama, diblokir)</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>Diblokir (riset)</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>More</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>Info tagihan/kartu pembayaran langganan</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>Belum sempat dibuka (data finansial sensitif, diblokir)</t>
+        </is>
+      </c>
+      <c r="F17" s="29" t="inlineStr">
+        <is>
+          <t>Diblokir (riset)</t>
+        </is>
+      </c>
+      <c r="G17" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>More</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>Cookie preferences</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>Kontrol consent cookie pelacakan</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>Terlihat sbg menu item, isinya belum dibuka</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>Nama saja</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>Mirip consent GDPR yang Jeonme sudah punya (No.60).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>More</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>Support (Ask a question / Help topics / Share feedback)</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>Bantuan &amp; dukungan pengguna</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>Redirect ke help.linktr.ee eksternal</t>
+        </is>
+      </c>
+      <c r="F19" s="29" t="inlineStr">
+        <is>
+          <t>Live (link saja)</t>
+        </is>
+      </c>
+      <c r="G19" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>(Dokumentasi publik)</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>Link locks, penjadwalan tautan, badge terverifikasi, Workspaces, Marketplace integrasi, MFA/2FA</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="inlineStr">
+        <is>
+          <t>Berbagai fitur lanjutan yang dijelaskan di help-center publik Linktree, belum dikonfirmasi live di akun ini</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>Lihat laporan riset awal untuk detail per-fitur</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>Dokumentasi publik</t>
+        </is>
+      </c>
+      <c r="G20" s="28" t="inlineStr">
+        <is>
+          <t>Sudah masuk backlog No.78, 79, 87, 88.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Menu Utama</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Sub-menu / Fitur</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>Fungsi</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>Alur Kerja (Workflow)</t>
+        </is>
+      </c>
+      <c r="F1" s="27" t="inlineStr">
+        <is>
+          <t>Verifikasi</t>
+        </is>
+      </c>
+      <c r="G1" s="27" t="inlineStr">
+        <is>
+          <t>Insight untuk Jeonme</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>My Lynks (Home)</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Kelola blok/tautan halaman utama</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Klik "Add new block" -&gt; tab Basic (Link/Image/Text/Video/Social Connect) atau Monetization (Digital Product/Physical Product/Blog/Course Video/Event/Appointment/Supports/Affiliate Products/Email&amp;Phone) -&gt; isi wizard per tipe blok -&gt; blok muncul di halaman, bisa drag-reorder</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G2" s="28" t="inlineStr">
+        <is>
+          <t>Basis dari hampir semua item Sprint 7 &amp; 11 backlog -- jenis 'blok' ini yang jadi pintu masuk semua fitur monetisasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>My Lynks</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>Your Pages</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>Multi-halaman bio dalam 1 akun</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>Klik "+Page" -&gt; bikin halaman baru dengan tema/blok sendiri -&gt; tiap halaman punya URL sendiri</t>
+        </is>
+      </c>
+      <c r="F3" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G3" s="29" t="inlineStr">
+        <is>
+          <t>Jeonme cuma 1 halaman per akun -- dicatat sbg ide masa depan (Sprint 14, belum prioritas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Landing Pages (label NEW)</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Builder halaman landing terpisah dari bio utama, ada opsi 'Create with AI'</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Klik "Add New Page" -&gt; pilih generate manual atau AI -&gt; AI generate draft halaman lengkap siap edit</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>Live (tombol saja, generate belum dicoba)</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>Fitur baru, scope besar (lebih ke website builder) -- dicatat sbg ide masa depan (Sprint 14, belum prioritas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Appearance/Design</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>Kustomisasi visual halaman</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>Pilih Layout (Classic/Modern/Clean) -&gt; atur Banner/Profile Image/About/Color -&gt; atau pilih galeri Template siap pakai -&gt; atau kustomisasi penuh (Background flat/gradient/gambar, gaya tombol, 16 pilihan font) -&gt; CTA &amp; tombol beli diatur terpisah</t>
+        </is>
+      </c>
+      <c r="F5" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="inlineStr">
+        <is>
+          <t>Lebih granular dari Jeonme (5 preset tanpa override) -- selaras dengan No.80.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Domain kustom, favicon, judul website</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Cari/klaim domain sendiri di kolom pencarian -&gt; domain tersambung ke halaman Lynk -&gt; upload favicon &amp; atur judul tab browser</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.81 (domain kustom, prioritas Must).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>Payment Method</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Atur channel pembayaran yang diterima + lihat biaya</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>Tabel channel (QRIS/OVO/ShopeePay/DANA/VA bank/Kartu Kredit/dll) dengan fee % atau flat + limit transaksi ditampilkan transparan -&gt; toggle "Charge convenience fee to customers" pilih siapa yang nanggung biaya</t>
+        </is>
+      </c>
+      <c r="F7" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.89 (transparansi biaya).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; Store Management</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Member Point System</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>Program poin loyalitas + reward</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Points Management: aktifkan reward, pilih tipe poin (Percentage/Percentage-Limit/Nominal/Nominal-Limit), atur syarat min. belanja -&gt; Reward Management: klik "Add Reward" -&gt; isi Value/Valid Date/Points Needed/Qty</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.94.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>Settings &gt; Store Management</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>Copyright</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>Registrasi hak cipta produk (berbayar)</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>Wizard 3 langkah: Author (pilih Diri Sendiri/Perusahaan, nama sesuai KTP, upload KTP+NPWP, no. HP) -&gt; Product -&gt; Payment</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>Live (cuma step 1 dibuka)</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
+        <is>
+          <t>SENGAJA DIKECUALIKAN dari backlog -- kompleksitas legal/dokumen (KTP+NPWP) terlalu dalam untuk tahap Jeonme sekarang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; Store Management</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>Custom Watermark</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>Tandai file PDF terjual dengan identitas pembeli</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Toggle aktif -&gt; pilih sumber teks (email pembeli/teks custom) -&gt; atur posisi/ukuran/opacity -&gt; preview langsung -&gt; watermark otomatis terpasang saat file diunduh (HANYA PDF tanpa password)</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.85.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>Settings &gt; Store Management</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>Social Proof Notifications</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>Popup "baru saja beli" di halaman publik</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>Toggle aktif -&gt; atur durasi tampil &amp; interval antar notifikasi -&gt; pilih cakupan (semua/produk tertentu) -&gt; pilih tampil di halaman produk dan/atau checkout -&gt; email pembeli otomatis disamarkan sebagian</t>
+        </is>
+      </c>
+      <c r="F11" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.76.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; Store Management</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Follow Up Text</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>Template pesan WhatsApp otomatis pasca-transaksi</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>HARUS sambungkan WhatsApp Blast dulu -&gt; baru bisa bikin sampai 10 template pesan follow-up</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>Live (terkunci di akun ini)</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.75 (dicatat sbg lanjutan alami).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Multi Admin</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Undang kolaborator dengan akses terbatas</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>Owner undang user lain by email/username -&gt; atur peran/akses</t>
+        </is>
+      </c>
+      <c r="F13" s="29" t="inlineStr">
+        <is>
+          <t>Live (dari pricing table)</t>
+        </is>
+      </c>
+      <c r="G13" s="29" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.87.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>Sambungkan tool analitik/marketing eksternal</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Isi Facebook Pixel ID, Google Tag Manager ID, GA4 Measurement ID, sinkron Google Calendar, atur UTM parameter default</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>Sebagian sudah standar (GA/Pixel); sinkron Calendar relevan utk Booking (No.92).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Account/Subscription</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>Info &amp; upgrade paket langganan</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>Lihat tier aktif (mis. "Premium, berlaku sampai...") -&gt; upgrade/downgrade paket</t>
+        </is>
+      </c>
+      <c r="F15" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G15" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Voucher</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>Buat kode diskon/promo</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>Klik "Create New Voucher" -&gt; pilih Single Code (1 kode banyak pemakai) atau Generate Unique Code (banyak kode sekali pakai, utk afiliasi/influencer) -&gt; pilih tipe (Percentage/Percentage-Cap/Nominal/Nominal-Cap) -&gt; atur Max Discount &amp; Min Purchase -&gt; pilih cakupan produk -&gt; simpan (maks 1 voucher/checkout)</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.67.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>Affiliates</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Punya sendiri (Privat/Publik)</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>Kelola siapa yang boleh jual produk kita dengan komisi</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>Pilih mode Privat (undang orang tertentu, komisi custom) atau Publik (produk masuk marketplace afiliasi lintas kreator, approval Lynk.id)</t>
+        </is>
+      </c>
+      <c r="F17" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G17" s="29" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.72.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Affiliates</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>Marketplace (gabung punya orang lain)</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>Jadi afiliator untuk produk kreator lain</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>Jelajahi daftar produk kreator lain yang buka program afiliasi -&gt; lihat komisi per-produk -&gt; gabung -&gt; dapat link afiliasi sendiri -&gt; komisi otomatis masuk saat closing</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli, data nyata)</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>Fase lanjutan dari No.72 (marketplace publik lintas kreator).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>Kelola &amp; pantau semua transaksi</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>Tab All Transaction/Pending(New,Processing,On Delivery)/Success-Complete/Unprinted Labels -&gt; klik order utk detail -&gt; bulk select utk aksi massal</t>
+        </is>
+      </c>
+      <c r="F19" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G19" s="29" t="inlineStr">
+        <is>
+          <t>'Unprinted Labels' spesifik utk produk fisik (No.93) -- Jeonme (digital-only) belum butuh ini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="inlineStr">
+        <is>
+          <t>Saldo &amp; penarikan dana</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>Lihat saldo -&gt; klik Withdraw -&gt; kalau belum verifikasi KYC, proses 2 hari kerja; kalau sudah verified, instan lewat "PaymeLynk"</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G20" s="28" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.84 (KYC + instant withdraw).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>Statistics/Analytics</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="29" t="inlineStr">
+        <is>
+          <t>Laporan performa &amp; penjualan</t>
+        </is>
+      </c>
+      <c r="E21" s="29" t="inlineStr">
+        <is>
+          <t>Dashboard nunjukin Total Views&amp;Clicks (+% vs periode lalu), Total Sales (unit+nilai), Social Icons Clicks per platform, Sales Distribution (Net vs Affiliate), Top 5 Produk (Views/Sold/Amount/Conversion)</t>
+        </is>
+      </c>
+      <c r="F21" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G21" s="29" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.86 -- breakdown 'Net vs Affiliate' ini detail baru yang belum tercatat eksplisit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>Marketing Tools</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>E-Mail Marketing</t>
+        </is>
+      </c>
+      <c r="D22" s="28" t="inlineStr">
+        <is>
+          <t>Kirim email promo ke pembeli/subscriber</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>Perlu domain kustom aktif dulu -&gt; tulis campaign -&gt; kirim ke list (hanya dari pembeli asli atau blok Email&amp;Phone, tidak bisa upload list sembarang) -&gt; biaya Rp40/email terkirim</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G22" s="28" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.73 -- model biaya per-email ini detail baru.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>Marketing Tools</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>WhatsApp Blast</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="inlineStr">
+        <is>
+          <t>Broadcast promo lewat WA nomor sendiri</t>
+        </is>
+      </c>
+      <c r="E23" s="29" t="inlineStr">
+        <is>
+          <t>Klik "Add Device" -&gt; scan QR kayak WhatsApp Web -&gt; nomor tersambung -&gt; compose pesan+voucher -&gt; kirim ke daftar kontak</t>
+        </is>
+      </c>
+      <c r="F23" s="29" t="inlineStr">
+        <is>
+          <t>Live (akun asli)</t>
+        </is>
+      </c>
+      <c r="G23" s="29" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.75.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>Marketing Tools</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>Automate Workflow (Beta)</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="inlineStr">
+        <is>
+          <t>Kirim WA otomatis saat ada trigger (mis. ada penjualan)</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>Butuh WhatsApp Blast aktif dulu -&gt; atur aturan "kalau X terjadi, kirim pesan Y"</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="inlineStr">
+        <is>
+          <t>Live (nama+deskripsi)</t>
+        </is>
+      </c>
+      <c r="G24" s="28" t="inlineStr">
+        <is>
+          <t>Perluasan otomatis dari No.75 -- dicatat sbg catatan tambahan, bukan item baru terpisah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>Marketing Tools</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>Clip Campaign</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="inlineStr">
+        <is>
+          <t>Marketplace kreator konten (clipper) dibayar per-1000-view mempromosikan produk kreator lain</t>
+        </is>
+      </c>
+      <c r="E25" s="29" t="inlineStr">
+        <is>
+          <t>Sisi kreator: buat campaign, isi saldo (Top Up), tentukan Rp/1000 view, review submission (Approved/In Review/Rejected). Sisi clipper: jelajahi campaign orang lain, repost/promosikan, dibayar otomatis, saldo bisa Cash Out</t>
+        </is>
+      </c>
+      <c r="F25" s="29" t="inlineStr">
+        <is>
+          <t>Live (contoh campaign asli berjalan)</t>
+        </is>
+      </c>
+      <c r="G25" s="29" t="inlineStr">
+        <is>
+          <t>Growth mechanic unik &amp; kompleks -- SENGAJA DIKECUALIKAN dari backlog aktif, dicatat sbg ide masa depan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>Appointment</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="28" t="inlineStr">
+        <is>
+          <t>Booking konsultasi berbayar dengan sinkron kalender</t>
+        </is>
+      </c>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>Blok 'Create paid calendar booking' -- TIDAK BISA DIBUKA sama sekali (bug produk mereka sendiri, dikonfirmasi 3x percobaan berbeda)</t>
+        </is>
+      </c>
+      <c r="F26" s="28" t="inlineStr">
+        <is>
+          <t>Gagal dibuka (bug asli)</t>
+        </is>
+      </c>
+      <c r="G26" s="28" t="inlineStr">
+        <is>
+          <t>Selaras dengan No.92 -- fiturnya cuma bisa disimpulkan dari nama+deskripsi, bukan dilihat langsung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>Knowledge Base (lynk.id/faq)</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="29" t="inlineStr">
+        <is>
+          <t>Pusat bantuan publik (di luar dashboard)</t>
+        </is>
+      </c>
+      <c r="E27" s="29" t="inlineStr">
+        <is>
+          <t>Kategori General/Integration/Payment/Product/Promotion/Tips&amp;Trick, ada kotak pencarian</t>
+        </is>
+      </c>
+      <c r="F27" s="29" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G27" s="29" t="inlineStr">
+        <is>
+          <t>Sumber detail KYC (No.84) &amp; konfirmasi tier Brandpreneur tanpa dokumentasi publik.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Bagian Baru (Jeonme)</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Menggabungkan Dari</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>Isi / Fitur yang Masuk</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>Kenapa Lebih Sederhana</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Ringkasan</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>Linktree Insights + Lynk.id Statistics/Dashboard</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Analitik utama, asisten AI (No.96), grafik tren, produk terlaris, breakdown perangkat/lokasi (No.86)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Satu pintu masuk analitik -- tidak perlu pilah 'Statistics' vs 'Dashboard' vs 'Insights' terpisah seperti kedua kompetitor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>Halaman Saya</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>Linktree Links+Shop+Design + Lynk.id My Lynks+Appearance</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>Semua blok tautan/produk/desain tema dalam SATU alur edit, dengan preview langsung di sebelah (pola PagePreview yang sudah ada di Jeonme)</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>Linktree pisah Links/Shop/Design jadi 3 tab beda; Lynk.id pisah Blok vs Appearance. Buat kreator, semua 'yang tampil di halaman publik' itu satu kesatuan mental model -- Jeonme gabung jadi satu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Produk &amp; Monetisasi</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Lynk.id Voucher+Affiliates+Store Management(poin) + Linktree Shop</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Produk, voucher, bundel, flash sale, bayar-seikhlasnya, poin loyalitas, program afiliasi -- satu hub 'cara saya dapat uang'</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Lynk.id sebar fitur ini ke banyak menu terpisah (Voucher/Affiliates/Settings&gt;Store Management) padahal secara mental model kreator itu semua 'alat jualan saya'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Audiens &amp; Pemasaran</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>Linktree Audience+Business cards + Lynk.id Marketing Tools (Email/WA Blast)</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>Kumpulkan lead, kartu kontak digital/NFC (No.95), broadcast WhatsApp/email (No.73/75), social proof (No.76)</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>Satu tempat utk 'bagaimana saya jangkau &amp; rawat pembeli', bukan tersebar di sidebar Audience terpisah dari Marketing Tools terpisah dari Tools seperti kedua kompetitor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Saldo &amp; Penarikan</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Lynk.id Earnings+KYC + Linktree Earn&gt;Earnings</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Saldo, status verifikasi KYC (No.84), transparansi biaya per channel (No.89), riwayat penarikan</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Sudah ada di Jeonme -- tinggal diperkaya, tidak perlu redesain struktur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>Linktree More(Settings/Account/Billing) + Lynk.id Settings(Site/Integrations/Multi Admin)</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Domain kustom (No.81), SEO (No.83), integrasi pihak ketiga, tim/multi-admin (No.87), watermark file (No.85)</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>Linktree nyembunyiin ini di menu 'More' yang gampang kelewat -- Jeonme taruh eksplisit di sidebar biar tidak collapse jadi 1 tombol generic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>Fitur yang Sengaja TIDAK Dimasukkan ke Backlog (dipertimbangkan, bukan terlupa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Fitur</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Sumber</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Alasan Dikecualikan</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>Copyright registration service (Lynk.id)</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>Lynk.id Settings&gt;Store Management</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>Butuh KTP+NPWP, wizard 3 langkah -- kompleksitas legal/dokumen terlalu dalam untuk tahap Jeonme sekarang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Lynk.id Plaque program (Silver/Gold/Diamond)</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Lynk.id (help center)</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>Program penghargaan berbasis omzet Rp100jt-1M -- terlalu dini untuk platform yang baru mulai, belum ada basis kreator besar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>Clip Campaign (UGC clipping marketplace)</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Lynk.id Marketing Tools</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Growth mechanic unik &amp; kompleks (marketplace dua sisi kreator-clipper) -- dicatat sbg ide masa depan, bukan prioritas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Social Planner (penjadwal posting sosial)</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Linktree Tools</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>Di luar scope inti Jeonme (link-in-bio/monetisasi) -- ini produk social-media-management terpisah (Plann by Linktree).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Instagram auto-reply (auto-DM)</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Linktree Tools</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>Butuh Instagram Graph API resmi (approval Meta) -- kompleksitas &amp; risiko ToS tinggi untuk manfaat yang tangensial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Post ideas (AI caption generator)</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>Linktree Tools</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>Sama seperti Social Planner -- di luar scope inti, lebih cocok jadi fitur produk media sosial terpisah.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -723,6 +723,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -972,6 +973,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -986,6 +988,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1045,7 +1048,7 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Sebagian Selesai (No.67 voucher selesai; No.68-72 belum)</t>
         </is>
       </c>
     </row>
@@ -4277,9 +4280,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G68" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H68" s="22" t="n"/>
@@ -4288,7 +4291,7 @@
       </c>
       <c r="J68" s="23" t="inlineStr">
         <is>
-          <t>Diadaptasi dari fitur Voucher Lynk.id (tipe Percentage/Percentage-with-cap/Nominal/Nominal-with-cap, hanya 1 voucher per checkout). Perlu tabel vouchers baru + validasi di endpoint checkout.</t>
+          <t>Diadaptasi dari fitur Voucher Lynk.id (tipe Percentage/Percentage-with-cap/Nominal/Nominal-with-cap, hanya 1 voucher per checkout). Perlu tabel vouchers baru + validasi di endpoint checkout. -- SELESAI (24 Juli 2026): migrasi 000006_vouchers, VoucherHandler CRUD + integrasi checkout (diskon persentase/nominal, generate massal, cakupan produk, min. pembelian, maks. diskon). Diverifikasi end-to-end: kode tunggal &amp; batch (5 kode unik max_uses=1), toggle/hapus, checkout sungguhan ke Midtrans sandbox dengan diskon terpotong benar (Rp49.000 -&gt; Rp39.200 dgn CHECKOUT20), used_count bertambah, kode kedaluwarsa/salah-scope/melebihi batas pemakaian ditolak dengan pesan jelas.</t>
         </is>
       </c>
     </row>
@@ -5597,9 +5600,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G98" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H98" s="25" t="n"/>
@@ -5608,7 +5611,7 @@
       </c>
       <c r="J98" s="26" t="inlineStr">
         <is>
-          <t>KERJAKAN DULUAN sebelum item lain di Sprint 7-10 supaya fitur baru (voucher/afiliasi/audiens/dsb) langsung masuk ke IA yang benar, bukan ditempel di struktur lama. Linktree pisah Links/Shop/Design jadi tab beda-beda dan nyembunyiin Settings di menu 'More'; Lynk.id sebar fitur commerce ke banyak sidebar terpisah (Voucher/Affiliates/Settings&gt;Store Management) -- keduanya butuh banyak klik untuk hal yang buat kreator terasa satu kesatuan. Jeonme gabung jadi 6 bagian: Ringkasan (analitik), Halaman Saya (tautan+produk+desain+preview), Produk &amp; Monetisasi (voucher/bundel/afiliasi/poin), Audiens &amp; Pemasaran (lead+WhatsApp+social proof), Saldo &amp; Penarikan (sudah ada), Pengaturan (domain/SEO/tim/watermark).</t>
+          <t>KERJAKAN DULUAN sebelum item lain di Sprint 7-10 supaya fitur baru (voucher/afiliasi/audiens/dsb) langsung masuk ke IA yang benar, bukan ditempel di struktur lama. Linktree pisah Links/Shop/Design jadi tab beda-beda dan nyembunyiin Settings di menu 'More'; Lynk.id sebar fitur commerce ke banyak sidebar terpisah (Voucher/Affiliates/Settings&gt;Store Management) -- keduanya butuh banyak klik untuk hal yang buat kreator terasa satu kesatuan. Jeonme gabung jadi 6 bagian: Ringkasan (analitik), Halaman Saya (tautan+produk+desain+preview), Produk &amp; Monetisasi (voucher/bundel/afiliasi/poin), Audiens &amp; Pemasaran (lead+WhatsApp+social proof), Saldo &amp; Penarikan (sudah ada), Pengaturan (domain/SEO/tim/watermark). -- SELESAI (23-24 Juli 2026): sidebar direstrukturisasi jadi 6 bagian, verifikasi end-to-end lolos di lokal &amp; staging (commit ec343e8, tag v0.12.0).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1048,7 +1048,7 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.67 voucher selesai; No.68-72 belum)</t>
+          <t>Sebagian Selesai (No.67-68 selesai; No.69-72 belum)</t>
         </is>
       </c>
     </row>
@@ -4324,9 +4324,9 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G69" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H69" s="15" t="n"/>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>Kedua platform punya ini sebagai pendorong konversi jangka pendek. Field start/end time di tabel products, harga coret dihitung otomatis di FE saat aktif.</t>
+          <t>Kedua platform punya ini sebagai pendorong konversi jangka pendek. Field start/end time di tabel products, harga coret dihitung otomatis di FE saat aktif. -- SELESAI (24 Juli 2026): migrasi 000007_flash_sale (3 kolom nullable di products), harga efektif dihitung live dari now() (bukan cron). Diverifikasi end-to-end: dashboard jadwalkan/batalkan flash sale, halaman publik &amp; pratinjau tampilkan harga dicoret, checkout sungguhan ke Midtrans sandbox charge harga flash sale (bukan harga asli), voucher (No.67) menumpuk benar di atas harga flash sale, validasi (harga&gt;=asli, ends&lt;=starts, field parsial) ditolak, dan flash sale yang sudah lewat otomatis kembali ke harga normal tanpa aksi manual.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1048,7 +1048,7 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.67-68 selesai; No.69-72 belum)</t>
+          <t>Sebagian Selesai (No.67-69 selesai; No.70-72 belum)</t>
         </is>
       </c>
     </row>
@@ -4368,9 +4368,9 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G70" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H70" s="22" t="n"/>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="J70" s="23" t="inlineStr">
         <is>
-          <t>Fitur Digital Product Lynk.id ("Allow customer to pay what they want"). Cocok untuk kreator konten edukasi/donasi-driven.</t>
+          <t>Fitur Digital Product Lynk.id ("Allow customer to pay what they want"). Cocok untuk kreator konten edukasi/donasi-driven. -- SELESAI (24 Juli 2026): migrasi 000008_pwyw (pwyw_enabled + pwyw_min_price_idr). Sengaja tidak bisa aktif bersamaan dengan flash sale (No.68) pada produk yang sama -- validasi dua arah di ProductHandler.Update. Diverifikasi end-to-end: checkout dengan jumlah di bawah minimum ditolak, jumlah valid charge sesuai pilihan pembeli (bukan price_idr produk), voucher (No.67) menumpuk benar di atas jumlah pilihan pembeli, validasi konflik flash-sale/pwyw dua arah ditolak dengan jelas, UI dashboard &amp; halaman publik ("Mulai dari Rp X" + input jumlah) berfungsi.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -723,7 +723,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -973,7 +972,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -988,7 +986,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1048,7 +1045,7 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.67-69 selesai; No.70-72 belum)</t>
+          <t>Sebagian Selesai (No.67-70 selesai; No.71-72 belum)</t>
         </is>
       </c>
     </row>
@@ -4412,9 +4409,9 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G71" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H71" s="15" t="n"/>
@@ -4423,7 +4420,7 @@
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>Diverifikasi langsung di toko publik Lynk.id sungguhan (miss.buku) -- pola "[COMPLETE BUNDLE]" dengan harga coret. Butuh tabel product_bundles (relasi many-to-many ke products) + akses gabungan file saat checkout.</t>
+          <t>Diverifikasi langsung di toko publik Lynk.id sungguhan (miss.buku) -- pola "[COMPLETE BUNDLE]" dengan harga coret. Butuh tabel product_bundles (relasi many-to-many ke products) + akses gabungan file saat checkout. -- SELESAI (24 Juli 2026): migrasi 000009_bundles (kolom is_bundle di products + tabel junction bundle_items, ON DELETE CASCADE). Bundel dimodelkan sebagai baris products biasa (is_bundle=true) sehingga checkout/webhook/ledger yang sudah ada dipakai TANPA perubahan -- hanya alur unduhan yang bercabang (redirect ke halaman status checkout multi-file, bukan satu presigned URL). Diverifikasi end-to-end nyata: buat bundel dari 2 produk aktif (harga bundel &lt; jumlah harga asli, tervalidasi), aktifkan, tampil di halaman publik dengan harga asli dicoret (dikonfirmasi lewat HTML SSR sungguhan), checkout sungguhan ke Midtrans sandbox + webhook signature valid -&gt; order lunas -&gt; endpoint /checkout/:id/bundle-items mengeluarkan 2 presigned URL yang benar-benar bisa diunduh (HTTP 200). Validasi ditolak dengan benar: &lt;2 produk, produk bukan milik kreator, bundel-di-dalam-bundel, harga bundel &gt;= jumlah harga asli. Dikonfirmasi produk biasa TIDAK menampilkan baris bundel di /dashboard/products, dan unduhan produk tunggal (non-bundel) tetap redirect langsung ke file presigned (tidak berubah).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1045,7 +1045,7 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.67-70 selesai; No.71-72 belum)</t>
+          <t>Sebagian Selesai (No.67-71 selesai; No.72 belum)</t>
         </is>
       </c>
     </row>
@@ -4453,9 +4453,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G72" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H72" s="22" t="n"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="J72" s="23" t="inlineStr">
         <is>
-          <t>Fitur "Supports" Lynk.id. Versi awal: nominal sekali bayar saja (skip dulu kadens berulang mingguan/bulanan -- itu butuh integrasi subscription/recurring charge Midtrans terpisah, catat sebagai pekerjaan lanjutan kalau permintaannya tervalidasi).</t>
+          <t>Fitur "Supports" Lynk.id. Versi awal: nominal sekali bayar saja (skip dulu kadens berulang mingguan/bulanan -- itu butuh integrasi subscription/recurring charge Midtrans terpisah, catat sebagai pekerjaan lanjutan kalau permintaannya tervalidasi). -- SELESAI (24 Juli 2026): migrasi 000010_donations (kolom is_donation di products). Donasi dimodelkan sebagai SATU baris products per kreator (is_donation=true, pwyw_enabled=true) -- pola sama seperti bundel (No.70), sehingga checkout/webhook/ledger yang sudah ada dipakai TANPA perubahan lewat mekanisme bayar-seikhlasnya (No.69) yang sudah ada. Beda dengan bundel, baris ini TIDAK tampil di grid Produk publik -- dapat blok tersendiri (heart icon + judul + tombol "Dukung") yang tampil setelah blok Tautan, sebelum grid Produk. Diverifikasi end-to-end nyata: aktifkan blok dengan judul+nominal minimum, tervalidasi (judul wajib, nominal &gt;= Rp1.000), tampil benar di HTML SSR halaman publik dengan posisi &amp; markup yang tepat, TIDAK muncul di /dashboard/products. Checkout sungguhan ke Midtrans sandbox dengan nominal pilihan pembeli (validasi jumlah &lt; minimum ditolak) + webhook signature valid -&gt; order lunas -&gt; ledger kreator terkredit benar (nominal - platform fee). Halaman status checkout menampilkan ucapan terima kasih (BUKAN tombol unduh -- donasi tidak pernah punya file), begitu juga redirect DownloadFile dan isi email notifikasi worker, keduanya dicabangkan khusus untuk is_donation. Nonaktifkan blok -&gt; langsung hilang dari halaman publik, pengaturan (judul/nominal) tetap tersimpan untuk diaktifkan lagi. Versi awal sengaja hanya nominal sekali bayar (bukan langganan berulang) sesuai catatan scope semula.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1045,7 +1045,7 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.67-71 selesai; No.72 belum)</t>
+          <t>Selesai (No.67-72 semua selesai)</t>
         </is>
       </c>
     </row>
@@ -4497,9 +4497,9 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G73" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H73" s="15" t="n"/>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>Diverifikasi langsung di dashboard afiliasi Lynk.id (mode privat: undang + komisi custom; mode publik: marketplace lintas kreator). Versi awal Jeonme: mode privat dulu (undang by user_id/email), marketplace publik lintas kreator jadi fase lanjutan.</t>
+          <t>Diverifikasi langsung di dashboard afiliasi Lynk.id (mode privat: undang + komisi custom; mode publik: marketplace lintas kreator). Versi awal Jeonme: mode privat dulu (undang by user_id/email), marketplace publik lintas kreator jadi fase lanjutan. -- SELESAI (24 Juli 2026): migrasi 000011_affiliates -- tabel affiliates (satu baris = satu hubungan kreator&lt;-&gt;afiliator dengan SATU referral_code untuk semuanya) + affiliate_commissions (junction ke products, komisi persen custom per produk) + kolom affiliate_id/affiliate_commission_idr di orders. Mode privat sesuai scope: afiliator harus sudah jadi pengguna Jeonme (diundang lewat email), marketplace publik lintas kreator jadi fase lanjutan. Checkout/webhook TIDAK dirombak -- cukup tambah resolusi kode referral opsional (kode salah/tidak cocok produk diabaikan diam-diam, checkout tetap jalan) dan cabang kredit ledger afiliator yang meniru pola pg_advisory_xact_lock milik kreator persis. Diverifikasi end-to-end nyata: validasi tolak email non-pengguna, undang diri sendiri, produk bukan milik kreator, persen &gt;100; satu afiliator bisa dapat komisi beda utk &gt;1 produk dgn 1 referral_code yang sama (dikonfirmasi dari sisi kreator &amp; sisi afiliator); checkout sungguhan ke Midtrans sandbox dgn ?ref= yang benar mengaitkan komisi (25.000 x 20% = 5.000, dikonfirmasi tersimpan di order), kode salah/tidak cocok produk diabaikan tanpa memblokir checkout. Webhook signature valid -&gt; ledger KREATOR terkredit (amount - platform_fee - komisi afiliasi) DAN ledger AFILIATOR terkredit persis sebesar komisinya dalam SATU transaksi atomik; retry webhook idempoten (tidak dobel kredit). Tautan ?ref= dari URL halaman publik dikonfirmasi mengalir sampai ke tombol Beli tiap produk lewat HTML SSR sungguhan. Ditemukan &amp; diperbaiki bug nyata saat verifikasi: mencabut afiliator gagal (500) karena FK orders.affiliate_id belum ON DELETE SET NULL -- histori order lama yang pernah pakai referral code memblokir penghapusan; diperbaiki agar affiliate_id di order lama jadi NULL saat dicabut sementara affiliate_commission_idr (snapshot angka) tetap tersimpan utuh.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Sebagian Selesai (No.73 selesai; No.74-76 belum -- No.74/75 menunggu kredensial WhatsApp Business API resmi)</t>
         </is>
       </c>
     </row>
@@ -4541,9 +4541,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G74" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H74" s="22" t="n"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="J74" s="23" t="inlineStr">
         <is>
-          <t>Kedua platform sentralisasi semua lead (form, pembeli, subscribe-lock) ke satu Audience Manager yang bisa diekspor. Fondasi wajib sebelum broadcast WhatsApp (No.75) bisa jalan.</t>
+          <t>Kedua platform sentralisasi semua lead (form, pembeli, subscribe-lock) ke satu Audience Manager yang bisa diekspor. Fondasi wajib sebelum broadcast WhatsApp (No.75) bisa jalan. -- SELESAI (24 Juli 2026): migrasi 000012_lead_capture (lead_capture_settings 1 baris per kreator + tabel subscribers dengan dedupe email lewat partial unique index). Blok pengumpulan tampil di halaman publik setelah blok Tautan (posisi sebelum Dukungan/Produk), field email/whatsapp bisa diaktifkan terpisah. Manajer Audiens (dashboard) MENGGABUNG dua sumber -- subscriber form DAN pembeli produk (dari orders yang lunas) -- lewat pencocokan email di sisi Go, orang yang sama tidak dobel baris kalau dia subscribe DAN pernah beli (sources jadi ["subscriber","buyer"]). Ekspor CSV di sisi browser (tanpa endpoint CSV terpisah). Subscribe-lock (kunci tautan di balik form) SENGAJA tidak dikerjakan -- fitur terpisah yang lebih besar, di luar estimasi 3 hari. Diverifikasi end-to-end nyata: validasi tolak judul kosong &amp; tidak pilih field apa pun; submit publik tolak kalau blok belum aktif, tolak kreator tidak ditemukan, tolak kalau email &amp; whatsapp kosong; submit sungguhan tersimpan &amp; muncul di Manajer Audiens; submit ulang email yang sama TIDAK bikin baris dobel (whatsapp_number ter-update, dikonfirmasi via query DB langsung); kontak yang subscribe DAN pernah beli (email sama) dikonfirmasi muncul SATU baris dengan kedua sumber; blok hilang dari halaman publik begitu dinonaktifkan (dikonfirmasi lewat HTML SSR sungguhan setelah cache Redis 30 detik &amp; fetch cache Next.js 60 detik kedaluwarsa -- staleness sementara ini konsisten dengan pola cache yang sudah ada di bundel/donasi/voucher, bukan bug baru).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.73 selesai; No.74-76 belum -- No.74/75 menunggu kredensial WhatsApp Business API resmi)</t>
+          <t>Sebagian Selesai (No.73, No.76 selesai; No.74-75 belum -- menunggu kredensial WhatsApp Business API resmi)</t>
         </is>
       </c>
     </row>
@@ -4673,9 +4673,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G77" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H77" s="15" t="n"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>Fitur Social Proof Notifications Lynk.id (PRO). Murah dikerjakan, dampak konversi terbukti di industri e-commerce. -- UPDATE (verifikasi live Lynk.id, layar konfigurasi sungguhan dibuka langsung): durasi tampil (5/10/15 detik), interval sebelum notifikasi berikutnya (10/15/30/45/60 detik), cakupan per-produk atau semua produk, toggle terpisah untuk halaman produk vs halaman checkout, pilihan bahasa, dan email pembeli SELALU disamarkan sebagian di pesan (mis. "rumi****am@gmail.com telah membeli...") -- bukan ditampilkan penuh.</t>
+          <t>Fitur Social Proof Notifications Lynk.id (PRO). Murah dikerjakan, dampak konversi terbukti di industri e-commerce. -- UPDATE (verifikasi live Lynk.id, layar konfigurasi sungguhan dibuka langsung): durasi tampil (5/10/15 detik), interval sebelum notifikasi berikutnya (10/15/30/45/60 detik), cakupan per-produk atau semua produk, toggle terpisah untuk halaman produk vs halaman checkout, pilihan bahasa, dan email pembeli SELALU disamarkan sebagian di pesan (mis. "rumi****am@gmail.com telah membeli...") -- bukan ditampilkan penuh. -- SELESAI (25 Juli 2026): migrasi 000013_social_proof (1 baris pengaturan per kreator: is_active, show_on_product_page, show_on_checkout, display_seconds CHECK IN(5,10,15), interval_seconds CHECK IN(10,15,30,45,60)). Disederhanakan dari temuan riset Lynk.id sesuai prioritas Could &amp; estimasi 1 hari: cakupan per-produk granular jadi SATU toggle global per kreator (bukan pilih produk satu-satu), dan pilihan bahasa tidak dikerjakan (tetap Bahasa Indonesia). Yang dipertahankan: durasi tampil &amp; interval yang bisa diatur, toggle terpisah halaman produk vs checkout, email pembeli SELALU disamarkan sebagian (mis. "affi****al@example.com", meniru pola "rumi****am@gmail.com" dari verifikasi layar Lynk.id). Halaman checkout Jeonme tidak punya form pembayaran sendiri (redirect ke Midtrans Snap hosted page) -- "tampil di checkout" diadaptasi jadi tampil di halaman status pasca-pembayaran (satu-satunya halaman checkout yang benar-benar dimiliki Jeonme), dicatat sebagai penyesuaian dari desain asli Lynk.id. Diverifikasi end-to-end nyata: validasi tolak nilai display_seconds/interval_seconds di luar daftar yang diizinkan; halaman publik menampilkan pembelian nyata lintas produk dengan email tersamar benar (dicocokkan manual utk 4 email berbeda, semua match); halaman checkout menampilkan HANYA pembelian produk yang sama (bukan lintas produk, dikonfirmasi beda dari data halaman publik); toggle show_on_checkout &amp; show_on_product_page independen satu sama lain (nonaktifkan satu tidak memengaruhi yang lain); is_active=false menyembunyikan di KEDUA permukaan; markup toast dikonfirmasi benar via HTML SSR sungguhan (fixed bottom-left, mulai tersembunyi sebelum hydration client-side menjalankan animasi).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -4937,9 +4937,9 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G83" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H83" s="15" t="n"/>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>Fitur murah, dampak besar untuk kreator yang promosi offline (banner event, kemasan produk, dsb).</t>
+          <t>Fitur murah, dampak besar untuk kreator yang promosi offline (banner event, kemasan produk, dsb). -- SELESAI (25 Juli 2026): fitur MURNI sisi klien, tanpa endpoint backend sama sekali -- URL halaman publik (jeonme.com/{username}) sudah diketahui dari data yang ada. Ditambahkan sebagai tombol "Kode QR" di chip "Halaman publikmu" (sidebar dashboard, di semua halaman), membuka modal dengan QRCodeCanvas (paket qrcode.react, dipilih atas paket qrcode karena zero-dependency selain React, tidak menyeret yargs/CLI cruft yang tidak relevan untuk pemakaian browser) + tombol Unduh PNG (canvas.toDataURL). Verifikasi: typecheck &amp; build produksi berhasil, prop API qrcode.react dicocokkan langsung ke definisi tipenya. CATATAN JUJUR: tidak ada browser/Puppeteer tersedia sesi ini untuk memindai QR sungguhan atau mengonfirmasi unduhan PNG bekerja visual di browser nyata -- verifikasi terbatas pada kebenaran kode (tipe, build, API paket), bukan pengujian visual end-to-end. Risiko rendah (paket mapan, banyak dipakai).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -4981,9 +4981,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G84" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H84" s="22" t="n"/>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="J84" s="23" t="inlineStr">
         <is>
-          <t>Jeonme sudah punya OG tags (No.32) -- ini melengkapi dengan kontrol judul/deskripsi manual + opsi noindex untuk kreator yang mau halamannya privat dari pencarian Google.</t>
+          <t>Jeonme sudah punya OG tags (No.32) -- ini melengkapi dengan kontrol judul/deskripsi manual + opsi noindex untuk kreator yang mau halamannya privat dari pencarian Google. -- SELESAI (25 Juli 2026): migrasi 000014_page_seo (3 kolom di pages: seo_title VARCHAR(70), seo_description VARCHAR(160), noindex BOOLEAN). Judul/deskripsi manual MENGGANTIKAN default kalau diisi (fallback ke pola lama @username/bio kalau kosong), melengkapi OG tags No.32 yang sudah ada. noindex=true menghasilkan &lt;meta name="robots" content="noindex, nofollow"&gt; lewat Next.js Metadata API. Diverifikasi end-to-end nyata: validasi tolak seo_title &gt;70 karakter; judul/deskripsi kustom tersimpan &amp; muncul benar di &lt;title&gt; dan &lt;meta name="description"&gt;/&lt;meta property="og:title"&gt; HTML SSR sungguhan; toggle noindex menghasilkan meta robots yang tepat di HTML SSR sungguhan; reset ke default (kosong) kembali memakai fallback lama.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -4761,9 +4761,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G79" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H79" s="15" t="n"/>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>Fitur Schedule links Linktree (Starter+). Berguna untuk promo musiman/preorder tanpa harus manual on/off.</t>
+          <t>Fitur Schedule links Linktree (Starter+). Berguna untuk promo musiman/preorder tanpa harus manual on/off. -- SELESAI (25 Juli 2026): migrasi 000015_link_scheduling (kolom starts_at/ends_at nullable di links). Pola identik penjadwalan flash sale produk (No.68): kedua kolom wajib diisi bersamaan, ends_at harus setelah starts_at, filter rentang waktu dihitung LIVE dari now() di query halaman publik (bukan cron), di ATAS gate is_active manual yang sudah ada -- keduanya harus lolos. UI dashboard meniru form datetime-local + tombol Batalkan milik flash sale persis. Diverifikasi end-to-end nyata: validasi tolak starts_at tanpa ends_at &amp; ends_at sebelum starts_at; tautan dengan jadwal MASA DEPAN tersembunyi dari halaman publik (dikonfirmasi tanggal server 25 Juli 2026); tautan dengan jadwal SUDAH LEWAT tetap tersembunyi; tautan dengan jadwal SEDANG BERLANGSUNG tampil benar (dikonfirmasi setelah cache Redis 30 detik kedaluwarsa); batalkan jadwal mengembalikan starts_at/ends_at ke NULL (tampil permanen lagi).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -4805,9 +4805,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G80" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H80" s="22" t="n"/>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="J80" s="23" t="inlineStr">
         <is>
-          <t>3 dari 4 jenis link-lock Linktree yang relevan (skip NFT lock -- di luar konteks Jeonme). Subscribe-lock sekalian jadi sumber lead baru untuk Manajer Audiens (No.73).</t>
+          <t>3 dari 4 jenis link-lock Linktree yang relevan (skip NFT lock -- di luar konteks Jeonme). Subscribe-lock sekalian jadi sumber lead baru untuk Manajer Audiens (No.73). -- SELESAI (25 Juli 2026): migrasi 000016_link_lock (lock_type/lock_code/lock_min_age nullable/kosong di links). 3 jenis kunci sesuai scope (NFT lock di-skip): kode akses, konfirmasi usia (murni klik persetujuan, tanpa verifikasi identitas sungguhan -- konsisten dengan perilaku age-lock Linktree yang sebenarnya), dan wajib subscribe (INSERT ke tabel subscribers YANG SAMA dengan lead capture No.73, jadi benar-benar sumber lead baru untuk Manajer Audiens seperti dicatat). URL asli TIDAK PERNAH dikirim di payload halaman publik untuk tautan terkunci -- baru didapat lewat endpoint publik POST /links/:id/unlock setelah gerbang terlewati, dengan rate limit 15/menit (anti brute-force tebak kode). Diverifikasi end-to-end nyata: validasi tolak lock_type tanpa field pendukungnya &amp; lock_type tidak dikenal; ketiga jenis kunci diuji sungguhan (kode salah ditolak, kode benar &amp; usia &amp; subscribe semua mengembalikan URL asli yang benar); email dari subscribe-lock dikonfirmasi masuk tabel subscribers DAN muncul di endpoint Manajer Audiens (No.73); dikonfirmasi lewat HTML SSR sungguhan bahwa tautan terkunci dirender sebagai tombol gerbang (bukan &lt;a href&gt; langsung) sementara tautan tanpa kunci tetap &lt;a href&gt; normal; buka kunci (clear_lock) mengembalikan tautan ke keadaan normal.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -4717,9 +4717,9 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G78" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H78" s="22" t="n"/>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="J78" s="23" t="inlineStr">
         <is>
-          <t>Saat ini Jeonme hanya punya tautan polos. Ketiga tipe blok ini paling sering dipakai di kedua platform berdasarkan katalog blok "Add new block".</t>
+          <t>Saat ini Jeonme hanya punya tautan polos. Ketiga tipe blok ini paling sering dipakai di kedua platform berdasarkan katalog blok "Add new block". -- SELESAI (25 Juli 2026): migrasi 000017_content_blocks (kolom block_type VARCHAR default 'link' + block_data JSONB default '{}' di links). Blok baru dimodelkan sebagai baris links BIASA (pola identik bundel No.70) -- tampil TERCAMPUR dalam satu urutan yang sama dengan tautan biasa (drag-reorder yang sudah ada langsung berlaku), bukan seksi terpisah. Video embed dibatasi ke YouTube/TikTok saja (bukan iframe generik sembarang situs, demi keamanan) dengan deteksi otomatis format embed URL dari kedua platform (termasuk youtu.be &amp; /shorts/). Formulir kontak SENGAJA tanpa kustomisasi field (selalu nama/email/pesan) -- notifikasi ke kreator dikirim ASINKRON lewat queue.TypeContactFormNotification (worker terpisah), pengunjung tidak pernah menunggu SMTP. FAQ pakai accordion satu-terbuka-sekaligus. Diverifikasi end-to-end nyata: validasi tolak block_type tidak dikenal, video_url bukan YouTube/TikTok, FAQ tanpa item; ketiga blok dibuat sungguhan &amp; tampil BENAR TERCAMPUR di antara tautan biasa (posisi 3/4/5 setelah 3 tautan awal) di HTML SSR halaman publik (iframe TikTok dgn src benar, accordion FAQ, form kontak dgn field lengkap); submit ke blok bukan formulir kontak ditolak; submit sungguhan ke formulir kontak dikonfirmasi diproses worker &amp; email terkirim ke ALAMAT KREATOR (bukan pengunjung); edit isi blok (ganti video_url ke TikTok) lewat endpoint Update yang sudah ada tervalidasi &amp; tersimpan benar, tercermin di halaman publik.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -4849,9 +4849,9 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G81" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H81" s="15" t="n"/>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>Kedua platform expose kustomisasi jauh lebih dalam dari preset saja (Lynk.id: background flat/gradient/gambar + 16 pilihan font + gaya tombol fill/outline/shadow terpisah dari warna tombol).</t>
+          <t>Kedua platform expose kustomisasi jauh lebih dalam dari preset saja (Lynk.id: background flat/gradient/gambar + 16 pilihan font + gaya tombol fill/outline/shadow terpisah dari warna tombol). -- SELESAI (25 Juli 2026): migrasi 000018_custom_theme (custom_background_type/value, custom_font, custom_button_color di pages). Theme "custom" jadi pilihan ke-6 di samping 5 preset. DISEDERHANAKAN dari temuan riset (16 pilihan font Lynk.id -&gt; 5 pilihan cukup beda karakter; gaya tombol fill/outline/shadow terpisah dari warna -&gt; tidak dikerjakan, hanya warna tombol; gradient latar -&gt; tidak dikerjakan, hanya solid/gambar) sesuai keterbatasan waktu utk estimasi 2.5 hari. Pendekatan teknis: warna/gambar latar &amp; warna tombol dipasang lewat CSS custom property (--custom-bg, --custom-button-bg) di elemen &lt;main&gt;, dirujuk oleh kelas Tailwind arbitrary-value (bg-[color:var(...)] / bg-[image:var(...)]) -- SENGAJA tidak meneruskan prop style baru ke tiap komponen tombol (BuyProductButton/LeadCaptureForm/ContactFormBlock/dst) karena custom property CSS otomatis mewarisi ke seluruh turunan DOM. Font tambahan (Playfair Display, Lora, Montserrat, Roboto Mono) dimuat via next/font/google sebagai CSS variable, dipilih lewat font-family inline di &lt;main&gt; juga. Diverifikasi end-to-end nyata: validasi tolak background_type/font/warna tombol yang tidak dikenal; tema custom (solid+Playfair+warna custom) tersimpan &amp; tercermin BENAR di style inline &lt;main&gt; HTML SSR sungguhan; ganti ke jenis latar gambar mengubah kelas &amp; nilai CSS var dengan benar; kembali ke preset (sunrise) mengembalikan kelas Tailwind statis TANPA sisa style inline apa pun.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Selesai (No.81 domain kustom: lingkup aplikasi selesai &amp; terverifikasi, wiring Apache/SSL produksi ditunda sampai ada domain uji sungguhan)</t>
         </is>
       </c>
     </row>
@@ -4893,9 +4893,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G82" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H82" s="22" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="J82" s="23" t="inlineStr">
         <is>
-          <t>DIFERENSIATOR: Linktree eksplisit TIDAK menyediakan domain kustom maupun domain forwarding sama sekali (dikonfirmasi di help center mereka) -- ini peluang nyata Jeonme unggul dari kompetitor terbesar sekaligus menyamai fitur PRO Lynk.id.</t>
+          <t>DIFERENSIATOR: Linktree eksplisit TIDAK menyediakan domain kustom maupun domain forwarding sama sekali (dikonfirmasi di help center mereka) -- ini peluang nyata Jeonme unggul dari kompetitor terbesar sekaligus menyamai fitur PRO Lynk.id. -- SELESAI (LINGKUP APLIKASI, 25 Juli 2026, per keputusan eksplisit pengguna): migrasi 000019_custom_domain (custom_domain, custom_domain_verified, custom_domain_token di pages + unique partial index). Backend baru CustomDomainHandler: Get/Set/Verify/Delete di dashboard (auth) + endpoint publik GET /domains/:domain/resolve dipakai proxy Next.js. Verifikasi kepemilikan domain memakai DUA record DNS wajib sekaligus (CNAME ke custom.jeonme.com DAN TXT _jeonme-verify.{domain} berisi token unik) -- CNAME saja tidak cukup karena siapa pun bisa mengarahkan CNAME tanpa benar-benar memiliki domainnya; TXT membuktikan kontrol DNS sungguhan. Domain hanya di-resolve ke username kalau custom_domain_verified=true DAN is_published=true. Next.js diimplementasikan lewat proxy.ts (bukan middleware.ts -- dikoreksi setelah build memberi peringatan deprecation Next.js 16) yang me-rewrite Host header tak dikenal ke /{username} lewat endpoint resolve publik di atas. Diverifikasi end-to-end nyata: validasi tolak format domain salah; konflik domain yang sudah dipakai kreator lain ditolak 409; endpoint Verify memberi pesan kegagalan yang tepat saat DNS belum diatur; endpoint resolve publik mengembalikan 404 seragam baik untuk domain belum-diverifikasi maupun domain yang benar-benar tidak terdaftar (tidak membocorkan status); setelah domain disimulasikan terverifikasi+halaman dipublikasikan, proxy.ts BENAR me-rewrite request ber-Host-header domain kustom ke halaman publik kreator yang tepat (dites langsung lewat curl -H Host terhadap dev server), sementara Host dikenal (jeonme.com dst.) dan Host tak cocok apa pun tetap berjalan seperti biasa tanpa terganggu. BELUM DIKERJAKAN (sengaja ditunda, bagian infrastruktur produksi): konfigurasi Apache/reverse-proxy supaya Host header domain kustom sungguhan benar-benar sampai ke container Jeonme, dan otomasi sertifikat SSL per domain (mis. Certbot) -- keduanya butuh domain uji nyata yang diarahkan ke server produksi, dicatat sebagai pekerjaan lanjutan begitu ada domain uji yang tersedia. Halaman dashboard sudah mencantumkan disclaimer ini secara eksplisit ke pengguna.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Sebagian Selesai (No.84 selesai; No.85-89 belum dikerjakan)</t>
         </is>
       </c>
     </row>
@@ -5025,9 +5025,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G85" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H85" s="15" t="n"/>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>Melanjutkan catatan No.51 ("rekening TIDAK diverifikasi"). Di Lynk.id, akun ter-KYC dapat pencairan instan sementara akun belum terverifikasi tertahan -- pola yang sama bisa diterapkan Jeonme untuk kurangi risiko fraud penarikan. -- UPDATE (verifikasi live Lynk.id lewat FAQ resmi mereka): checklist KYC lengkap -- nama di KTP harus sama persis dengan nama rekening bank, selfie sambil pegang KTP, bukti buku tabungan/e-statement, alamat domisili lengkap, penjelasan bisnis+kanal promosi, halaman sudah punya minimal 1 produk aktif, SLA review 3x24 jam hari kerja. Verifikasi ini SEKALIGUS membuka 3 hal: pencairan instan, partisipasi affiliate publik, dan fitur pembayaran personal ("PaymeLynk"). CATATAN TAMBAHAN: Lynk.id juga baru menambah langkah "Bank Account Revalidation" terpisah (April 2026) di atas KYC awal -- kemungkinan besar dorongan kepatuhan PSP/regulasi, bukan sekadar fitur produk. Akun BELUM terverifikasi tetap bisa jualan &amp; tarik dana, hanya lebih lambat (2 hari kerja) -- desain Jeonme sebaiknya ikuti pola ini (jangan blokir total, hanya perlambat).</t>
+          <t>Melanjutkan catatan No.51 ("rekening TIDAK diverifikasi"). Di Lynk.id, akun ter-KYC dapat pencairan instan sementara akun belum terverifikasi tertahan -- pola yang sama bisa diterapkan Jeonme untuk kurangi risiko fraud penarikan. -- UPDATE (verifikasi live Lynk.id lewat FAQ resmi mereka): checklist KYC lengkap -- nama di KTP harus sama persis dengan nama rekening bank, selfie sambil pegang KTP, bukti buku tabungan/e-statement, alamat domisili lengkap, penjelasan bisnis+kanal promosi, halaman sudah punya minimal 1 produk aktif, SLA review 3x24 jam hari kerja. Verifikasi ini SEKALIGUS membuka 3 hal: pencairan instan, partisipasi affiliate publik, dan fitur pembayaran personal ("PaymeLynk"). CATATAN TAMBAHAN: Lynk.id juga baru menambah langkah "Bank Account Revalidation" terpisah (April 2026) di atas KYC awal -- kemungkinan besar dorongan kepatuhan PSP/regulasi, bukan sekadar fitur produk. Akun BELUM terverifikasi tetap bisa jualan &amp; tarik dana, hanya lebih lambat (2 hari kerja) -- desain Jeonme sebaiknya ikuti pola ini (jangan blokir total, hanya perlambat). -- SELESAI (25 Juli 2026): migrasi 000020_kyc_verification (tabel kyc_verifications: status unverified/pending/verified/rejected, data KTP/rekening/domisili/bisnis/kanal promosi, 3 key file dokumen; kolom payouts.kyc_status_at_request untuk snapshot). Backend baru KycHandler: kreator submit (multipart: 5 field teks + foto KTP + foto selfie + bukti rekening, validasi wajib halaman sudah punya &gt;=1 produk aktif persis seperti checklist Lynk.id), admin list/detail (URL presigned 15 menit ke tiap dokumen)/approve-reject dengan alasan penolakan wajib. SESUAI ARAHAN RISET: TIDAK memblokir penjualan/penarikan sama sekali untuk akun belum terverifikasi -- status KYC hanya dicatat sebagai SNAPSHOT di setiap pengajuan penarikan (bukan live join, supaya riwayat lama tidak berubah kalau status berubah belakangan) dan dipakai admin untuk memprioritaskan antrian proses manual (ORDER BY verified DESC, lalu requested_at ASC) -- pola ini eksplisit meniru catatan Lynk.id sendiri ("akun belum terverifikasi tetap bisa jualan &amp; tarik dana, hanya lebih lambat"). TIDAK mengerjakan "Bank Account Revalidation" terpisah ala Lynk.id (langkah tambahan April 2026 mereka) maupun integrasi Disbursement API otomatis (proses pencairan tetap 100% manual admin, belum berubah dari Sprint 4). Diverifikasi end-to-end nyata: pengajuan ditolak kalau belum ada produk aktif; diterima &amp; berubah ke status pending setelah produk aktif dibuat; pengajuan ulang ditolak selama masih pending; endpoint admin diblokir untuk non-admin (403); daftar admin menampilkan pengajuan pending; presigned URL dokumen BENAR bisa diunduh (file yang diunggah sungguhan berhasil diambil kembali); penolakan tanpa alasan ditolak validasi; persetujuan berhasil mengubah status ke verified; persetujuan kedua kali ditolak (409, sudah final); pengajuan penarikan SETELAH verified BENAR menyimpan snapshot kyc_status_at_request='verified' dan tampil diprioritaskan lebih dulu di daftar admin dibanding pengajuan lain yang lebih baru tapi belum terverifikasi.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.84 selesai; No.85-89 belum dikerjakan)</t>
+          <t>Sebagian Selesai (No.84, No.85 selesai; No.86-89 belum dikerjakan)</t>
         </is>
       </c>
     </row>
@@ -5069,9 +5069,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G86" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H86" s="22" t="n"/>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="J86" s="23" t="inlineStr">
         <is>
-          <t>Fitur Custom Watermark Lynk.id (PRO) -- anti-pembajakan/pelacakan kebocoran file. Realistis hanya untuk file PDF dulu (paling mudah disisipi watermark terprogram). -- UPDATE (verifikasi live Lynk.id, layar konfigurasi sungguhan dibuka langsung): sumber teks watermark bisa email pembeli ATAU teks custom, posisi (tengah/atas/bawah), ukuran (kecil/sedang/besar), slider opacity (default 50%), dengan preview posisi langsung di layar. CATATAN PENTING dari Lynk.id sendiri: watermark HANYA berfungsi untuk PDF yang tidak dikunci password -- file yang sudah diproteksi password tidak bisa diberi watermark.</t>
+          <t>Fitur Custom Watermark Lynk.id (PRO) -- anti-pembajakan/pelacakan kebocoran file. Realistis hanya untuk file PDF dulu (paling mudah disisipi watermark terprogram). -- UPDATE (verifikasi live Lynk.id, layar konfigurasi sungguhan dibuka langsung): sumber teks watermark bisa email pembeli ATAU teks custom, posisi (tengah/atas/bawah), ukuran (kecil/sedang/besar), slider opacity (default 50%), dengan preview posisi langsung di layar. CATATAN PENTING dari Lynk.id sendiri: watermark HANYA berfungsi untuk PDF yang tidak dikunci password -- file yang sudah diproteksi password tidak bisa diberi watermark. -- SELESAI (25 Juli 2026): migrasi 000021_watermark (kolom products.watermark_enabled, default false). Backend memakai pustaka pdfcpu (Apache-2.0, murni Go, tanpa dependensi native) untuk menyisipkan watermark teks langsung di memori (io.ReadSeeker/io.Writer, tanpa sentuh disk) -- posisi tengah-bawah, opacity 35%, abu-abu, ukuran kecil (TETAP, bukan bisa diatur kreator seperti Lynk.id PRO yang punya pilihan posisi/ukuran/opacity/preview langsung -- disederhanakan sesuai estimasi 1.5 hari). Teks watermark otomatis "email pembeli | ID pesanan" (Lynk.id memberi pilihan email vs teks custom, di sini disederhanakan jadi format tetap). Toggle per-produk di /dashboard/products, HANYA bisa diaktifkan kalau file produk berformat .pdf (ditolak untuk tipe lain, sesuai batasan Lynk.id sendiri: "watermark HANYA berfungsi untuk PDF yang tidak dikunci password" -- Jeonme tidak pernah mengenkripsi file produk jadi syarat itu otomatis terpenuhi). Watermark diproses ON-DEMAND setiap unduhan pembeli (file asli TIDAK PERNAH diubah -- disalin ke key terpisah "watermarked/{order_id}/..." sebelum di-presign), jadi mengubah toggle langsung berlaku untuk unduhan berikutnya tanpa migrasi data. Bundel (No.70) ikut kebagian -- tiap produk DI DALAM bundel punya toggle watermark sendiri-sendiri karena tetap baris products biasa. Diverifikasi end-to-end nyata: watermark ditolak untuk file non-PDF; berhasil aktif untuk file PDF; unduhan pembeli (order status=paid) BENAR menghasilkan salinan ber-watermark yang bisa dibuka &amp; watermark-nya terlihat SECARA VISUAL berisi email pembeli + ID pesanan yang tepat (diverifikasi dengan membuka PDF hasil unduhan langsung); file ASLI di key penyimpanan produk terbukti byte-per-byte TIDAK BERUBAH; menonaktifkan toggle langsung membuat unduhan berikutnya kembali ke file asli tanpa watermark.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.84, No.85 selesai; No.86-89 belum dikerjakan)</t>
+          <t>Sebagian Selesai (No.84, No.85 selesai; No.86 sebagian -- lokasi pengunjung menunggu keputusan geo-IP; No.87-89 belum dikerjakan)</t>
         </is>
       </c>
     </row>
@@ -5113,9 +5113,9 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G87" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>Sebagian Selesai</t>
         </is>
       </c>
       <c r="H87" s="15" t="n"/>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>Analitik Jeonme saat ini (No.56/57) baru total view/klik + tren 30 hari + produk terlaris + referrer. Kedua kompetitor jauh lebih dalam (device/lokasi/rentang custom/CSV export).</t>
+          <t>Analitik Jeonme saat ini (No.56/57) baru total view/klik + tren 30 hari + produk terlaris + referrer. Kedua kompetitor jauh lebih dalam (device/lokasi/rentang custom/CSV export). -- SEBAGIAN SELESAI (25 Juli 2026): filter rentang tanggal kustom (from/to bebas, bukan cuma preset 7/30/90 hari, maksimum 366 hari sekali tarik), breakdown PERANGKAT pengunjung (mobile/desktop/tablet, diklasifikasi dari header User-Agent yang sudah ada di tiap request -- tanpa dependensi baru), dan ekspor CSV (deret harian kunjungan+klik untuk rentang yang dipilih) SUDAH SELESAI &amp; diverifikasi nyata (migrasi 000022_analytics_device menambah kolom device_type; endpoint GET /dashboard/analytics/summary menerima ?from=&amp;to= ATAU ?range_days=; GET /dashboard/analytics/export mengunduh file .csv sungguhan). BELUM DIKERJAKAN: breakdown LOKASI (negara/kota) pengunjung -- ini butuh geo-IP (basis data MaxMind GeoLite2 yang perlu akun+lisensi gratis, ATAU API pihak ketiga berbayar/rate-limited seperti ip-api.com/ipapi.co) yang belum ada keputusan produk/kredensial untuk itu, situasinya mirip blocker WhatsApp Business API (No.74/75) -- BUKAN sesuatu yang bisa diasumsikan sepihak karena menyangkut pilihan vendor &amp; kemungkinan biaya berlangganan. Menunggu keputusan pengguna sebelum dikerjakan, dicatat sebagai pekerjaan lanjutan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.84, No.85 selesai; No.86 sebagian -- lokasi pengunjung menunggu keputusan geo-IP; No.87-89 belum dikerjakan)</t>
+          <t>Sebagian Selesai (No.84, No.85, No.87 selesai; No.86 sebagian -- lokasi pengunjung menunggu keputusan geo-IP; No.88-89 belum dikerjakan)</t>
         </is>
       </c>
     </row>
@@ -5157,9 +5157,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G88" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H88" s="22" t="n"/>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="J88" s="23" t="inlineStr">
         <is>
-          <t>Berguna untuk kreator yang pakai jasa admin/tim kecil (fitur Admin Invites Linktree &amp; Multi Admin Lynk.id, keduanya paid-tier).</t>
+          <t>Berguna untuk kreator yang pakai jasa admin/tim kecil (fitur Admin Invites Linktree &amp; Multi Admin Lynk.id, keduanya paid-tier). -- SELESAI (25 Juli 2026): migrasi 000023_collaborators (undangan lewat email, 3 flag izin tetap: can_edit_links/can_edit_products/can_edit_design, status invited/active/revoked). Pendekatan teknis kunci: middleware baru ActAsOwner (backend) dipasang HANYA pada 3 sub-grup rute dashboard (tautan+blok, produk+voucher+bundel+donasi+afiliasi, halaman/desain) -- membaca header X-Act-As-Owner, memvalidasi kolaborator AKTIF dengan flag izin terkait, lalu MENGGANTI userID di context request ke ID pemilik SEBELUM diteruskan ke handler yang sudah ada, sehingga TIDAK PERLU mengubah satu pun handler yang sudah ada satu per satu. Saldo/penarikan/verifikasi KYC/hapus akun/domain kustom/audiens SENGAJA TIDAK dipasangi middleware ini SAMA SEKALI -- bukan cuma soal validasi izin, tapi batas ARSITEKTUR: kolaborator tidak mungkin menjangkau rute itu lewat mekanisme ini walau ketiga izinnya di-set true sekalipun. Tidak ada pengiriman EMAIL undangan (belum ada wiring mailer utk ini) -- kolaborator menemukan undangan lewat daftar "Undangan untuk Saya" di /dashboard/team miliknya sendiri, dicocokkan lewat alamat email akun. DISEDERHANAKAN dari kompetitor: 3 flag tetap, bukan sistem permission granular per-endpoint. Diverifikasi end-to-end nyata dengan 2 akun sungguhan (pemilik + kolaborator): undangan dibuat &amp; tampil di daftar "Undangan untuk Saya" kolaborator; act-as-owner DITOLAK 403 sebelum undangan diterima; setelah diterima, kolaborator BENAR bisa membuat produk ATAS NAMA pemilik (diverifikasi langsung lewat query database bahwa produk baru user_id-nya adalah pemilik, BUKAN kolaborator); akses ke izin yang TIDAK diberikan (desain) ditolak 403; akses ke saldo &amp; KYC BENAR SELALU mengembalikan data milik kolaborator sendiri (bukan pemilik) walau header X-Act-As-Owner disertakan -- membuktikan batas arsitektur berfungsi, bukan cuma validasi izin yang bisa salah konfigurasi; mencabut akses BENAR langsung memblokir act-as-owner berikutnya (403) tanpa jeda.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.84, No.85, No.87 selesai; No.86 sebagian -- lokasi pengunjung menunggu keputusan geo-IP; No.88-89 belum dikerjakan)</t>
+          <t>Sebagian Selesai (No.84, No.85, No.87, No.88 selesai; No.86 sebagian -- lokasi pengunjung menunggu keputusan geo-IP; No.89 belum dikerjakan)</t>
         </is>
       </c>
     </row>
@@ -5201,9 +5201,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G89" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H89" s="15" t="n"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>Sinyal kepercayaan murah untuk pembeli, memakai data yang sudah ada di sistem (tidak perlu proses manual review seperti Linktree).</t>
+          <t>Sinyal kepercayaan murah untuk pembeli, memakai data yang sudah ada di sistem (tidak perlu proses manual review seperti Linktree). -- SELESAI (25 Juli 2026): TIDAK BUTUH migrasi/tabel baru sama sekali -- is_verified dihitung LANGSUNG dari data yang sudah ada (email_verified_at pada users, bio+avatar_url pada pages, EXISTS order status='paid' milik kreator), sesuai catatan riset: sinyal kepercayaan murah, TANPA proses review manual seperti Linktree. Ditambahkan ke publicPageResponse (halaman publik) dan myPageResponse (dashboard, dalam bentuk objek verification dengan 3 flag terpisah supaya dashboard bisa menunjukkan progres "2/3 syarat" bukan cuma boolean tunggal). Badge tampil sebagai ikon centang di sebelah @username, dipakai bersama oleh halaman publik &amp; panel pratinjau langsung dashboard (satu komponen PagePreview). Diverifikasi end-to-end nyata dengan progres bertahap: kondisi awal ketiga syarat false; mengisi bio SAJA belum cukup (profil belum lengkap, benar menuntut bio DAN foto profil); menambah foto profil membuat profile_complete true tapi is_verified masih false (2 syarat lain belum terpenuhi); memverifikasi email lewat kolom email_verified_at membuat email_verified true; menambah 1 order status='paid' sungguhan membuat has_paid_order true DAN is_verified akhirnya true; dikonfirmasi tampil di endpoint halaman publik SUNGGUHAN (bukan cuma dashboard) DAN benar-benar dirender di HTML SSR halaman publik (elemen dengan title "Kreator terverifikasi" muncul di markup).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.84, No.85, No.87, No.88 selesai; No.86 sebagian -- lokasi pengunjung menunggu keputusan geo-IP; No.89 belum dikerjakan)</t>
+          <t>Selesai untuk lingkup yang bisa diselesaikan (No.84/85/87/88/89 selesai; No.86 sebagian -- breakdown lokasi pengunjung menunggu keputusan geo-IP, seluruh sisanya sudah shipped)</t>
         </is>
       </c>
     </row>
@@ -5245,9 +5245,9 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G90" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G90" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H90" s="22" t="n"/>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="J90" s="23" t="inlineStr">
         <is>
-          <t>Lynk.id menampilkan tabel biaya per channel secara eksplisit ke penjual (mis. QRIS 0.70%, VA flat Rp3-4rb). Jeonme saat ini memotong platform_fee_idr flat tanpa rincian per channel pembayaran ke kreator.</t>
+          <t>Lynk.id menampilkan tabel biaya per channel secara eksplisit ke penjual (mis. QRIS 0.70%, VA flat Rp3-4rb). Jeonme saat ini memotong platform_fee_idr flat tanpa rincian per channel pembayaran ke kreator. -- SELESAI (25 Juli 2026): BUG NYATA ditemukan &amp; diperbaiki sekalian -- payments.method SEBELUMNYA selalu diisi literal 'snap' (nama widget checkout Midtrans, BUKAN kanal pembayaran sesungguhnya), payload webhook Midtrans TIDAK PERNAH menangkap field payment_type asli (qris/bank_transfer/gopay/shopeepay/credit_card) sama sekali sejak awal. Endpoint baru GET /dashboard/balance/fee-breakdown mengembalikan DUA bagian: "reference" (tabel estimasi umum per kanal, PLACEHOLDER bisnis mirip status minPayoutIDR -- sumber angka dari riset publik Lynk.id, TIDAK dipakai untuk menghitung platform_fee_idr sungguhan di mana pun, murni edukasi) dan "actual" (rincian NYATA dari transaksi lunas kreator, dikelompokkan per kanal ASLI yang dipilih pembeli, dihitung dari data payments.method+orders.platform_fee_idr sungguhan). Ditampilkan di halaman Saldo &amp; Penarikan ("ringkasan saldo" sesuai permintaan) -- TIDAK ditambahkan ke halaman checkout pembeli (rincian biaya platform adalah informasi untuk KREATOR, bukan pembeli). platform_fee_idr SENGAJA TETAP flat (PlatformFeePercent) -- mengubah jadi tarif berbeda per kanal adalah keputusan bisnis/kontrak Midtrans yang belum ada datanya, di luar cakupan perbaikan transparansi ini. Diverifikasi end-to-end nyata: breakdown kosong menampilkan tabel referensi tanpa data aktual untuk akun baru; 3 transaksi lunas simulasi (2 QRIS + 1 GoPay) BENAR terkelompok &amp; terjumlah tepat; webhook Midtrans SUNGGUHAN (payload bertanda tangan valid, payment_type="bank_transfer") BENAR menyimpan method='bank_transfer' di payments (BUKAN lagi 'snap') DAN langsung tampil di breakdown; ledger crediting (saldo dikreditkan amount-fee) dipastikan TIDAK REGRESI setelah perubahan query INSERT payments.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Selesai untuk lingkup yang bisa diselesaikan (No.84/85/87/88/89 selesai; No.86 sebagian -- breakdown lokasi pengunjung menunggu keputusan geo-IP, seluruh sisanya sudah shipped)</t>
+          <t>Selesai (No.84-89 semua selesai; No.86 breakdown lokasi diputuskan tidak dikerjakan -- keputusan final pengguna 25 Juli 2026)</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>Analitik Jeonme saat ini (No.56/57) baru total view/klik + tren 30 hari + produk terlaris + referrer. Kedua kompetitor jauh lebih dalam (device/lokasi/rentang custom/CSV export). -- SEBAGIAN SELESAI (25 Juli 2026): filter rentang tanggal kustom (from/to bebas, bukan cuma preset 7/30/90 hari, maksimum 366 hari sekali tarik), breakdown PERANGKAT pengunjung (mobile/desktop/tablet, diklasifikasi dari header User-Agent yang sudah ada di tiap request -- tanpa dependensi baru), dan ekspor CSV (deret harian kunjungan+klik untuk rentang yang dipilih) SUDAH SELESAI &amp; diverifikasi nyata (migrasi 000022_analytics_device menambah kolom device_type; endpoint GET /dashboard/analytics/summary menerima ?from=&amp;to= ATAU ?range_days=; GET /dashboard/analytics/export mengunduh file .csv sungguhan). BELUM DIKERJAKAN: breakdown LOKASI (negara/kota) pengunjung -- ini butuh geo-IP (basis data MaxMind GeoLite2 yang perlu akun+lisensi gratis, ATAU API pihak ketiga berbayar/rate-limited seperti ip-api.com/ipapi.co) yang belum ada keputusan produk/kredensial untuk itu, situasinya mirip blocker WhatsApp Business API (No.74/75) -- BUKAN sesuatu yang bisa diasumsikan sepihak karena menyangkut pilihan vendor &amp; kemungkinan biaya berlangganan. Menunggu keputusan pengguna sebelum dikerjakan, dicatat sebagai pekerjaan lanjutan.</t>
+          <t>Analitik Jeonme saat ini (No.56/57) baru total view/klik + tren 30 hari + produk terlaris + referrer. Kedua kompetitor jauh lebih dalam (device/lokasi/rentang custom/CSV export). -- SEBAGIAN SELESAI (25 Juli 2026): filter rentang tanggal kustom (from/to bebas, bukan cuma preset 7/30/90 hari, maksimum 366 hari sekali tarik), breakdown PERANGKAT pengunjung (mobile/desktop/tablet, diklasifikasi dari header User-Agent yang sudah ada di tiap request -- tanpa dependensi baru), dan ekspor CSV (deret harian kunjungan+klik untuk rentang yang dipilih) SUDAH SELESAI &amp; diverifikasi nyata (migrasi 000022_analytics_device menambah kolom device_type; endpoint GET /dashboard/analytics/summary menerima ?from=&amp;to= ATAU ?range_days=; GET /dashboard/analytics/export mengunduh file .csv sungguhan). BELUM DIKERJAKAN: breakdown LOKASI (negara/kota) pengunjung -- ini butuh geo-IP (basis data MaxMind GeoLite2 yang perlu akun+lisensi gratis, ATAU API pihak ketiga berbayar/rate-limited seperti ip-api.com/ipapi.co) yang belum ada keputusan produk/kredensial untuk itu, situasinya mirip blocker WhatsApp Business API (No.74/75) -- BUKAN sesuatu yang bisa diasumsikan sepihak karena menyangkut pilihan vendor &amp; kemungkinan biaya berlangganan. Menunggu keputusan pengguna sebelum dikerjakan, dicatat sebagai pekerjaan lanjutan. -- KEPUTUSAN FINAL (25 Juli 2026, pengguna): breakdown lokasi TIDAK dikerjakan sama sekali, bukan lagi sekadar ditunda -- biaya/akun vendor geo-IP dianggap tidak sepadan untuk saat ini, breakdown perangkat (mobile/desktop/tablet) sudah dianggap cukup mewakili nilai fitur ini. Sisa lingkup No.86 (rentang tanggal kustom, breakdown perangkat, ekspor CSV) SELESAI sepenuhnya sebagaimana tercatat di atas.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Sebagian Selesai (No.90 selesai; No.91-92 belum dikerjakan)</t>
         </is>
       </c>
     </row>
@@ -5289,9 +5289,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G91" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G91" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H91" s="15" t="n"/>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>Fitur Event block Lynk.id -- ticketing sederhana untuk event online/offline, dijual seperti produk biasa lewat mesin checkout yang sudah ada.</t>
+          <t>Fitur Event block Lynk.id -- ticketing sederhana untuk event online/offline, dijual seperti produk biasa lewat mesin checkout yang sudah ada. -- SELESAI (25 Juli 2026): migrasi 000024_event_block menambah is_event, event_starts_at/ends_at, event_timezone, event_location, event_is_online, event_capacity di products. Event adalah baris products biasa (pola identik bundel/donasi) -- dijual lewat mesin checkout yang SAMA PERSIS TANPA PERUBAHAN (REQ-F-401..405), file_key selalu kosong (yang dijual tiket/kehadiran, bukan file, jadi lolos dari pengecekan wajib-unggah-file yang berlaku produk biasa). Kuota peserta dihitung dari SELURUH order produk ini (status apa pun), pola identik used_count voucher (No.67) -- slot dianggap terpakai sejak checkout DIBUAT bukan setelah lunas, supaya dua pembeli tidak berebut slot terakhir yang sama. Zona waktu divalidasi lewat time.LoadLocation (nama IANA valid apa pun, bukan daftar putih manual). Dashboard memakai peta statis offset UTC tetap (WIB/WITA/WIT, Indonesia tidak pakai DST) untuk membangun RFC3339 dari input datetime-local browser tanpa perlu pustaka timezone. Diverifikasi end-to-end nyata: zona waktu tidak dikenal &amp; waktu berakhir sebelum mulai ditolak validasi; event dibuat &amp; BISA diaktifkan tanpa upload file sama sekali; muncul di halaman publik dengan spots_left terhitung benar (2 slot -&gt; 0 setelah 2 order masuk, termasuk yang masih 'pending' bukan cuma yang lunas); checkout pembeli ke-3 pada event penuh DITOLAK dengan pesan jelas; checkout ke event yang sudah lewat tanggal berakhirnya DITOLAK; event yang sudah lewat otomatis TIDAK tampil lagi di halaman publik.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.90 selesai; No.91-92 belum dikerjakan)</t>
+          <t>Sebagian Selesai (No.90, No.91 selesai; No.92 belum dikerjakan)</t>
         </is>
       </c>
     </row>
@@ -5333,9 +5333,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G92" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H92" s="22" t="n"/>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="J92" s="23" t="inlineStr">
         <is>
-          <t>Fitur Course Video Lynk.id &amp; Digital Products/Courses Linktree. Perluasan natural dari produk digital yang sudah ada (file upload) jadi terstruktur per-bab.</t>
+          <t>Fitur Course Video Lynk.id &amp; Digital Products/Courses Linktree. Perluasan natural dari produk digital yang sudah ada (file upload) jadi terstruktur per-bab. -- SELESAI (25 Juli 2026): migrasi 000025_course_block menambah is_course + course_prerequisites di products, dan tabel baru course_chapters (title, description, video_url, position per bab). Kursus adalah baris products biasa (pola identik bundel/event) -- tampil di grid Produk yang SAMA seperti produk biasa (bukan blok tersendiri seperti Event/Donation), cukup ditandai badge "X Bab". DISEDERHANAKAN dari fitur kompetitor: video per-bab WAJIB tautan YouTube/TikTok (reuse validator embed persis dari blok video No.77), BUKAN upload/hosting video sendiri -- itu perlu infrastruktur streaming terpisah yang jauh di luar cakupan. Prasyarat cuma teks bebas, bukan validasi terhubung ke kursus lain. Edit bab pakai endpoint "ganti semua bab sekaligus" (bukan CRUD granular tambah/hapus/reorder per-bab) -- lebih sederhana &amp; aman dari salah urutan posisi, dan mengedit kursus diperkirakan jarang terjadi. Setelah lunas, pembeli melihat bab video lewat halaman status checkout (component VideoEmbedBlock yang SAMA dipakai ulang dari No.77) -- TIDAK perlu presigned URL sama sekali karena video selalu tautan embed publik, beda dari bundel yang filenya privat di storage. Diverifikasi end-to-end nyata: video bukan YouTube/TikTok &amp; bab kosong ditolak validasi; kursus dibuat &amp; BISA diaktifkan tanpa upload file; muncul di grid Produk halaman publik dengan chapter_count benar; ganti-semua-bab (replace) BENAR mengganti seluruh isi lama; status checkout pembeli menampilkan is_course=true; endpoint bab kursus mengembalikan seluruh bab terurut untuk order lunas, DITOLAK untuk order belum lunas (403), order tidak ditemukan (404), dan order produk BUKAN kursus (400).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.90, No.91 selesai; No.92 belum dikerjakan)</t>
+          <t>Selesai (No.90, No.91, No.92 semua selesai -- No.92 tanpa sinkronisasi Google Calendar per keputusan pengguna, kredensial OAuth belum ada)</t>
         </is>
       </c>
     </row>
@@ -5377,9 +5377,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G93" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H93" s="15" t="n"/>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>Fitur Bookings (Linktree, gratis di semua tier) &amp; Appointment (Lynk.id). Butuh integrasi Google Calendar API (OAuth terpisah dari login) untuk cegah bentrok jadwal.</t>
+          <t>Fitur Bookings (Linktree, gratis di semua tier) &amp; Appointment (Lynk.id). Butuh integrasi Google Calendar API (OAuth terpisah dari login) untuk cegah bentrok jadwal. -- SELESAI (LINGKUP TANPA GOOGLE CALENDAR, 25 Juli 2026, per keputusan eksplisit pengguna): migrasi 000026_booking_block menambah is_booking + booking_duration_minutes di products, dan tabel baru booking_slots (starts_at/ends_at/order_id, unique index per produk+starts_at). SENGAJA TIDAK terhubung ke Google Calendar API -- itu butuh proyek Google Cloud + OAuth client TERPISAH dari login yang kredensialnya belum ada, situasinya identik blocker WhatsApp Business API (No.74/75). Pencegahan bentrok jadwal TETAP SUNGGUHAN (bukan cuma UI kosmetik) -- dijamin oleh klaim slot ATOMIK di database sendiri lewat UPDATE booking_slots SET order_id=$1 WHERE ... AND order_id IS NULL di dalam transaksi checkout yang sama (pola sama seperti used_count voucher/kuota event), BUKAN oleh sinkronisasi ke kalender pribadi kreator. Kreator menambah slot SATU PER SATU secara manual (bukan generator jadwal berulang mingguan) -- disederhanakan dari fitur penuh Booking Linktree/Appointment Lynk.id sesuai keterbatasan waktu &amp; blocker kredensial. Booking tampil sebagai blok tersendiri di halaman publik (bukan grid Produk biasa) karena pembeli WAJIB pilih slot dulu sebelum checkout bisa dimulai. Diverifikasi end-to-end nyata DENGAN RACE CONDITION SUNGGUHAN: durasi tidak valid &amp; slot di waktu lampau ditolak validasi; slot dibuat dengan waktu berakhir otomatis terhitung benar dari durasi; checkout tanpa slot_id ditolak; checkout SUNGGUHAN lewat Midtrans sandbox BENAR mengklaim slot; PEMBELI KEDUA yang mencoba slot YANG SAMA persis DITOLAK 409 (bukti nyata pencegahan bentrok jadwal berfungsi, bukan asumsi); webhook pembayaran sungguhan (signature valid) BENAR mengonfirmasi booking &amp; mengkredit ledger tanpa regresi; slot yang SUDAH dipesan ditolak untuk dihapus (409), slot yang BELUM dipesan berhasil dihapus; status checkout menampilkan waktu slot yang dipesan untuk ditampilkan ke pembeli.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Ditunda (No.93 menunggu validasi permintaan pasar produk fisik + kredensial API ongkir -- keputusan pengguna 25 Juli 2026)</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="J94" s="23" t="inlineStr">
         <is>
-          <t>Fitur commerce terdalam Lynk.id (listing 20 kategori, kalkulasi ongkir, banyak kurir). CATATAN PENTING: ini perluasan besar di luar fokus awal Jeonme sebagai platform produk DIGITAL kreator -- menambah kompleksitas logistik/fulfillment signifikan (integrasi ongkir, pelacakan pengiriman, retur). Validasi permintaan pasar dulu sebelum dikerjakan, jangan asumsikan otomatis dibutuhkan.</t>
+          <t>Fitur commerce terdalam Lynk.id (listing 20 kategori, kalkulasi ongkir, banyak kurir). CATATAN PENTING: ini perluasan besar di luar fokus awal Jeonme sebagai platform produk DIGITAL kreator -- menambah kompleksitas logistik/fulfillment signifikan (integrasi ongkir, pelacakan pengiriman, retur). Validasi permintaan pasar dulu sebelum dikerjakan, jangan asumsikan otomatis dibutuhkan. -- DITUNDA (25 Juli 2026, keputusan eksplisit pengguna): demand pasar untuk produk fisik BELUM divalidasi, sesuai anjuran catatan di atas untuk tidak mengasumsikan fitur ini otomatis dibutuhkan. Juga butuh API tarif ongkir pihak ketiga (RajaOngkir/Biteship/sejenisnya) dengan kredensial sendiri -- blocker eksternal serupa WhatsApp Business API &amp; Google Calendar. Menunggu validasi permintaan pasar sebelum dikerjakan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Sebagian Selesai (No.94 poin loyalitas selesai; No.95 kartu kontak digital &amp; No.96 asisten analitik AI belum dikerjakan)</t>
         </is>
       </c>
     </row>
@@ -5465,9 +5465,9 @@
           <t>Should</t>
         </is>
       </c>
-      <c r="G95" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G95" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H95" s="15" t="n"/>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>Diverifikasi langsung di akun Lynk.id sungguhan ("Member Point System"): tipe poin Percentage/Percentage-with-Limit/Nominal/Nominal-with-Limit + field Min Purchase, dan halaman Reward Management terpisah (katalog reward: Value/Valid Date/Points Needed/Redeemed/Publish). Cocok disandingkan dengan voucher (No.67) sebagai mekanisme retensi pembeli berulang.</t>
+          <t>Diverifikasi langsung di akun Lynk.id sungguhan ("Member Point System"): tipe poin Percentage/Percentage-with-Limit/Nominal/Nominal-with-Limit + field Min Purchase, dan halaman Reward Management terpisah (katalog reward: Value/Valid Date/Points Needed/Redeemed/Publish). Cocok disandingkan dengan voucher (No.67) sebagai mekanisme retensi pembeli berulang. -- SELESAI (25 Juli 2026): dibangun sebagai atribut products/loyalty_settings/loyalty_rewards/loyalty_points_ledger baru (bukan entitas terpisah), memakai kembali mesin voucher (No.67) sebagai mekanisme penukaran reward (tiap penukaran membuat 1 voucher max_uses=1 kode REWARD-xxxxxxxx). Poin dihitung PER KREATOR (bukan lintas platform), dikreditkan otomatis di CheckoutHandler.Webhook setelah ledger kreator &amp; afiliasi (kalau ada) dikredit, mendukung tipe nominal (poin per Rp10.000) dan percentage (poin per Rp100.000), syarat minimum pembelian, dan batas maks poin per transaksi. Penukaran reward dikunci dengan pg_advisory_xact_lock per kreator+pembeli untuk cegah double-spend poin lewat request paralel. Diverifikasi E2E NYATA: aktivasi pengaturan, buat+publish reward, checkout sungguhan ke Midtrans sandbox + webhook bertanda tangan SHA512 asli -&gt; poin ter-kredit benar untuk nominal (200rb @ rate 1 = 20 poin), percentage (200rb @ rate 2 = 4 poin), batas min_purchase_idr (order di bawah minimum TIDAK dapat poin), dan points_limit (poin dipotong ke batas maks). Penukaran reward berhasil menghasilkan voucher yang BENAR-BENAR dipakai di checkout sungguhan (diskon 10% terpotong dari harga produk). Ditolak dengan benar: poin tidak cukup, reward belum dipublikasikan, reward kedaluwarsa. RACE CONDITION diuji NYATA (2 request redeem paralel dengan saldo poin yang cuma cukup untuk 1x tukar): 1 berhasil (200), 1 ditolak (400 poin tidak cukup) -- tidak ada double-spend. Semua data uji (users/pages/products/orders/payments/ledger_entries/loyalty_*/vouchers/audit_log) dibersihkan sesuai urutan FK setelah verifikasi selesai.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.94 poin loyalitas selesai; No.95 kartu kontak digital &amp; No.96 asisten analitik AI belum dikerjakan)</t>
+          <t>Sebagian Selesai (No.94 poin loyalitas &amp; No.95 kartu kontak digital selesai; No.95 tanpa Apple/Google Wallet; No.96 asisten analitik AI belum dikerjakan)</t>
         </is>
       </c>
     </row>
@@ -5509,9 +5509,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G96" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H96" s="25" t="n"/>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="J96" s="26" t="inlineStr">
         <is>
-          <t>Ditemukan lewat tur live dashboard Linktree sungguhan (bukan cuma dokumentasi publik) -- fitur "Business Cards" beneran menghasilkan QR code + Apple Wallet pass, dengan toggle "Let visitors share their details back" yang mengumpulkan nama/email pengunjung yang scan balik. Beda dari kunci tautan (No.79) -- ini pertukaran kontak DUA ARAH, bukan gerbang akses konten.</t>
+          <t>Ditemukan lewat tur live dashboard Linktree sungguhan (bukan cuma dokumentasi publik) -- fitur "Business Cards" beneran menghasilkan QR code + Apple Wallet pass, dengan toggle "Let visitors share their details back" yang mengumpulkan nama/email pengunjung yang scan balik. Beda dari kunci tautan (No.79) -- ini pertukaran kontak DUA ARAH, bukan gerbang akses konten. -- SELESAI (25 Juli 2026), LINGKUP DIPERSEMPIT: Apple Wallet/Google Wallet pass TIDAK dibangun -- butuh kredensial Apple Developer Program + Google Wallet API yang belum tersedia (blocker eksternal serupa WhatsApp Business API/No.74-75). Sebagai gantinya: pengunjung mengunduh file vCard (.vcf) standar yang dibuat di sisi frontend (didukung native oleh aplikasi Kontak iOS &amp; Android tanpa integrasi pihak ketiga apa pun). Dibangun: tabel business_cards baru (nama/jabatan/perusahaan/telepon/whatsapp/email/website + toggle aktif &amp; toggle terima-kontak-balik), halaman publik terpisah jeonme.com/card/{username} (BUKAN halaman utama kreator) dengan kode QR sendiri (pakai ulang QRCodeModal, dibuat generik lewat prop title/description), dan formulir pertukaran DUA ARAH -- kontak yang dibagikan pengunjung balik disimpan ke tabel subscribers (No.73, Manajer Audiens) yang diperluas dengan kolom name &amp; source eksplisit (lead_capture/buyer/business_card) supaya ketiga sumber kontak tergabung dalam SATU daftar Manajer Audiens, bukan tabel terpisah. Diverifikasi E2E NYATA: validasi nama wajib saat aktivasi, endpoint publik 404 kalau kartu belum aktif, penukaran kontak balik berhasil tersimpan dengan source=business_card &amp; tampil benar di Manajer Audiens, ditolak kalau toggle terima-kontak-balik nonaktif, ditolak kalau email &amp; whatsapp keduanya kosong, kartu hilang dari endpoint publik begitu dinonaktifkan, dan REGRESI No.73 (lead capture) dipastikan tetap jalan normal dengan skema subscribers yang diperluas. Halaman publik kartu (/card/username) dicek render sungguhan lewat curl ke dev server Next.js -- menampilkan data lengkap &amp; kedua aksi (unduh vCard, formulir kontak balik) dengan benar. CATATAN JUJUR: halaman pengaturan dashboard (/dashboard/business-card) TIDAK diverifikasi visual di browser sungguhan (perlu sesi login nyata di browser, di luar jangkauan verifikasi curl) -- tsc/eslint/build semua bersih dan shell halaman termuat tanpa error di server dev, tapi interaksi UI (toggle, form) belum dicek visual.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -678,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -690,6 +690,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -723,6 +724,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -972,6 +974,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -986,6 +989,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1231,7 +1235,7 @@
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.94 poin loyalitas &amp; No.95 kartu kontak digital selesai; No.95 tanpa Apple/Google Wallet; No.96 asisten analitik AI belum dikerjakan)</t>
+          <t>Selesai (No.94 poin loyalitas, No.95 kartu kontak digital, No.96 asisten analitik semua selesai -- No.95 tanpa Apple/Google Wallet, No.96 tanpa LLM API berbayar, keduanya lingkup dipersempit per keputusan pengguna)</t>
         </is>
       </c>
     </row>
@@ -5553,9 +5557,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G97" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H97" s="15" t="n"/>
@@ -5564,7 +5568,7 @@
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>Ditemukan lewat tur live dashboard Linktree -- panel "Ask Linktree AI" aktif secara default di tab Insight dengan prompt siap pakai ("Where is my traffic coming from?", dst). CATATAN: hitung dulu biaya API LLM per-query sebelum komit -- jangan asumsikan gratis seperti fitur analitik biasa (No.86).</t>
+          <t>Ditemukan lewat tur live dashboard Linktree -- panel "Ask Linktree AI" aktif secara default di tab Insight dengan prompt siap pakai ("Where is my traffic coming from?", dst). CATATAN: hitung dulu biaya API LLM per-query sebelum komit -- jangan asumsikan gratis seperti fitur analitik biasa (No.86). -- SELESAI (25 Juli 2026), LINGKUP DIPERSEMPIT (keputusan eksplisit pengguna): TANPA panggilan API LLM sungguhan (OpenAI/Anthropic/dst) yang berbayar per-query -- belum ada keputusan anggaran untuk itu, sesuai anjuran catatan asli backlog ini. Sebagai gantinya: pencocokan kata kunci sederhana atas pertanyaan bahasa natural (traffic/sumber, produk/laku, tren/naik-turun, perangkat/device, tautan/klik), dipetakan ke query analitik yang SUDAH ADA (No.86, direfaktor jadi computeSummary supaya dipakai ulang tanpa duplikasi), lalu jawaban dirangkai jadi kalimat dari angka NYATA -- NOL biaya per-query. Panel "Tanya Analitik" di halaman Ringkasan dashboard, dengan 4 tombol contoh pertanyaan siap pakai (meniru "Ask Linktree AI"), riwayat tanya-jawab gaya chat, dan disclaimer jujur bahwa ini BUKAN model AI berbayar. Diverifikasi E2E NYATA dengan data analitik sungguhan (order lunas + event view/click dengan referrer &amp; User-Agent berbeda + data backdated multi-hari lewat SQL langsung): jawaban sumber trafik &amp; produk terlaris &amp; perangkat &amp; tautan terpopuler semua cocok PERSIS dengan angka di endpoint summary yang sudah ada; jawaban tren kunjungan diuji BENAR mendeteksi arah naik (paruh pertama 2 kunjungan vs paruh kedua 17 kunjungan pada data 3-hari) dengan pembagian paruh yang akurat; pertanyaan tak dikenali mendapat jawaban fallback berisi daftar topik yang dipahami, bukan error atau jawaban kosong.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -678,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="B2:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -690,7 +690,6 @@
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -724,7 +723,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -974,7 +972,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -989,7 +986,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -5645,9 +5641,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G99" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H99" s="22" t="n"/>
@@ -5656,7 +5652,7 @@
       </c>
       <c r="J99" s="23" t="inlineStr">
         <is>
-          <t>Diverifikasi live: 1 akun bisa punya beberapa halaman bio terpisah (masing-masing URL sendiri). Berguna untuk kreator yang kelola beberapa brand/proyek dari satu akun. Belum prioritas -- Jeonme masih fokus perkuat 1 halaman per kreator dulu.</t>
+          <t>Diverifikasi live: 1 akun bisa punya beberapa halaman bio terpisah (masing-masing URL sendiri). Berguna untuk kreator yang kelola beberapa brand/proyek dari satu akun. Belum prioritas -- Jeonme masih fokus perkuat 1 halaman per kreator dulu. -- SELESAI (25 Juli 2026), dibangun MESKIPUN catatan asli bilang belum prioritas (keputusan eksplisit pengguna). Halaman UTAMA (jeonme.com/{username}) TIDAK BERUBAH sama sekali -- semua rute lama tetap hanya menjangkau halaman utama lewat kolom baru pages.is_primary (default true, dijamin PERSIS 1 per akun lewat unique index parsial). Halaman TAMBAHAN (is_primary=false) diakses lewat jeonme.com/p/{slug} -- namespace terpisah dari username akun. LINGKUP: halaman tambahan punya bio/tema/tautan SENDIRI, tapi berbagi katalog produk &amp; seluruh fitur monetisasi (voucher/bundel/event/booking/loyalty/dst) yang SAMA dengan kreatornya -- monetisasi tetap per-AKUN, bukan per-halaman. Dashboard baru /dashboard/pages (buat/kelola halaman tambahan: nama/slug/bio/tema/publish + tautan sendiri per halaman, reorder sendiri) menyatu dengan grup ActAsOwner can_edit_design/can_edit_links yang sudah ada (kolaborator bisa ikut kelola). Analitik TIDAK dicampur: tracking view/klik halaman tambahan lewat endpoint slug terpisah (POST /p/:slug/track), TIDAK memakai endpoint username (yang akan salah tercatat ke halaman utama kreator yang sama -- ditemukan &amp; diperbaiki SEBELUM commit lewat audit menyeluruh semua query "pages WHERE user_id" di seluruh backend yang berasumsi 1 halaman per akun). Diverifikasi E2E NYATA: buat halaman tambahan, tolak slug duplikat &amp; format slug invalid, publish &amp; akses publik lewat slug, ISOLASI tautan dua arah dibuktikan (tautan halaman utama TIDAK muncul di halaman tambahan dan sebaliknya), produk yang sama TERBUKTI muncul di KEDUA halaman (monetisasi bersama), tracking view+klik lewat slug tersimpan dengan page_id yang benar TANPA mencemari analitik halaman utama (dibuktikan count=0 di halaman utama setelah tracking di halaman tambahan), reorder tautan halaman tambahan, penghapusan halaman utama ditolak lewat endpoint halaman tambahan (404), penghapusan halaman tambahan BERHASIL membersihkan tautan + analytics_events terkait dalam satu transaksi (FK analytics_events.link_id tidak CASCADE, dibersihkan manual dulu) TANPA orphan tersisa, dan cache Redis halaman publik terbukti invalidasi benar saat halaman tambahan diperbarui. Migrasi 000029 diterapkan lokal &amp; seluruh test suite (go test ./...) tetap hijau setelah audit ulang skema.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -678,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -690,6 +690,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -723,6 +724,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -972,6 +974,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -986,6 +989,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1262,7 +1266,7 @@
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Selesai (No.98 multi-halaman bio &amp; No.99 builder landing page dibangun MESKIPUN catatan asli bilang belum prioritas -- keputusan eksplisit pengguna; No.99 tanpa Create with AI, murni builder blok manual)</t>
         </is>
       </c>
     </row>
@@ -5685,9 +5689,9 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G100" s="24" t="inlineStr">
-        <is>
-          <t>Belum Mulai</t>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="H100" s="25" t="n"/>
@@ -5696,7 +5700,7 @@
       </c>
       <c r="J100" s="26" t="inlineStr">
         <is>
-          <t>Diverifikasi live: fitur baru Linktree, tombol 'Create with AI' untuk generate draft halaman landing lengkap. Ini lebih ke arah website builder daripada link-in-bio -- scope besar &amp; tangensial dari fokus Jeonme, dicatat sebagai ide masa depan bukan prioritas sekarang.</t>
+          <t>Diverifikasi live: fitur baru Linktree, tombol 'Create with AI' untuk generate draft halaman landing lengkap. Ini lebih ke arah website builder daripada link-in-bio -- scope besar &amp; tangensial dari fokus Jeonme, dicatat sebagai ide masa depan bukan prioritas sekarang. -- SELESAI (25 Juli 2026), LINGKUP DIPERSEMPIT (keputusan eksplisit pengguna): TANPA tombol "Create with AI" -- fitur asli Linktree generate draft lewat LLM, butuh keputusan biaya API per-query yang belum ada (sama seperti catatan No.96). Sebagai gantinya: builder BLOK MANUAL (heading/teks/gambar/tombol CTA), dibangun sebagai perluasan RINGAN dari infrastruktur halaman tambahan (No.98) yang baru selesai -- landing page HANYALAH baris pages lain dengan page_type='landing' (kolom baru, CHECK constraint bio/landing) alih-alih 'bio', dan blok-bloknya baris links biasa (4 block_type baru: heading/text/image/button, dipetakan ke kolom title/url/block_data yang SUDAH ADA -- TIDAK ada tabel baru sama sekali). Halaman landing dirender TERPISAH dari halaman bio (komponen LandingPagePreview baru): TANPA avatar/username-header/produk/monetisasi -- fokus tunggal ke blok kampanye, beda signifikan dari halaman bio No.98 yang tetap menampilkan katalog produk bersama. Diverifikasi E2E NYATA: buat halaman page_type=landing, tambah keempat jenis blok (heading/text/image/button) lewat endpoint /dashboard/pages/:id/blocks yang baru, validasi tiap tipe ditolak dengan benar kalau field wajib kosong (teks kosong, URL gambar tidak valid, URL tombol kosong), publish &amp; akses publik lewat slug menampilkan page_type="landing" dengan urutan blok benar, dan HTML hasil render dicek langsung (curl ke Next.js dev server) membuktikan keempat blok tampil dengan konten benar TANPA header avatar/username bio (class avatar h-24 w-24 terbukti tidak ada di body). Penghapusan halaman landing memakai ulang endpoint DeletePage yang SAMA persis seperti No.98 (FK-safe cleanup blok + analytics_events tanpa perubahan kode), dibuktikan bersih tanpa orphan. Migrasi 000030 diterapkan lokal, seluruh test suite tetap hijau.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -283,6 +283,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -678,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A2:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -690,7 +691,6 @@
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -724,7 +724,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -974,7 +973,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -989,7 +987,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1267,6 +1264,37 @@
       <c r="G27" s="21" t="inlineStr">
         <is>
           <t>Selesai (No.98 multi-halaman bio &amp; No.99 builder landing page dibangun MESKIPUN catatan asli bilang belum prioritas -- keputusan eksplisit pengguna; No.99 tanpa Create with AI, murni builder blok manual)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 15</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Desain 2.0 (Permintaan Langsung Pengguna)</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Minggu 29</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Ditambahkan langsung oleh pengguna (bukan dari riset kompetitor asli): galeri template 5-&gt;10 preset, gaya tombol fill/outline/shadow, latar gradien, font 5-&gt;9 pilihan</t>
+        </is>
+      </c>
+      <c r="F28" s="8">
+        <f>COUNTIF(Backlog!B:B,"Sprint 15")</f>
+        <v/>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>Selesai (galeri template, gaya tombol, gradien, font lebih banyak -- semua selesai &amp; terverifikasi)</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5701,6 +5729,49 @@
       <c r="J100" s="26" t="inlineStr">
         <is>
           <t>Diverifikasi live: fitur baru Linktree, tombol 'Create with AI' untuk generate draft halaman landing lengkap. Ini lebih ke arah website builder daripada link-in-bio -- scope besar &amp; tangensial dari fokus Jeonme, dicatat sebagai ide masa depan bukan prioritas sekarang. -- SELESAI (25 Juli 2026), LINGKUP DIPERSEMPIT (keputusan eksplisit pengguna): TANPA tombol "Create with AI" -- fitur asli Linktree generate draft lewat LLM, butuh keputusan biaya API per-query yang belum ada (sama seperti catatan No.96). Sebagai gantinya: builder BLOK MANUAL (heading/teks/gambar/tombol CTA), dibangun sebagai perluasan RINGAN dari infrastruktur halaman tambahan (No.98) yang baru selesai -- landing page HANYALAH baris pages lain dengan page_type='landing' (kolom baru, CHECK constraint bio/landing) alih-alih 'bio', dan blok-bloknya baris links biasa (4 block_type baru: heading/text/image/button, dipetakan ke kolom title/url/block_data yang SUDAH ADA -- TIDAK ada tabel baru sama sekali). Halaman landing dirender TERPISAH dari halaman bio (komponen LandingPagePreview baru): TANPA avatar/username-header/produk/monetisasi -- fokus tunggal ke blok kampanye, beda signifikan dari halaman bio No.98 yang tetap menampilkan katalog produk bersama. Diverifikasi E2E NYATA: buat halaman page_type=landing, tambah keempat jenis blok (heading/text/image/button) lewat endpoint /dashboard/pages/:id/blocks yang baru, validasi tiap tipe ditolak dengan benar kalau field wajib kosong (teks kosong, URL gambar tidak valid, URL tombol kosong), publish &amp; akses publik lewat slug menampilkan page_type="landing" dengan urutan blok benar, dan HTML hasil render dicek langsung (curl ke Next.js dev server) membuktikan keempat blok tampil dengan konten benar TANPA header avatar/username bio (class avatar h-24 w-24 terbukti tidak ada di body). Penghapusan halaman landing memakai ulang endpoint DeletePage yang SAMA persis seperti No.98 (FK-safe cleanup blok + analytics_events tanpa perubahan kode), dibuktikan bersih tanpa orphan. Migrasi 000030 diterapkan lokal, seluruh test suite tetap hijau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Sprint 15</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BE+FE</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Desain 2.0 -- galeri template diperluas (5-&gt;10 preset), gaya tombol (fill/outline/shadow), latar gradien, font lebih banyak (5-&gt;9)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (di luar riset kompetitor asli)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G101" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna (bukan dari riset kompetitor Linktree/Lynk.id di backlog No.67-99) -- permintaan eksplisit: fitur desain "Halaman Saya" dinilai masih terlalu simpel dibanding kedua platform referensi. Mengerjakan 3 hal yang SENGAJA diskip di No.80 (Sprint 9) karena keterbatasan waktu waktu itu: gaya tombol (fill/outline/shadow, sebelumnya cuma fill), latar gradien (sebelumnya cuma solid/gambar), dan preset tema diperluas jadi galeri 10 (rose/ocean/lavender/noir/peach baru, palet warna LEPAS dari brand Jeonme karena halaman ini milik kreator) -- SELESAI (25 Juli 2026): migrasi 000031 (kolom custom_button_style baru, default 'fill'); gradien memakai ulang kolom custom_background_value yang sudah ada (disimpan sebagai string CSS linear-gradient(...) lengkap, backend tetap memperlakukannya sebagai string opaque); font diperluas dari 5 jadi 9 (tambah Poppins/Quicksand/Merriweather/Space Grotesk lewat next/font/google). Dashboard Desain diganti dari daftar pill kecil jadi galeri grid visual, plus panel Kustomisasi Lanjutan diperluas dengan 3 pilihan jenis latar (solid/gradien/gambar, gradien pakai 2 color picker awal-akhir) dan selector Gaya Tombol baru. LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): layout struktural ala Lynk.id (Classic/Modern/Clean, mengubah struktur DOM bukan sekadar warna -- effort jauh lebih besar), stickers/elemen dekoratif ala Linktree (kosmetik, nilai rendah), bentuk avatar (butuh berlaku di SEMUA tema bukan cuma custom, kompleksitas tambahan tanpa banyak nilai), override manual per elemen ala Linktree (Header/Wallpaper/Buttons/Text terpisah -- sudah cukup terwakili mode Custom yang ada). Diverifikasi E2E NYATA: kelima preset baru diterima &amp; tersimpan lewat PATCH /dashboard/page, tercermin benar di GET /pages/:username; validasi menolak tema/gaya tombol/jenis latar yang tidak dikenal (400); tema custom dengan gaya tombol outline &amp; shadow DIBUKTIKAN merender kelas Tailwind yang benar di HTML SSR sungguhan (border+teks berwarna utk outline, shadow berwarna utk shadow) lewat fetch yang genuinely tidak ter-cache; latar gradien DIBUKTIKAN --custom-bg berisi string linear-gradient(...) lengkap di style inline &lt;main&gt;; font baru (Space Grotesk dkk) DIBUKTIKAN font-family mengarah ke CSS variable yang benar; parity penuh diverifikasi juga di halaman tambahan (No.98) lewat PATCH /dashboard/pages/:id. Semua data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -679,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G28"/>
+  <dimension ref="A2:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1298,6 +1298,37 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Tautan Advanced (Permintaan Langsung Pengguna)</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Minggu 29</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Ditambahkan langsung oleh pengguna: deteksi ikon platform otomatis (YouTube/TikTok/WhatsApp/dll) per tautan + polish UI/UX dashboard</t>
+        </is>
+      </c>
+      <c r="F29" s="8">
+        <f>COUNTIF(Backlog!B:B,"Sprint 16")</f>
+        <v/>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>Selesai (deteksi ikon 9 platform + fallback, form tautan collapsed-by-default -- selesai &amp; terverifikasi)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1309,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5772,6 +5803,49 @@
       <c r="J101" t="inlineStr">
         <is>
           <t>DITAMBAHKAN LANGSUNG oleh pengguna (bukan dari riset kompetitor Linktree/Lynk.id di backlog No.67-99) -- permintaan eksplisit: fitur desain "Halaman Saya" dinilai masih terlalu simpel dibanding kedua platform referensi. Mengerjakan 3 hal yang SENGAJA diskip di No.80 (Sprint 9) karena keterbatasan waktu waktu itu: gaya tombol (fill/outline/shadow, sebelumnya cuma fill), latar gradien (sebelumnya cuma solid/gambar), dan preset tema diperluas jadi galeri 10 (rose/ocean/lavender/noir/peach baru, palet warna LEPAS dari brand Jeonme karena halaman ini milik kreator) -- SELESAI (25 Juli 2026): migrasi 000031 (kolom custom_button_style baru, default 'fill'); gradien memakai ulang kolom custom_background_value yang sudah ada (disimpan sebagai string CSS linear-gradient(...) lengkap, backend tetap memperlakukannya sebagai string opaque); font diperluas dari 5 jadi 9 (tambah Poppins/Quicksand/Merriweather/Space Grotesk lewat next/font/google). Dashboard Desain diganti dari daftar pill kecil jadi galeri grid visual, plus panel Kustomisasi Lanjutan diperluas dengan 3 pilihan jenis latar (solid/gradien/gambar, gradien pakai 2 color picker awal-akhir) dan selector Gaya Tombol baru. LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): layout struktural ala Lynk.id (Classic/Modern/Clean, mengubah struktur DOM bukan sekadar warna -- effort jauh lebih besar), stickers/elemen dekoratif ala Linktree (kosmetik, nilai rendah), bentuk avatar (butuh berlaku di SEMUA tema bukan cuma custom, kompleksitas tambahan tanpa banyak nilai), override manual per elemen ala Linktree (Header/Wallpaper/Buttons/Text terpisah -- sudah cukup terwakili mode Custom yang ada). Diverifikasi E2E NYATA: kelima preset baru diterima &amp; tersimpan lewat PATCH /dashboard/page, tercermin benar di GET /pages/:username; validasi menolak tema/gaya tombol/jenis latar yang tidak dikenal (400); tema custom dengan gaya tombol outline &amp; shadow DIBUKTIKAN merender kelas Tailwind yang benar di HTML SSR sungguhan (border+teks berwarna utk outline, shadow berwarna utk shadow) lewat fetch yang genuinely tidak ter-cache; latar gradien DIBUKTIKAN --custom-bg berisi string linear-gradient(...) lengkap di style inline &lt;main&gt;; font baru (Space Grotesk dkk) DIBUKTIKAN font-family mengarah ke CSS variable yang benar; parity penuh diverifikasi juga di halaman tambahan (No.98) lewat PATCH /dashboard/pages/:id. Semua data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Tautan lebih advanced -- deteksi ikon platform otomatis per tautan (YouTube/TikTok/WhatsApp/dll) + polish UI/UX dashboard</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (di luar riset kompetitor asli)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G102" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -679,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G29"/>
+  <dimension ref="B2:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5802,7 +5802,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna (bukan dari riset kompetitor Linktree/Lynk.id di backlog No.67-99) -- permintaan eksplisit: fitur desain "Halaman Saya" dinilai masih terlalu simpel dibanding kedua platform referensi. Mengerjakan 3 hal yang SENGAJA diskip di No.80 (Sprint 9) karena keterbatasan waktu waktu itu: gaya tombol (fill/outline/shadow, sebelumnya cuma fill), latar gradien (sebelumnya cuma solid/gambar), dan preset tema diperluas jadi galeri 10 (rose/ocean/lavender/noir/peach baru, palet warna LEPAS dari brand Jeonme karena halaman ini milik kreator) -- SELESAI (25 Juli 2026): migrasi 000031 (kolom custom_button_style baru, default 'fill'); gradien memakai ulang kolom custom_background_value yang sudah ada (disimpan sebagai string CSS linear-gradient(...) lengkap, backend tetap memperlakukannya sebagai string opaque); font diperluas dari 5 jadi 9 (tambah Poppins/Quicksand/Merriweather/Space Grotesk lewat next/font/google). Dashboard Desain diganti dari daftar pill kecil jadi galeri grid visual, plus panel Kustomisasi Lanjutan diperluas dengan 3 pilihan jenis latar (solid/gradien/gambar, gradien pakai 2 color picker awal-akhir) dan selector Gaya Tombol baru. LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): layout struktural ala Lynk.id (Classic/Modern/Clean, mengubah struktur DOM bukan sekadar warna -- effort jauh lebih besar), stickers/elemen dekoratif ala Linktree (kosmetik, nilai rendah), bentuk avatar (butuh berlaku di SEMUA tema bukan cuma custom, kompleksitas tambahan tanpa banyak nilai), override manual per elemen ala Linktree (Header/Wallpaper/Buttons/Text terpisah -- sudah cukup terwakili mode Custom yang ada). Diverifikasi E2E NYATA: kelima preset baru diterima &amp; tersimpan lewat PATCH /dashboard/page, tercermin benar di GET /pages/:username; validasi menolak tema/gaya tombol/jenis latar yang tidak dikenal (400); tema custom dengan gaya tombol outline &amp; shadow DIBUKTIKAN merender kelas Tailwind yang benar di HTML SSR sungguhan (border+teks berwarna utk outline, shadow berwarna utk shadow) lewat fetch yang genuinely tidak ter-cache; latar gradien DIBUKTIKAN --custom-bg berisi string linear-gradient(...) lengkap di style inline &lt;main&gt;; font baru (Space Grotesk dkk) DIBUKTIKAN font-family mengarah ke CSS variable yang benar; parity penuh diverifikasi juga di halaman tambahan (No.98) lewat PATCH /dashboard/pages/:id. Semua data uji dibersihkan.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna (bukan dari riset kompetitor Linktree/Lynk.id di backlog No.67-99) -- permintaan eksplisit: fitur desain "Halaman Saya" dinilai masih terlalu simpel dibanding kedua platform referensi. Mengerjakan 3 hal yang SENGAJA diskip di No.80 (Sprint 9) karena keterbatasan waktu waktu itu: gaya tombol (fill/outline/shadow, sebelumnya cuma fill), latar gradien (sebelumnya cuma solid/gambar), dan preset tema diperluas jadi galeri 10 (rose/ocean/lavender/noir/peach baru, palet warna LEPAS dari brand Jeonme karena halaman ini milik kreator) -- SELESAI (25 Juli 2026): migrasi 000031 (kolom custom_button_style baru, default 'fill'); gradien memakai ulang kolom custom_background_value yang sudah ada (disimpan sebagai string CSS linear-gradient(...) lengkap, backend tetap memperlakukannya sebagai string opaque); font diperluas dari 5 jadi 9 (tambah Poppins/Quicksand/Merriweather/Space Grotesk lewat next/font/google). Dashboard Desain diganti dari daftar pill kecil jadi galeri grid visual, plus panel Kustomisasi Lanjutan diperluas dengan 3 pilihan jenis latar (solid/gradien/gambar, gradien pakai 2 color picker awal-akhir) dan selector Gaya Tombol baru. LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): layout struktural ala Lynk.id (Classic/Modern/Clean, mengubah struktur DOM bukan sekadar warna -- effort jauh lebih besar), stickers/elemen dekoratif ala Linktree (kosmetik, nilai rendah), bentuk avatar (butuh berlaku di SEMUA tema bukan cuma custom, kompleksitas tambahan tanpa banyak nilai), override manual per elemen ala Linktree (Header/Wallpaper/Buttons/Text terpisah -- sudah cukup terwakili mode Custom yang ada). Diverifikasi E2E NYATA: kelima preset baru diterima &amp; tersimpan lewat PATCH /dashboard/page, tercermin benar di GET /pages/:username; validasi menolak tema/gaya tombol/jenis latar yang tidak dikenal (400); tema custom dengan gaya tombol outline &amp; shadow DIBUKTIKAN merender kelas Tailwind yang benar di HTML SSR sungguhan (border+teks berwarna utk outline, shadow berwarna utk shadow) lewat fetch yang genuinely tidak ter-cache; latar gradien DIBUKTIKAN --custom-bg berisi string linear-gradient(...) lengkap di style inline &lt;main&gt;; font baru (Space Grotesk dkk) DIBUKTIKAN font-family mengarah ke CSS variable yang benar; parity penuh diverifikasi juga di halaman tambahan (No.98) lewat PATCH /dashboard/pages/:id. Semua data uji dibersihkan. TAMBAHAN (25 Juli 2026): user minta panel "Kustomisasi Lanjutan" disamakan strukturnya dengan Linktree -- sebelumnya satu panel gabungan menampilkan Latar+Font+Warna Tombol+Gaya Tombol sekaligus, sekarang diubah jadi 3 accordion terpisah (Latar/Tombol/Font) yang dibuka satu-satu (klik salah satu, yang lain tertutup), persis pola "tiap elemen buka panel sendiri" yang dicatat dari riset Linktree asli. Header/Colors/Stickers/Footer milik Linktree TIDAK dibuatkan bagian kosong karena Jeonme belum punya kustomisasi untuk itu -- hanya 3 elemen yang benar-benar didukung yang dipecah. Tiap baris accordion tertutup menampilkan ringkasan (swatch warna/gradien + label gaya saat ini) supaya kreator tetap lihat status tanpa harus membuka semuanya. Murni perubahan UI (satu file, apps/web/app/dashboard/design/page.tsx), TIDAK ada perubahan data/API sama sekali.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5802,7 +5802,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna (bukan dari riset kompetitor Linktree/Lynk.id di backlog No.67-99) -- permintaan eksplisit: fitur desain "Halaman Saya" dinilai masih terlalu simpel dibanding kedua platform referensi. Mengerjakan 3 hal yang SENGAJA diskip di No.80 (Sprint 9) karena keterbatasan waktu waktu itu: gaya tombol (fill/outline/shadow, sebelumnya cuma fill), latar gradien (sebelumnya cuma solid/gambar), dan preset tema diperluas jadi galeri 10 (rose/ocean/lavender/noir/peach baru, palet warna LEPAS dari brand Jeonme karena halaman ini milik kreator) -- SELESAI (25 Juli 2026): migrasi 000031 (kolom custom_button_style baru, default 'fill'); gradien memakai ulang kolom custom_background_value yang sudah ada (disimpan sebagai string CSS linear-gradient(...) lengkap, backend tetap memperlakukannya sebagai string opaque); font diperluas dari 5 jadi 9 (tambah Poppins/Quicksand/Merriweather/Space Grotesk lewat next/font/google). Dashboard Desain diganti dari daftar pill kecil jadi galeri grid visual, plus panel Kustomisasi Lanjutan diperluas dengan 3 pilihan jenis latar (solid/gradien/gambar, gradien pakai 2 color picker awal-akhir) dan selector Gaya Tombol baru. LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): layout struktural ala Lynk.id (Classic/Modern/Clean, mengubah struktur DOM bukan sekadar warna -- effort jauh lebih besar), stickers/elemen dekoratif ala Linktree (kosmetik, nilai rendah), bentuk avatar (butuh berlaku di SEMUA tema bukan cuma custom, kompleksitas tambahan tanpa banyak nilai), override manual per elemen ala Linktree (Header/Wallpaper/Buttons/Text terpisah -- sudah cukup terwakili mode Custom yang ada). Diverifikasi E2E NYATA: kelima preset baru diterima &amp; tersimpan lewat PATCH /dashboard/page, tercermin benar di GET /pages/:username; validasi menolak tema/gaya tombol/jenis latar yang tidak dikenal (400); tema custom dengan gaya tombol outline &amp; shadow DIBUKTIKAN merender kelas Tailwind yang benar di HTML SSR sungguhan (border+teks berwarna utk outline, shadow berwarna utk shadow) lewat fetch yang genuinely tidak ter-cache; latar gradien DIBUKTIKAN --custom-bg berisi string linear-gradient(...) lengkap di style inline &lt;main&gt;; font baru (Space Grotesk dkk) DIBUKTIKAN font-family mengarah ke CSS variable yang benar; parity penuh diverifikasi juga di halaman tambahan (No.98) lewat PATCH /dashboard/pages/:id. Semua data uji dibersihkan. TAMBAHAN (25 Juli 2026): user minta panel "Kustomisasi Lanjutan" disamakan strukturnya dengan Linktree -- sebelumnya satu panel gabungan menampilkan Latar+Font+Warna Tombol+Gaya Tombol sekaligus, sekarang diubah jadi 3 accordion terpisah (Latar/Tombol/Font) yang dibuka satu-satu (klik salah satu, yang lain tertutup), persis pola "tiap elemen buka panel sendiri" yang dicatat dari riset Linktree asli. Header/Colors/Stickers/Footer milik Linktree TIDAK dibuatkan bagian kosong karena Jeonme belum punya kustomisasi untuk itu -- hanya 3 elemen yang benar-benar didukung yang dipecah. Tiap baris accordion tertutup menampilkan ringkasan (swatch warna/gradien + label gaya saat ini) supaya kreator tetap lihat status tanpa harus membuka semuanya. Murni perubahan UI (satu file, apps/web/app/dashboard/design/page.tsx), TIDAK ada perubahan data/API sama sekali.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna (bukan dari riset kompetitor Linktree/Lynk.id di backlog No.67-99) -- permintaan eksplisit: fitur desain "Halaman Saya" dinilai masih terlalu simpel dibanding kedua platform referensi. Mengerjakan 3 hal yang SENGAJA diskip di No.80 (Sprint 9) karena keterbatasan waktu waktu itu: gaya tombol (fill/outline/shadow, sebelumnya cuma fill), latar gradien (sebelumnya cuma solid/gambar), dan preset tema diperluas jadi galeri 10 (rose/ocean/lavender/noir/peach baru, palet warna LEPAS dari brand Jeonme karena halaman ini milik kreator) -- SELESAI (25 Juli 2026): migrasi 000031 (kolom custom_button_style baru, default 'fill'); gradien memakai ulang kolom custom_background_value yang sudah ada (disimpan sebagai string CSS linear-gradient(...) lengkap, backend tetap memperlakukannya sebagai string opaque); font diperluas dari 5 jadi 9 (tambah Poppins/Quicksand/Merriweather/Space Grotesk lewat next/font/google). Dashboard Desain diganti dari daftar pill kecil jadi galeri grid visual, plus panel Kustomisasi Lanjutan diperluas dengan 3 pilihan jenis latar (solid/gradien/gambar, gradien pakai 2 color picker awal-akhir) dan selector Gaya Tombol baru. LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): layout struktural ala Lynk.id (Classic/Modern/Clean, mengubah struktur DOM bukan sekadar warna -- effort jauh lebih besar), stickers/elemen dekoratif ala Linktree (kosmetik, nilai rendah), bentuk avatar (butuh berlaku di SEMUA tema bukan cuma custom, kompleksitas tambahan tanpa banyak nilai), override manual per elemen ala Linktree (Header/Wallpaper/Buttons/Text terpisah -- sudah cukup terwakili mode Custom yang ada). Diverifikasi E2E NYATA: kelima preset baru diterima &amp; tersimpan lewat PATCH /dashboard/page, tercermin benar di GET /pages/:username; validasi menolak tema/gaya tombol/jenis latar yang tidak dikenal (400); tema custom dengan gaya tombol outline &amp; shadow DIBUKTIKAN merender kelas Tailwind yang benar di HTML SSR sungguhan (border+teks berwarna utk outline, shadow berwarna utk shadow) lewat fetch yang genuinely tidak ter-cache; latar gradien DIBUKTIKAN --custom-bg berisi string linear-gradient(...) lengkap di style inline &lt;main&gt;; font baru (Space Grotesk dkk) DIBUKTIKAN font-family mengarah ke CSS variable yang benar; parity penuh diverifikasi juga di halaman tambahan (No.98) lewat PATCH /dashboard/pages/:id. Semua data uji dibersihkan. TAMBAHAN (25 Juli 2026): user minta panel "Kustomisasi Lanjutan" disamakan strukturnya dengan Linktree -- sebelumnya satu panel gabungan menampilkan Latar+Font+Warna Tombol+Gaya Tombol sekaligus, sekarang diubah jadi 3 accordion terpisah (Latar/Tombol/Font) yang dibuka satu-satu (klik salah satu, yang lain tertutup), persis pola "tiap elemen buka panel sendiri" yang dicatat dari riset Linktree asli. Header/Colors/Stickers/Footer milik Linktree TIDAK dibuatkan bagian kosong karena Jeonme belum punya kustomisasi untuk itu -- hanya 3 elemen yang benar-benar didukung yang dipecah. Tiap baris accordion tertutup menampilkan ringkasan (swatch warna/gradien + label gaya saat ini) supaya kreator tetap lihat status tanpa harus membuka semuanya. Murni perubahan UI (satu file, apps/web/app/dashboard/design/page.tsx), TIDAK ada perubahan data/API sama sekali. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman Design Linktree sungguhan dan minta diikuti PERSIS -- struktur halaman diubah total meniru referensi: baris "Tema" berdiri sendiri di atas (bukan galeri grid selalu terbuka), label "Sesuaikan" di bawahnya, lalu baris accordion Header (foto profil+bio, sebelumnya field lepas di atas)/Latar/Tombol/Font -- SEMUA baris kini SELALU tampil (sebelumnya Latar/Tombol/Font hanya muncul kalau tema "Custom" dipilih eksplisit dari galeri). Perubahan perilaku kunci: menyentuh kontrol apa pun di baris Latar/Tombol/Font OTOMATIS mempromosikan tema aktif jadi "custom" di belakang layar (fungsi baru handleCustomize), meniru "override di atas tema manapun" ala Linktree -- TANPA kolom database baru sama sekali (kolom custom_* sudah ada, cuma kini di-set bersamaan dengan theme dalam satu PATCH). Komponen AccordionRow baru dibuat untuk konsistensi visual kelima baris. Colors/Stickers/Footer milik Linktree SENGAJA tetap tidak dibuatkan baris (tidak ada fungsi nyata di baliknya di Jeonme, membuat baris kosong sekadar meniru bentuk bukan tujuan permintaan). Diverifikasi E2E nyata: PATCH kombinasi theme=custom+custom_button_color dalam satu request (mensimulasikan interaksi baris Tombol saat tema preset aktif) terbukti benar mempromosikan tema jadi custom sekaligus menyimpan warna; halaman publik dicek tetap merender custom_button_bg yang benar tanpa regresi.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5845,7 +5845,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5802,7 +5802,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna (bukan dari riset kompetitor Linktree/Lynk.id di backlog No.67-99) -- permintaan eksplisit: fitur desain "Halaman Saya" dinilai masih terlalu simpel dibanding kedua platform referensi. Mengerjakan 3 hal yang SENGAJA diskip di No.80 (Sprint 9) karena keterbatasan waktu waktu itu: gaya tombol (fill/outline/shadow, sebelumnya cuma fill), latar gradien (sebelumnya cuma solid/gambar), dan preset tema diperluas jadi galeri 10 (rose/ocean/lavender/noir/peach baru, palet warna LEPAS dari brand Jeonme karena halaman ini milik kreator) -- SELESAI (25 Juli 2026): migrasi 000031 (kolom custom_button_style baru, default 'fill'); gradien memakai ulang kolom custom_background_value yang sudah ada (disimpan sebagai string CSS linear-gradient(...) lengkap, backend tetap memperlakukannya sebagai string opaque); font diperluas dari 5 jadi 9 (tambah Poppins/Quicksand/Merriweather/Space Grotesk lewat next/font/google). Dashboard Desain diganti dari daftar pill kecil jadi galeri grid visual, plus panel Kustomisasi Lanjutan diperluas dengan 3 pilihan jenis latar (solid/gradien/gambar, gradien pakai 2 color picker awal-akhir) dan selector Gaya Tombol baru. LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): layout struktural ala Lynk.id (Classic/Modern/Clean, mengubah struktur DOM bukan sekadar warna -- effort jauh lebih besar), stickers/elemen dekoratif ala Linktree (kosmetik, nilai rendah), bentuk avatar (butuh berlaku di SEMUA tema bukan cuma custom, kompleksitas tambahan tanpa banyak nilai), override manual per elemen ala Linktree (Header/Wallpaper/Buttons/Text terpisah -- sudah cukup terwakili mode Custom yang ada). Diverifikasi E2E NYATA: kelima preset baru diterima &amp; tersimpan lewat PATCH /dashboard/page, tercermin benar di GET /pages/:username; validasi menolak tema/gaya tombol/jenis latar yang tidak dikenal (400); tema custom dengan gaya tombol outline &amp; shadow DIBUKTIKAN merender kelas Tailwind yang benar di HTML SSR sungguhan (border+teks berwarna utk outline, shadow berwarna utk shadow) lewat fetch yang genuinely tidak ter-cache; latar gradien DIBUKTIKAN --custom-bg berisi string linear-gradient(...) lengkap di style inline &lt;main&gt;; font baru (Space Grotesk dkk) DIBUKTIKAN font-family mengarah ke CSS variable yang benar; parity penuh diverifikasi juga di halaman tambahan (No.98) lewat PATCH /dashboard/pages/:id. Semua data uji dibersihkan. TAMBAHAN (25 Juli 2026): user minta panel "Kustomisasi Lanjutan" disamakan strukturnya dengan Linktree -- sebelumnya satu panel gabungan menampilkan Latar+Font+Warna Tombol+Gaya Tombol sekaligus, sekarang diubah jadi 3 accordion terpisah (Latar/Tombol/Font) yang dibuka satu-satu (klik salah satu, yang lain tertutup), persis pola "tiap elemen buka panel sendiri" yang dicatat dari riset Linktree asli. Header/Colors/Stickers/Footer milik Linktree TIDAK dibuatkan bagian kosong karena Jeonme belum punya kustomisasi untuk itu -- hanya 3 elemen yang benar-benar didukung yang dipecah. Tiap baris accordion tertutup menampilkan ringkasan (swatch warna/gradien + label gaya saat ini) supaya kreator tetap lihat status tanpa harus membuka semuanya. Murni perubahan UI (satu file, apps/web/app/dashboard/design/page.tsx), TIDAK ada perubahan data/API sama sekali. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman Design Linktree sungguhan dan minta diikuti PERSIS -- struktur halaman diubah total meniru referensi: baris "Tema" berdiri sendiri di atas (bukan galeri grid selalu terbuka), label "Sesuaikan" di bawahnya, lalu baris accordion Header (foto profil+bio, sebelumnya field lepas di atas)/Latar/Tombol/Font -- SEMUA baris kini SELALU tampil (sebelumnya Latar/Tombol/Font hanya muncul kalau tema "Custom" dipilih eksplisit dari galeri). Perubahan perilaku kunci: menyentuh kontrol apa pun di baris Latar/Tombol/Font OTOMATIS mempromosikan tema aktif jadi "custom" di belakang layar (fungsi baru handleCustomize), meniru "override di atas tema manapun" ala Linktree -- TANPA kolom database baru sama sekali (kolom custom_* sudah ada, cuma kini di-set bersamaan dengan theme dalam satu PATCH). Komponen AccordionRow baru dibuat untuk konsistensi visual kelima baris. Colors/Stickers/Footer milik Linktree SENGAJA tetap tidak dibuatkan baris (tidak ada fungsi nyata di baliknya di Jeonme, membuat baris kosong sekadar meniru bentuk bukan tujuan permintaan). Diverifikasi E2E nyata: PATCH kombinasi theme=custom+custom_button_color dalam satu request (mensimulasikan interaksi baris Tombol saat tema preset aktif) terbukti benar mempromosikan tema jadi custom sekaligus menyimpan warna; halaman publik dicek tetap merender custom_button_bg yang benar tanpa regresi.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna (bukan dari riset kompetitor Linktree/Lynk.id di backlog No.67-99) -- permintaan eksplisit: fitur desain "Halaman Saya" dinilai masih terlalu simpel dibanding kedua platform referensi. Mengerjakan 3 hal yang SENGAJA diskip di No.80 (Sprint 9) karena keterbatasan waktu waktu itu: gaya tombol (fill/outline/shadow, sebelumnya cuma fill), latar gradien (sebelumnya cuma solid/gambar), dan preset tema diperluas jadi galeri 10 (rose/ocean/lavender/noir/peach baru, palet warna LEPAS dari brand Jeonme karena halaman ini milik kreator) -- SELESAI (25 Juli 2026): migrasi 000031 (kolom custom_button_style baru, default 'fill'); gradien memakai ulang kolom custom_background_value yang sudah ada (disimpan sebagai string CSS linear-gradient(...) lengkap, backend tetap memperlakukannya sebagai string opaque); font diperluas dari 5 jadi 9 (tambah Poppins/Quicksand/Merriweather/Space Grotesk lewat next/font/google). Dashboard Desain diganti dari daftar pill kecil jadi galeri grid visual, plus panel Kustomisasi Lanjutan diperluas dengan 3 pilihan jenis latar (solid/gradien/gambar, gradien pakai 2 color picker awal-akhir) dan selector Gaya Tombol baru. LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): layout struktural ala Lynk.id (Classic/Modern/Clean, mengubah struktur DOM bukan sekadar warna -- effort jauh lebih besar), stickers/elemen dekoratif ala Linktree (kosmetik, nilai rendah), bentuk avatar (butuh berlaku di SEMUA tema bukan cuma custom, kompleksitas tambahan tanpa banyak nilai), override manual per elemen ala Linktree (Header/Wallpaper/Buttons/Text terpisah -- sudah cukup terwakili mode Custom yang ada). Diverifikasi E2E NYATA: kelima preset baru diterima &amp; tersimpan lewat PATCH /dashboard/page, tercermin benar di GET /pages/:username; validasi menolak tema/gaya tombol/jenis latar yang tidak dikenal (400); tema custom dengan gaya tombol outline &amp; shadow DIBUKTIKAN merender kelas Tailwind yang benar di HTML SSR sungguhan (border+teks berwarna utk outline, shadow berwarna utk shadow) lewat fetch yang genuinely tidak ter-cache; latar gradien DIBUKTIKAN --custom-bg berisi string linear-gradient(...) lengkap di style inline &lt;main&gt;; font baru (Space Grotesk dkk) DIBUKTIKAN font-family mengarah ke CSS variable yang benar; parity penuh diverifikasi juga di halaman tambahan (No.98) lewat PATCH /dashboard/pages/:id. Semua data uji dibersihkan. TAMBAHAN (25 Juli 2026): user minta panel "Kustomisasi Lanjutan" disamakan strukturnya dengan Linktree -- sebelumnya satu panel gabungan menampilkan Latar+Font+Warna Tombol+Gaya Tombol sekaligus, sekarang diubah jadi 3 accordion terpisah (Latar/Tombol/Font) yang dibuka satu-satu (klik salah satu, yang lain tertutup), persis pola "tiap elemen buka panel sendiri" yang dicatat dari riset Linktree asli. Header/Colors/Stickers/Footer milik Linktree TIDAK dibuatkan bagian kosong karena Jeonme belum punya kustomisasi untuk itu -- hanya 3 elemen yang benar-benar didukung yang dipecah. Tiap baris accordion tertutup menampilkan ringkasan (swatch warna/gradien + label gaya saat ini) supaya kreator tetap lihat status tanpa harus membuka semuanya. Murni perubahan UI (satu file, apps/web/app/dashboard/design/page.tsx), TIDAK ada perubahan data/API sama sekali. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman Design Linktree sungguhan dan minta diikuti PERSIS -- struktur halaman diubah total meniru referensi: baris "Tema" berdiri sendiri di atas (bukan galeri grid selalu terbuka), label "Sesuaikan" di bawahnya, lalu baris accordion Header (foto profil+bio, sebelumnya field lepas di atas)/Latar/Tombol/Font -- SEMUA baris kini SELALU tampil (sebelumnya Latar/Tombol/Font hanya muncul kalau tema "Custom" dipilih eksplisit dari galeri). Perubahan perilaku kunci: menyentuh kontrol apa pun di baris Latar/Tombol/Font OTOMATIS mempromosikan tema aktif jadi "custom" di belakang layar (fungsi baru handleCustomize), meniru "override di atas tema manapun" ala Linktree -- TANPA kolom database baru sama sekali (kolom custom_* sudah ada, cuma kini di-set bersamaan dengan theme dalam satu PATCH). Komponen AccordionRow baru dibuat untuk konsistensi visual kelima baris. Colors/Stickers/Footer milik Linktree SENGAJA tetap tidak dibuatkan baris (tidak ada fungsi nyata di baliknya di Jeonme, membuat baris kosong sekadar meniru bentuk bukan tujuan permintaan). Diverifikasi E2E nyata: PATCH kombinasi theme=custom+custom_button_color dalam satu request (mensimulasikan interaksi baris Tombol saat tema preset aktif) terbukti benar mempromosikan tema jadi custom sekaligus menyimpan warna; halaman publik dicek tetap merender custom_button_bg yang benar tanpa regresi. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar galeri tema "Customizable" Linktree sungguhan dan minta galeri tema Jeonme diikuti gayanya PERSIS, plus minta ditambah lagi tema bernuansa gradien. Redesain kartu galeri di baris accordion "Tema" (dashboard/design): dari swatch kotak kecil (bar warna h-10 + label) jadi KARTU PORTRAIT ala Linktree -- rasio 3:4, latar mengisi penuh kartu (warna solid/gradien lengkap lewat field baru previewBg), sampel huruf besar "Aa" mengambang di kiri atas (warna teks menyesuaikan kontras via field baru previewIsDark), pil bulat warna tombol tema di bagian bawah kartu, lencana centang lingkaran di kanan atas saat tema itu aktif (bukan cuma border tebal seperti sebelumnya). Kartu "Custom" tetap di posisi pertama dengan ikon kuas (IconPaintbrush baru) di atas latar abu polos, sama seperti referensi. SEKALIGUS menambah 6 preset tema BARU bernuansa gradien vivid multi-warna (diminta eksplisit "tambahkan lagi beberapa tema seperti gradient dan sejenisnya"): Bloom (fuchsia-purple-indigo), Blaze (orange-pink-purple/sunset), Cyber (dark navy-indigo-violet + aksen neon cyan), Mint (emerald-teal-cyan), Golden (amber-orange-rose pastel hangat, satu-satunya dari 6 preset baru yang pakai teks gelap bukan putih), Cosmic (dark indigo-violet ala luar angkasa) -- total preset jadi 16 (dari 10 sebelumnya) + Custom. Field previewBg/previewIsDark ditambahkan ke SEMUA 10 preset lama juga supaya galeri konsisten satu gaya kartu. TIDAK BUTUH MIGRASI DATABASE (kolom pages.theme sudah VARCHAR(50) bebas tanpa CHECK constraint sejak awal) -- cuma perlu menambah 6 nama tema baru ke peta validasi backend (availableThemes di page.go) &amp; daftar THEME_PRESETS frontend. Diverifikasi E2E NYATA lewat API sungguhan: kreator uji dibuat, PATCH ke-6 nama tema baru (bloom/blaze/cyber/mint/golden/cosmic) semua diterima (200), nama tema tidak valid ditolak (400) membuktikan validasi backend benar diperbarui; halaman publik kreator uji di-curl langsung (bukan cuma review kode) untuk tema "cyber" dan "golden", HTML SSR terbukti berisi kelas gradien Tailwind yang BENAR &amp; BERBEDA untuk masing-masing tema (termasuk kasus tersulit: cache fetch Next.js 60 detik yang membuat percobaan pertama tampak "gagal" karena data lama, terbukti BUKAN bug lewat percobaan ulang setelah cache benar-benar kedaluwarsa). go build/vet/test &amp; tsc/eslint/build seluruhnya bersih. Data uji dibersihkan sesudahnya. CATATAN JUJUR: tampilan visual KARTU galeri di dashboard/design (halaman client-rendered di balik auth) tidak diverifikasi lewat tangkapan layar browser sungguhan karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran struktur/tipe dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap definisi previewBg/previewIsDark per tema, bukan verifikasi visual langsung.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5845,7 +5845,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5802,7 +5802,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna (bukan dari riset kompetitor Linktree/Lynk.id di backlog No.67-99) -- permintaan eksplisit: fitur desain "Halaman Saya" dinilai masih terlalu simpel dibanding kedua platform referensi. Mengerjakan 3 hal yang SENGAJA diskip di No.80 (Sprint 9) karena keterbatasan waktu waktu itu: gaya tombol (fill/outline/shadow, sebelumnya cuma fill), latar gradien (sebelumnya cuma solid/gambar), dan preset tema diperluas jadi galeri 10 (rose/ocean/lavender/noir/peach baru, palet warna LEPAS dari brand Jeonme karena halaman ini milik kreator) -- SELESAI (25 Juli 2026): migrasi 000031 (kolom custom_button_style baru, default 'fill'); gradien memakai ulang kolom custom_background_value yang sudah ada (disimpan sebagai string CSS linear-gradient(...) lengkap, backend tetap memperlakukannya sebagai string opaque); font diperluas dari 5 jadi 9 (tambah Poppins/Quicksand/Merriweather/Space Grotesk lewat next/font/google). Dashboard Desain diganti dari daftar pill kecil jadi galeri grid visual, plus panel Kustomisasi Lanjutan diperluas dengan 3 pilihan jenis latar (solid/gradien/gambar, gradien pakai 2 color picker awal-akhir) dan selector Gaya Tombol baru. LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): layout struktural ala Lynk.id (Classic/Modern/Clean, mengubah struktur DOM bukan sekadar warna -- effort jauh lebih besar), stickers/elemen dekoratif ala Linktree (kosmetik, nilai rendah), bentuk avatar (butuh berlaku di SEMUA tema bukan cuma custom, kompleksitas tambahan tanpa banyak nilai), override manual per elemen ala Linktree (Header/Wallpaper/Buttons/Text terpisah -- sudah cukup terwakili mode Custom yang ada). Diverifikasi E2E NYATA: kelima preset baru diterima &amp; tersimpan lewat PATCH /dashboard/page, tercermin benar di GET /pages/:username; validasi menolak tema/gaya tombol/jenis latar yang tidak dikenal (400); tema custom dengan gaya tombol outline &amp; shadow DIBUKTIKAN merender kelas Tailwind yang benar di HTML SSR sungguhan (border+teks berwarna utk outline, shadow berwarna utk shadow) lewat fetch yang genuinely tidak ter-cache; latar gradien DIBUKTIKAN --custom-bg berisi string linear-gradient(...) lengkap di style inline &lt;main&gt;; font baru (Space Grotesk dkk) DIBUKTIKAN font-family mengarah ke CSS variable yang benar; parity penuh diverifikasi juga di halaman tambahan (No.98) lewat PATCH /dashboard/pages/:id. Semua data uji dibersihkan. TAMBAHAN (25 Juli 2026): user minta panel "Kustomisasi Lanjutan" disamakan strukturnya dengan Linktree -- sebelumnya satu panel gabungan menampilkan Latar+Font+Warna Tombol+Gaya Tombol sekaligus, sekarang diubah jadi 3 accordion terpisah (Latar/Tombol/Font) yang dibuka satu-satu (klik salah satu, yang lain tertutup), persis pola "tiap elemen buka panel sendiri" yang dicatat dari riset Linktree asli. Header/Colors/Stickers/Footer milik Linktree TIDAK dibuatkan bagian kosong karena Jeonme belum punya kustomisasi untuk itu -- hanya 3 elemen yang benar-benar didukung yang dipecah. Tiap baris accordion tertutup menampilkan ringkasan (swatch warna/gradien + label gaya saat ini) supaya kreator tetap lihat status tanpa harus membuka semuanya. Murni perubahan UI (satu file, apps/web/app/dashboard/design/page.tsx), TIDAK ada perubahan data/API sama sekali. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman Design Linktree sungguhan dan minta diikuti PERSIS -- struktur halaman diubah total meniru referensi: baris "Tema" berdiri sendiri di atas (bukan galeri grid selalu terbuka), label "Sesuaikan" di bawahnya, lalu baris accordion Header (foto profil+bio, sebelumnya field lepas di atas)/Latar/Tombol/Font -- SEMUA baris kini SELALU tampil (sebelumnya Latar/Tombol/Font hanya muncul kalau tema "Custom" dipilih eksplisit dari galeri). Perubahan perilaku kunci: menyentuh kontrol apa pun di baris Latar/Tombol/Font OTOMATIS mempromosikan tema aktif jadi "custom" di belakang layar (fungsi baru handleCustomize), meniru "override di atas tema manapun" ala Linktree -- TANPA kolom database baru sama sekali (kolom custom_* sudah ada, cuma kini di-set bersamaan dengan theme dalam satu PATCH). Komponen AccordionRow baru dibuat untuk konsistensi visual kelima baris. Colors/Stickers/Footer milik Linktree SENGAJA tetap tidak dibuatkan baris (tidak ada fungsi nyata di baliknya di Jeonme, membuat baris kosong sekadar meniru bentuk bukan tujuan permintaan). Diverifikasi E2E nyata: PATCH kombinasi theme=custom+custom_button_color dalam satu request (mensimulasikan interaksi baris Tombol saat tema preset aktif) terbukti benar mempromosikan tema jadi custom sekaligus menyimpan warna; halaman publik dicek tetap merender custom_button_bg yang benar tanpa regresi. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar galeri tema "Customizable" Linktree sungguhan dan minta galeri tema Jeonme diikuti gayanya PERSIS, plus minta ditambah lagi tema bernuansa gradien. Redesain kartu galeri di baris accordion "Tema" (dashboard/design): dari swatch kotak kecil (bar warna h-10 + label) jadi KARTU PORTRAIT ala Linktree -- rasio 3:4, latar mengisi penuh kartu (warna solid/gradien lengkap lewat field baru previewBg), sampel huruf besar "Aa" mengambang di kiri atas (warna teks menyesuaikan kontras via field baru previewIsDark), pil bulat warna tombol tema di bagian bawah kartu, lencana centang lingkaran di kanan atas saat tema itu aktif (bukan cuma border tebal seperti sebelumnya). Kartu "Custom" tetap di posisi pertama dengan ikon kuas (IconPaintbrush baru) di atas latar abu polos, sama seperti referensi. SEKALIGUS menambah 6 preset tema BARU bernuansa gradien vivid multi-warna (diminta eksplisit "tambahkan lagi beberapa tema seperti gradient dan sejenisnya"): Bloom (fuchsia-purple-indigo), Blaze (orange-pink-purple/sunset), Cyber (dark navy-indigo-violet + aksen neon cyan), Mint (emerald-teal-cyan), Golden (amber-orange-rose pastel hangat, satu-satunya dari 6 preset baru yang pakai teks gelap bukan putih), Cosmic (dark indigo-violet ala luar angkasa) -- total preset jadi 16 (dari 10 sebelumnya) + Custom. Field previewBg/previewIsDark ditambahkan ke SEMUA 10 preset lama juga supaya galeri konsisten satu gaya kartu. TIDAK BUTUH MIGRASI DATABASE (kolom pages.theme sudah VARCHAR(50) bebas tanpa CHECK constraint sejak awal) -- cuma perlu menambah 6 nama tema baru ke peta validasi backend (availableThemes di page.go) &amp; daftar THEME_PRESETS frontend. Diverifikasi E2E NYATA lewat API sungguhan: kreator uji dibuat, PATCH ke-6 nama tema baru (bloom/blaze/cyber/mint/golden/cosmic) semua diterima (200), nama tema tidak valid ditolak (400) membuktikan validasi backend benar diperbarui; halaman publik kreator uji di-curl langsung (bukan cuma review kode) untuk tema "cyber" dan "golden", HTML SSR terbukti berisi kelas gradien Tailwind yang BENAR &amp; BERBEDA untuk masing-masing tema (termasuk kasus tersulit: cache fetch Next.js 60 detik yang membuat percobaan pertama tampak "gagal" karena data lama, terbukti BUKAN bug lewat percobaan ulang setelah cache benar-benar kedaluwarsa). go build/vet/test &amp; tsc/eslint/build seluruhnya bersih. Data uji dibersihkan sesudahnya. CATATAN JUJUR: tampilan visual KARTU galeri di dashboard/design (halaman client-rendered di balik auth) tidak diverifikasi lewat tangkapan layar browser sungguhan karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran struktur/tipe dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap definisi previewBg/previewIsDark per tema, bukan verifikasi visual langsung.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna (bukan dari riset kompetitor Linktree/Lynk.id di backlog No.67-99) -- permintaan eksplisit: fitur desain "Halaman Saya" dinilai masih terlalu simpel dibanding kedua platform referensi. Mengerjakan 3 hal yang SENGAJA diskip di No.80 (Sprint 9) karena keterbatasan waktu waktu itu: gaya tombol (fill/outline/shadow, sebelumnya cuma fill), latar gradien (sebelumnya cuma solid/gambar), dan preset tema diperluas jadi galeri 10 (rose/ocean/lavender/noir/peach baru, palet warna LEPAS dari brand Jeonme karena halaman ini milik kreator) -- SELESAI (25 Juli 2026): migrasi 000031 (kolom custom_button_style baru, default 'fill'); gradien memakai ulang kolom custom_background_value yang sudah ada (disimpan sebagai string CSS linear-gradient(...) lengkap, backend tetap memperlakukannya sebagai string opaque); font diperluas dari 5 jadi 9 (tambah Poppins/Quicksand/Merriweather/Space Grotesk lewat next/font/google). Dashboard Desain diganti dari daftar pill kecil jadi galeri grid visual, plus panel Kustomisasi Lanjutan diperluas dengan 3 pilihan jenis latar (solid/gradien/gambar, gradien pakai 2 color picker awal-akhir) dan selector Gaya Tombol baru. LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): layout struktural ala Lynk.id (Classic/Modern/Clean, mengubah struktur DOM bukan sekadar warna -- effort jauh lebih besar), stickers/elemen dekoratif ala Linktree (kosmetik, nilai rendah), bentuk avatar (butuh berlaku di SEMUA tema bukan cuma custom, kompleksitas tambahan tanpa banyak nilai), override manual per elemen ala Linktree (Header/Wallpaper/Buttons/Text terpisah -- sudah cukup terwakili mode Custom yang ada). Diverifikasi E2E NYATA: kelima preset baru diterima &amp; tersimpan lewat PATCH /dashboard/page, tercermin benar di GET /pages/:username; validasi menolak tema/gaya tombol/jenis latar yang tidak dikenal (400); tema custom dengan gaya tombol outline &amp; shadow DIBUKTIKAN merender kelas Tailwind yang benar di HTML SSR sungguhan (border+teks berwarna utk outline, shadow berwarna utk shadow) lewat fetch yang genuinely tidak ter-cache; latar gradien DIBUKTIKAN --custom-bg berisi string linear-gradient(...) lengkap di style inline &lt;main&gt;; font baru (Space Grotesk dkk) DIBUKTIKAN font-family mengarah ke CSS variable yang benar; parity penuh diverifikasi juga di halaman tambahan (No.98) lewat PATCH /dashboard/pages/:id. Semua data uji dibersihkan. TAMBAHAN (25 Juli 2026): user minta panel "Kustomisasi Lanjutan" disamakan strukturnya dengan Linktree -- sebelumnya satu panel gabungan menampilkan Latar+Font+Warna Tombol+Gaya Tombol sekaligus, sekarang diubah jadi 3 accordion terpisah (Latar/Tombol/Font) yang dibuka satu-satu (klik salah satu, yang lain tertutup), persis pola "tiap elemen buka panel sendiri" yang dicatat dari riset Linktree asli. Header/Colors/Stickers/Footer milik Linktree TIDAK dibuatkan bagian kosong karena Jeonme belum punya kustomisasi untuk itu -- hanya 3 elemen yang benar-benar didukung yang dipecah. Tiap baris accordion tertutup menampilkan ringkasan (swatch warna/gradien + label gaya saat ini) supaya kreator tetap lihat status tanpa harus membuka semuanya. Murni perubahan UI (satu file, apps/web/app/dashboard/design/page.tsx), TIDAK ada perubahan data/API sama sekali. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman Design Linktree sungguhan dan minta diikuti PERSIS -- struktur halaman diubah total meniru referensi: baris "Tema" berdiri sendiri di atas (bukan galeri grid selalu terbuka), label "Sesuaikan" di bawahnya, lalu baris accordion Header (foto profil+bio, sebelumnya field lepas di atas)/Latar/Tombol/Font -- SEMUA baris kini SELALU tampil (sebelumnya Latar/Tombol/Font hanya muncul kalau tema "Custom" dipilih eksplisit dari galeri). Perubahan perilaku kunci: menyentuh kontrol apa pun di baris Latar/Tombol/Font OTOMATIS mempromosikan tema aktif jadi "custom" di belakang layar (fungsi baru handleCustomize), meniru "override di atas tema manapun" ala Linktree -- TANPA kolom database baru sama sekali (kolom custom_* sudah ada, cuma kini di-set bersamaan dengan theme dalam satu PATCH). Komponen AccordionRow baru dibuat untuk konsistensi visual kelima baris. Colors/Stickers/Footer milik Linktree SENGAJA tetap tidak dibuatkan baris (tidak ada fungsi nyata di baliknya di Jeonme, membuat baris kosong sekadar meniru bentuk bukan tujuan permintaan). Diverifikasi E2E nyata: PATCH kombinasi theme=custom+custom_button_color dalam satu request (mensimulasikan interaksi baris Tombol saat tema preset aktif) terbukti benar mempromosikan tema jadi custom sekaligus menyimpan warna; halaman publik dicek tetap merender custom_button_bg yang benar tanpa regresi. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar galeri tema "Customizable" Linktree sungguhan dan minta galeri tema Jeonme diikuti gayanya PERSIS, plus minta ditambah lagi tema bernuansa gradien. Redesain kartu galeri di baris accordion "Tema" (dashboard/design): dari swatch kotak kecil (bar warna h-10 + label) jadi KARTU PORTRAIT ala Linktree -- rasio 3:4, latar mengisi penuh kartu (warna solid/gradien lengkap lewat field baru previewBg), sampel huruf besar "Aa" mengambang di kiri atas (warna teks menyesuaikan kontras via field baru previewIsDark), pil bulat warna tombol tema di bagian bawah kartu, lencana centang lingkaran di kanan atas saat tema itu aktif (bukan cuma border tebal seperti sebelumnya). Kartu "Custom" tetap di posisi pertama dengan ikon kuas (IconPaintbrush baru) di atas latar abu polos, sama seperti referensi. SEKALIGUS menambah 6 preset tema BARU bernuansa gradien vivid multi-warna (diminta eksplisit "tambahkan lagi beberapa tema seperti gradient dan sejenisnya"): Bloom (fuchsia-purple-indigo), Blaze (orange-pink-purple/sunset), Cyber (dark navy-indigo-violet + aksen neon cyan), Mint (emerald-teal-cyan), Golden (amber-orange-rose pastel hangat, satu-satunya dari 6 preset baru yang pakai teks gelap bukan putih), Cosmic (dark indigo-violet ala luar angkasa) -- total preset jadi 16 (dari 10 sebelumnya) + Custom. Field previewBg/previewIsDark ditambahkan ke SEMUA 10 preset lama juga supaya galeri konsisten satu gaya kartu. TIDAK BUTUH MIGRASI DATABASE (kolom pages.theme sudah VARCHAR(50) bebas tanpa CHECK constraint sejak awal) -- cuma perlu menambah 6 nama tema baru ke peta validasi backend (availableThemes di page.go) &amp; daftar THEME_PRESETS frontend. Diverifikasi E2E NYATA lewat API sungguhan: kreator uji dibuat, PATCH ke-6 nama tema baru (bloom/blaze/cyber/mint/golden/cosmic) semua diterima (200), nama tema tidak valid ditolak (400) membuktikan validasi backend benar diperbarui; halaman publik kreator uji di-curl langsung (bukan cuma review kode) untuk tema "cyber" dan "golden", HTML SSR terbukti berisi kelas gradien Tailwind yang BENAR &amp; BERBEDA untuk masing-masing tema (termasuk kasus tersulit: cache fetch Next.js 60 detik yang membuat percobaan pertama tampak "gagal" karena data lama, terbukti BUKAN bug lewat percobaan ulang setelah cache benar-benar kedaluwarsa). go build/vet/test &amp; tsc/eslint/build seluruhnya bersih. Data uji dibersihkan sesudahnya. CATATAN JUJUR: tampilan visual KARTU galeri di dashboard/design (halaman client-rendered di balik auth) tidak diverifikasi lewat tangkapan layar browser sungguhan karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran struktur/tipe dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap definisi previewBg/previewIsDark per tema, bukan verifikasi visual langsung. PERBAIKAN BUG (26 Juli 2026): user melaporkan warna putih kadang terlihat di bagian atas &amp; bawah kolom "Pratinjau Langsung" (PhoneFrame.tsx, dipakai bersama oleh dashboard Tautan/Desain/Produk). Akar masalah DITEMUKAN via analisis CSS, bukan tebakan: (1) wrapper notch atas memakan tinggi flow 26px (padding-top 10px + tinggi pil 16px), tapi konten cuma ditarik naik -mt-4 (16px) -- selisih 10px itu membocorkan bg-white layar HP di ATAS latar tema, paling kentara untuk tema gelap (Midnight/Noir/Cyber/Cosmic/dst). (2) wrapper konten sebelumnya berketinggian auto (tidak pasti), padahal isinya (PagePreview) pakai kelas `min-h-full` -- persentase tinggi CSS TIDAK bisa dihitung tanpa induk berketinggian pasti, jadi untuk halaman pendek (kreator baru, sedikit tautan) latar tema berhenti sebelum memenuhi 640px, membocorkan bg-white di BAWAH. Perbaikan: samakan -mt-4 jadi -mt-[26px] persis sesuai tinggi wrapper notch, dan jadikan wrapper konten `flex-1` di dalam induk `flex flex-col` supaya benar-benar punya tinggi pasti (memenuhi sisa 640px) TANPA merusak scroll internal untuk halaman panjang (default flexbox `min-height: auto` mencegah item flex mengecil di bawah tinggi konten aslinya, jadi halaman dengan banyak tautan tetap bisa di-scroll penuh seperti sebelumnya). Perbaikan di SATU komponen bersama (PhoneFrame.tsx) otomatis berlaku di semua halaman dashboard yang memakai kolom pratinjau ini. tsc/eslint/build bersih. TANPA perubahan backend. CATATAN JUJUR: perbaikan divalidasi lewat analisis matematis CSS (perhitungan piksel persis dari kelas Tailwind yang dipakai) dan tsc/eslint/build bersih, BUKAN lewat tangkapan layar visual sungguhan di browser (tidak ada alat otomasi browser tersedia di sesi ini) -- kalau celah putih masih terlihat setelah dites langsung oleh pengguna, kemungkinan ada faktor tambahan (mis. tema tertentu yang belum dicek) yang perlu dilaporkan ulang.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5671,7 +5671,7 @@
       </c>
       <c r="J98" s="26" t="inlineStr">
         <is>
-          <t>KERJAKAN DULUAN sebelum item lain di Sprint 7-10 supaya fitur baru (voucher/afiliasi/audiens/dsb) langsung masuk ke IA yang benar, bukan ditempel di struktur lama. Linktree pisah Links/Shop/Design jadi tab beda-beda dan nyembunyiin Settings di menu 'More'; Lynk.id sebar fitur commerce ke banyak sidebar terpisah (Voucher/Affiliates/Settings&gt;Store Management) -- keduanya butuh banyak klik untuk hal yang buat kreator terasa satu kesatuan. Jeonme gabung jadi 6 bagian: Ringkasan (analitik), Halaman Saya (tautan+produk+desain+preview), Produk &amp; Monetisasi (voucher/bundel/afiliasi/poin), Audiens &amp; Pemasaran (lead+WhatsApp+social proof), Saldo &amp; Penarikan (sudah ada), Pengaturan (domain/SEO/tim/watermark). -- SELESAI (23-24 Juli 2026): sidebar direstrukturisasi jadi 6 bagian, verifikasi end-to-end lolos di lokal &amp; staging (commit ec343e8, tag v0.12.0).</t>
+          <t>KERJAKAN DULUAN sebelum item lain di Sprint 7-10 supaya fitur baru (voucher/afiliasi/audiens/dsb) langsung masuk ke IA yang benar, bukan ditempel di struktur lama. Linktree pisah Links/Shop/Design jadi tab beda-beda dan nyembunyiin Settings di menu 'More'; Lynk.id sebar fitur commerce ke banyak sidebar terpisah (Voucher/Affiliates/Settings&gt;Store Management) -- keduanya butuh banyak klik untuk hal yang buat kreator terasa satu kesatuan. Jeonme gabung jadi 6 bagian: Ringkasan (analitik), Halaman Saya (tautan+produk+desain+preview), Produk &amp; Monetisasi (voucher/bundel/afiliasi/poin), Audiens &amp; Pemasaran (lead+WhatsApp+social proof), Saldo &amp; Penarikan (sudah ada), Pengaturan (domain/SEO/tim/watermark). -- SELESAI (23-24 Juli 2026): sidebar direstrukturisasi jadi 6 bagian, verifikasi end-to-end lolos di lokal &amp; staging (commit ec343e8, tag v0.12.0). TAMBAHAN (26 Juli 2026): permintaan langsung pengguna -- 3 grup navigasi (Halaman Saya/Produk &amp; Monetisasi/Audiens &amp; Pemasaran, total ~16 item) diubah jadi COLLAPSIBLE (accordion, ikon panah berputar 90 derajat, pola visual sama seperti AccordionRow di halaman Desain) -- sebelumnya SEMUA grup selalu tampil terbuka penuh sekaligus, sidebar jadi sangat panjang mengingat backlog sudah lengkap (Sprint 0-14 + banyak penambahan ad-hoc). Grup yang berisi halaman aktif saat sidebar PERTAMA dimuat otomatis terbuka (dihitung sekali dari pathname saat render pertama); sesudahnya sepenuhnya dikendalikan klik manual pengguna (SENGAJA TIDAK dipaksa terbuka ulang lewat React effect setiap pindah halaman -- selain melanggar aturan lint react-hooks/set-state-in-effect, itu juga akan membuat tombol tutup terasa rusak karena grup berisi halaman aktif tidak akan pernah benar-benar bisa ditutup). Label grup tetap berwarna primary kalau berisi halaman aktif, terlepas dari status buka/tutup, supaya kreator tetap tahu sedang di bagian mana. TANPA perubahan backend. tsc/eslint (termasuk aturan react-hooks yang sempat menangkap draf pertama pakai useEffect+setState, diperbaiki jadi murni derived state dari useState initializer)/build seluruhnya bersih. CATATAN JUJUR: interaksi klik buka/tutup tidak diverifikasi lewat klik langsung di browser sungguhan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran logika dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual, bukan verifikasi visual/interaktif.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5671,7 +5671,7 @@
       </c>
       <c r="J98" s="26" t="inlineStr">
         <is>
-          <t>KERJAKAN DULUAN sebelum item lain di Sprint 7-10 supaya fitur baru (voucher/afiliasi/audiens/dsb) langsung masuk ke IA yang benar, bukan ditempel di struktur lama. Linktree pisah Links/Shop/Design jadi tab beda-beda dan nyembunyiin Settings di menu 'More'; Lynk.id sebar fitur commerce ke banyak sidebar terpisah (Voucher/Affiliates/Settings&gt;Store Management) -- keduanya butuh banyak klik untuk hal yang buat kreator terasa satu kesatuan. Jeonme gabung jadi 6 bagian: Ringkasan (analitik), Halaman Saya (tautan+produk+desain+preview), Produk &amp; Monetisasi (voucher/bundel/afiliasi/poin), Audiens &amp; Pemasaran (lead+WhatsApp+social proof), Saldo &amp; Penarikan (sudah ada), Pengaturan (domain/SEO/tim/watermark). -- SELESAI (23-24 Juli 2026): sidebar direstrukturisasi jadi 6 bagian, verifikasi end-to-end lolos di lokal &amp; staging (commit ec343e8, tag v0.12.0). TAMBAHAN (26 Juli 2026): permintaan langsung pengguna -- 3 grup navigasi (Halaman Saya/Produk &amp; Monetisasi/Audiens &amp; Pemasaran, total ~16 item) diubah jadi COLLAPSIBLE (accordion, ikon panah berputar 90 derajat, pola visual sama seperti AccordionRow di halaman Desain) -- sebelumnya SEMUA grup selalu tampil terbuka penuh sekaligus, sidebar jadi sangat panjang mengingat backlog sudah lengkap (Sprint 0-14 + banyak penambahan ad-hoc). Grup yang berisi halaman aktif saat sidebar PERTAMA dimuat otomatis terbuka (dihitung sekali dari pathname saat render pertama); sesudahnya sepenuhnya dikendalikan klik manual pengguna (SENGAJA TIDAK dipaksa terbuka ulang lewat React effect setiap pindah halaman -- selain melanggar aturan lint react-hooks/set-state-in-effect, itu juga akan membuat tombol tutup terasa rusak karena grup berisi halaman aktif tidak akan pernah benar-benar bisa ditutup). Label grup tetap berwarna primary kalau berisi halaman aktif, terlepas dari status buka/tutup, supaya kreator tetap tahu sedang di bagian mana. TANPA perubahan backend. tsc/eslint (termasuk aturan react-hooks yang sempat menangkap draf pertama pakai useEffect+setState, diperbaiki jadi murni derived state dari useState initializer)/build seluruhnya bersih. CATATAN JUJUR: interaksi klik buka/tutup tidak diverifikasi lewat klik langsung di browser sungguhan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran logika dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual, bukan verifikasi visual/interaktif.</t>
+          <t>KERJAKAN DULUAN sebelum item lain di Sprint 7-10 supaya fitur baru (voucher/afiliasi/audiens/dsb) langsung masuk ke IA yang benar, bukan ditempel di struktur lama. Linktree pisah Links/Shop/Design jadi tab beda-beda dan nyembunyiin Settings di menu 'More'; Lynk.id sebar fitur commerce ke banyak sidebar terpisah (Voucher/Affiliates/Settings&gt;Store Management) -- keduanya butuh banyak klik untuk hal yang buat kreator terasa satu kesatuan. Jeonme gabung jadi 6 bagian: Ringkasan (analitik), Halaman Saya (tautan+produk+desain+preview), Produk &amp; Monetisasi (voucher/bundel/afiliasi/poin), Audiens &amp; Pemasaran (lead+WhatsApp+social proof), Saldo &amp; Penarikan (sudah ada), Pengaturan (domain/SEO/tim/watermark). -- SELESAI (23-24 Juli 2026): sidebar direstrukturisasi jadi 6 bagian, verifikasi end-to-end lolos di lokal &amp; staging (commit ec343e8, tag v0.12.0). TAMBAHAN (26 Juli 2026): permintaan langsung pengguna -- 3 grup navigasi (Halaman Saya/Produk &amp; Monetisasi/Audiens &amp; Pemasaran, total ~16 item) diubah jadi COLLAPSIBLE (accordion, ikon panah berputar 90 derajat, pola visual sama seperti AccordionRow di halaman Desain) -- sebelumnya SEMUA grup selalu tampil terbuka penuh sekaligus, sidebar jadi sangat panjang mengingat backlog sudah lengkap (Sprint 0-14 + banyak penambahan ad-hoc). Grup yang berisi halaman aktif saat sidebar PERTAMA dimuat otomatis terbuka (dihitung sekali dari pathname saat render pertama); sesudahnya sepenuhnya dikendalikan klik manual pengguna (SENGAJA TIDAK dipaksa terbuka ulang lewat React effect setiap pindah halaman -- selain melanggar aturan lint react-hooks/set-state-in-effect, itu juga akan membuat tombol tutup terasa rusak karena grup berisi halaman aktif tidak akan pernah benar-benar bisa ditutup). Label grup tetap berwarna primary kalau berisi halaman aktif, terlepas dari status buka/tutup, supaya kreator tetap tahu sedang di bagian mana. TANPA perubahan backend. tsc/eslint (termasuk aturan react-hooks yang sempat menangkap draf pertama pakai useEffect+setState, diperbaiki jadi murni derived state dari useState initializer)/build seluruhnya bersih. CATATAN JUJUR: interaksi klik buka/tutup tidak diverifikasi lewat klik langsung di browser sungguhan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran logika dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual, bukan verifikasi visual/interaktif. TAMBAHAN KEDUA (26 Juli 2026): permintaan langsung pengguna -- semua kotak "belum ada data" di ruang kosong (14 halaman dashboard: Tautan/Produk/Voucher/Bundel/Booking/Kursus/Event/Saldo/Tim/Afiliasi/Loyalitas/Audiens/Halaman Tambahan/Ringkasan) sebelumnya rata KIRI (ikon+teks sebaris menempel kiri kotak bergaris putus-putus) diubah jadi rata TENGAH (ikon di atas, teks di bawah, keduanya di tengah). Markup yang sebelumnya diduplikasi HAMPIR IDENTIK di 14 file diekstrak jadi satu komponen bersama `EmptyState` (apps/web/components/EmptyState.tsx, props: text/as="div"|"li"/bordered/className) supaya tampilannya konsisten di semua halaman dan perubahan gaya berikutnya cukup satu tempat. Kasus khusus juga dirapikan: baris "EmptyRow" di Ringkasan (dipakai utk daftar Top Tautan/Top Produk kosong) &amp; banner "Belum ada kunjungan" di Ringkasan turut dipusatkan. SENGAJA TIDAK diubah: teks bantuan kecil di dalam form yang sedang aktif (mis. "Belum ada produk aktif" di form Bundel, "Belum ada slot" di form Booking) -- itu bukan "ruang kosong" halaman, cuma baris status ringkas di dalam panel yang sedang dipakai, mengubahnya rata tengah justru akan terasa janggal berdampingan dengan label form yang rata kiri. tsc/eslint/build seluruhnya bersih (termasuk pembersihan import IconInbox yang jadi tidak terpakai di 12 file setelah diganti EmptyState). Sanity check: ke-14 halaman dashboard diakses langsung lewat dev server, semua merespons 200 tanpa error render. TANPA perubahan backend. CATATAN JUJUR: tampilan visual rata-tengah tidak diverifikasi lewat tangkapan layar browser sungguhan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran dipastikan lewat tsc/eslint/build bersih, sanity check HTTP 200 di tiap halaman, dan tinjauan kode manual terhadap kelas Tailwind (flex-col items-center justify-center text-center) di komponen EmptyState.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G29" s="21" t="inlineStr">
         <is>
-          <t>Selesai (deteksi ikon 9 platform + fallback, form tautan collapsed-by-default -- selesai &amp; terverifikasi)</t>
+          <t>Selesai (deteksi ikon 9 platform + fallback, form tautan collapsed-by-default -- selesai &amp; terverifikasi) Ditambah No.102: logo &amp; favicon Jeonme dibuat (badge gradien identitas + monogram J) dan dipasang lewat konvensi ikon Next.js -- selesai &amp; terverifikasi.</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5846,6 +5846,49 @@
       <c r="J102" t="inlineStr">
         <is>
           <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Buat logo &amp; ikon Jeonme, pasang sebagai favicon situs</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (di luar riset kompetitor asli)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G103" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna (26 Juli 2026) -- situs sebelumnya SAMA SEKALI belum punya favicon/logo (tab browser tampil ikon generik kosong). Dibuat programatik lewat Python (Pillow + numpy, TANPA alat rasterisasi SVG eksternal seperti cairosvg/rsvg-convert/Inkscape yang tidak tersedia di lingkungan ini): badge persegi membulat (rounded-2xl, senada estetika UI) berisi gradien identitas Jeonme yang SUDAH ada persis sama dengan kelas .text-gradient/.gradient-cta di globals.css (135deg, #1B4D3E -&gt; #1F7A6C 55% -&gt; #C9A24B), diisi monogram "J" putih tebal (font Segoe UI Bold -- font sistem yang tersedia, dipilih karena bentuk geometris/membulatnya senada dengan Poppins ExtraBold yang dipakai untuk heading di seluruh produk). Diverifikasi terbaca jelas di ukuran actual favicon (32x32 dan 16x16), bukan cuma di resolusi besar. Dipasang lewat KONVENSI file bawaan Next.js App Router (apps/web/app/icon.png 512x512 + apps/web/app/apple-icon.png 180x180) -- TIDAK perlu kode metadata manual sama sekali, Next.js otomatis mendeteksi file ini dan menyuntik tag &lt;link rel="icon"&gt;/&lt;link rel="apple-touch-icon"&gt; yang benar; ditambah apps/web/public/favicon.ico (multi-resolusi 16/32/48 dalam satu file .ico) sebagai jaring pengaman untuk crawler lama yang meminta /favicon.ico langsung tanpa membaca tag HTML. SEKALIGUS dibuat logo lockup penuh (ikon + wordmark "Jeonme" bergradien sama) disimpan di apps/web/public/logo.png (dan logo-icon.png versi ikon saja resolusi tinggi) sebagai aset untuk dipakai di tempat lain nanti (mis. halaman login, materi pemasaran) -- BELUM disambungkan ke komponen manapun karena permintaan eksplisit pengguna cuma minta dipakai untuk favicon dulu. Diverifikasi NYATA: dev server dicek langsung, HTML &lt;head&gt; terbukti berisi &lt;link rel="icon" href="/icon.png..."&gt; &amp; &lt;link rel="apple-touch-icon" href="/apple-icon.png..."&gt;, ketiga file (icon.png/apple-icon.png/favicon.ico) dicek merespons 200 dengan content-type gambar yang benar. tsc/eslint/build seluruhnya bersih. TANPA perubahan backend.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5671,7 +5671,7 @@
       </c>
       <c r="J98" s="26" t="inlineStr">
         <is>
-          <t>KERJAKAN DULUAN sebelum item lain di Sprint 7-10 supaya fitur baru (voucher/afiliasi/audiens/dsb) langsung masuk ke IA yang benar, bukan ditempel di struktur lama. Linktree pisah Links/Shop/Design jadi tab beda-beda dan nyembunyiin Settings di menu 'More'; Lynk.id sebar fitur commerce ke banyak sidebar terpisah (Voucher/Affiliates/Settings&gt;Store Management) -- keduanya butuh banyak klik untuk hal yang buat kreator terasa satu kesatuan. Jeonme gabung jadi 6 bagian: Ringkasan (analitik), Halaman Saya (tautan+produk+desain+preview), Produk &amp; Monetisasi (voucher/bundel/afiliasi/poin), Audiens &amp; Pemasaran (lead+WhatsApp+social proof), Saldo &amp; Penarikan (sudah ada), Pengaturan (domain/SEO/tim/watermark). -- SELESAI (23-24 Juli 2026): sidebar direstrukturisasi jadi 6 bagian, verifikasi end-to-end lolos di lokal &amp; staging (commit ec343e8, tag v0.12.0). TAMBAHAN (26 Juli 2026): permintaan langsung pengguna -- 3 grup navigasi (Halaman Saya/Produk &amp; Monetisasi/Audiens &amp; Pemasaran, total ~16 item) diubah jadi COLLAPSIBLE (accordion, ikon panah berputar 90 derajat, pola visual sama seperti AccordionRow di halaman Desain) -- sebelumnya SEMUA grup selalu tampil terbuka penuh sekaligus, sidebar jadi sangat panjang mengingat backlog sudah lengkap (Sprint 0-14 + banyak penambahan ad-hoc). Grup yang berisi halaman aktif saat sidebar PERTAMA dimuat otomatis terbuka (dihitung sekali dari pathname saat render pertama); sesudahnya sepenuhnya dikendalikan klik manual pengguna (SENGAJA TIDAK dipaksa terbuka ulang lewat React effect setiap pindah halaman -- selain melanggar aturan lint react-hooks/set-state-in-effect, itu juga akan membuat tombol tutup terasa rusak karena grup berisi halaman aktif tidak akan pernah benar-benar bisa ditutup). Label grup tetap berwarna primary kalau berisi halaman aktif, terlepas dari status buka/tutup, supaya kreator tetap tahu sedang di bagian mana. TANPA perubahan backend. tsc/eslint (termasuk aturan react-hooks yang sempat menangkap draf pertama pakai useEffect+setState, diperbaiki jadi murni derived state dari useState initializer)/build seluruhnya bersih. CATATAN JUJUR: interaksi klik buka/tutup tidak diverifikasi lewat klik langsung di browser sungguhan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran logika dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual, bukan verifikasi visual/interaktif. TAMBAHAN KEDUA (26 Juli 2026): permintaan langsung pengguna -- semua kotak "belum ada data" di ruang kosong (14 halaman dashboard: Tautan/Produk/Voucher/Bundel/Booking/Kursus/Event/Saldo/Tim/Afiliasi/Loyalitas/Audiens/Halaman Tambahan/Ringkasan) sebelumnya rata KIRI (ikon+teks sebaris menempel kiri kotak bergaris putus-putus) diubah jadi rata TENGAH (ikon di atas, teks di bawah, keduanya di tengah). Markup yang sebelumnya diduplikasi HAMPIR IDENTIK di 14 file diekstrak jadi satu komponen bersama `EmptyState` (apps/web/components/EmptyState.tsx, props: text/as="div"|"li"/bordered/className) supaya tampilannya konsisten di semua halaman dan perubahan gaya berikutnya cukup satu tempat. Kasus khusus juga dirapikan: baris "EmptyRow" di Ringkasan (dipakai utk daftar Top Tautan/Top Produk kosong) &amp; banner "Belum ada kunjungan" di Ringkasan turut dipusatkan. SENGAJA TIDAK diubah: teks bantuan kecil di dalam form yang sedang aktif (mis. "Belum ada produk aktif" di form Bundel, "Belum ada slot" di form Booking) -- itu bukan "ruang kosong" halaman, cuma baris status ringkas di dalam panel yang sedang dipakai, mengubahnya rata tengah justru akan terasa janggal berdampingan dengan label form yang rata kiri. tsc/eslint/build seluruhnya bersih (termasuk pembersihan import IconInbox yang jadi tidak terpakai di 12 file setelah diganti EmptyState). Sanity check: ke-14 halaman dashboard diakses langsung lewat dev server, semua merespons 200 tanpa error render. TANPA perubahan backend. CATATAN JUJUR: tampilan visual rata-tengah tidak diverifikasi lewat tangkapan layar browser sungguhan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran dipastikan lewat tsc/eslint/build bersih, sanity check HTTP 200 di tiap halaman, dan tinjauan kode manual terhadap kelas Tailwind (flex-col items-center justify-center text-center) di komponen EmptyState.</t>
+          <t>KERJAKAN DULUAN sebelum item lain di Sprint 7-10 supaya fitur baru (voucher/afiliasi/audiens/dsb) langsung masuk ke IA yang benar, bukan ditempel di struktur lama. Linktree pisah Links/Shop/Design jadi tab beda-beda dan nyembunyiin Settings di menu 'More'; Lynk.id sebar fitur commerce ke banyak sidebar terpisah (Voucher/Affiliates/Settings&gt;Store Management) -- keduanya butuh banyak klik untuk hal yang buat kreator terasa satu kesatuan. Jeonme gabung jadi 6 bagian: Ringkasan (analitik), Halaman Saya (tautan+produk+desain+preview), Produk &amp; Monetisasi (voucher/bundel/afiliasi/poin), Audiens &amp; Pemasaran (lead+WhatsApp+social proof), Saldo &amp; Penarikan (sudah ada), Pengaturan (domain/SEO/tim/watermark). -- SELESAI (23-24 Juli 2026): sidebar direstrukturisasi jadi 6 bagian, verifikasi end-to-end lolos di lokal &amp; staging (commit ec343e8, tag v0.12.0). TAMBAHAN (26 Juli 2026): permintaan langsung pengguna -- 3 grup navigasi (Halaman Saya/Produk &amp; Monetisasi/Audiens &amp; Pemasaran, total ~16 item) diubah jadi COLLAPSIBLE (accordion, ikon panah berputar 90 derajat, pola visual sama seperti AccordionRow di halaman Desain) -- sebelumnya SEMUA grup selalu tampil terbuka penuh sekaligus, sidebar jadi sangat panjang mengingat backlog sudah lengkap (Sprint 0-14 + banyak penambahan ad-hoc). Grup yang berisi halaman aktif saat sidebar PERTAMA dimuat otomatis terbuka (dihitung sekali dari pathname saat render pertama); sesudahnya sepenuhnya dikendalikan klik manual pengguna (SENGAJA TIDAK dipaksa terbuka ulang lewat React effect setiap pindah halaman -- selain melanggar aturan lint react-hooks/set-state-in-effect, itu juga akan membuat tombol tutup terasa rusak karena grup berisi halaman aktif tidak akan pernah benar-benar bisa ditutup). Label grup tetap berwarna primary kalau berisi halaman aktif, terlepas dari status buka/tutup, supaya kreator tetap tahu sedang di bagian mana. TANPA perubahan backend. tsc/eslint (termasuk aturan react-hooks yang sempat menangkap draf pertama pakai useEffect+setState, diperbaiki jadi murni derived state dari useState initializer)/build seluruhnya bersih. CATATAN JUJUR: interaksi klik buka/tutup tidak diverifikasi lewat klik langsung di browser sungguhan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran logika dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual, bukan verifikasi visual/interaktif. TAMBAHAN KEDUA (26 Juli 2026): permintaan langsung pengguna -- semua kotak "belum ada data" di ruang kosong (14 halaman dashboard: Tautan/Produk/Voucher/Bundel/Booking/Kursus/Event/Saldo/Tim/Afiliasi/Loyalitas/Audiens/Halaman Tambahan/Ringkasan) sebelumnya rata KIRI (ikon+teks sebaris menempel kiri kotak bergaris putus-putus) diubah jadi rata TENGAH (ikon di atas, teks di bawah, keduanya di tengah). Markup yang sebelumnya diduplikasi HAMPIR IDENTIK di 14 file diekstrak jadi satu komponen bersama `EmptyState` (apps/web/components/EmptyState.tsx, props: text/as="div"|"li"/bordered/className) supaya tampilannya konsisten di semua halaman dan perubahan gaya berikutnya cukup satu tempat. Kasus khusus juga dirapikan: baris "EmptyRow" di Ringkasan (dipakai utk daftar Top Tautan/Top Produk kosong) &amp; banner "Belum ada kunjungan" di Ringkasan turut dipusatkan. SENGAJA TIDAK diubah: teks bantuan kecil di dalam form yang sedang aktif (mis. "Belum ada produk aktif" di form Bundel, "Belum ada slot" di form Booking) -- itu bukan "ruang kosong" halaman, cuma baris status ringkas di dalam panel yang sedang dipakai, mengubahnya rata tengah justru akan terasa janggal berdampingan dengan label form yang rata kiri. tsc/eslint/build seluruhnya bersih (termasuk pembersihan import IconInbox yang jadi tidak terpakai di 12 file setelah diganti EmptyState). Sanity check: ke-14 halaman dashboard diakses langsung lewat dev server, semua merespons 200 tanpa error render. TANPA perubahan backend. CATATAN JUJUR: tampilan visual rata-tengah tidak diverifikasi lewat tangkapan layar browser sungguhan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran dipastikan lewat tsc/eslint/build bersih, sanity check HTTP 200 di tiap halaman, dan tinjauan kode manual terhadap kelas Tailwind (flex-col items-center justify-center text-center) di komponen EmptyState. TAMBAHAN KETIGA (26 Juli 2026): user tunjukkan tangkapan layar halaman Ringkasan -- sisi kanan halaman menyisakan banyak ruang kosong di layar lebar karena wrapper konten (mis. &lt;div className="max-w-3xl"&gt;) TIDAK punya mx-auto, jadi menempel rata KIRI alih-alih rata TENGAH di dalam &lt;main&gt; yang melebar penuh. Diperbaiki di SEMUA 18 halaman dashboard single-column yang punya pola sama persis (max-w-3xl/max-w-2xl/max-w-lg tanpa mx-auto): Ringkasan, Tautan-tidak (lihat catatan di bawah), Produk-tidak, Desain-tidak, Afiliasi, Audiens, Saldo, Booking, Bundel, Kartu Kontak, Kursus, Domain Kustom, Donasi, Event, KYC, Loyalitas, Halaman Tambahan, Pengaturan, Social Proof, Tim, Voucher. SENGAJA TIDAK disentuh: Tautan/Produk/Desain -- ketiganya sudah memakai layout grid 2 kolom (lg:grid lg:grid-cols-[1fr_360px]) dengan panel Pratinjau Langsung di kanan, jadi sisi kanan SUDAH terisi, tidak punya masalah ruang kosong yang sama. tsc/eslint/build bersih, sanity check HTTP 200 di ke-19 halaman yang disentuh (18 halaman + Ringkasan). TANPA perubahan backend. CATATAN JUJUR: tidak diverifikasi lewat tangkapan layar browser sungguhan (tidak ada alat otomasi browser tersedia di sesi ini).</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5845,7 +5845,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih. TAMBAHAN KELIMA (26 Juli 2026): user kirim tangkapan layar dashboard Links Linktree AKUN SUNGGUHAN milik mereka sendiri (linktr.ee/pikocarwashandcafe) dan minta "redesign seperti ini" -- ikon platform di pratinjau publik &amp; baris list dashboard sebelumnya monokrom (warna ikut tema aktif), diubah jadi BADGE LINGKARAN BERWARNA BRAND ASLI (WhatsApp hijau #25D366, Instagram gradien kuning-pink-ungu asli, TikTok hitam, YouTube merah #FF0000, Facebook biru #1877F2, Telegram biru #26A5E4, X hitam, Spotify hijau #1DB954, LinkedIn biru #0A66C2, Email abu tua) -- persis seperti badge berwarna di referensi, bukan lagi ikon monokrom netral. Field baru `badgeClass` ditambahkan ke return value detectLinkIcon (lib/link-icons.ts) dan disebar ke 3 tempat pemakaian: baris tautan pratinjau publik (PagePreview.tsx, 2 varian render), badge di baris list dashboard (dashboard/links/page.tsx), dan baris platform di modal "Tambah" (SUGGESTED_PLATFORMS array, badge warna disamakan persis). Tautan generik/tidak dikenali tetap fallback ke badge netral (bg-primary-subtle) seperti sebelumnya. SENGAJA TIDAK DIKERJAKAN LAGI (dicatat transparan, konsisten dengan keputusan-keputusan sebelumnya di tambahan pertama/ketiga): baris profil (avatar+bio+quick-add ikon berbadge "+") di atas -- sudah dikelola halaman Desain; tombol "Add collection"/"View archive" -- konsep grup/arsip belum ada; ikon aksi tambahan per tautan (gear/gambar/bintang di referensi, mewakili thumbnail/pin/gaya CTA per tautan) -- fitur-fitur itu tidak ada di Jeonme, membuat ikon kosong tanpa fungsi nyata bukan tujuan permintaan; indikator tren klik naik/turun (↑/↓ di sebelah jumlah klik) -- butuh perbandingan periode sebelum/sesudah yang belum ada logikanya di backend, effort lebih besar dari sekadar styling, ditunda. Diverifikasi E2E NYATA: 3 tautan uji dibuat (WhatsApp/Instagram/URL generik) lewat API sungguhan, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas badgeClass yang BENAR untuk ketiganya (bg-[#25D366] untuk WhatsApp, gradien kuning-pink-ungu untuk Instagram, bg-primary-subtle netral untuk URL generik tak dikenali). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. Data uji dibersihkan sesudahnya.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5845,7 +5845,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih. TAMBAHAN KELIMA (26 Juli 2026): user kirim tangkapan layar dashboard Links Linktree AKUN SUNGGUHAN milik mereka sendiri (linktr.ee/pikocarwashandcafe) dan minta "redesign seperti ini" -- ikon platform di pratinjau publik &amp; baris list dashboard sebelumnya monokrom (warna ikut tema aktif), diubah jadi BADGE LINGKARAN BERWARNA BRAND ASLI (WhatsApp hijau #25D366, Instagram gradien kuning-pink-ungu asli, TikTok hitam, YouTube merah #FF0000, Facebook biru #1877F2, Telegram biru #26A5E4, X hitam, Spotify hijau #1DB954, LinkedIn biru #0A66C2, Email abu tua) -- persis seperti badge berwarna di referensi, bukan lagi ikon monokrom netral. Field baru `badgeClass` ditambahkan ke return value detectLinkIcon (lib/link-icons.ts) dan disebar ke 3 tempat pemakaian: baris tautan pratinjau publik (PagePreview.tsx, 2 varian render), badge di baris list dashboard (dashboard/links/page.tsx), dan baris platform di modal "Tambah" (SUGGESTED_PLATFORMS array, badge warna disamakan persis). Tautan generik/tidak dikenali tetap fallback ke badge netral (bg-primary-subtle) seperti sebelumnya. SENGAJA TIDAK DIKERJAKAN LAGI (dicatat transparan, konsisten dengan keputusan-keputusan sebelumnya di tambahan pertama/ketiga): baris profil (avatar+bio+quick-add ikon berbadge "+") di atas -- sudah dikelola halaman Desain; tombol "Add collection"/"View archive" -- konsep grup/arsip belum ada; ikon aksi tambahan per tautan (gear/gambar/bintang di referensi, mewakili thumbnail/pin/gaya CTA per tautan) -- fitur-fitur itu tidak ada di Jeonme, membuat ikon kosong tanpa fungsi nyata bukan tujuan permintaan; indikator tren klik naik/turun (↑/↓ di sebelah jumlah klik) -- butuh perbandingan periode sebelum/sesudah yang belum ada logikanya di backend, effort lebih besar dari sekadar styling, ditunda. Diverifikasi E2E NYATA: 3 tautan uji dibuat (WhatsApp/Instagram/URL generik) lewat API sungguhan, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas badgeClass yang BENAR untuk ketiganya (bg-[#25D366] untuk WhatsApp, gradien kuning-pink-ungu untuk Instagram, bg-primary-subtle netral untuk URL generik tak dikenali). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. Data uji dibersihkan sesudahnya.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih. TAMBAHAN KELIMA (26 Juli 2026): user kirim tangkapan layar dashboard Links Linktree AKUN SUNGGUHAN milik mereka sendiri (linktr.ee/pikocarwashandcafe) dan minta "redesign seperti ini" -- ikon platform di pratinjau publik &amp; baris list dashboard sebelumnya monokrom (warna ikut tema aktif), diubah jadi BADGE LINGKARAN BERWARNA BRAND ASLI (WhatsApp hijau #25D366, Instagram gradien kuning-pink-ungu asli, TikTok hitam, YouTube merah #FF0000, Facebook biru #1877F2, Telegram biru #26A5E4, X hitam, Spotify hijau #1DB954, LinkedIn biru #0A66C2, Email abu tua) -- persis seperti badge berwarna di referensi, bukan lagi ikon monokrom netral. Field baru `badgeClass` ditambahkan ke return value detectLinkIcon (lib/link-icons.ts) dan disebar ke 3 tempat pemakaian: baris tautan pratinjau publik (PagePreview.tsx, 2 varian render), badge di baris list dashboard (dashboard/links/page.tsx), dan baris platform di modal "Tambah" (SUGGESTED_PLATFORMS array, badge warna disamakan persis). Tautan generik/tidak dikenali tetap fallback ke badge netral (bg-primary-subtle) seperti sebelumnya. SENGAJA TIDAK DIKERJAKAN LAGI (dicatat transparan, konsisten dengan keputusan-keputusan sebelumnya di tambahan pertama/ketiga): baris profil (avatar+bio+quick-add ikon berbadge "+") di atas -- sudah dikelola halaman Desain; tombol "Add collection"/"View archive" -- konsep grup/arsip belum ada; ikon aksi tambahan per tautan (gear/gambar/bintang di referensi, mewakili thumbnail/pin/gaya CTA per tautan) -- fitur-fitur itu tidak ada di Jeonme, membuat ikon kosong tanpa fungsi nyata bukan tujuan permintaan; indikator tren klik naik/turun (↑/↓ di sebelah jumlah klik) -- butuh perbandingan periode sebelum/sesudah yang belum ada logikanya di backend, effort lebih besar dari sekadar styling, ditunda. Diverifikasi E2E NYATA: 3 tautan uji dibuat (WhatsApp/Instagram/URL generik) lewat API sungguhan, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas badgeClass yang BENAR untuk ketiganya (bg-[#25D366] untuk WhatsApp, gradien kuning-pink-ungu untuk Instagram, bg-primary-subtle netral untuk URL generik tak dikenali). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. Data uji dibersihkan sesudahnya. PERBAIKAN BUG PENTING (26 Juli 2026): user laporkan error 500 sungguhan di STAGING saat menghapus tautan yang sudah pernah diklik ("DELETE .../dashboard/links/{id} 500 Internal Server Error"), ditemukan lewat tautan populer (2000+ klik) di akun mereka sendiri. AKAR MASALAH ditemukan lewat investigasi kode &amp; skema database (bukan tebakan): kolom analytics_events.link_id (migrasi 000001, sejak AWAL proyek) adalah FOREIGN KEY ke links(id) TANPA klausa ON DELETE apa pun, jadi default Postgres (NO ACTION) MENOLAK setiap DELETE FROM links selama masih ada baris analytics_events yang merujuknya -- artinya SEMAKIN POPULER sebuah tautan (semakin banyak klik/kunjungan tercatat), semakin PASTI tautan itu tidak bisa dihapus sama sekali, bug ini ada sejak Sprint 0 dan baru ketahuan sekarang. DIPERBAIKI lewat migrasi baru 000032_analytics_link_delete_fix: constraint diubah jadi ON DELETE SET NULL (BUKAN CASCADE) -- riwayat klik/kunjungan pada level HALAMAN (page_id) tetap utuh untuk laporan analitik agregat (total kunjungan/klik halaman tidak berkurang), cuma referensi ke tautan yang sudah dihapus itu yang di-null-kan, event-nya sendiri TIDAK ikut terhapus. Diverifikasi E2E NYATA (bukan cuma baca kode): tautan uji dibuat, 5 event klik disimulasikan lewat endpoint track publik sungguhan (mereproduksi PERSIS skenario bug), DELETE dicoba SEBELUM migrasi (gagal, memverifikasi bug benar ada) lalu SESUDAH migrasi diterapkan (berhasil 200, pesan "tautan dihapus"), lalu dicek langsung ke database bahwa ke-5 baris analytics_events TETAP ADA (COUNT=5) dengan link_id ter-null-kan (COUNT WHERE link_id IS NOT NULL = 0) -- membuktikan riwayat analitik tidak hilang. go build/vet/test seluruhnya bersih. Data uji dibersihkan. Migrasi ini WAJIB dijalankan di staging &amp; production saat deploy (migrate up otomatis lewat pipeline CI/CD yang sudah ada). TAMBAHAN KEENAM: user juga minta bagian ATAS halaman Tautan diikutkan tangkapan layar dashboard Links Linktree (foto profil + nama + bio + baris ikon quick-add) -- MEMBALIK keputusan sebelumnya yang sengaja tidak mereplikasi header ini (dulu beralasan "sudah dikelola di halaman Desain"). Sekarang ditambahkan sebagai PRATINJAU BACA-SAJA (foto profil/nama/bio tampil, TIDAK bisa diedit dari sini -- mengedit tetap lewat halaman Desain, jadi cuma SATU sumber kebenaran untuk mengubahnya, tidak duplikat form edit di dua tempat), plus baris quick-add 3 ikon bulat (Video/FAQ/Formulir Kontak, masing-masing berlencana "+" kecil di pojok) yang langsung membuka form blok terkait (memakai ulang handleSelectContentTile yang sudah ada dari modal "Tambah"), diakhiri tombol "+" generik yang membuka modal lengkap yang sama. Ikon galeri gambar/koleksi ala referensi SENGAJA tidak ditiru -- Jeonme belum punya blok galeri gambar di halaman utama (beda dari halaman landing builder No.99 yang punya blok "image" tersendiri, itu untuk halaman TAMBAHAN bukan halaman utama). tsc/eslint/build bersih.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5845,7 +5845,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih. TAMBAHAN KELIMA (26 Juli 2026): user kirim tangkapan layar dashboard Links Linktree AKUN SUNGGUHAN milik mereka sendiri (linktr.ee/pikocarwashandcafe) dan minta "redesign seperti ini" -- ikon platform di pratinjau publik &amp; baris list dashboard sebelumnya monokrom (warna ikut tema aktif), diubah jadi BADGE LINGKARAN BERWARNA BRAND ASLI (WhatsApp hijau #25D366, Instagram gradien kuning-pink-ungu asli, TikTok hitam, YouTube merah #FF0000, Facebook biru #1877F2, Telegram biru #26A5E4, X hitam, Spotify hijau #1DB954, LinkedIn biru #0A66C2, Email abu tua) -- persis seperti badge berwarna di referensi, bukan lagi ikon monokrom netral. Field baru `badgeClass` ditambahkan ke return value detectLinkIcon (lib/link-icons.ts) dan disebar ke 3 tempat pemakaian: baris tautan pratinjau publik (PagePreview.tsx, 2 varian render), badge di baris list dashboard (dashboard/links/page.tsx), dan baris platform di modal "Tambah" (SUGGESTED_PLATFORMS array, badge warna disamakan persis). Tautan generik/tidak dikenali tetap fallback ke badge netral (bg-primary-subtle) seperti sebelumnya. SENGAJA TIDAK DIKERJAKAN LAGI (dicatat transparan, konsisten dengan keputusan-keputusan sebelumnya di tambahan pertama/ketiga): baris profil (avatar+bio+quick-add ikon berbadge "+") di atas -- sudah dikelola halaman Desain; tombol "Add collection"/"View archive" -- konsep grup/arsip belum ada; ikon aksi tambahan per tautan (gear/gambar/bintang di referensi, mewakili thumbnail/pin/gaya CTA per tautan) -- fitur-fitur itu tidak ada di Jeonme, membuat ikon kosong tanpa fungsi nyata bukan tujuan permintaan; indikator tren klik naik/turun (↑/↓ di sebelah jumlah klik) -- butuh perbandingan periode sebelum/sesudah yang belum ada logikanya di backend, effort lebih besar dari sekadar styling, ditunda. Diverifikasi E2E NYATA: 3 tautan uji dibuat (WhatsApp/Instagram/URL generik) lewat API sungguhan, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas badgeClass yang BENAR untuk ketiganya (bg-[#25D366] untuk WhatsApp, gradien kuning-pink-ungu untuk Instagram, bg-primary-subtle netral untuk URL generik tak dikenali). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. Data uji dibersihkan sesudahnya. PERBAIKAN BUG PENTING (26 Juli 2026): user laporkan error 500 sungguhan di STAGING saat menghapus tautan yang sudah pernah diklik ("DELETE .../dashboard/links/{id} 500 Internal Server Error"), ditemukan lewat tautan populer (2000+ klik) di akun mereka sendiri. AKAR MASALAH ditemukan lewat investigasi kode &amp; skema database (bukan tebakan): kolom analytics_events.link_id (migrasi 000001, sejak AWAL proyek) adalah FOREIGN KEY ke links(id) TANPA klausa ON DELETE apa pun, jadi default Postgres (NO ACTION) MENOLAK setiap DELETE FROM links selama masih ada baris analytics_events yang merujuknya -- artinya SEMAKIN POPULER sebuah tautan (semakin banyak klik/kunjungan tercatat), semakin PASTI tautan itu tidak bisa dihapus sama sekali, bug ini ada sejak Sprint 0 dan baru ketahuan sekarang. DIPERBAIKI lewat migrasi baru 000032_analytics_link_delete_fix: constraint diubah jadi ON DELETE SET NULL (BUKAN CASCADE) -- riwayat klik/kunjungan pada level HALAMAN (page_id) tetap utuh untuk laporan analitik agregat (total kunjungan/klik halaman tidak berkurang), cuma referensi ke tautan yang sudah dihapus itu yang di-null-kan, event-nya sendiri TIDAK ikut terhapus. Diverifikasi E2E NYATA (bukan cuma baca kode): tautan uji dibuat, 5 event klik disimulasikan lewat endpoint track publik sungguhan (mereproduksi PERSIS skenario bug), DELETE dicoba SEBELUM migrasi (gagal, memverifikasi bug benar ada) lalu SESUDAH migrasi diterapkan (berhasil 200, pesan "tautan dihapus"), lalu dicek langsung ke database bahwa ke-5 baris analytics_events TETAP ADA (COUNT=5) dengan link_id ter-null-kan (COUNT WHERE link_id IS NOT NULL = 0) -- membuktikan riwayat analitik tidak hilang. go build/vet/test seluruhnya bersih. Data uji dibersihkan. Migrasi ini WAJIB dijalankan di staging &amp; production saat deploy (migrate up otomatis lewat pipeline CI/CD yang sudah ada). TAMBAHAN KEENAM: user juga minta bagian ATAS halaman Tautan diikutkan tangkapan layar dashboard Links Linktree (foto profil + nama + bio + baris ikon quick-add) -- MEMBALIK keputusan sebelumnya yang sengaja tidak mereplikasi header ini (dulu beralasan "sudah dikelola di halaman Desain"). Sekarang ditambahkan sebagai PRATINJAU BACA-SAJA (foto profil/nama/bio tampil, TIDAK bisa diedit dari sini -- mengedit tetap lewat halaman Desain, jadi cuma SATU sumber kebenaran untuk mengubahnya, tidak duplikat form edit di dua tempat), plus baris quick-add 3 ikon bulat (Video/FAQ/Formulir Kontak, masing-masing berlencana "+" kecil di pojok) yang langsung membuka form blok terkait (memakai ulang handleSelectContentTile yang sudah ada dari modal "Tambah"), diakhiri tombol "+" generik yang membuka modal lengkap yang sama. Ikon galeri gambar/koleksi ala referensi SENGAJA tidak ditiru -- Jeonme belum punya blok galeri gambar di halaman utama (beda dari halaman landing builder No.99 yang punya blok "image" tersendiri, itu untuk halaman TAMBAHAN bukan halaman utama). tsc/eslint/build bersih.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih. TAMBAHAN KELIMA (26 Juli 2026): user kirim tangkapan layar dashboard Links Linktree AKUN SUNGGUHAN milik mereka sendiri (linktr.ee/pikocarwashandcafe) dan minta "redesign seperti ini" -- ikon platform di pratinjau publik &amp; baris list dashboard sebelumnya monokrom (warna ikut tema aktif), diubah jadi BADGE LINGKARAN BERWARNA BRAND ASLI (WhatsApp hijau #25D366, Instagram gradien kuning-pink-ungu asli, TikTok hitam, YouTube merah #FF0000, Facebook biru #1877F2, Telegram biru #26A5E4, X hitam, Spotify hijau #1DB954, LinkedIn biru #0A66C2, Email abu tua) -- persis seperti badge berwarna di referensi, bukan lagi ikon monokrom netral. Field baru `badgeClass` ditambahkan ke return value detectLinkIcon (lib/link-icons.ts) dan disebar ke 3 tempat pemakaian: baris tautan pratinjau publik (PagePreview.tsx, 2 varian render), badge di baris list dashboard (dashboard/links/page.tsx), dan baris platform di modal "Tambah" (SUGGESTED_PLATFORMS array, badge warna disamakan persis). Tautan generik/tidak dikenali tetap fallback ke badge netral (bg-primary-subtle) seperti sebelumnya. SENGAJA TIDAK DIKERJAKAN LAGI (dicatat transparan, konsisten dengan keputusan-keputusan sebelumnya di tambahan pertama/ketiga): baris profil (avatar+bio+quick-add ikon berbadge "+") di atas -- sudah dikelola halaman Desain; tombol "Add collection"/"View archive" -- konsep grup/arsip belum ada; ikon aksi tambahan per tautan (gear/gambar/bintang di referensi, mewakili thumbnail/pin/gaya CTA per tautan) -- fitur-fitur itu tidak ada di Jeonme, membuat ikon kosong tanpa fungsi nyata bukan tujuan permintaan; indikator tren klik naik/turun (↑/↓ di sebelah jumlah klik) -- butuh perbandingan periode sebelum/sesudah yang belum ada logikanya di backend, effort lebih besar dari sekadar styling, ditunda. Diverifikasi E2E NYATA: 3 tautan uji dibuat (WhatsApp/Instagram/URL generik) lewat API sungguhan, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas badgeClass yang BENAR untuk ketiganya (bg-[#25D366] untuk WhatsApp, gradien kuning-pink-ungu untuk Instagram, bg-primary-subtle netral untuk URL generik tak dikenali). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. Data uji dibersihkan sesudahnya. PERBAIKAN BUG PENTING (26 Juli 2026): user laporkan error 500 sungguhan di STAGING saat menghapus tautan yang sudah pernah diklik ("DELETE .../dashboard/links/{id} 500 Internal Server Error"), ditemukan lewat tautan populer (2000+ klik) di akun mereka sendiri. AKAR MASALAH ditemukan lewat investigasi kode &amp; skema database (bukan tebakan): kolom analytics_events.link_id (migrasi 000001, sejak AWAL proyek) adalah FOREIGN KEY ke links(id) TANPA klausa ON DELETE apa pun, jadi default Postgres (NO ACTION) MENOLAK setiap DELETE FROM links selama masih ada baris analytics_events yang merujuknya -- artinya SEMAKIN POPULER sebuah tautan (semakin banyak klik/kunjungan tercatat), semakin PASTI tautan itu tidak bisa dihapus sama sekali, bug ini ada sejak Sprint 0 dan baru ketahuan sekarang. DIPERBAIKI lewat migrasi baru 000032_analytics_link_delete_fix: constraint diubah jadi ON DELETE SET NULL (BUKAN CASCADE) -- riwayat klik/kunjungan pada level HALAMAN (page_id) tetap utuh untuk laporan analitik agregat (total kunjungan/klik halaman tidak berkurang), cuma referensi ke tautan yang sudah dihapus itu yang di-null-kan, event-nya sendiri TIDAK ikut terhapus. Diverifikasi E2E NYATA (bukan cuma baca kode): tautan uji dibuat, 5 event klik disimulasikan lewat endpoint track publik sungguhan (mereproduksi PERSIS skenario bug), DELETE dicoba SEBELUM migrasi (gagal, memverifikasi bug benar ada) lalu SESUDAH migrasi diterapkan (berhasil 200, pesan "tautan dihapus"), lalu dicek langsung ke database bahwa ke-5 baris analytics_events TETAP ADA (COUNT=5) dengan link_id ter-null-kan (COUNT WHERE link_id IS NOT NULL = 0) -- membuktikan riwayat analitik tidak hilang. go build/vet/test seluruhnya bersih. Data uji dibersihkan. Migrasi ini WAJIB dijalankan di staging &amp; production saat deploy (migrate up otomatis lewat pipeline CI/CD yang sudah ada). TAMBAHAN KEENAM: user juga minta bagian ATAS halaman Tautan diikutkan tangkapan layar dashboard Links Linktree (foto profil + nama + bio + baris ikon quick-add) -- MEMBALIK keputusan sebelumnya yang sengaja tidak mereplikasi header ini (dulu beralasan "sudah dikelola di halaman Desain"). Sekarang ditambahkan sebagai PRATINJAU BACA-SAJA (foto profil/nama/bio tampil, TIDAK bisa diedit dari sini -- mengedit tetap lewat halaman Desain, jadi cuma SATU sumber kebenaran untuk mengubahnya, tidak duplikat form edit di dua tempat), plus baris quick-add 3 ikon bulat (Video/FAQ/Formulir Kontak, masing-masing berlencana "+" kecil di pojok) yang langsung membuka form blok terkait (memakai ulang handleSelectContentTile yang sudah ada dari modal "Tambah"), diakhiri tombol "+" generik yang membuka modal lengkap yang sama. Ikon galeri gambar/koleksi ala referensi SENGAJA tidak ditiru -- Jeonme belum punya blok galeri gambar di halaman utama (beda dari halaman landing builder No.99 yang punya blok "image" tersendiri, itu untuk halaman TAMBAHAN bukan halaman utama). tsc/eslint/build bersih. TAMBAHAN KETUJUH (26 Juli 2026): user kirim tangkapan layar halaman PUBLIK Linktree (bukan dashboard) dan minta "hasil linknya" (halaman publik kreator) diikutkan 4 hal spesifik: (1) tombol share ke semua platform, (2) logo Jeonme tampil di halaman, (3) footer tentang Jeonme, (4) border radius kartu dikurangi. Keempatnya dikerjakan di PagePreview.tsx (dipakai bersama oleh halaman publik sungguhan &amp; pratinjau dashboard): (1) ShareButton.tsx baru (komponen client terpisah, pola sama seperti ReportButton yang sudah ada) memakai Web Share API bawaan browser (navigator.share) -- membuka lembar berbagi NATIF perangkat pengunjung berisi SEMUA aplikasi yang bisa menerima share (WhatsApp/Telegram/Messages/Mail/dll tergantung apa yang terpasang), fallback salin tautan ke clipboard untuk browser yang tidak mendukung (kebanyakan desktop non-Safari/Edge). Ini yang membuatnya benar-benar "ke semua platform" tanpa perlu membuat &amp; merawat daftar tombol per-platform sendiri. (2) Logo Jeonme (aset logo-icon.png yang dibuat No.102 sebelumnya) ditampilkan di pojok kiri-atas sebagai tautan ke jeonme.com, sebaris dengan tombol share di kanan -- berlaku di halaman bio biasa DAN halaman landing (No.99). (3) Footer diubah dari tautan teks polos "Dibuat dengan Jeonme" jadi PIL bermerek "Buat halaman gratis di Jeonme" (logo kecil + teks, latar putih, tautan ke jeonme.com/register) -- CTA konversi setara "Join X on Linktree" di referensi, tombol Laporkan halaman yang sudah ada dipindah jadi baris kedua di bawahnya. Baris footer utilitas tambahan ala referensi ("Cookie Preferences · Privacy · Explore · About this account") SENGAJA TIDAK ditiru -- halaman-halaman itu belum ada di Jeonme (cuma /login, /register, /card, /p, /[username]), membuat tautan ke halaman yang tidak ada bukan tujuan permintaan ini. (4) SEMUA 23 kemunculan rounded-2xl di PagePreview.tsx (kartu tautan, produk, video/FAQ/formulir kontak, event, booking, loyalitas, lead capture, gambar) diubah jadi rounded-xl -- lebih persegi/tidak terlalu membulat, sesuai tangkapan layar. HANYA di PagePreview.tsx (halaman publik) -- dashboard TIDAK disentuh, tetap pakai rounded-2xl seperti sebelumnya (bahasa visual terpisah, tidak diminta berubah). Diverifikasi E2E NYATA: kreator uji dibuat, halaman publik di-curl langsung, HTML SSR terbukti berisi logo topbar, tombol share (aria-label benar), footer CTA lengkap dengan tautan register yang benar, dan rounded-2xl TERBUKTI NOL kemunculan (rounded-xl menggantikannya). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend. Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5889,6 +5889,49 @@
       <c r="J103" t="inlineStr">
         <is>
           <t>DITAMBAHKAN LANGSUNG oleh pengguna (26 Juli 2026) -- situs sebelumnya SAMA SEKALI belum punya favicon/logo (tab browser tampil ikon generik kosong). Dibuat programatik lewat Python (Pillow + numpy, TANPA alat rasterisasi SVG eksternal seperti cairosvg/rsvg-convert/Inkscape yang tidak tersedia di lingkungan ini): badge persegi membulat (rounded-2xl, senada estetika UI) berisi gradien identitas Jeonme yang SUDAH ada persis sama dengan kelas .text-gradient/.gradient-cta di globals.css (135deg, #1B4D3E -&gt; #1F7A6C 55% -&gt; #C9A24B), diisi monogram "J" putih tebal (font Segoe UI Bold -- font sistem yang tersedia, dipilih karena bentuk geometris/membulatnya senada dengan Poppins ExtraBold yang dipakai untuk heading di seluruh produk). Diverifikasi terbaca jelas di ukuran actual favicon (32x32 dan 16x16), bukan cuma di resolusi besar. Dipasang lewat KONVENSI file bawaan Next.js App Router (apps/web/app/icon.png 512x512 + apps/web/app/apple-icon.png 180x180) -- TIDAK perlu kode metadata manual sama sekali, Next.js otomatis mendeteksi file ini dan menyuntik tag &lt;link rel="icon"&gt;/&lt;link rel="apple-touch-icon"&gt; yang benar; ditambah apps/web/public/favicon.ico (multi-resolusi 16/32/48 dalam satu file .ico) sebagai jaring pengaman untuk crawler lama yang meminta /favicon.ico langsung tanpa membaca tag HTML. SEKALIGUS dibuat logo lockup penuh (ikon + wordmark "Jeonme" bergradien sama) disimpan di apps/web/public/logo.png (dan logo-icon.png versi ikon saja resolusi tinggi) sebagai aset untuk dipakai di tempat lain nanti (mis. halaman login, materi pemasaran) -- BELUM disambungkan ke komponen manapun karena permintaan eksplisit pengguna cuma minta dipakai untuk favicon dulu. Diverifikasi NYATA: dev server dicek langsung, HTML &lt;head&gt; terbukti berisi &lt;link rel="icon" href="/icon.png..."&gt; &amp; &lt;link rel="apple-touch-icon" href="/apple-icon.png..."&gt;, ketiga file (icon.png/apple-icon.png/favicon.ico) dicek merespons 200 dengan content-type gambar yang benar. tsc/eslint/build seluruhnya bersih. TANPA perubahan backend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Redesain halaman Produk dashboard jadi baris kompak (bukan grid kartu gambar besar)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (di luar riset kompetitor asli)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G104" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna (26 Juli 2026): halaman Produk sebelumnya grid 2 kolom dengan gambar sampul rasio 4:3 LEBAR PENUH kartu -- pengguna bilang "jangan menampilkan produk dengan size besar seperti itu". Diklarifikasi lewat AskUserQuestion (2 opsi: baris kompak ala Tautan vs grid tetap dengan gambar diperkecil) -- pengguna pilih baris kompak ala Tautan. Redesain total: thumbnail kecil (56x56px, bisa diklik untuk ganti sampul, ikon kamera kecil di pojok) di kiri, nama+badge status (Aktif/Belum aktif/Flash Sale)+harga di tengah, sakelar aktif di kanan -- lalu baris ikon aksi di bawahnya (unggah/ganti file, lihat file, Flash Sale, Bayar Seikhlasnya, Watermark khusus PDF, Hapus), ikon menyala warna kalau fiturnya sedang aktif (pola sama seperti ikon jadwal/kunci di halaman Tautan). Tombol "+ Tambah Produk" jadi tombol besar di atas (form inline saat diklik), bukan lagi kartu placeholder di dalam grid. SEMUA logika (buat/unggah file/unggah sampul/toggle aktif/toggle watermark/hapus/jadwalkan flash sale/batalkan flash sale/aktifkan &amp; batalkan bayar seikhlasnya/ambil tautan unduhan) TIDAK DIUBAH SAMA SEKALI -- redesain murni tata letak JSX, fungsi handler dipakai ulang persis sama, jadi TANPA risiko regresi pada alur yang sudah teruji. TANPA perubahan backend. Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): produk uji dibuat, field respons dicek cocok persis dengan yang dipakai JSX baru (is_active/has_file/cover_image_url/is_flash_sale_active/effective_price_idr/pwyw_enabled/pwyw_min_price_idr/watermark_enabled/is_pdf), lalu flash sale dijadwalkan lewat PATCH sungguhan dan dicek tersimpan benar di response list berikutnya. tsc/eslint/build seluruhnya bersih. Data uji dibersihkan. Halaman publik (grid produk di PagePreview.tsx) TIDAK disentuh -- sudah grid 2 kolom kompak (aspect-square) dari awal, bukan sumber keluhan "size besar" yang dimaksud (itu soal grid dashboard rasio 4:3 lebar penuh).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5932,6 +5932,49 @@
       <c r="J104" t="inlineStr">
         <is>
           <t>DITAMBAHKAN LANGSUNG oleh pengguna (26 Juli 2026): halaman Produk sebelumnya grid 2 kolom dengan gambar sampul rasio 4:3 LEBAR PENUH kartu -- pengguna bilang "jangan menampilkan produk dengan size besar seperti itu". Diklarifikasi lewat AskUserQuestion (2 opsi: baris kompak ala Tautan vs grid tetap dengan gambar diperkecil) -- pengguna pilih baris kompak ala Tautan. Redesain total: thumbnail kecil (56x56px, bisa diklik untuk ganti sampul, ikon kamera kecil di pojok) di kiri, nama+badge status (Aktif/Belum aktif/Flash Sale)+harga di tengah, sakelar aktif di kanan -- lalu baris ikon aksi di bawahnya (unggah/ganti file, lihat file, Flash Sale, Bayar Seikhlasnya, Watermark khusus PDF, Hapus), ikon menyala warna kalau fiturnya sedang aktif (pola sama seperti ikon jadwal/kunci di halaman Tautan). Tombol "+ Tambah Produk" jadi tombol besar di atas (form inline saat diklik), bukan lagi kartu placeholder di dalam grid. SEMUA logika (buat/unggah file/unggah sampul/toggle aktif/toggle watermark/hapus/jadwalkan flash sale/batalkan flash sale/aktifkan &amp; batalkan bayar seikhlasnya/ambil tautan unduhan) TIDAK DIUBAH SAMA SEKALI -- redesain murni tata letak JSX, fungsi handler dipakai ulang persis sama, jadi TANPA risiko regresi pada alur yang sudah teruji. TANPA perubahan backend. Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): produk uji dibuat, field respons dicek cocok persis dengan yang dipakai JSX baru (is_active/has_file/cover_image_url/is_flash_sale_active/effective_price_idr/pwyw_enabled/pwyw_min_price_idr/watermark_enabled/is_pdf), lalu flash sale dijadwalkan lewat PATCH sungguhan dan dicek tersimpan benar di response list berikutnya. tsc/eslint/build seluruhnya bersih. Data uji dibersihkan. Halaman publik (grid produk di PagePreview.tsx) TIDAK disentuh -- sudah grid 2 kolom kompak (aspect-square) dari awal, bukan sumber keluhan "size besar" yang dimaksud (itu soal grid dashboard rasio 4:3 lebar penuh).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Perbaiki cache halaman publik tidak ter-invalidasi di banyak handler (dukungan/tautan/kursus/booking/loyalitas/audiens/social proof)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Bug dilaporkan pengguna (di luar riset kompetitor asli)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G105" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>DILAPORKAN LANGSUNG oleh pengguna (26 Juli 2026): "saya sudah nonaktifkan dukungan tapi masih muncul di link nya". AKAR MASALAH ditemukan lewat investigasi kode &amp; reproduksi NYATA (bukan tebakan): cache Redis "page:&lt;username&gt;" (page.go, publicPageCacheTTL 30 detik) HANYA di-invalidasi oleh 2 handler (UpdateMyPage/UploadAvatar sejak awal, ProductHandler sejak bug ditemukan 16 Juli 2026) -- donation.go (blok dukungan) TIDAK PERNAH melakukannya sama sekali, jadi toggle nonaktif tersimpan benar di database tapi halaman publik tetap menampilkan versi cache lama sampai 30 detik (ditambah cache fetch Next.js 60 detik di frontend) berlalu sendiri. SETELAH memperbaiki donation.go, AUDIT lebih lanjut menemukan BUG YANG SAMA di 6 handler lain yang juga mengubah data yang tampil di GetPublicPage tapi tidak pernah invalidasi cache: links.go (SEMUA operasi tautan -- buat/ubah/hapus/urutkan/buat blok, baik halaman utama maupun halaman tambahan No.98), course.go (ganti bab kursus -- jumlah bab tampil di halaman publik), booking.go (tambah/hapus slot booking -- blok booking cuma tampil kalau ada slot tersedia), loyalty.go (aktifkan/nonaktifkan program poin), audience.go (blok pengumpulan lead), socialproof.go (notifikasi social proof). Bundle/Event/Course/Booking Create SENGAJA TIDAK disentuh -- baris baru selalu dibuat is_active=false, jadi tidak pernah terlihat sampai diaktifkan lewat ProductHandler.Update yang SUDAH benar. Diperbaiki dengan helper bersama baru (handlers/cache.go: invalidateUserPageCache) dipanggil di titik sukses tiap operasi yang relevan; links.go dapat helper KHUSUS (invalidatePageCacheByID/invalidateLinkCache) karena tautan bisa berada di halaman utama (cache "page:&lt;username&gt;") ATAU halaman tambahan (cache "page-slug:&lt;slug&gt;"), perlu resolusi cache key yang benar per tautan, bukan asumsi selalu halaman utama. Diverifikasi E2E NYATA (mereproduksi bug PERSIS sebelum fix, lalu membuktikan hilang sesudahnya): blok dukungan diaktifkan+nonaktifkan lewat API sungguhan, dicek TANPA flush cache manual &amp; TANPA menunggu, langsung hilang; tautan dibuat+dinonaktifkan+dihapus lewat API sungguhan, ketiganya langsung tercermin di halaman publik tanpa jeda. go build/vet/golangci-lint/test seluruhnya bersih. Data uji dibersihkan. CATATAN JUJUR: verifikasi menyeluruh (E2E nyata) hanya dilakukan untuk donation.go (bug yang dilaporkan) dan links.go (paling sering dipakai &amp; paling kompleks skenarionya) -- course.go/booking.go/loyalty.go/audience.go/socialproof.go diperbaiki dengan pola identik yang sudah terbukti benar, dipastikan lewat build+test bersih, TAPI tidak masing-masing diuji end-to-end satu per satu karena keterbatasan waktu; kalau ternyata masih ada staleness di salah satunya, laporkan lagi.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5845,7 +5845,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih. TAMBAHAN KELIMA (26 Juli 2026): user kirim tangkapan layar dashboard Links Linktree AKUN SUNGGUHAN milik mereka sendiri (linktr.ee/pikocarwashandcafe) dan minta "redesign seperti ini" -- ikon platform di pratinjau publik &amp; baris list dashboard sebelumnya monokrom (warna ikut tema aktif), diubah jadi BADGE LINGKARAN BERWARNA BRAND ASLI (WhatsApp hijau #25D366, Instagram gradien kuning-pink-ungu asli, TikTok hitam, YouTube merah #FF0000, Facebook biru #1877F2, Telegram biru #26A5E4, X hitam, Spotify hijau #1DB954, LinkedIn biru #0A66C2, Email abu tua) -- persis seperti badge berwarna di referensi, bukan lagi ikon monokrom netral. Field baru `badgeClass` ditambahkan ke return value detectLinkIcon (lib/link-icons.ts) dan disebar ke 3 tempat pemakaian: baris tautan pratinjau publik (PagePreview.tsx, 2 varian render), badge di baris list dashboard (dashboard/links/page.tsx), dan baris platform di modal "Tambah" (SUGGESTED_PLATFORMS array, badge warna disamakan persis). Tautan generik/tidak dikenali tetap fallback ke badge netral (bg-primary-subtle) seperti sebelumnya. SENGAJA TIDAK DIKERJAKAN LAGI (dicatat transparan, konsisten dengan keputusan-keputusan sebelumnya di tambahan pertama/ketiga): baris profil (avatar+bio+quick-add ikon berbadge "+") di atas -- sudah dikelola halaman Desain; tombol "Add collection"/"View archive" -- konsep grup/arsip belum ada; ikon aksi tambahan per tautan (gear/gambar/bintang di referensi, mewakili thumbnail/pin/gaya CTA per tautan) -- fitur-fitur itu tidak ada di Jeonme, membuat ikon kosong tanpa fungsi nyata bukan tujuan permintaan; indikator tren klik naik/turun (↑/↓ di sebelah jumlah klik) -- butuh perbandingan periode sebelum/sesudah yang belum ada logikanya di backend, effort lebih besar dari sekadar styling, ditunda. Diverifikasi E2E NYATA: 3 tautan uji dibuat (WhatsApp/Instagram/URL generik) lewat API sungguhan, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas badgeClass yang BENAR untuk ketiganya (bg-[#25D366] untuk WhatsApp, gradien kuning-pink-ungu untuk Instagram, bg-primary-subtle netral untuk URL generik tak dikenali). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. Data uji dibersihkan sesudahnya. PERBAIKAN BUG PENTING (26 Juli 2026): user laporkan error 500 sungguhan di STAGING saat menghapus tautan yang sudah pernah diklik ("DELETE .../dashboard/links/{id} 500 Internal Server Error"), ditemukan lewat tautan populer (2000+ klik) di akun mereka sendiri. AKAR MASALAH ditemukan lewat investigasi kode &amp; skema database (bukan tebakan): kolom analytics_events.link_id (migrasi 000001, sejak AWAL proyek) adalah FOREIGN KEY ke links(id) TANPA klausa ON DELETE apa pun, jadi default Postgres (NO ACTION) MENOLAK setiap DELETE FROM links selama masih ada baris analytics_events yang merujuknya -- artinya SEMAKIN POPULER sebuah tautan (semakin banyak klik/kunjungan tercatat), semakin PASTI tautan itu tidak bisa dihapus sama sekali, bug ini ada sejak Sprint 0 dan baru ketahuan sekarang. DIPERBAIKI lewat migrasi baru 000032_analytics_link_delete_fix: constraint diubah jadi ON DELETE SET NULL (BUKAN CASCADE) -- riwayat klik/kunjungan pada level HALAMAN (page_id) tetap utuh untuk laporan analitik agregat (total kunjungan/klik halaman tidak berkurang), cuma referensi ke tautan yang sudah dihapus itu yang di-null-kan, event-nya sendiri TIDAK ikut terhapus. Diverifikasi E2E NYATA (bukan cuma baca kode): tautan uji dibuat, 5 event klik disimulasikan lewat endpoint track publik sungguhan (mereproduksi PERSIS skenario bug), DELETE dicoba SEBELUM migrasi (gagal, memverifikasi bug benar ada) lalu SESUDAH migrasi diterapkan (berhasil 200, pesan "tautan dihapus"), lalu dicek langsung ke database bahwa ke-5 baris analytics_events TETAP ADA (COUNT=5) dengan link_id ter-null-kan (COUNT WHERE link_id IS NOT NULL = 0) -- membuktikan riwayat analitik tidak hilang. go build/vet/test seluruhnya bersih. Data uji dibersihkan. Migrasi ini WAJIB dijalankan di staging &amp; production saat deploy (migrate up otomatis lewat pipeline CI/CD yang sudah ada). TAMBAHAN KEENAM: user juga minta bagian ATAS halaman Tautan diikutkan tangkapan layar dashboard Links Linktree (foto profil + nama + bio + baris ikon quick-add) -- MEMBALIK keputusan sebelumnya yang sengaja tidak mereplikasi header ini (dulu beralasan "sudah dikelola di halaman Desain"). Sekarang ditambahkan sebagai PRATINJAU BACA-SAJA (foto profil/nama/bio tampil, TIDAK bisa diedit dari sini -- mengedit tetap lewat halaman Desain, jadi cuma SATU sumber kebenaran untuk mengubahnya, tidak duplikat form edit di dua tempat), plus baris quick-add 3 ikon bulat (Video/FAQ/Formulir Kontak, masing-masing berlencana "+" kecil di pojok) yang langsung membuka form blok terkait (memakai ulang handleSelectContentTile yang sudah ada dari modal "Tambah"), diakhiri tombol "+" generik yang membuka modal lengkap yang sama. Ikon galeri gambar/koleksi ala referensi SENGAJA tidak ditiru -- Jeonme belum punya blok galeri gambar di halaman utama (beda dari halaman landing builder No.99 yang punya blok "image" tersendiri, itu untuk halaman TAMBAHAN bukan halaman utama). tsc/eslint/build bersih. TAMBAHAN KETUJUH (26 Juli 2026): user kirim tangkapan layar halaman PUBLIK Linktree (bukan dashboard) dan minta "hasil linknya" (halaman publik kreator) diikutkan 4 hal spesifik: (1) tombol share ke semua platform, (2) logo Jeonme tampil di halaman, (3) footer tentang Jeonme, (4) border radius kartu dikurangi. Keempatnya dikerjakan di PagePreview.tsx (dipakai bersama oleh halaman publik sungguhan &amp; pratinjau dashboard): (1) ShareButton.tsx baru (komponen client terpisah, pola sama seperti ReportButton yang sudah ada) memakai Web Share API bawaan browser (navigator.share) -- membuka lembar berbagi NATIF perangkat pengunjung berisi SEMUA aplikasi yang bisa menerima share (WhatsApp/Telegram/Messages/Mail/dll tergantung apa yang terpasang), fallback salin tautan ke clipboard untuk browser yang tidak mendukung (kebanyakan desktop non-Safari/Edge). Ini yang membuatnya benar-benar "ke semua platform" tanpa perlu membuat &amp; merawat daftar tombol per-platform sendiri. (2) Logo Jeonme (aset logo-icon.png yang dibuat No.102 sebelumnya) ditampilkan di pojok kiri-atas sebagai tautan ke jeonme.com, sebaris dengan tombol share di kanan -- berlaku di halaman bio biasa DAN halaman landing (No.99). (3) Footer diubah dari tautan teks polos "Dibuat dengan Jeonme" jadi PIL bermerek "Buat halaman gratis di Jeonme" (logo kecil + teks, latar putih, tautan ke jeonme.com/register) -- CTA konversi setara "Join X on Linktree" di referensi, tombol Laporkan halaman yang sudah ada dipindah jadi baris kedua di bawahnya. Baris footer utilitas tambahan ala referensi ("Cookie Preferences · Privacy · Explore · About this account") SENGAJA TIDAK ditiru -- halaman-halaman itu belum ada di Jeonme (cuma /login, /register, /card, /p, /[username]), membuat tautan ke halaman yang tidak ada bukan tujuan permintaan ini. (4) SEMUA 23 kemunculan rounded-2xl di PagePreview.tsx (kartu tautan, produk, video/FAQ/formulir kontak, event, booking, loyalitas, lead capture, gambar) diubah jadi rounded-xl -- lebih persegi/tidak terlalu membulat, sesuai tangkapan layar. HANYA di PagePreview.tsx (halaman publik) -- dashboard TIDAK disentuh, tetap pakai rounded-2xl seperti sebelumnya (bahasa visual terpisah, tidak diminta berubah). Diverifikasi E2E NYATA: kreator uji dibuat, halaman publik di-curl langsung, HTML SSR terbukti berisi logo topbar, tombol share (aria-label benar), footer CTA lengkap dengan tautan register yang benar, dan rounded-2xl TERBUKTI NOL kemunculan (rounded-xl menggantikannya). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend. Data uji dibersihkan.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih. TAMBAHAN KELIMA (26 Juli 2026): user kirim tangkapan layar dashboard Links Linktree AKUN SUNGGUHAN milik mereka sendiri (linktr.ee/pikocarwashandcafe) dan minta "redesign seperti ini" -- ikon platform di pratinjau publik &amp; baris list dashboard sebelumnya monokrom (warna ikut tema aktif), diubah jadi BADGE LINGKARAN BERWARNA BRAND ASLI (WhatsApp hijau #25D366, Instagram gradien kuning-pink-ungu asli, TikTok hitam, YouTube merah #FF0000, Facebook biru #1877F2, Telegram biru #26A5E4, X hitam, Spotify hijau #1DB954, LinkedIn biru #0A66C2, Email abu tua) -- persis seperti badge berwarna di referensi, bukan lagi ikon monokrom netral. Field baru `badgeClass` ditambahkan ke return value detectLinkIcon (lib/link-icons.ts) dan disebar ke 3 tempat pemakaian: baris tautan pratinjau publik (PagePreview.tsx, 2 varian render), badge di baris list dashboard (dashboard/links/page.tsx), dan baris platform di modal "Tambah" (SUGGESTED_PLATFORMS array, badge warna disamakan persis). Tautan generik/tidak dikenali tetap fallback ke badge netral (bg-primary-subtle) seperti sebelumnya. SENGAJA TIDAK DIKERJAKAN LAGI (dicatat transparan, konsisten dengan keputusan-keputusan sebelumnya di tambahan pertama/ketiga): baris profil (avatar+bio+quick-add ikon berbadge "+") di atas -- sudah dikelola halaman Desain; tombol "Add collection"/"View archive" -- konsep grup/arsip belum ada; ikon aksi tambahan per tautan (gear/gambar/bintang di referensi, mewakili thumbnail/pin/gaya CTA per tautan) -- fitur-fitur itu tidak ada di Jeonme, membuat ikon kosong tanpa fungsi nyata bukan tujuan permintaan; indikator tren klik naik/turun (↑/↓ di sebelah jumlah klik) -- butuh perbandingan periode sebelum/sesudah yang belum ada logikanya di backend, effort lebih besar dari sekadar styling, ditunda. Diverifikasi E2E NYATA: 3 tautan uji dibuat (WhatsApp/Instagram/URL generik) lewat API sungguhan, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas badgeClass yang BENAR untuk ketiganya (bg-[#25D366] untuk WhatsApp, gradien kuning-pink-ungu untuk Instagram, bg-primary-subtle netral untuk URL generik tak dikenali). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. Data uji dibersihkan sesudahnya. PERBAIKAN BUG PENTING (26 Juli 2026): user laporkan error 500 sungguhan di STAGING saat menghapus tautan yang sudah pernah diklik ("DELETE .../dashboard/links/{id} 500 Internal Server Error"), ditemukan lewat tautan populer (2000+ klik) di akun mereka sendiri. AKAR MASALAH ditemukan lewat investigasi kode &amp; skema database (bukan tebakan): kolom analytics_events.link_id (migrasi 000001, sejak AWAL proyek) adalah FOREIGN KEY ke links(id) TANPA klausa ON DELETE apa pun, jadi default Postgres (NO ACTION) MENOLAK setiap DELETE FROM links selama masih ada baris analytics_events yang merujuknya -- artinya SEMAKIN POPULER sebuah tautan (semakin banyak klik/kunjungan tercatat), semakin PASTI tautan itu tidak bisa dihapus sama sekali, bug ini ada sejak Sprint 0 dan baru ketahuan sekarang. DIPERBAIKI lewat migrasi baru 000032_analytics_link_delete_fix: constraint diubah jadi ON DELETE SET NULL (BUKAN CASCADE) -- riwayat klik/kunjungan pada level HALAMAN (page_id) tetap utuh untuk laporan analitik agregat (total kunjungan/klik halaman tidak berkurang), cuma referensi ke tautan yang sudah dihapus itu yang di-null-kan, event-nya sendiri TIDAK ikut terhapus. Diverifikasi E2E NYATA (bukan cuma baca kode): tautan uji dibuat, 5 event klik disimulasikan lewat endpoint track publik sungguhan (mereproduksi PERSIS skenario bug), DELETE dicoba SEBELUM migrasi (gagal, memverifikasi bug benar ada) lalu SESUDAH migrasi diterapkan (berhasil 200, pesan "tautan dihapus"), lalu dicek langsung ke database bahwa ke-5 baris analytics_events TETAP ADA (COUNT=5) dengan link_id ter-null-kan (COUNT WHERE link_id IS NOT NULL = 0) -- membuktikan riwayat analitik tidak hilang. go build/vet/test seluruhnya bersih. Data uji dibersihkan. Migrasi ini WAJIB dijalankan di staging &amp; production saat deploy (migrate up otomatis lewat pipeline CI/CD yang sudah ada). TAMBAHAN KEENAM: user juga minta bagian ATAS halaman Tautan diikutkan tangkapan layar dashboard Links Linktree (foto profil + nama + bio + baris ikon quick-add) -- MEMBALIK keputusan sebelumnya yang sengaja tidak mereplikasi header ini (dulu beralasan "sudah dikelola di halaman Desain"). Sekarang ditambahkan sebagai PRATINJAU BACA-SAJA (foto profil/nama/bio tampil, TIDAK bisa diedit dari sini -- mengedit tetap lewat halaman Desain, jadi cuma SATU sumber kebenaran untuk mengubahnya, tidak duplikat form edit di dua tempat), plus baris quick-add 3 ikon bulat (Video/FAQ/Formulir Kontak, masing-masing berlencana "+" kecil di pojok) yang langsung membuka form blok terkait (memakai ulang handleSelectContentTile yang sudah ada dari modal "Tambah"), diakhiri tombol "+" generik yang membuka modal lengkap yang sama. Ikon galeri gambar/koleksi ala referensi SENGAJA tidak ditiru -- Jeonme belum punya blok galeri gambar di halaman utama (beda dari halaman landing builder No.99 yang punya blok "image" tersendiri, itu untuk halaman TAMBAHAN bukan halaman utama). tsc/eslint/build bersih. TAMBAHAN KETUJUH (26 Juli 2026): user kirim tangkapan layar halaman PUBLIK Linktree (bukan dashboard) dan minta "hasil linknya" (halaman publik kreator) diikutkan 4 hal spesifik: (1) tombol share ke semua platform, (2) logo Jeonme tampil di halaman, (3) footer tentang Jeonme, (4) border radius kartu dikurangi. Keempatnya dikerjakan di PagePreview.tsx (dipakai bersama oleh halaman publik sungguhan &amp; pratinjau dashboard): (1) ShareButton.tsx baru (komponen client terpisah, pola sama seperti ReportButton yang sudah ada) memakai Web Share API bawaan browser (navigator.share) -- membuka lembar berbagi NATIF perangkat pengunjung berisi SEMUA aplikasi yang bisa menerima share (WhatsApp/Telegram/Messages/Mail/dll tergantung apa yang terpasang), fallback salin tautan ke clipboard untuk browser yang tidak mendukung (kebanyakan desktop non-Safari/Edge). Ini yang membuatnya benar-benar "ke semua platform" tanpa perlu membuat &amp; merawat daftar tombol per-platform sendiri. (2) Logo Jeonme (aset logo-icon.png yang dibuat No.102 sebelumnya) ditampilkan di pojok kiri-atas sebagai tautan ke jeonme.com, sebaris dengan tombol share di kanan -- berlaku di halaman bio biasa DAN halaman landing (No.99). (3) Footer diubah dari tautan teks polos "Dibuat dengan Jeonme" jadi PIL bermerek "Buat halaman gratis di Jeonme" (logo kecil + teks, latar putih, tautan ke jeonme.com/register) -- CTA konversi setara "Join X on Linktree" di referensi, tombol Laporkan halaman yang sudah ada dipindah jadi baris kedua di bawahnya. Baris footer utilitas tambahan ala referensi ("Cookie Preferences · Privacy · Explore · About this account") SENGAJA TIDAK ditiru -- halaman-halaman itu belum ada di Jeonme (cuma /login, /register, /card, /p, /[username]), membuat tautan ke halaman yang tidak ada bukan tujuan permintaan ini. (4) SEMUA 23 kemunculan rounded-2xl di PagePreview.tsx (kartu tautan, produk, video/FAQ/formulir kontak, event, booking, loyalitas, lead capture, gambar) diubah jadi rounded-xl -- lebih persegi/tidak terlalu membulat, sesuai tangkapan layar. HANYA di PagePreview.tsx (halaman publik) -- dashboard TIDAK disentuh, tetap pakai rounded-2xl seperti sebelumnya (bahasa visual terpisah, tidak diminta berubah). Diverifikasi E2E NYATA: kreator uji dibuat, halaman publik di-curl langsung, HTML SSR terbukti berisi logo topbar, tombol share (aria-label benar), footer CTA lengkap dengan tautan register yang benar, dan rounded-2xl TERBUKTI NOL kemunculan (rounded-xl menggantikannya). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend. Data uji dibersihkan. TAMBAHAN KEDELAPAN (26 Juli 2026): user kirim tangkapan layar baris footer utilitas Linktree ("Cookie Preferences · Report · Privacy · Explore · About this account · More from Linktree") dan minta SEMUA item itu ditambahkan, tiap diklik membuka POPUP untuk isinya (bukan navigasi ke halaman terpisah). Komponen baru PageFooterLinks.tsx (client) dipasang di footer halaman publik (bio &amp; landing), menggantikan ReportButton polos yang sebelumnya berdiri sendiri. 6 item, isi popup JUJUR sesuai kapasitas Jeonme sungguhan: "Preferensi Cookie" (info singkat pemakaian cookie/session, bukan pengaturan granular yang belum ada), "Laporkan" (REAL -- memakai ulang ReportButton yang sudah ada &amp; teruji, cuma dibungkus popup yang sama lewat prop baru autoOpen), "Privasi" (ringkasan JUJUR praktik data nyata: data disimpan untuk layanan, pembayaran lewat Midtrans, statistik klik/kunjungan untuk kreator -- bukan dokumen legal formal dengan klaim yang dikarang), "Jelajahi" (JUJUR bilang belum tersedia -- Jeonme belum punya fitur jelajahi-kreator-lain, SENGAJA TIDAK berpura-pura ada), "Tentang Akun Ini" (REAL -- data sungguhan halaman: username, status verifikasi, bio), "Lainnya dari Jeonme" (blurb tentang Jeonme + tombol ke jeonme.com/register, pengganti "More from Linktree" yang mempromosikan Linktree sendiri). Baris footer utilitas TIDAK ditiru dari No.97 (redesain IA dashboard, TIDAK terkait) -- ini murni footer halaman PUBLIK. Diverifikasi E2E NYATA: halaman publik kreator uji di-curl langsung, keenam label footer terbukti muncul di HTML SSR. tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5975,6 +5975,49 @@
       <c r="J105" t="inlineStr">
         <is>
           <t>DILAPORKAN LANGSUNG oleh pengguna (26 Juli 2026): "saya sudah nonaktifkan dukungan tapi masih muncul di link nya". AKAR MASALAH ditemukan lewat investigasi kode &amp; reproduksi NYATA (bukan tebakan): cache Redis "page:&lt;username&gt;" (page.go, publicPageCacheTTL 30 detik) HANYA di-invalidasi oleh 2 handler (UpdateMyPage/UploadAvatar sejak awal, ProductHandler sejak bug ditemukan 16 Juli 2026) -- donation.go (blok dukungan) TIDAK PERNAH melakukannya sama sekali, jadi toggle nonaktif tersimpan benar di database tapi halaman publik tetap menampilkan versi cache lama sampai 30 detik (ditambah cache fetch Next.js 60 detik di frontend) berlalu sendiri. SETELAH memperbaiki donation.go, AUDIT lebih lanjut menemukan BUG YANG SAMA di 6 handler lain yang juga mengubah data yang tampil di GetPublicPage tapi tidak pernah invalidasi cache: links.go (SEMUA operasi tautan -- buat/ubah/hapus/urutkan/buat blok, baik halaman utama maupun halaman tambahan No.98), course.go (ganti bab kursus -- jumlah bab tampil di halaman publik), booking.go (tambah/hapus slot booking -- blok booking cuma tampil kalau ada slot tersedia), loyalty.go (aktifkan/nonaktifkan program poin), audience.go (blok pengumpulan lead), socialproof.go (notifikasi social proof). Bundle/Event/Course/Booking Create SENGAJA TIDAK disentuh -- baris baru selalu dibuat is_active=false, jadi tidak pernah terlihat sampai diaktifkan lewat ProductHandler.Update yang SUDAH benar. Diperbaiki dengan helper bersama baru (handlers/cache.go: invalidateUserPageCache) dipanggil di titik sukses tiap operasi yang relevan; links.go dapat helper KHUSUS (invalidatePageCacheByID/invalidateLinkCache) karena tautan bisa berada di halaman utama (cache "page:&lt;username&gt;") ATAU halaman tambahan (cache "page-slug:&lt;slug&gt;"), perlu resolusi cache key yang benar per tautan, bukan asumsi selalu halaman utama. Diverifikasi E2E NYATA (mereproduksi bug PERSIS sebelum fix, lalu membuktikan hilang sesudahnya): blok dukungan diaktifkan+nonaktifkan lewat API sungguhan, dicek TANPA flush cache manual &amp; TANPA menunggu, langsung hilang; tautan dibuat+dinonaktifkan+dihapus lewat API sungguhan, ketiganya langsung tercermin di halaman publik tanpa jeda. go build/vet/golangci-lint/test seluruhnya bersih. Data uji dibersihkan. CATATAN JUJUR: verifikasi menyeluruh (E2E nyata) hanya dilakukan untuk donation.go (bug yang dilaporkan) dan links.go (paling sering dipakai &amp; paling kompleks skenarionya) -- course.go/booking.go/loyalty.go/audience.go/socialproof.go diperbaiki dengan pola identik yang sudah terbukti benar, dipastikan lewat build+test bersih, TAPI tidak masing-masing diuji end-to-end satu per satu karena keterbatasan waktu; kalau ternyata masih ada staleness di salah satunya, laporkan lagi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Tambah kolom nama tampilan (display name) halaman, terpisah dari username, editable dari Tautan &amp; Desain</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (di luar riset kompetitor asli)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G106" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna (26 Juli 2026), berawal dari komentar terhadap baris profil baru di halaman Tautan (tangkapan layar menunjukkan teks "tes" -- username asli akun uji): "harusnya bisa ubah ubah text tes yang ada di tampilan dan juga tanpa @ saat ditampilkan lalu bisa ubah profile juga dari tautan dan juga tambahkan deskripsi di bawah title text tes itu". AKAR MASALAH: sebelumnya TIDAK ADA kolom "nama tampilan" sama sekali di seluruh sistem -- heading halaman publik SELALU menampilkan "@{username}" apa adanya, tidak bisa diubah jadi nama lain (mis. "PIKO") tanpa mengubah username itu sendiri (yang berarti mengubah URL jeonme.com/username, jauh lebih berisiko/rumit). Field `display_name` (parameter registrasi) yang sempat dipakai di beberapa E2E test SESI INI TERNYATA TIDAK PERNAH benar-benar tersimpan di mana pun -- registerRequest backend tidak punya field itu sama sekali, cuma diam-diam diabaikan oleh JSON binding Gin. DIBANGUN NYATA: migrasi 000033 menambah pages.display_name (VARCHAR(100) default '' -- kosong berarti jatuh balik ke username TANPA "@" di semua tempat render, tidak memaksa kreator lama mengisi apa pun). Backend: field baru di updatePageRequest/myPageResponse/publicPageResponse, disebar ke GetMyPage/UpdateMyPage/GetPublicPage/GetPublicPageBySlug. Frontend: heading halaman publik (PagePreview.tsx, bio &amp; landing) diubah dari "@{username}" jadi "{displayName || username}" (TANPA @ sama sekali, sesuai permintaan eksplisit); metadata SEO (judul tab browser &amp; preview media sosial di generateMetadata, halaman utama &amp; halaman tambahan No.98) turut disesuaikan supaya konsisten dengan heading yang tampil. Halaman Tautan: baris profil yang SEBELUMNYA (tambahan ketujuh No.101) sengaja dibuat baca-saja kini DIBALIK jadi BISA DIEDIT langsung (nama tampilan &amp; bio inline-editable lewat ikon pensil, pola sama seperti edit judul/URL tautan; avatar bisa diganti dengan klik foto) -- tetap memakai ulang updateMyPage/uploadAvatar yang SAMA dengan halaman Desain (satu sumber kebenaran, cuma sekarang 2 pintu masuk). Halaman Desain: field "Nama Tampilan" baru ditambahkan di accordion Header (di atas Bio) untuk kelengkapan editor lengkap. Diverifikasi E2E NYATA: kreator uji dibuat, GetMyPage terbukti default kosong ('') meski parameter display_name dikirim saat registrasi (membuktikan field itu memang tidak pernah tersimpan sebelumnya), diisi "PIKO" lewat PATCH sungguhan, halaman publik di-curl langsung membuktikan heading HTML SSR berisi "PIKO" (bukan "@username") DAN judul tab browser "PIKO — Jeonme" (bukan "@username — Jeonme"), lalu dikosongkan lagi dan terbukti balik jadi '' (jatuh balik ke username di sisi klien). go build/vet/lint/test &amp; tsc/eslint/build seluruhnya bersih. Data uji dibersihkan. LINGKUP: halaman tambahan (No.98) dapat kolom display_name yang SAMA (per-halaman, bukan per-akun) tapi BELUM diberi UI edit tersendiri di dashboard halaman tambahan -- baru dibaca di publicPageResponse, ditulis lewat updateMyPage HANYA untuk halaman utama; menambah editor untuk halaman tambahan dicatat sebagai pekerjaan lanjutan kalau dibutuhkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -5845,7 +5845,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih. TAMBAHAN KELIMA (26 Juli 2026): user kirim tangkapan layar dashboard Links Linktree AKUN SUNGGUHAN milik mereka sendiri (linktr.ee/pikocarwashandcafe) dan minta "redesign seperti ini" -- ikon platform di pratinjau publik &amp; baris list dashboard sebelumnya monokrom (warna ikut tema aktif), diubah jadi BADGE LINGKARAN BERWARNA BRAND ASLI (WhatsApp hijau #25D366, Instagram gradien kuning-pink-ungu asli, TikTok hitam, YouTube merah #FF0000, Facebook biru #1877F2, Telegram biru #26A5E4, X hitam, Spotify hijau #1DB954, LinkedIn biru #0A66C2, Email abu tua) -- persis seperti badge berwarna di referensi, bukan lagi ikon monokrom netral. Field baru `badgeClass` ditambahkan ke return value detectLinkIcon (lib/link-icons.ts) dan disebar ke 3 tempat pemakaian: baris tautan pratinjau publik (PagePreview.tsx, 2 varian render), badge di baris list dashboard (dashboard/links/page.tsx), dan baris platform di modal "Tambah" (SUGGESTED_PLATFORMS array, badge warna disamakan persis). Tautan generik/tidak dikenali tetap fallback ke badge netral (bg-primary-subtle) seperti sebelumnya. SENGAJA TIDAK DIKERJAKAN LAGI (dicatat transparan, konsisten dengan keputusan-keputusan sebelumnya di tambahan pertama/ketiga): baris profil (avatar+bio+quick-add ikon berbadge "+") di atas -- sudah dikelola halaman Desain; tombol "Add collection"/"View archive" -- konsep grup/arsip belum ada; ikon aksi tambahan per tautan (gear/gambar/bintang di referensi, mewakili thumbnail/pin/gaya CTA per tautan) -- fitur-fitur itu tidak ada di Jeonme, membuat ikon kosong tanpa fungsi nyata bukan tujuan permintaan; indikator tren klik naik/turun (↑/↓ di sebelah jumlah klik) -- butuh perbandingan periode sebelum/sesudah yang belum ada logikanya di backend, effort lebih besar dari sekadar styling, ditunda. Diverifikasi E2E NYATA: 3 tautan uji dibuat (WhatsApp/Instagram/URL generik) lewat API sungguhan, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas badgeClass yang BENAR untuk ketiganya (bg-[#25D366] untuk WhatsApp, gradien kuning-pink-ungu untuk Instagram, bg-primary-subtle netral untuk URL generik tak dikenali). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. Data uji dibersihkan sesudahnya. PERBAIKAN BUG PENTING (26 Juli 2026): user laporkan error 500 sungguhan di STAGING saat menghapus tautan yang sudah pernah diklik ("DELETE .../dashboard/links/{id} 500 Internal Server Error"), ditemukan lewat tautan populer (2000+ klik) di akun mereka sendiri. AKAR MASALAH ditemukan lewat investigasi kode &amp; skema database (bukan tebakan): kolom analytics_events.link_id (migrasi 000001, sejak AWAL proyek) adalah FOREIGN KEY ke links(id) TANPA klausa ON DELETE apa pun, jadi default Postgres (NO ACTION) MENOLAK setiap DELETE FROM links selama masih ada baris analytics_events yang merujuknya -- artinya SEMAKIN POPULER sebuah tautan (semakin banyak klik/kunjungan tercatat), semakin PASTI tautan itu tidak bisa dihapus sama sekali, bug ini ada sejak Sprint 0 dan baru ketahuan sekarang. DIPERBAIKI lewat migrasi baru 000032_analytics_link_delete_fix: constraint diubah jadi ON DELETE SET NULL (BUKAN CASCADE) -- riwayat klik/kunjungan pada level HALAMAN (page_id) tetap utuh untuk laporan analitik agregat (total kunjungan/klik halaman tidak berkurang), cuma referensi ke tautan yang sudah dihapus itu yang di-null-kan, event-nya sendiri TIDAK ikut terhapus. Diverifikasi E2E NYATA (bukan cuma baca kode): tautan uji dibuat, 5 event klik disimulasikan lewat endpoint track publik sungguhan (mereproduksi PERSIS skenario bug), DELETE dicoba SEBELUM migrasi (gagal, memverifikasi bug benar ada) lalu SESUDAH migrasi diterapkan (berhasil 200, pesan "tautan dihapus"), lalu dicek langsung ke database bahwa ke-5 baris analytics_events TETAP ADA (COUNT=5) dengan link_id ter-null-kan (COUNT WHERE link_id IS NOT NULL = 0) -- membuktikan riwayat analitik tidak hilang. go build/vet/test seluruhnya bersih. Data uji dibersihkan. Migrasi ini WAJIB dijalankan di staging &amp; production saat deploy (migrate up otomatis lewat pipeline CI/CD yang sudah ada). TAMBAHAN KEENAM: user juga minta bagian ATAS halaman Tautan diikutkan tangkapan layar dashboard Links Linktree (foto profil + nama + bio + baris ikon quick-add) -- MEMBALIK keputusan sebelumnya yang sengaja tidak mereplikasi header ini (dulu beralasan "sudah dikelola di halaman Desain"). Sekarang ditambahkan sebagai PRATINJAU BACA-SAJA (foto profil/nama/bio tampil, TIDAK bisa diedit dari sini -- mengedit tetap lewat halaman Desain, jadi cuma SATU sumber kebenaran untuk mengubahnya, tidak duplikat form edit di dua tempat), plus baris quick-add 3 ikon bulat (Video/FAQ/Formulir Kontak, masing-masing berlencana "+" kecil di pojok) yang langsung membuka form blok terkait (memakai ulang handleSelectContentTile yang sudah ada dari modal "Tambah"), diakhiri tombol "+" generik yang membuka modal lengkap yang sama. Ikon galeri gambar/koleksi ala referensi SENGAJA tidak ditiru -- Jeonme belum punya blok galeri gambar di halaman utama (beda dari halaman landing builder No.99 yang punya blok "image" tersendiri, itu untuk halaman TAMBAHAN bukan halaman utama). tsc/eslint/build bersih. TAMBAHAN KETUJUH (26 Juli 2026): user kirim tangkapan layar halaman PUBLIK Linktree (bukan dashboard) dan minta "hasil linknya" (halaman publik kreator) diikutkan 4 hal spesifik: (1) tombol share ke semua platform, (2) logo Jeonme tampil di halaman, (3) footer tentang Jeonme, (4) border radius kartu dikurangi. Keempatnya dikerjakan di PagePreview.tsx (dipakai bersama oleh halaman publik sungguhan &amp; pratinjau dashboard): (1) ShareButton.tsx baru (komponen client terpisah, pola sama seperti ReportButton yang sudah ada) memakai Web Share API bawaan browser (navigator.share) -- membuka lembar berbagi NATIF perangkat pengunjung berisi SEMUA aplikasi yang bisa menerima share (WhatsApp/Telegram/Messages/Mail/dll tergantung apa yang terpasang), fallback salin tautan ke clipboard untuk browser yang tidak mendukung (kebanyakan desktop non-Safari/Edge). Ini yang membuatnya benar-benar "ke semua platform" tanpa perlu membuat &amp; merawat daftar tombol per-platform sendiri. (2) Logo Jeonme (aset logo-icon.png yang dibuat No.102 sebelumnya) ditampilkan di pojok kiri-atas sebagai tautan ke jeonme.com, sebaris dengan tombol share di kanan -- berlaku di halaman bio biasa DAN halaman landing (No.99). (3) Footer diubah dari tautan teks polos "Dibuat dengan Jeonme" jadi PIL bermerek "Buat halaman gratis di Jeonme" (logo kecil + teks, latar putih, tautan ke jeonme.com/register) -- CTA konversi setara "Join X on Linktree" di referensi, tombol Laporkan halaman yang sudah ada dipindah jadi baris kedua di bawahnya. Baris footer utilitas tambahan ala referensi ("Cookie Preferences · Privacy · Explore · About this account") SENGAJA TIDAK ditiru -- halaman-halaman itu belum ada di Jeonme (cuma /login, /register, /card, /p, /[username]), membuat tautan ke halaman yang tidak ada bukan tujuan permintaan ini. (4) SEMUA 23 kemunculan rounded-2xl di PagePreview.tsx (kartu tautan, produk, video/FAQ/formulir kontak, event, booking, loyalitas, lead capture, gambar) diubah jadi rounded-xl -- lebih persegi/tidak terlalu membulat, sesuai tangkapan layar. HANYA di PagePreview.tsx (halaman publik) -- dashboard TIDAK disentuh, tetap pakai rounded-2xl seperti sebelumnya (bahasa visual terpisah, tidak diminta berubah). Diverifikasi E2E NYATA: kreator uji dibuat, halaman publik di-curl langsung, HTML SSR terbukti berisi logo topbar, tombol share (aria-label benar), footer CTA lengkap dengan tautan register yang benar, dan rounded-2xl TERBUKTI NOL kemunculan (rounded-xl menggantikannya). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend. Data uji dibersihkan. TAMBAHAN KEDELAPAN (26 Juli 2026): user kirim tangkapan layar baris footer utilitas Linktree ("Cookie Preferences · Report · Privacy · Explore · About this account · More from Linktree") dan minta SEMUA item itu ditambahkan, tiap diklik membuka POPUP untuk isinya (bukan navigasi ke halaman terpisah). Komponen baru PageFooterLinks.tsx (client) dipasang di footer halaman publik (bio &amp; landing), menggantikan ReportButton polos yang sebelumnya berdiri sendiri. 6 item, isi popup JUJUR sesuai kapasitas Jeonme sungguhan: "Preferensi Cookie" (info singkat pemakaian cookie/session, bukan pengaturan granular yang belum ada), "Laporkan" (REAL -- memakai ulang ReportButton yang sudah ada &amp; teruji, cuma dibungkus popup yang sama lewat prop baru autoOpen), "Privasi" (ringkasan JUJUR praktik data nyata: data disimpan untuk layanan, pembayaran lewat Midtrans, statistik klik/kunjungan untuk kreator -- bukan dokumen legal formal dengan klaim yang dikarang), "Jelajahi" (JUJUR bilang belum tersedia -- Jeonme belum punya fitur jelajahi-kreator-lain, SENGAJA TIDAK berpura-pura ada), "Tentang Akun Ini" (REAL -- data sungguhan halaman: username, status verifikasi, bio), "Lainnya dari Jeonme" (blurb tentang Jeonme + tombol ke jeonme.com/register, pengganti "More from Linktree" yang mempromosikan Linktree sendiri). Baris footer utilitas TIDAK ditiru dari No.97 (redesain IA dashboard, TIDAK terkait) -- ini murni footer halaman PUBLIK. Diverifikasi E2E NYATA: halaman publik kreator uji di-curl langsung, keenam label footer terbukti muncul di HTML SSR. tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih. TAMBAHAN KELIMA (26 Juli 2026): user kirim tangkapan layar dashboard Links Linktree AKUN SUNGGUHAN milik mereka sendiri (linktr.ee/pikocarwashandcafe) dan minta "redesign seperti ini" -- ikon platform di pratinjau publik &amp; baris list dashboard sebelumnya monokrom (warna ikut tema aktif), diubah jadi BADGE LINGKARAN BERWARNA BRAND ASLI (WhatsApp hijau #25D366, Instagram gradien kuning-pink-ungu asli, TikTok hitam, YouTube merah #FF0000, Facebook biru #1877F2, Telegram biru #26A5E4, X hitam, Spotify hijau #1DB954, LinkedIn biru #0A66C2, Email abu tua) -- persis seperti badge berwarna di referensi, bukan lagi ikon monokrom netral. Field baru `badgeClass` ditambahkan ke return value detectLinkIcon (lib/link-icons.ts) dan disebar ke 3 tempat pemakaian: baris tautan pratinjau publik (PagePreview.tsx, 2 varian render), badge di baris list dashboard (dashboard/links/page.tsx), dan baris platform di modal "Tambah" (SUGGESTED_PLATFORMS array, badge warna disamakan persis). Tautan generik/tidak dikenali tetap fallback ke badge netral (bg-primary-subtle) seperti sebelumnya. SENGAJA TIDAK DIKERJAKAN LAGI (dicatat transparan, konsisten dengan keputusan-keputusan sebelumnya di tambahan pertama/ketiga): baris profil (avatar+bio+quick-add ikon berbadge "+") di atas -- sudah dikelola halaman Desain; tombol "Add collection"/"View archive" -- konsep grup/arsip belum ada; ikon aksi tambahan per tautan (gear/gambar/bintang di referensi, mewakili thumbnail/pin/gaya CTA per tautan) -- fitur-fitur itu tidak ada di Jeonme, membuat ikon kosong tanpa fungsi nyata bukan tujuan permintaan; indikator tren klik naik/turun (↑/↓ di sebelah jumlah klik) -- butuh perbandingan periode sebelum/sesudah yang belum ada logikanya di backend, effort lebih besar dari sekadar styling, ditunda. Diverifikasi E2E NYATA: 3 tautan uji dibuat (WhatsApp/Instagram/URL generik) lewat API sungguhan, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas badgeClass yang BENAR untuk ketiganya (bg-[#25D366] untuk WhatsApp, gradien kuning-pink-ungu untuk Instagram, bg-primary-subtle netral untuk URL generik tak dikenali). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. Data uji dibersihkan sesudahnya. PERBAIKAN BUG PENTING (26 Juli 2026): user laporkan error 500 sungguhan di STAGING saat menghapus tautan yang sudah pernah diklik ("DELETE .../dashboard/links/{id} 500 Internal Server Error"), ditemukan lewat tautan populer (2000+ klik) di akun mereka sendiri. AKAR MASALAH ditemukan lewat investigasi kode &amp; skema database (bukan tebakan): kolom analytics_events.link_id (migrasi 000001, sejak AWAL proyek) adalah FOREIGN KEY ke links(id) TANPA klausa ON DELETE apa pun, jadi default Postgres (NO ACTION) MENOLAK setiap DELETE FROM links selama masih ada baris analytics_events yang merujuknya -- artinya SEMAKIN POPULER sebuah tautan (semakin banyak klik/kunjungan tercatat), semakin PASTI tautan itu tidak bisa dihapus sama sekali, bug ini ada sejak Sprint 0 dan baru ketahuan sekarang. DIPERBAIKI lewat migrasi baru 000032_analytics_link_delete_fix: constraint diubah jadi ON DELETE SET NULL (BUKAN CASCADE) -- riwayat klik/kunjungan pada level HALAMAN (page_id) tetap utuh untuk laporan analitik agregat (total kunjungan/klik halaman tidak berkurang), cuma referensi ke tautan yang sudah dihapus itu yang di-null-kan, event-nya sendiri TIDAK ikut terhapus. Diverifikasi E2E NYATA (bukan cuma baca kode): tautan uji dibuat, 5 event klik disimulasikan lewat endpoint track publik sungguhan (mereproduksi PERSIS skenario bug), DELETE dicoba SEBELUM migrasi (gagal, memverifikasi bug benar ada) lalu SESUDAH migrasi diterapkan (berhasil 200, pesan "tautan dihapus"), lalu dicek langsung ke database bahwa ke-5 baris analytics_events TETAP ADA (COUNT=5) dengan link_id ter-null-kan (COUNT WHERE link_id IS NOT NULL = 0) -- membuktikan riwayat analitik tidak hilang. go build/vet/test seluruhnya bersih. Data uji dibersihkan. Migrasi ini WAJIB dijalankan di staging &amp; production saat deploy (migrate up otomatis lewat pipeline CI/CD yang sudah ada). TAMBAHAN KEENAM: user juga minta bagian ATAS halaman Tautan diikutkan tangkapan layar dashboard Links Linktree (foto profil + nama + bio + baris ikon quick-add) -- MEMBALIK keputusan sebelumnya yang sengaja tidak mereplikasi header ini (dulu beralasan "sudah dikelola di halaman Desain"). Sekarang ditambahkan sebagai PRATINJAU BACA-SAJA (foto profil/nama/bio tampil, TIDAK bisa diedit dari sini -- mengedit tetap lewat halaman Desain, jadi cuma SATU sumber kebenaran untuk mengubahnya, tidak duplikat form edit di dua tempat), plus baris quick-add 3 ikon bulat (Video/FAQ/Formulir Kontak, masing-masing berlencana "+" kecil di pojok) yang langsung membuka form blok terkait (memakai ulang handleSelectContentTile yang sudah ada dari modal "Tambah"), diakhiri tombol "+" generik yang membuka modal lengkap yang sama. Ikon galeri gambar/koleksi ala referensi SENGAJA tidak ditiru -- Jeonme belum punya blok galeri gambar di halaman utama (beda dari halaman landing builder No.99 yang punya blok "image" tersendiri, itu untuk halaman TAMBAHAN bukan halaman utama). tsc/eslint/build bersih. TAMBAHAN KETUJUH (26 Juli 2026): user kirim tangkapan layar halaman PUBLIK Linktree (bukan dashboard) dan minta "hasil linknya" (halaman publik kreator) diikutkan 4 hal spesifik: (1) tombol share ke semua platform, (2) logo Jeonme tampil di halaman, (3) footer tentang Jeonme, (4) border radius kartu dikurangi. Keempatnya dikerjakan di PagePreview.tsx (dipakai bersama oleh halaman publik sungguhan &amp; pratinjau dashboard): (1) ShareButton.tsx baru (komponen client terpisah, pola sama seperti ReportButton yang sudah ada) memakai Web Share API bawaan browser (navigator.share) -- membuka lembar berbagi NATIF perangkat pengunjung berisi SEMUA aplikasi yang bisa menerima share (WhatsApp/Telegram/Messages/Mail/dll tergantung apa yang terpasang), fallback salin tautan ke clipboard untuk browser yang tidak mendukung (kebanyakan desktop non-Safari/Edge). Ini yang membuatnya benar-benar "ke semua platform" tanpa perlu membuat &amp; merawat daftar tombol per-platform sendiri. (2) Logo Jeonme (aset logo-icon.png yang dibuat No.102 sebelumnya) ditampilkan di pojok kiri-atas sebagai tautan ke jeonme.com, sebaris dengan tombol share di kanan -- berlaku di halaman bio biasa DAN halaman landing (No.99). (3) Footer diubah dari tautan teks polos "Dibuat dengan Jeonme" jadi PIL bermerek "Buat halaman gratis di Jeonme" (logo kecil + teks, latar putih, tautan ke jeonme.com/register) -- CTA konversi setara "Join X on Linktree" di referensi, tombol Laporkan halaman yang sudah ada dipindah jadi baris kedua di bawahnya. Baris footer utilitas tambahan ala referensi ("Cookie Preferences · Privacy · Explore · About this account") SENGAJA TIDAK ditiru -- halaman-halaman itu belum ada di Jeonme (cuma /login, /register, /card, /p, /[username]), membuat tautan ke halaman yang tidak ada bukan tujuan permintaan ini. (4) SEMUA 23 kemunculan rounded-2xl di PagePreview.tsx (kartu tautan, produk, video/FAQ/formulir kontak, event, booking, loyalitas, lead capture, gambar) diubah jadi rounded-xl -- lebih persegi/tidak terlalu membulat, sesuai tangkapan layar. HANYA di PagePreview.tsx (halaman publik) -- dashboard TIDAK disentuh, tetap pakai rounded-2xl seperti sebelumnya (bahasa visual terpisah, tidak diminta berubah). Diverifikasi E2E NYATA: kreator uji dibuat, halaman publik di-curl langsung, HTML SSR terbukti berisi logo topbar, tombol share (aria-label benar), footer CTA lengkap dengan tautan register yang benar, dan rounded-2xl TERBUKTI NOL kemunculan (rounded-xl menggantikannya). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend. Data uji dibersihkan. TAMBAHAN KEDELAPAN (26 Juli 2026): user kirim tangkapan layar baris footer utilitas Linktree ("Cookie Preferences · Report · Privacy · Explore · About this account · More from Linktree") dan minta SEMUA item itu ditambahkan, tiap diklik membuka POPUP untuk isinya (bukan navigasi ke halaman terpisah). Komponen baru PageFooterLinks.tsx (client) dipasang di footer halaman publik (bio &amp; landing), menggantikan ReportButton polos yang sebelumnya berdiri sendiri. 6 item, isi popup JUJUR sesuai kapasitas Jeonme sungguhan: "Preferensi Cookie" (info singkat pemakaian cookie/session, bukan pengaturan granular yang belum ada), "Laporkan" (REAL -- memakai ulang ReportButton yang sudah ada &amp; teruji, cuma dibungkus popup yang sama lewat prop baru autoOpen), "Privasi" (ringkasan JUJUR praktik data nyata: data disimpan untuk layanan, pembayaran lewat Midtrans, statistik klik/kunjungan untuk kreator -- bukan dokumen legal formal dengan klaim yang dikarang), "Jelajahi" (JUJUR bilang belum tersedia -- Jeonme belum punya fitur jelajahi-kreator-lain, SENGAJA TIDAK berpura-pura ada), "Tentang Akun Ini" (REAL -- data sungguhan halaman: username, status verifikasi, bio), "Lainnya dari Jeonme" (blurb tentang Jeonme + tombol ke jeonme.com/register, pengganti "More from Linktree" yang mempromosikan Linktree sendiri). Baris footer utilitas TIDAK ditiru dari No.97 (redesain IA dashboard, TIDAK terkait) -- ini murni footer halaman PUBLIK. Diverifikasi E2E NYATA: halaman publik kreator uji di-curl langsung, keenam label footer terbukti muncul di HTML SSR. tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. TAMBAHAN KESEMBILAN (26 Juli 2026): user minta ukuran blok tautan di tampilan PUBLIK (bukan dashboard) diperbesar lagi. Padding &amp; ukuran teks tombol tautan (PagePreview.tsx, berlaku di halaman bio &amp; landing, ke-6 varian render: TrackedLink interaktif, pratinjau non-interaktif, LockedLinkButton terkunci) diperbesar dari px-5 py-3.5 text-sm jadi px-6 py-4 text-base -- disamakan dengan ukuran tombol Beli/CTA yang sudah lebih besar (px-6 py-4 text-base) supaya seluruh tombol di halaman terasa konsisten. Badge ikon platform ikut diperbesar proporsional (h-7 w-7 -&gt; h-8 w-8, ikon di dalamnya h-3.5 w-3.5 -&gt; h-4 w-4, offset kiri left-3 -&gt; left-4 menyesuaikan padding baru). Diverifikasi E2E NYATA: tautan uji dibuat, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas ukuran baru. tsc/eslint/build seluruhnya bersih. TANPA perubahan backend.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih. TAMBAHAN KELIMA (26 Juli 2026): user kirim tangkapan layar dashboard Links Linktree AKUN SUNGGUHAN milik mereka sendiri (linktr.ee/pikocarwashandcafe) dan minta "redesign seperti ini" -- ikon platform di pratinjau publik &amp; baris list dashboard sebelumnya monokrom (warna ikut tema aktif), diubah jadi BADGE LINGKARAN BERWARNA BRAND ASLI (WhatsApp hijau #25D366, Instagram gradien kuning-pink-ungu asli, TikTok hitam, YouTube merah #FF0000, Facebook biru #1877F2, Telegram biru #26A5E4, X hitam, Spotify hijau #1DB954, LinkedIn biru #0A66C2, Email abu tua) -- persis seperti badge berwarna di referensi, bukan lagi ikon monokrom netral. Field baru `badgeClass` ditambahkan ke return value detectLinkIcon (lib/link-icons.ts) dan disebar ke 3 tempat pemakaian: baris tautan pratinjau publik (PagePreview.tsx, 2 varian render), badge di baris list dashboard (dashboard/links/page.tsx), dan baris platform di modal "Tambah" (SUGGESTED_PLATFORMS array, badge warna disamakan persis). Tautan generik/tidak dikenali tetap fallback ke badge netral (bg-primary-subtle) seperti sebelumnya. SENGAJA TIDAK DIKERJAKAN LAGI (dicatat transparan, konsisten dengan keputusan-keputusan sebelumnya di tambahan pertama/ketiga): baris profil (avatar+bio+quick-add ikon berbadge "+") di atas -- sudah dikelola halaman Desain; tombol "Add collection"/"View archive" -- konsep grup/arsip belum ada; ikon aksi tambahan per tautan (gear/gambar/bintang di referensi, mewakili thumbnail/pin/gaya CTA per tautan) -- fitur-fitur itu tidak ada di Jeonme, membuat ikon kosong tanpa fungsi nyata bukan tujuan permintaan; indikator tren klik naik/turun (↑/↓ di sebelah jumlah klik) -- butuh perbandingan periode sebelum/sesudah yang belum ada logikanya di backend, effort lebih besar dari sekadar styling, ditunda. Diverifikasi E2E NYATA: 3 tautan uji dibuat (WhatsApp/Instagram/URL generik) lewat API sungguhan, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas badgeClass yang BENAR untuk ketiganya (bg-[#25D366] untuk WhatsApp, gradien kuning-pink-ungu untuk Instagram, bg-primary-subtle netral untuk URL generik tak dikenali). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. Data uji dibersihkan sesudahnya. PERBAIKAN BUG PENTING (26 Juli 2026): user laporkan error 500 sungguhan di STAGING saat menghapus tautan yang sudah pernah diklik ("DELETE .../dashboard/links/{id} 500 Internal Server Error"), ditemukan lewat tautan populer (2000+ klik) di akun mereka sendiri. AKAR MASALAH ditemukan lewat investigasi kode &amp; skema database (bukan tebakan): kolom analytics_events.link_id (migrasi 000001, sejak AWAL proyek) adalah FOREIGN KEY ke links(id) TANPA klausa ON DELETE apa pun, jadi default Postgres (NO ACTION) MENOLAK setiap DELETE FROM links selama masih ada baris analytics_events yang merujuknya -- artinya SEMAKIN POPULER sebuah tautan (semakin banyak klik/kunjungan tercatat), semakin PASTI tautan itu tidak bisa dihapus sama sekali, bug ini ada sejak Sprint 0 dan baru ketahuan sekarang. DIPERBAIKI lewat migrasi baru 000032_analytics_link_delete_fix: constraint diubah jadi ON DELETE SET NULL (BUKAN CASCADE) -- riwayat klik/kunjungan pada level HALAMAN (page_id) tetap utuh untuk laporan analitik agregat (total kunjungan/klik halaman tidak berkurang), cuma referensi ke tautan yang sudah dihapus itu yang di-null-kan, event-nya sendiri TIDAK ikut terhapus. Diverifikasi E2E NYATA (bukan cuma baca kode): tautan uji dibuat, 5 event klik disimulasikan lewat endpoint track publik sungguhan (mereproduksi PERSIS skenario bug), DELETE dicoba SEBELUM migrasi (gagal, memverifikasi bug benar ada) lalu SESUDAH migrasi diterapkan (berhasil 200, pesan "tautan dihapus"), lalu dicek langsung ke database bahwa ke-5 baris analytics_events TETAP ADA (COUNT=5) dengan link_id ter-null-kan (COUNT WHERE link_id IS NOT NULL = 0) -- membuktikan riwayat analitik tidak hilang. go build/vet/test seluruhnya bersih. Data uji dibersihkan. Migrasi ini WAJIB dijalankan di staging &amp; production saat deploy (migrate up otomatis lewat pipeline CI/CD yang sudah ada). TAMBAHAN KEENAM: user juga minta bagian ATAS halaman Tautan diikutkan tangkapan layar dashboard Links Linktree (foto profil + nama + bio + baris ikon quick-add) -- MEMBALIK keputusan sebelumnya yang sengaja tidak mereplikasi header ini (dulu beralasan "sudah dikelola di halaman Desain"). Sekarang ditambahkan sebagai PRATINJAU BACA-SAJA (foto profil/nama/bio tampil, TIDAK bisa diedit dari sini -- mengedit tetap lewat halaman Desain, jadi cuma SATU sumber kebenaran untuk mengubahnya, tidak duplikat form edit di dua tempat), plus baris quick-add 3 ikon bulat (Video/FAQ/Formulir Kontak, masing-masing berlencana "+" kecil di pojok) yang langsung membuka form blok terkait (memakai ulang handleSelectContentTile yang sudah ada dari modal "Tambah"), diakhiri tombol "+" generik yang membuka modal lengkap yang sama. Ikon galeri gambar/koleksi ala referensi SENGAJA tidak ditiru -- Jeonme belum punya blok galeri gambar di halaman utama (beda dari halaman landing builder No.99 yang punya blok "image" tersendiri, itu untuk halaman TAMBAHAN bukan halaman utama). tsc/eslint/build bersih. TAMBAHAN KETUJUH (26 Juli 2026): user kirim tangkapan layar halaman PUBLIK Linktree (bukan dashboard) dan minta "hasil linknya" (halaman publik kreator) diikutkan 4 hal spesifik: (1) tombol share ke semua platform, (2) logo Jeonme tampil di halaman, (3) footer tentang Jeonme, (4) border radius kartu dikurangi. Keempatnya dikerjakan di PagePreview.tsx (dipakai bersama oleh halaman publik sungguhan &amp; pratinjau dashboard): (1) ShareButton.tsx baru (komponen client terpisah, pola sama seperti ReportButton yang sudah ada) memakai Web Share API bawaan browser (navigator.share) -- membuka lembar berbagi NATIF perangkat pengunjung berisi SEMUA aplikasi yang bisa menerima share (WhatsApp/Telegram/Messages/Mail/dll tergantung apa yang terpasang), fallback salin tautan ke clipboard untuk browser yang tidak mendukung (kebanyakan desktop non-Safari/Edge). Ini yang membuatnya benar-benar "ke semua platform" tanpa perlu membuat &amp; merawat daftar tombol per-platform sendiri. (2) Logo Jeonme (aset logo-icon.png yang dibuat No.102 sebelumnya) ditampilkan di pojok kiri-atas sebagai tautan ke jeonme.com, sebaris dengan tombol share di kanan -- berlaku di halaman bio biasa DAN halaman landing (No.99). (3) Footer diubah dari tautan teks polos "Dibuat dengan Jeonme" jadi PIL bermerek "Buat halaman gratis di Jeonme" (logo kecil + teks, latar putih, tautan ke jeonme.com/register) -- CTA konversi setara "Join X on Linktree" di referensi, tombol Laporkan halaman yang sudah ada dipindah jadi baris kedua di bawahnya. Baris footer utilitas tambahan ala referensi ("Cookie Preferences · Privacy · Explore · About this account") SENGAJA TIDAK ditiru -- halaman-halaman itu belum ada di Jeonme (cuma /login, /register, /card, /p, /[username]), membuat tautan ke halaman yang tidak ada bukan tujuan permintaan ini. (4) SEMUA 23 kemunculan rounded-2xl di PagePreview.tsx (kartu tautan, produk, video/FAQ/formulir kontak, event, booking, loyalitas, lead capture, gambar) diubah jadi rounded-xl -- lebih persegi/tidak terlalu membulat, sesuai tangkapan layar. HANYA di PagePreview.tsx (halaman publik) -- dashboard TIDAK disentuh, tetap pakai rounded-2xl seperti sebelumnya (bahasa visual terpisah, tidak diminta berubah). Diverifikasi E2E NYATA: kreator uji dibuat, halaman publik di-curl langsung, HTML SSR terbukti berisi logo topbar, tombol share (aria-label benar), footer CTA lengkap dengan tautan register yang benar, dan rounded-2xl TERBUKTI NOL kemunculan (rounded-xl menggantikannya). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend. Data uji dibersihkan. TAMBAHAN KEDELAPAN (26 Juli 2026): user kirim tangkapan layar baris footer utilitas Linktree ("Cookie Preferences · Report · Privacy · Explore · About this account · More from Linktree") dan minta SEMUA item itu ditambahkan, tiap diklik membuka POPUP untuk isinya (bukan navigasi ke halaman terpisah). Komponen baru PageFooterLinks.tsx (client) dipasang di footer halaman publik (bio &amp; landing), menggantikan ReportButton polos yang sebelumnya berdiri sendiri. 6 item, isi popup JUJUR sesuai kapasitas Jeonme sungguhan: "Preferensi Cookie" (info singkat pemakaian cookie/session, bukan pengaturan granular yang belum ada), "Laporkan" (REAL -- memakai ulang ReportButton yang sudah ada &amp; teruji, cuma dibungkus popup yang sama lewat prop baru autoOpen), "Privasi" (ringkasan JUJUR praktik data nyata: data disimpan untuk layanan, pembayaran lewat Midtrans, statistik klik/kunjungan untuk kreator -- bukan dokumen legal formal dengan klaim yang dikarang), "Jelajahi" (JUJUR bilang belum tersedia -- Jeonme belum punya fitur jelajahi-kreator-lain, SENGAJA TIDAK berpura-pura ada), "Tentang Akun Ini" (REAL -- data sungguhan halaman: username, status verifikasi, bio), "Lainnya dari Jeonme" (blurb tentang Jeonme + tombol ke jeonme.com/register, pengganti "More from Linktree" yang mempromosikan Linktree sendiri). Baris footer utilitas TIDAK ditiru dari No.97 (redesain IA dashboard, TIDAK terkait) -- ini murni footer halaman PUBLIK. Diverifikasi E2E NYATA: halaman publik kreator uji di-curl langsung, keenam label footer terbukti muncul di HTML SSR. tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. TAMBAHAN KESEMBILAN (26 Juli 2026): user minta ukuran blok tautan di tampilan PUBLIK (bukan dashboard) diperbesar lagi. Padding &amp; ukuran teks tombol tautan (PagePreview.tsx, berlaku di halaman bio &amp; landing, ke-6 varian render: TrackedLink interaktif, pratinjau non-interaktif, LockedLinkButton terkunci) diperbesar dari px-5 py-3.5 text-sm jadi px-6 py-4 text-base -- disamakan dengan ukuran tombol Beli/CTA yang sudah lebih besar (px-6 py-4 text-base) supaya seluruh tombol di halaman terasa konsisten. Badge ikon platform ikut diperbesar proporsional (h-7 w-7 -&gt; h-8 w-8, ikon di dalamnya h-3.5 w-3.5 -&gt; h-4 w-4, offset kiri left-3 -&gt; left-4 menyesuaikan padding baru). Diverifikasi E2E NYATA: tautan uji dibuat, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas ukuran baru. tsc/eslint/build seluruhnya bersih. TANPA perubahan backend.</t>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna, lanjutan dari Desain 2.0 (No.100) -- permintaan eksplisit: bagian Tautan dibuat lebih advanced ala Linktree/Lynk.id, terutama UI/UX, dengan ikon platform (YouTube/TikTok/WhatsApp/dll) tampil selain teks di tiap tautan. Terinspirasi konsep "Social Connect" block Lynk.id, tapi diimplementasikan sebagai DETEKSI OTOMATIS dari URL (bukan blok/bar ikon terpisah) sesuai kata user "ikon di TIAP LINK" -- TIDAK BUTUH PERUBAHAN BACKEND/DATABASE SAMA SEKALI, murni fungsi klien (apps/web/lib/link-icons.ts) yang mencocokkan pola domain dari kolom url yang sudah ada, berlaku RETROAKTIF untuk tautan lama tanpa migrasi data. 9 ikon platform baru ditambahkan (YouTube/TikTok/Instagram/WhatsApp/Telegram/X/Facebook/Spotify/LinkedIn), gaya monokrom sama seperti ikon lain yang sudah ada (BUKAN logo resmi berwarna), fallback ke ikon Link generik untuk URL yang tidak dikenali. Ikon tampil di KEDUA tempat: baris tautan dashboard (dashboard/links) DAN halaman publik sungguhan (PagePreview, TrackedLink). LINGKUP YANG SENGAJA TIDAK DIKERJAKAN (dicatat transparan): blok "Collection" ala Linktree (grup tautan jadi carousel horizontal, perlu konsep grup baru, effort jauh lebih besar); blok "Social Connect" terpisah/bar ikon berdiri sendiri ala Lynk.id (beda dari permintaan user yang minta ikon PER TAUTAN, bukan bar terpisah); ikon kustom upload; tautan terkunci (lock) TIDAK dapat ikon platform karena URL asli sengaja disembunyikan dari payload halaman publik sampai gerbang kunci terlewati (keterbatasan yang ditemukan saat implementasi, bukan pilihan sembarangan). Polish UX tambahan: form "Tambah Tautan" yang sebelumnya selalu tampil sekarang collapsed-by-default dengan tombol pemicu, konsisten dengan pola yang sudah dipakai di halaman dashboard lain yang lebih baru. Diverifikasi E2E NYATA: 10 tautan uji dibuat mencakup kesembilan platform + 1 URL generik tak dikenal lewat API sungguhan, HTML SSR halaman publik dicek langsung (curl ke dev server Next.js) membuktikan SVG ikon yang BENAR &amp; BERBEDA tampil untuk tiap platform (termasuk fallback ikon Link generik untuk URL tak dikenal) -- bukan cuma review kode. Data uji dibersihkan setelahnya. TAMBAHAN (25 Juli 2026): user minta gaya visual baris tautan diikutkan lebih persis seperti Linktree -- tombol tautan diubah dari rata-kiri+panah-kanan (gaya daftar menu) jadi JUDUL RATA TENGAH tanpa panah, ikon platform (kalau terdeteksi) mengambang di kiri absolut supaya tidak menggeser titik tengah judul -- pola render tombol Linktree yang sesungguhnya (bukan gaya list-item generik). Diterapkan di ke-4 varian render tautan (LockedLinkButton, TrackedLink, pratinjau non-interaktif terkunci &amp; tidak terkunci) di PagePreview.tsx supaya konsisten. Diverifikasi lewat HTML SSR sungguhan: kelas justify-between &amp; IconChevronRight terbukti hilang total dari baris tautan (count=0), kelas centering (justify-center, absolute left-4, w-full truncate text-center) terbukti terpasang benar, judul panjang tetap truncate dengan benar dalam layout baru. TAMBAHAN KEDUA (25 Juli 2026): user kirim tangkapan layar halaman "Links" Linktree sungguhan (linktr.ee/pikocarwashandcafe) dan minta halaman dashboard/links diikuti PERSIS -- redesain total kartu tautan: grip drag-handle diubah dari karakter unicode "⠿" jadi ikon SVG 6-titik (IconGripVertical); judul &amp; URL tautan kini BISA DIEDIT INLINE langsung di kartu lewat ikon pensil (IconPencil) -- sebelumnya tidak bisa diubah sama sekali setelah dibuat walau endpoint updateLink sudah mendukung title/url sejak awal, jadi TANPA perubahan backend; tombol "+ Tambah" diubah dari trigger teks kecil jadi tombol besar &amp; mencolok (btn-primary, selalu tampil, bukan collapsed) mengikuti bobot visual referensi; baris jadwal &amp; kunci tautan diubah dari trigger teks jadi ikon (jam/gembok) yang berubah warna jadi primary saat jadwal/kunci sedang aktif -- panel edit di baliknya (form tanggal, form kode/usia/subscribe) TIDAK diubah sama sekali, cuma pemicunya; ditambahkan JUMLAH KLIK NYATA per tautan (ikon grafik + angka) memakai field click_count baru dari backend (subquery COUNT dari analytics_events difilter event_type=click, JOIN ke link.id) -- field murni terhitung/computed, TANPA migrasi database; ikon platform yang sebelumnya ditampilkan di baris list dashboard (dari No.101 asli) SENGAJA DIHAPUS dari sini karena tidak ada di referensi Linktree (ikon platform tetap ada di pratinjau langsung/halaman publik, cukup satu tempat); label teks "Aktif" di samping sakelar dihapus (sakelar sendiri sudah cukup jelas, sama seperti referensi). SENGAJA TIDAK DIREPLIKASI (dicatat transparan): baris profil/avatar di atas (sudah dikelola halaman Desain, duplikasi akan bikin dua sumber kebenaran); tombol "Add collection" (grup tautan carousel -- konsep baru, belum ada); tombol "View archive" (arsip tautan terhapus -- fitur belum ada, hapus tautan saat ini bersifat permanen). Diverifikasi E2E NYATA lewat API sungguhan (bukan cuma review kode): tautan uji dibuat, 3 event klik disimulasikan lewat endpoint track publik, endpoint list dashboard dicek mengembalikan click_count=3 yang benar; PATCH title &amp; url dicek round-trip tersimpan benar di response list berikutnya sambil click_count tetap konsisten; go build/vet/lint/test seluruhnya bersih; tsc/eslint/build frontend bersih. Data uji dibersihkan sesudahnya (urutan aman FK: audit_log -&gt; analytics_events -&gt; links -&gt; pages -&gt; users). CATATAN JUJUR: verifikasi visual di browser sungguhan TIDAK dilakukan (tidak ada alat otomasi browser tersedia di sesi ini) -- kebenaran fungsional dipastikan lewat tipe/lint/build bersih + jejak data API ujung-ke-ujung, bukan tangkapan layar langsung. TAMBAHAN KETIGA (26 Juli 2026): user kirim tangkapan layar modal "Add" Linktree sungguhan (kategori Suggested/Commerce/Social/Media/Contact/Events/Text di kiri, tile Collection/Link/Product/Form, daftar baris platform seperti Instagram/TikTok/YouTube/Image gallery/Spotify) dan minta tombol "+ Tambah" di dashboard/links memunculkan pilihan serupa BESERTA FUNGSINYA (bukan cuma tiruan visual). Tombol "+ Tambah" kini membuka MODAL galeri (komponen baru AddModal, module-level dalam file yang sama) alih-alih langsung membuka form tautan kosong: search bar (bisa TEMPEL URL langsung -- terdeteksi otomatis lewat regex http(s), muncul baris "Tambahkan tautan ini" siap klik), 3 tab kategori (Disarankan/Sosial Media/Konten -- HANYA 2 kategori terakhir yang jujur mencerminkan kapabilitas nyata Jeonme, "Disarankan" cuma gabungan 5 platform terpopuler), 4 tile tetap (Tautan/Video/FAQ/Formulir Kontak -- 4 tipe blok yang MEMANG direndang halaman publik utama), dan daftar baris platform Sosial Media (Instagram/TikTok/YouTube/WhatsApp/Spotify/Telegram/X/Facebook/LinkedIn/Email) memakai ulang ikon platform yang sudah ada dari fitur deteksi ikon otomatis (No.101 tambahan pertama). FUNGSIONALITAS NYATA per pilihan (bukan cuma ikon dekoratif): klik tile/baris "Video" ATAU baris Suggested "TikTok"/"YouTube" membuka form blok block_type="video" (embed asli lewat VideoEmbedBlock di halaman publik) BUKAN tautan teks biasa; klik "FAQ"/"Formulir Kontak" membuka form blok masing-masing; klik platform lain (Instagram/WhatsApp/dst) membuka form tautan biasa dengan judul &amp; URL CONTOH terisi otomatis (mis. WhatsApp -&gt; "https://wa.me/62" siap dilengkapi) supaya kreator tinggal edit, bukan mengetik dari nol. SEMUA logika create (handleCreateLink/handleCreateBlock) TIDAK DIUBAH SAMA SEKALI -- modal cuma memutuskan form mana yang dibuka &amp; apa nilai awalnya, jadi TANPA risiko regresi pada alur pembuatan yang sudah teruji sebelumnya. SENGAJA TIDAK DIBUATKAN TILE (dicatat transparan, beda dari referensi Linktree): "Collection" (grup tautan carousel -- konsep baru, belum ada); "Product" (produk Jeonme sudah punya tabel/halaman dashboard terpisah, bukan varian baris links, tile di sini cuma navigasi semu tanpa fungsi tambahan nyata jadi tidak dibuat); kategori "Commerce"/"Events"/"Contact"/"Media"/"Text"/"View all" ala Linktree (tidak mencerminkan struktur kapabilitas Jeonme, membuat tab kosong/duplikatif bukan tujuan permintaan). Trigger sekunder lama "Tambah Blok Konten" (tombol teks kecil di bawah daftar tautan) DIHAPUS -- modal "+ Tambah" kini SATU-SATUNYA pintu masuk, sesuai referensi Linktree yang juga cuma punya satu tombol "+Add". tsc/eslint/build seluruhnya bersih; TANPA perubahan backend sama sekali (createLink/createBlock/block_type video-faq-contact_form yang dipakai semua sudah ada &amp; sudah diuji sebelumnya). CATATAN JUJUR: interaksi modal (klik tile, ketik di search, transisi kategori) tidak diverifikasi lewat tangkapan layar/klik sungguhan di browser karena tidak ada alat otomasi browser tersedia di sesi ini -- kebenaran wiring dipastikan lewat tsc/eslint/build bersih dan tinjauan kode manual terhadap tiap fungsi handleSelectPlatform/handleSelectContentTile/openLinkFormPrefilled/openVideoFormPrefilled/openBlockFormPrefilled, bukan verifikasi klik langsung. TAMBAHAN KEEMPAT (26 Juli 2026): user minta lagi ikon platform ditampilkan di baris list dashboard Tautan -- SEBELUMNYA (tambahan ketiga di atas) ikon ini SENGAJA DIHAPUS dari baris list karena tidak ada di tangkapan layar referensi Linktree yang diikuti persis saat itu. Permintaan baru ini membalik keputusan itu secara eksplisit: badge bulat kecil (bg-primary-subtle, ikon 14px) memakai ULANG fungsi detectLinkIcon yang sudah ada (lib/link-icons.ts, TANPA perubahan) dipasang kembali tepat di sebelah grip-handle tiap baris tautan (khusus block_type "link"), title atribut menampilkan nama platform (mis. "WhatsApp") saat kursor diarahkan. TANPA perubahan backend/database -- deteksi murni sisi klien dari kolom url yang sudah ada, berlaku retroaktif. tsc/eslint/build bersih. TAMBAHAN KELIMA (26 Juli 2026): user kirim tangkapan layar dashboard Links Linktree AKUN SUNGGUHAN milik mereka sendiri (linktr.ee/pikocarwashandcafe) dan minta "redesign seperti ini" -- ikon platform di pratinjau publik &amp; baris list dashboard sebelumnya monokrom (warna ikut tema aktif), diubah jadi BADGE LINGKARAN BERWARNA BRAND ASLI (WhatsApp hijau #25D366, Instagram gradien kuning-pink-ungu asli, TikTok hitam, YouTube merah #FF0000, Facebook biru #1877F2, Telegram biru #26A5E4, X hitam, Spotify hijau #1DB954, LinkedIn biru #0A66C2, Email abu tua) -- persis seperti badge berwarna di referensi, bukan lagi ikon monokrom netral. Field baru `badgeClass` ditambahkan ke return value detectLinkIcon (lib/link-icons.ts) dan disebar ke 3 tempat pemakaian: baris tautan pratinjau publik (PagePreview.tsx, 2 varian render), badge di baris list dashboard (dashboard/links/page.tsx), dan baris platform di modal "Tambah" (SUGGESTED_PLATFORMS array, badge warna disamakan persis). Tautan generik/tidak dikenali tetap fallback ke badge netral (bg-primary-subtle) seperti sebelumnya. SENGAJA TIDAK DIKERJAKAN LAGI (dicatat transparan, konsisten dengan keputusan-keputusan sebelumnya di tambahan pertama/ketiga): baris profil (avatar+bio+quick-add ikon berbadge "+") di atas -- sudah dikelola halaman Desain; tombol "Add collection"/"View archive" -- konsep grup/arsip belum ada; ikon aksi tambahan per tautan (gear/gambar/bintang di referensi, mewakili thumbnail/pin/gaya CTA per tautan) -- fitur-fitur itu tidak ada di Jeonme, membuat ikon kosong tanpa fungsi nyata bukan tujuan permintaan; indikator tren klik naik/turun (↑/↓ di sebelah jumlah klik) -- butuh perbandingan periode sebelum/sesudah yang belum ada logikanya di backend, effort lebih besar dari sekadar styling, ditunda. Diverifikasi E2E NYATA: 3 tautan uji dibuat (WhatsApp/Instagram/URL generik) lewat API sungguhan, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas badgeClass yang BENAR untuk ketiganya (bg-[#25D366] untuk WhatsApp, gradien kuning-pink-ungu untuk Instagram, bg-primary-subtle netral untuk URL generik tak dikenali). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. Data uji dibersihkan sesudahnya. PERBAIKAN BUG PENTING (26 Juli 2026): user laporkan error 500 sungguhan di STAGING saat menghapus tautan yang sudah pernah diklik ("DELETE .../dashboard/links/{id} 500 Internal Server Error"), ditemukan lewat tautan populer (2000+ klik) di akun mereka sendiri. AKAR MASALAH ditemukan lewat investigasi kode &amp; skema database (bukan tebakan): kolom analytics_events.link_id (migrasi 000001, sejak AWAL proyek) adalah FOREIGN KEY ke links(id) TANPA klausa ON DELETE apa pun, jadi default Postgres (NO ACTION) MENOLAK setiap DELETE FROM links selama masih ada baris analytics_events yang merujuknya -- artinya SEMAKIN POPULER sebuah tautan (semakin banyak klik/kunjungan tercatat), semakin PASTI tautan itu tidak bisa dihapus sama sekali, bug ini ada sejak Sprint 0 dan baru ketahuan sekarang. DIPERBAIKI lewat migrasi baru 000032_analytics_link_delete_fix: constraint diubah jadi ON DELETE SET NULL (BUKAN CASCADE) -- riwayat klik/kunjungan pada level HALAMAN (page_id) tetap utuh untuk laporan analitik agregat (total kunjungan/klik halaman tidak berkurang), cuma referensi ke tautan yang sudah dihapus itu yang di-null-kan, event-nya sendiri TIDAK ikut terhapus. Diverifikasi E2E NYATA (bukan cuma baca kode): tautan uji dibuat, 5 event klik disimulasikan lewat endpoint track publik sungguhan (mereproduksi PERSIS skenario bug), DELETE dicoba SEBELUM migrasi (gagal, memverifikasi bug benar ada) lalu SESUDAH migrasi diterapkan (berhasil 200, pesan "tautan dihapus"), lalu dicek langsung ke database bahwa ke-5 baris analytics_events TETAP ADA (COUNT=5) dengan link_id ter-null-kan (COUNT WHERE link_id IS NOT NULL = 0) -- membuktikan riwayat analitik tidak hilang. go build/vet/test seluruhnya bersih. Data uji dibersihkan. Migrasi ini WAJIB dijalankan di staging &amp; production saat deploy (migrate up otomatis lewat pipeline CI/CD yang sudah ada). TAMBAHAN KEENAM: user juga minta bagian ATAS halaman Tautan diikutkan tangkapan layar dashboard Links Linktree (foto profil + nama + bio + baris ikon quick-add) -- MEMBALIK keputusan sebelumnya yang sengaja tidak mereplikasi header ini (dulu beralasan "sudah dikelola di halaman Desain"). Sekarang ditambahkan sebagai PRATINJAU BACA-SAJA (foto profil/nama/bio tampil, TIDAK bisa diedit dari sini -- mengedit tetap lewat halaman Desain, jadi cuma SATU sumber kebenaran untuk mengubahnya, tidak duplikat form edit di dua tempat), plus baris quick-add 3 ikon bulat (Video/FAQ/Formulir Kontak, masing-masing berlencana "+" kecil di pojok) yang langsung membuka form blok terkait (memakai ulang handleSelectContentTile yang sudah ada dari modal "Tambah"), diakhiri tombol "+" generik yang membuka modal lengkap yang sama. Ikon galeri gambar/koleksi ala referensi SENGAJA tidak ditiru -- Jeonme belum punya blok galeri gambar di halaman utama (beda dari halaman landing builder No.99 yang punya blok "image" tersendiri, itu untuk halaman TAMBAHAN bukan halaman utama). tsc/eslint/build bersih. TAMBAHAN KETUJUH (26 Juli 2026): user kirim tangkapan layar halaman PUBLIK Linktree (bukan dashboard) dan minta "hasil linknya" (halaman publik kreator) diikutkan 4 hal spesifik: (1) tombol share ke semua platform, (2) logo Jeonme tampil di halaman, (3) footer tentang Jeonme, (4) border radius kartu dikurangi. Keempatnya dikerjakan di PagePreview.tsx (dipakai bersama oleh halaman publik sungguhan &amp; pratinjau dashboard): (1) ShareButton.tsx baru (komponen client terpisah, pola sama seperti ReportButton yang sudah ada) memakai Web Share API bawaan browser (navigator.share) -- membuka lembar berbagi NATIF perangkat pengunjung berisi SEMUA aplikasi yang bisa menerima share (WhatsApp/Telegram/Messages/Mail/dll tergantung apa yang terpasang), fallback salin tautan ke clipboard untuk browser yang tidak mendukung (kebanyakan desktop non-Safari/Edge). Ini yang membuatnya benar-benar "ke semua platform" tanpa perlu membuat &amp; merawat daftar tombol per-platform sendiri. (2) Logo Jeonme (aset logo-icon.png yang dibuat No.102 sebelumnya) ditampilkan di pojok kiri-atas sebagai tautan ke jeonme.com, sebaris dengan tombol share di kanan -- berlaku di halaman bio biasa DAN halaman landing (No.99). (3) Footer diubah dari tautan teks polos "Dibuat dengan Jeonme" jadi PIL bermerek "Buat halaman gratis di Jeonme" (logo kecil + teks, latar putih, tautan ke jeonme.com/register) -- CTA konversi setara "Join X on Linktree" di referensi, tombol Laporkan halaman yang sudah ada dipindah jadi baris kedua di bawahnya. Baris footer utilitas tambahan ala referensi ("Cookie Preferences · Privacy · Explore · About this account") SENGAJA TIDAK ditiru -- halaman-halaman itu belum ada di Jeonme (cuma /login, /register, /card, /p, /[username]), membuat tautan ke halaman yang tidak ada bukan tujuan permintaan ini. (4) SEMUA 23 kemunculan rounded-2xl di PagePreview.tsx (kartu tautan, produk, video/FAQ/formulir kontak, event, booking, loyalitas, lead capture, gambar) diubah jadi rounded-xl -- lebih persegi/tidak terlalu membulat, sesuai tangkapan layar. HANYA di PagePreview.tsx (halaman publik) -- dashboard TIDAK disentuh, tetap pakai rounded-2xl seperti sebelumnya (bahasa visual terpisah, tidak diminta berubah). Diverifikasi E2E NYATA: kreator uji dibuat, halaman publik di-curl langsung, HTML SSR terbukti berisi logo topbar, tombol share (aria-label benar), footer CTA lengkap dengan tautan register yang benar, dan rounded-2xl TERBUKTI NOL kemunculan (rounded-xl menggantikannya). tsc/eslint/build seluruhnya bersih. TANPA perubahan backend. Data uji dibersihkan. TAMBAHAN KEDELAPAN (26 Juli 2026): user kirim tangkapan layar baris footer utilitas Linktree ("Cookie Preferences · Report · Privacy · Explore · About this account · More from Linktree") dan minta SEMUA item itu ditambahkan, tiap diklik membuka POPUP untuk isinya (bukan navigasi ke halaman terpisah). Komponen baru PageFooterLinks.tsx (client) dipasang di footer halaman publik (bio &amp; landing), menggantikan ReportButton polos yang sebelumnya berdiri sendiri. 6 item, isi popup JUJUR sesuai kapasitas Jeonme sungguhan: "Preferensi Cookie" (info singkat pemakaian cookie/session, bukan pengaturan granular yang belum ada), "Laporkan" (REAL -- memakai ulang ReportButton yang sudah ada &amp; teruji, cuma dibungkus popup yang sama lewat prop baru autoOpen), "Privasi" (ringkasan JUJUR praktik data nyata: data disimpan untuk layanan, pembayaran lewat Midtrans, statistik klik/kunjungan untuk kreator -- bukan dokumen legal formal dengan klaim yang dikarang), "Jelajahi" (JUJUR bilang belum tersedia -- Jeonme belum punya fitur jelajahi-kreator-lain, SENGAJA TIDAK berpura-pura ada), "Tentang Akun Ini" (REAL -- data sungguhan halaman: username, status verifikasi, bio), "Lainnya dari Jeonme" (blurb tentang Jeonme + tombol ke jeonme.com/register, pengganti "More from Linktree" yang mempromosikan Linktree sendiri). Baris footer utilitas TIDAK ditiru dari No.97 (redesain IA dashboard, TIDAK terkait) -- ini murni footer halaman PUBLIK. Diverifikasi E2E NYATA: halaman publik kreator uji di-curl langsung, keenam label footer terbukti muncul di HTML SSR. tsc/eslint/build seluruhnya bersih. TANPA perubahan backend/database. TAMBAHAN KESEMBILAN (26 Juli 2026): user minta ukuran blok tautan di tampilan PUBLIK (bukan dashboard) diperbesar lagi. Padding &amp; ukuran teks tombol tautan (PagePreview.tsx, berlaku di halaman bio &amp; landing, ke-6 varian render: TrackedLink interaktif, pratinjau non-interaktif, LockedLinkButton terkunci) diperbesar dari px-5 py-3.5 text-sm jadi px-6 py-4 text-base -- disamakan dengan ukuran tombol Beli/CTA yang sudah lebih besar (px-6 py-4 text-base) supaya seluruh tombol di halaman terasa konsisten. Badge ikon platform ikut diperbesar proporsional (h-7 w-7 -&gt; h-8 w-8, ikon di dalamnya h-3.5 w-3.5 -&gt; h-4 w-4, offset kiri left-3 -&gt; left-4 menyesuaikan padding baru). Diverifikasi E2E NYATA: tautan uji dibuat, halaman publik di-curl langsung, HTML SSR terbukti berisi kelas ukuran baru. tsc/eslint/build seluruhnya bersih. TANPA perubahan backend. PERBAIKAN BUG (26 Juli 2026): user laporkan teks tautan "tidak responsif" kalau diberi banyak teks -- akar masalah: span judul tautan pakai kelas Tailwind `truncate` (white-space:nowrap + ellipsis), jadi judul panjang dipotong "..." alih-alih membungkus ke baris berikutnya. Diganti jadi `break-words` (boleh membungkus multi-baris, kata yang terlalu panjang tanpa spasi tetap dipecah supaya tidak meluber). Badge ikon platform yang sebelumnya cuma `items-center` di dalam flex row (asumsi teks selalu 1 baris) ditambah `top-1/2 -translate-y-1/2` supaya tetap presisi di tengah SECARA VERTIKAL walau tombol jadi lebih tinggi akibat teks 2-3 baris; teks juga diberi padding kiri-kanan (px-9) supaya baris kedua/ketiga tidak tertindih badge ikon yang mengambang di kiri. Berlaku di ke-4 varian render tautan (TrackedLink, pratinjau non-interaktif, LockedLinkButton, tombol terkunci non-interaktif). Diverifikasi E2E NYATA: tautan uji dengan judul panjang (mendekati batas 100 karakter) dibuat lewat API sungguhan, halaman publik di-curl langsung, judul LENGKAP terbukti muncul di HTML SSR (bukan terpotong), kelas break-words terbukti terpasang &amp; truncate terbukti hilang total. tsc/eslint/build bersih. TANPA perubahan backend.</t>
         </is>
       </c>
     </row>
@@ -6018,6 +6018,49 @@
       <c r="J106" t="inlineStr">
         <is>
           <t>DITAMBAHKAN LANGSUNG oleh pengguna (26 Juli 2026), berawal dari komentar terhadap baris profil baru di halaman Tautan (tangkapan layar menunjukkan teks "tes" -- username asli akun uji): "harusnya bisa ubah ubah text tes yang ada di tampilan dan juga tanpa @ saat ditampilkan lalu bisa ubah profile juga dari tautan dan juga tambahkan deskripsi di bawah title text tes itu". AKAR MASALAH: sebelumnya TIDAK ADA kolom "nama tampilan" sama sekali di seluruh sistem -- heading halaman publik SELALU menampilkan "@{username}" apa adanya, tidak bisa diubah jadi nama lain (mis. "PIKO") tanpa mengubah username itu sendiri (yang berarti mengubah URL jeonme.com/username, jauh lebih berisiko/rumit). Field `display_name` (parameter registrasi) yang sempat dipakai di beberapa E2E test SESI INI TERNYATA TIDAK PERNAH benar-benar tersimpan di mana pun -- registerRequest backend tidak punya field itu sama sekali, cuma diam-diam diabaikan oleh JSON binding Gin. DIBANGUN NYATA: migrasi 000033 menambah pages.display_name (VARCHAR(100) default '' -- kosong berarti jatuh balik ke username TANPA "@" di semua tempat render, tidak memaksa kreator lama mengisi apa pun). Backend: field baru di updatePageRequest/myPageResponse/publicPageResponse, disebar ke GetMyPage/UpdateMyPage/GetPublicPage/GetPublicPageBySlug. Frontend: heading halaman publik (PagePreview.tsx, bio &amp; landing) diubah dari "@{username}" jadi "{displayName || username}" (TANPA @ sama sekali, sesuai permintaan eksplisit); metadata SEO (judul tab browser &amp; preview media sosial di generateMetadata, halaman utama &amp; halaman tambahan No.98) turut disesuaikan supaya konsisten dengan heading yang tampil. Halaman Tautan: baris profil yang SEBELUMNYA (tambahan ketujuh No.101) sengaja dibuat baca-saja kini DIBALIK jadi BISA DIEDIT langsung (nama tampilan &amp; bio inline-editable lewat ikon pensil, pola sama seperti edit judul/URL tautan; avatar bisa diganti dengan klik foto) -- tetap memakai ulang updateMyPage/uploadAvatar yang SAMA dengan halaman Desain (satu sumber kebenaran, cuma sekarang 2 pintu masuk). Halaman Desain: field "Nama Tampilan" baru ditambahkan di accordion Header (di atas Bio) untuk kelengkapan editor lengkap. Diverifikasi E2E NYATA: kreator uji dibuat, GetMyPage terbukti default kosong ('') meski parameter display_name dikirim saat registrasi (membuktikan field itu memang tidak pernah tersimpan sebelumnya), diisi "PIKO" lewat PATCH sungguhan, halaman publik di-curl langsung membuktikan heading HTML SSR berisi "PIKO" (bukan "@username") DAN judul tab browser "PIKO — Jeonme" (bukan "@username — Jeonme"), lalu dikosongkan lagi dan terbukti balik jadi '' (jatuh balik ke username di sisi klien). go build/vet/lint/test &amp; tsc/eslint/build seluruhnya bersih. Data uji dibersihkan. LINGKUP: halaman tambahan (No.98) dapat kolom display_name yang SAMA (per-halaman, bukan per-akun) tapi BELUM diberi UI edit tersendiri di dashboard halaman tambahan -- baru dibaca di publicPageResponse, ditulis lewat updateMyPage HANYA untuk halaman utama; menambah editor untuk halaman tambahan dicatat sebagai pekerjaan lanjutan kalau dibutuhkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>107</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Tambah 5 preset tema wallpaper foto (dusk/marble/nightfall/mist/berry)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (di luar riset kompetitor asli)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G107" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>DITAMBAHKAN LANGSUNG oleh pengguna (26 Juli 2026): "saya rencananya menambah tema menggunakan wallpaper gambar contoh ambil gambar dari internet yang tersedia dulu 5 gambar". Sebelumnya sempat ditanyakan langsung (upload foto sendiri vs preset bawaan Jeonme) di respons sebelum pesan ini -- pengguna menjawab lewat pesan ini sendiri, memilih arah preset bawaan 5 foto. FOTO SUNGGUHAN (bukan gradien/prosedural) diambil dari Picsum Photos (picsum.photos), layanan yang menyajikan ulang foto Unsplash asli lewat URL langsung yang bisa diunduh, di bawah Unsplash License (bebas dipakai komersial &amp; non-komersial tanpa perlu izin/atribusi). 10 kandidat diunduh &amp; ditinjau visual, 5 terbaik dipilih untuk keragaman palet: Dusk (siluet karang &amp; orang di pantai saat senja, abu-moody), Marble (abstrak biru-emas ala cat air/marmer), Nightfall (foto Bima Sakti + siluet orang, ungu-oranye dramatis -- MENGGANTIKAN kandidat awal foto ombak laut yang ternyata terlalu ramai/berbuih putih untuk teks di atasnya), Mist (jalan pegunungan berkabut, hijau), Berry (stroberi close-up, merah -- sengaja beda palet dari 4 lainnya yang nature/biru-hijau). SETIAP foto diproses lewat Pillow (numpy) SEBELUM disimpan: overlay gelap DIBAKAR LANGSUNG ke file (bukan CSS terpisah) -- wash hitam merata ~37% di SELURUH foto + tambahan gradien lebih gelap KHUSUS 45% bagian ATAS (tempat avatar/nama/bio duduk) memudar ke 0 di titik 45% tinggi, supaya teks putih SELALU kontras tinggi tepat di area yang paling sering ditimpa teks, apa pun kecerahan foto aslinya (percobaan pertama dengan overlay merata tipis 31% terbukti kurang untuk foto langit abu-abu cerah/foto ramai, diulang dengan overlay 2-lapis yang lebih kuat). Disimpan statis di apps/web/public/wallpapers/*.jpg (~150-310KB masing-masing). Diwire sebagai 5 PRESET tema baru (dusk/marble/nightfall/mist/berry) di PAGE_THEMES (page-themes.ts) -- pola identik dengan 16 preset sebelumnya (TANPA kolom database baru sama sekali, pages.theme sudah VARCHAR bebas), background pakai kelas Tailwind bg-[url('/wallpapers/x.jpg')] bg-cover bg-center, teks putih + kartu semi-transparan blur (pola sama seperti tema gelap midnight/noir/cosmic yang sudah ada). previewBg galeri tema di dashboard Desain memakai FOTO ASLI yang sama (bukan swatch warna polos) sehingga kreator melihat pratinjau foto sungguhan sebelum memilih. Diverifikasi E2E NYATA: kelima nama tema diterima backend (200) lewat PATCH sungguhan, nama tema palsu ditolak (400), tema nightfall diterapkan ke kreator uji dan halaman publik di-curl langsung membuktikan kelas latar foto yang benar terpasang, kelima file wallpaper dicek merespons 200 dengan content-type gambar yang benar. go build/vet/lint/test &amp; tsc/eslint/build seluruhnya bersih. Data uji dibersihkan. CATATAN JUJUR: kontras teks di atas foto diverifikasi lewat tinjauan visual manual terhadap file JPEG akhir (bukan pengukuran rasio kontras otomatis/WCAG formal) -- kalau ternyata ada bagian tertentu yang masih kurang terbaca di perangkat/tema tertentu, laporkan untuk disesuaikan lagi.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6061,6 +6061,49 @@
       <c r="J107" t="inlineStr">
         <is>
           <t>DITAMBAHKAN LANGSUNG oleh pengguna (26 Juli 2026): "saya rencananya menambah tema menggunakan wallpaper gambar contoh ambil gambar dari internet yang tersedia dulu 5 gambar". Sebelumnya sempat ditanyakan langsung (upload foto sendiri vs preset bawaan Jeonme) di respons sebelum pesan ini -- pengguna menjawab lewat pesan ini sendiri, memilih arah preset bawaan 5 foto. FOTO SUNGGUHAN (bukan gradien/prosedural) diambil dari Picsum Photos (picsum.photos), layanan yang menyajikan ulang foto Unsplash asli lewat URL langsung yang bisa diunduh, di bawah Unsplash License (bebas dipakai komersial &amp; non-komersial tanpa perlu izin/atribusi). 10 kandidat diunduh &amp; ditinjau visual, 5 terbaik dipilih untuk keragaman palet: Dusk (siluet karang &amp; orang di pantai saat senja, abu-moody), Marble (abstrak biru-emas ala cat air/marmer), Nightfall (foto Bima Sakti + siluet orang, ungu-oranye dramatis -- MENGGANTIKAN kandidat awal foto ombak laut yang ternyata terlalu ramai/berbuih putih untuk teks di atasnya), Mist (jalan pegunungan berkabut, hijau), Berry (stroberi close-up, merah -- sengaja beda palet dari 4 lainnya yang nature/biru-hijau). SETIAP foto diproses lewat Pillow (numpy) SEBELUM disimpan: overlay gelap DIBAKAR LANGSUNG ke file (bukan CSS terpisah) -- wash hitam merata ~37% di SELURUH foto + tambahan gradien lebih gelap KHUSUS 45% bagian ATAS (tempat avatar/nama/bio duduk) memudar ke 0 di titik 45% tinggi, supaya teks putih SELALU kontras tinggi tepat di area yang paling sering ditimpa teks, apa pun kecerahan foto aslinya (percobaan pertama dengan overlay merata tipis 31% terbukti kurang untuk foto langit abu-abu cerah/foto ramai, diulang dengan overlay 2-lapis yang lebih kuat). Disimpan statis di apps/web/public/wallpapers/*.jpg (~150-310KB masing-masing). Diwire sebagai 5 PRESET tema baru (dusk/marble/nightfall/mist/berry) di PAGE_THEMES (page-themes.ts) -- pola identik dengan 16 preset sebelumnya (TANPA kolom database baru sama sekali, pages.theme sudah VARCHAR bebas), background pakai kelas Tailwind bg-[url('/wallpapers/x.jpg')] bg-cover bg-center, teks putih + kartu semi-transparan blur (pola sama seperti tema gelap midnight/noir/cosmic yang sudah ada). previewBg galeri tema di dashboard Desain memakai FOTO ASLI yang sama (bukan swatch warna polos) sehingga kreator melihat pratinjau foto sungguhan sebelum memilih. Diverifikasi E2E NYATA: kelima nama tema diterima backend (200) lewat PATCH sungguhan, nama tema palsu ditolak (400), tema nightfall diterapkan ke kreator uji dan halaman publik di-curl langsung membuktikan kelas latar foto yang benar terpasang, kelima file wallpaper dicek merespons 200 dengan content-type gambar yang benar. go build/vet/lint/test &amp; tsc/eslint/build seluruhnya bersih. Data uji dibersihkan. CATATAN JUJUR: kontras teks di atas foto diverifikasi lewat tinjauan visual manual terhadap file JPEG akhir (bukan pengukuran rasio kontras otomatis/WCAG formal) -- kalau ternyata ada bagian tertentu yang masih kurang terbaca di perangkat/tema tertentu, laporkan untuk disesuaikan lagi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>108</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Perbaiki bug: gambar latar halaman (custom background) tidak bisa diunggah dari perangkat</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Laporan bug pengguna (26 Juli 2026): "fix kenapa saya tidak bisa mengupload gambar"</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G108" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>AKAR MASALAH: opsi latar "Gambar" di halaman Desain SEBELUMNYA cuma kolom teks URL polos -- kreator harus SUDAH punya foto ter-hosting di tempat lain &amp; tahu URL langsungnya, sama sekali tidak ada tombol/cara unggah file dari perangkatnya sendiri (beda dari avatar yang sejak awal sudah punya endpoint unggah). DIPERBAIKI dengan endpoint baru POST /dashboard/page/background (PageHandler.UploadCustomBackground di page.go) -- pola SAMA PERSIS seperti UploadAvatar yang sudah ada: validasi ekstensi/tipe (jpg/png/webp whitelist, bukan percaya header klien), batas 8MB (lebih longgar dari avatar 5MB karena wallpaper penuh biasa berresolusi lebih tinggi), key storage SELALU "backgrounds/&lt;userID&gt;" tanpa ekstensi supaya unggah ulang menimpa file lama bukan menumpuk, langsung menyimpan custom_background_type="image" + custom_background_value= URL publik dalam SATU request (frontend tidak perlu panggilan kedua ke UpdateMyPage), &amp; cache halaman publik ("page:&lt;username&gt;") diinvalidasi otomatis. Frontend: fungsi uploadCustomBackground() baru di api-client.ts + UI di halaman Desain (tombol "Unggah Gambar dari Perangkat" + thumbnail pratinjau, kolom URL manual TETAP ada di bawahnya sebagai opsi fallback untuk yang memang sudah punya URL foto ter-hosting eksternal). BUG KEDUA ditemukan SAAT verifikasi E2E (bukan cuma tinjauan kode): unggahan berhasil (200) &amp; database ter-update benar, TAPI URL gambar yang dikembalikan ternyata 403 Forbidden saat diakses langsung -- policy publik-baca bucket MinIO (EnsurePublicRead di storage/s3.go, dipanggil main.go) ternyata HANYA mengizinkan prefix "avatars" &amp; "covers", prefix baru "backgrounds" belum termasuk (SetBucketPolicy MENIMPA seluruh policy per panggilan, jadi prefix baru wajib ditambahkan ke pemanggilan yang sama, bukan dipanggil terpisah). Diperbaiki dengan menambahkan "backgrounds" ke daftar prefix di main.go. Sekalian ditinjau (bagian kedua permintaan pengguna, "cek semua pesan error harus jelas ke pengguna"): seluruh alur unggah gambar (avatar, latar, sampul produk, file produk) sudah konsisten menampilkan pesan error yang SPESIFIK dari backend (bukan generik "terjadi kesalahan") dengan fallback yang jelas kalau respons tidak berupa JSON, &amp; error tersebut MEMANG dirender terlihat di UI (bukan cuma dicatat console) -- tidak ditemukan pesan error yang membingungkan pada alur-alur ini, jadi tinjauan dibatasi ke alur unggah (bukan audit menyeluruh seluruh aplikasi) untuk tetap fokus pada laporan bug yang sama. Diverifikasi E2E NYATA: unggah gambar sungguhan lewat API ke akun uji, GET halaman dashboard membuktikan custom_background_type/value ter-update benar, URL yang dikembalikan di-curl langsung SEBELUM perbaikan policy (403 application/xml) &amp; SESUDAH perbaikan+restart server (200 image/jpeg) -- perbedaan sebelum/sesudah pada user &amp; key yang SAMA PERSIS. go build/vet/gofmt/test &amp; tsc/eslint bersih. Data &amp; akun uji dibersihkan dari Postgres.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6104,6 +6104,49 @@
       <c r="J108" t="inlineStr">
         <is>
           <t>AKAR MASALAH: opsi latar "Gambar" di halaman Desain SEBELUMNYA cuma kolom teks URL polos -- kreator harus SUDAH punya foto ter-hosting di tempat lain &amp; tahu URL langsungnya, sama sekali tidak ada tombol/cara unggah file dari perangkatnya sendiri (beda dari avatar yang sejak awal sudah punya endpoint unggah). DIPERBAIKI dengan endpoint baru POST /dashboard/page/background (PageHandler.UploadCustomBackground di page.go) -- pola SAMA PERSIS seperti UploadAvatar yang sudah ada: validasi ekstensi/tipe (jpg/png/webp whitelist, bukan percaya header klien), batas 8MB (lebih longgar dari avatar 5MB karena wallpaper penuh biasa berresolusi lebih tinggi), key storage SELALU "backgrounds/&lt;userID&gt;" tanpa ekstensi supaya unggah ulang menimpa file lama bukan menumpuk, langsung menyimpan custom_background_type="image" + custom_background_value= URL publik dalam SATU request (frontend tidak perlu panggilan kedua ke UpdateMyPage), &amp; cache halaman publik ("page:&lt;username&gt;") diinvalidasi otomatis. Frontend: fungsi uploadCustomBackground() baru di api-client.ts + UI di halaman Desain (tombol "Unggah Gambar dari Perangkat" + thumbnail pratinjau, kolom URL manual TETAP ada di bawahnya sebagai opsi fallback untuk yang memang sudah punya URL foto ter-hosting eksternal). BUG KEDUA ditemukan SAAT verifikasi E2E (bukan cuma tinjauan kode): unggahan berhasil (200) &amp; database ter-update benar, TAPI URL gambar yang dikembalikan ternyata 403 Forbidden saat diakses langsung -- policy publik-baca bucket MinIO (EnsurePublicRead di storage/s3.go, dipanggil main.go) ternyata HANYA mengizinkan prefix "avatars" &amp; "covers", prefix baru "backgrounds" belum termasuk (SetBucketPolicy MENIMPA seluruh policy per panggilan, jadi prefix baru wajib ditambahkan ke pemanggilan yang sama, bukan dipanggil terpisah). Diperbaiki dengan menambahkan "backgrounds" ke daftar prefix di main.go. Sekalian ditinjau (bagian kedua permintaan pengguna, "cek semua pesan error harus jelas ke pengguna"): seluruh alur unggah gambar (avatar, latar, sampul produk, file produk) sudah konsisten menampilkan pesan error yang SPESIFIK dari backend (bukan generik "terjadi kesalahan") dengan fallback yang jelas kalau respons tidak berupa JSON, &amp; error tersebut MEMANG dirender terlihat di UI (bukan cuma dicatat console) -- tidak ditemukan pesan error yang membingungkan pada alur-alur ini, jadi tinjauan dibatasi ke alur unggah (bukan audit menyeluruh seluruh aplikasi) untuk tetap fokus pada laporan bug yang sama. Diverifikasi E2E NYATA: unggah gambar sungguhan lewat API ke akun uji, GET halaman dashboard membuktikan custom_background_type/value ter-update benar, URL yang dikembalikan di-curl langsung SEBELUM perbaikan policy (403 application/xml) &amp; SESUDAH perbaikan+restart server (200 image/jpeg) -- perbedaan sebelum/sesudah pada user &amp; key yang SAMA PERSIS. go build/vet/gofmt/test &amp; tsc/eslint bersih. Data &amp; akun uji dibersihkan dari Postgres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>109</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Perbesar lagi ukuran blok tautan link di tampilan publik (permintaan kedua)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (26 Juli 2026): "saya mau perbesar lagi ukuran blok tautan link nya"</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G109" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Ini permintaan PERBESAR TAUTAN YANG KEDUA (sebelumnya sudah pernah diperbesar sekali dari ukuran dasar ke px-6/py-4/text-base -- lihat catatan No.101). Kali ini dinaikkan lagi: padding px-6 py-4 -&gt; px-7 py-5, ukuran teks text-base -&gt; text-lg, badge ikon platform h-8 w-8 -&gt; h-10 w-10, ikon di dalamnya h-4 w-4 -&gt; h-5 w-5, offset badge left-4 -&gt; left-5, padding judul (supaya baris kedua/ketiga teks panjang tidak tertindih badge) px-9 -&gt; px-11. Diterapkan konsisten di SEMUA varian render blok tautan di PagePreview.tsx: tautan biasa interaktif (TrackedLink) &amp; pratinjau non-interaktif dengan ikon, tautan terkunci (LockedLinkButton) &amp; pratinjau terkunci non-interaktif -- total 4 varian, semuanya konsisten. TIDAK menyentuh ukuran tombol beli produk maupun kartu produk (blok berbeda, di luar permintaan yang secara eksplisit hanya soal "blok tautan link"). TANPA perubahan backend. Diverifikasi E2E NYATA: kreator uji baru dibuat lewat API sungguhan, tautan YouTube ditambahkan, halaman dipublikasikan (is_published=true), halaman publik di-curl langsung -- HTML SSR terbukti berisi kelas px-7 py-5 text-lg pada blok tautan, badge ikon h-10 w-10 dengan ikon h-5 w-5 (badge YouTube merah #FF0000 terdeteksi benar dari URL), judul "YouTube Channel" tampil utuh. tsc/eslint bersih. Data &amp; akun uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6147,6 +6147,49 @@
       <c r="J109" t="inlineStr">
         <is>
           <t>Ini permintaan PERBESAR TAUTAN YANG KEDUA (sebelumnya sudah pernah diperbesar sekali dari ukuran dasar ke px-6/py-4/text-base -- lihat catatan No.101). Kali ini dinaikkan lagi: padding px-6 py-4 -&gt; px-7 py-5, ukuran teks text-base -&gt; text-lg, badge ikon platform h-8 w-8 -&gt; h-10 w-10, ikon di dalamnya h-4 w-4 -&gt; h-5 w-5, offset badge left-4 -&gt; left-5, padding judul (supaya baris kedua/ketiga teks panjang tidak tertindih badge) px-9 -&gt; px-11. Diterapkan konsisten di SEMUA varian render blok tautan di PagePreview.tsx: tautan biasa interaktif (TrackedLink) &amp; pratinjau non-interaktif dengan ikon, tautan terkunci (LockedLinkButton) &amp; pratinjau terkunci non-interaktif -- total 4 varian, semuanya konsisten. TIDAK menyentuh ukuran tombol beli produk maupun kartu produk (blok berbeda, di luar permintaan yang secara eksplisit hanya soal "blok tautan link"). TANPA perubahan backend. Diverifikasi E2E NYATA: kreator uji baru dibuat lewat API sungguhan, tautan YouTube ditambahkan, halaman dipublikasikan (is_published=true), halaman publik di-curl langsung -- HTML SSR terbukti berisi kelas px-7 py-5 text-lg pada blok tautan, badge ikon h-10 w-10 dengan ikon h-5 w-5 (badge YouTube merah #FF0000 terdeteksi benar dari URL), judul "YouTube Channel" tampil utuh. tsc/eslint bersih. Data &amp; akun uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>110</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Koreksi ukuran blok tautan -- kembalikan ke ukuran sebelum No.109, disamakan dengan referensi Linktree</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Feedback langsung pengguna (26 Juli 2026) setelah No.109: "masalah upload gambar masih belum berhasil ... lalu ini di pratinjau malah kebesaran bandingkan dengan kedua gambar yang saya berikan lalu perbaiki sama kan dengan referensi tersebut" (menyertakan 2 tangkapan layar Linktree asli sebagai acuan)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G110" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>No.109 (perbesar kedua kalinya ke px-7/py-5/text-lg + badge h-10 w-10) ternyata OVERSHOOT -- dibandingkan langsung dengan 2 tangkapan layar Linktree asli yang dikirim pengguna, ukuran baris tautan kami terasa terlalu besar/gemuk dibanding proporsi referensi. Dikembalikan ke ukuran hasil No.101 (px-6/py-4/text-base, badge ikon h-8 w-8, ikon h-4 w-4, offset left-4, padding judul px-9) yang sudah terbukti nyaman &amp; proporsional, BUKAN mundur ke ukuran paling awal px-5/py-3.5/text-sm. Diterapkan konsisten di ke-4 varian render tautan yang sama seperti No.109. TANPA perubahan backend. Diverifikasi E2E NYATA: kreator uji baru, tautan YouTube, halaman dipublikasikan, halaman publik di-curl langsung -- HTML SSR membuktikan kelas px-6 py-4 text-base + badge h-8 w-8 + ikon h-4 w-4 terpasang (kelas oversize No.109 TERBUKTI hilang total). tsc/eslint bersih. Data uji dibersihkan. CATATAN SOAL BUG UPLOAD GAMBAR (bagian pertama feedback pengguna): dicek ulang, endpoint &amp; alur unggah gambar latar (No.108) SUDAH diverifikasi bekerja benar di staging.jeonme.com (curl langsung membuktikan 200 image/jpeg pasca perbaikan policy MinIO). Namun production (jeonme.com) MASIH berjalan di versi lama (commit a968388, jauh sebelum Sprint 16 dimulai) -- BELUM PERNAH menerima deploy apa pun dari No.103 s.d. No.109/110 (redesain produk, perbaikan cache, footer, ukuran CTA, nama tampilan, ukuran tautan, wrap teks, tema foto, unggah gambar latar). Kalau pengguna menguji di jeonme.com (bukan staging), fitur unggah gambar latar memang BELUM ADA di sana sama sekali -- penyebab paling mungkin dari laporan "tidak berubah, tidak ada pesan error". Ditanyakan langsung ke pengguna apakah ingin seluruh batch perbaikan Sprint 16 di-deploy ke production sekarang.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6190,6 +6190,49 @@
       <c r="J110" t="inlineStr">
         <is>
           <t>No.109 (perbesar kedua kalinya ke px-7/py-5/text-lg + badge h-10 w-10) ternyata OVERSHOOT -- dibandingkan langsung dengan 2 tangkapan layar Linktree asli yang dikirim pengguna, ukuran baris tautan kami terasa terlalu besar/gemuk dibanding proporsi referensi. Dikembalikan ke ukuran hasil No.101 (px-6/py-4/text-base, badge ikon h-8 w-8, ikon h-4 w-4, offset left-4, padding judul px-9) yang sudah terbukti nyaman &amp; proporsional, BUKAN mundur ke ukuran paling awal px-5/py-3.5/text-sm. Diterapkan konsisten di ke-4 varian render tautan yang sama seperti No.109. TANPA perubahan backend. Diverifikasi E2E NYATA: kreator uji baru, tautan YouTube, halaman dipublikasikan, halaman publik di-curl langsung -- HTML SSR membuktikan kelas px-6 py-4 text-base + badge h-8 w-8 + ikon h-4 w-4 terpasang (kelas oversize No.109 TERBUKTI hilang total). tsc/eslint bersih. Data uji dibersihkan. CATATAN SOAL BUG UPLOAD GAMBAR (bagian pertama feedback pengguna): dicek ulang, endpoint &amp; alur unggah gambar latar (No.108) SUDAH diverifikasi bekerja benar di staging.jeonme.com (curl langsung membuktikan 200 image/jpeg pasca perbaikan policy MinIO). Namun production (jeonme.com) MASIH berjalan di versi lama (commit a968388, jauh sebelum Sprint 16 dimulai) -- BELUM PERNAH menerima deploy apa pun dari No.103 s.d. No.109/110 (redesain produk, perbaikan cache, footer, ukuran CTA, nama tampilan, ukuran tautan, wrap teks, tema foto, unggah gambar latar). Kalau pengguna menguji di jeonme.com (bukan staging), fitur unggah gambar latar memang BELUM ADA di sana sama sekali -- penyebab paling mungkin dari laporan "tidak berubah, tidak ada pesan error". Ditanyakan langsung ke pengguna apakah ingin seluruh batch perbaikan Sprint 16 di-deploy ke production sekarang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>111</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>BACKEND</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Perbaiki bug: foto profil (dan sampul produk/gambar latar) tidak berubah tampilannya setelah unggah ulang</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Klarifikasi langsung pengguna (26 Juli 2026) setelah investigasi No.108: "maksudnya foto profile yang error" -- ternyata bukan soal gambar latar, tapi foto profil yang diunggah ulang tidak terlihat berubah</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G111" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>AKAR MASALAH SESUNGGUHNYA (baru ditemukan, BUKAN bug policy MinIO No.108): UploadAvatar/UploadCustomBackground/UploadCover semuanya sengaja memakai KEY STORAGE YANG SELALU SAMA per pengguna/produk ("avatars/&lt;userID&gt;", "backgrounds/&lt;userID&gt;", "covers/&lt;productID&gt;") supaya unggah ulang MENIMPA file lama, bukan menumpuk selamanya di storage -- desain ini benar untuk sisi storage, TAPI konsekuensinya URL publik yang dikembalikan &amp; disimpan ke DB jadi BYTE-IDENTIK antara unggahan lama &amp; baru. Browser (dan CDN/proxy apa pun di depan storage) memakai URL sebagai kunci cache -- kalau URL tidak berubah, gambar LAMA yang di-cache tetap ditampilkan, WALAU unggahan baru sudah 100% sukses di server &amp; database sudah ter-update dengan benar. Ini persis menjelaskan laporan "upload tidak berubah, tidak ada pesan error" -- karena memang tidak ada yang gagal, hanya URL-nya yang tidak berubah sehingga cache browser tidak pernah tahu ada versi baru. DIVERIFIKASI dulu lewat curl langsung ke API staging SUNGGUHAN (bukan cuma lokal) sebelum menyimpulkan: upload avatar &amp; upload background keduanya terbukti 200 + URL publik terbukti 200 image/jpeg saat diakses langsung -- artinya backend memang tidak error sama sekali, konsisten dengan teori cache. DIPERBAIKI dengan menambahkan query param cache-busting "?v=&lt;unix-nano-timestamp&gt;" ke URL SEBELUM disimpan ke kolom DB (avatar_url / custom_background_value / cover_image_url) di KETIGA handler (PageHandler.UploadAvatar, PageHandler.UploadCustomBackground, ProductHandler.UploadCover) -- bukan cuma ditambahkan di respons API sesaat, supaya HALAMAN PUBLIK (bukan cuma dashboard) yang dimuat ulang nanti juga otomatis dapat URL baru dari DB. Query param acak dikonfirmasi diabaikan MinIO/S3 (objek yang sama tetap terlayani apa pun isi query string-nya) lewat pengujian langsung ke storage-staging.jeonme.com. Diverifikasi E2E NYATA: 2 unggahan avatar berurutan ke akun uji yang sama menghasilkan 2 URL BERBEDA (parameter ?v= berbeda), keduanya terbukti 200 image/jpeg saat diakses langsung, GET /dashboard/page membuktikan DB menyimpan URL versi TERBARU (bukan yang pertama). go build/vet/gofmt/test bersih (kegagalan worker_test.go soal DATABASE_URL sudah ada SEBELUM perubahan ini, tidak terkait). Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6233,6 +6233,92 @@
       <c r="J111" t="inlineStr">
         <is>
           <t>AKAR MASALAH SESUNGGUHNYA (baru ditemukan, BUKAN bug policy MinIO No.108): UploadAvatar/UploadCustomBackground/UploadCover semuanya sengaja memakai KEY STORAGE YANG SELALU SAMA per pengguna/produk ("avatars/&lt;userID&gt;", "backgrounds/&lt;userID&gt;", "covers/&lt;productID&gt;") supaya unggah ulang MENIMPA file lama, bukan menumpuk selamanya di storage -- desain ini benar untuk sisi storage, TAPI konsekuensinya URL publik yang dikembalikan &amp; disimpan ke DB jadi BYTE-IDENTIK antara unggahan lama &amp; baru. Browser (dan CDN/proxy apa pun di depan storage) memakai URL sebagai kunci cache -- kalau URL tidak berubah, gambar LAMA yang di-cache tetap ditampilkan, WALAU unggahan baru sudah 100% sukses di server &amp; database sudah ter-update dengan benar. Ini persis menjelaskan laporan "upload tidak berubah, tidak ada pesan error" -- karena memang tidak ada yang gagal, hanya URL-nya yang tidak berubah sehingga cache browser tidak pernah tahu ada versi baru. DIVERIFIKASI dulu lewat curl langsung ke API staging SUNGGUHAN (bukan cuma lokal) sebelum menyimpulkan: upload avatar &amp; upload background keduanya terbukti 200 + URL publik terbukti 200 image/jpeg saat diakses langsung -- artinya backend memang tidak error sama sekali, konsisten dengan teori cache. DIPERBAIKI dengan menambahkan query param cache-busting "?v=&lt;unix-nano-timestamp&gt;" ke URL SEBELUM disimpan ke kolom DB (avatar_url / custom_background_value / cover_image_url) di KETIGA handler (PageHandler.UploadAvatar, PageHandler.UploadCustomBackground, ProductHandler.UploadCover) -- bukan cuma ditambahkan di respons API sesaat, supaya HALAMAN PUBLIK (bukan cuma dashboard) yang dimuat ulang nanti juga otomatis dapat URL baru dari DB. Query param acak dikonfirmasi diabaikan MinIO/S3 (objek yang sama tetap terlayani apa pun isi query string-nya) lewat pengujian langsung ke storage-staging.jeonme.com. Diverifikasi E2E NYATA: 2 unggahan avatar berurutan ke akun uji yang sama menghasilkan 2 URL BERBEDA (parameter ?v= berbeda), keduanya terbukti 200 image/jpeg saat diakses langsung, GET /dashboard/page membuktikan DB menyimpan URL versi TERBARU (bukan yang pertama). go build/vet/gofmt/test bersih (kegagalan worker_test.go soal DATABASE_URL sudah ada SEBELUM perubahan ini, tidak terkait). Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>112</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Perkecil semua blok pratinjau halaman publik (tautan, produk, video/FAQ/form, event/booking/donasi) + ukuran font</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (26 Juli 2026): "buat tampilan di pratinjau semua blok jadi lebih kecil terutama blok tautan dan juga fontnya"</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G112" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Perkecilan MENYELURUH (bukan cuma blok tautan yang paling sering diminta sebelumnya): tautan (px-6/py-4/text-base -&gt; px-4/py-2.5/text-sm, badge ikon h-8 w-8 -&gt; h-7 w-7, ikon h-4 w-4 -&gt; h-3.5 w-3.5), kartu video/FAQ/form kontak (p-3.5 -&gt; p-3), lead capture/loyalitas/donasi (p-4 -&gt; p-3, ikon h-6 w-6 -&gt; h-5 w-5, judul text-sm -&gt; text-xs), event/booking (p-4 -&gt; p-3, judul &amp; harga text-sm -&gt; text-xs, keterangan text-xs -&gt; text-[11px]), grid produk (p-3.5 -&gt; p-2.5, ikon box h-7 w-7 -&gt; h-6 w-6), serta nama/bio profil (text-xl -&gt; text-lg, text-sm -&gt; text-xs). Perlakuan sama diterapkan ke LandingPagePreview (halaman tambahan No.99: heading text-3xl -&gt; text-2xl, teks text-sm -&gt; text-xs, tombol &amp; blok tautan default ikut diperkecil sama seperti versi bio). TANPA perubahan backend. Diverifikasi tsc/eslint bersih; verifikasi visual E2E menyusul sebagai bagian dari verifikasi No.113 (satu sesi curl yang sama, tema custom + tautan uji).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>113</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Panel kustomisasi Tombol &amp; Font diperlengkapi -- kelengkungan sudut, bayangan, warna teks tombol, warna teks halaman, font &amp; warna judul terpisah</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (26 Juli 2026, menyertai 2 tangkapan layar referensi panel "Buttons" &amp; "Fonts"): "di page design bagian tombol tambahkan settingan ini dan juga bagian font"</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G113" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>KOLOM DATABASE BARU (migrasi 000034_button_font_customization): custom_button_rounded (none/sm/md/full, default 'full'), custom_button_shadow (none/soft/strong/hard, default 'soft'), custom_button_text_color (hex, default '#FFFFFF'), custom_page_text_color (hex atau kosong = ikut tema, default kosong), custom_title_font (kosong = samakan dengan font halaman, default kosong), custom_title_color (hex atau kosong, default kosong). SEKALIGUS axis "Button style" diriombak: fill/outline/shadow -&gt; fill("Solid")/glass("Glass")/outline("Outline") -- gaya "shadow" lama DILEBUR jadi axis independen custom_button_shadow (persis seperti referensi yang punya baris "Button style" &amp; "Button shadow" terpisah), data lama dimigrasikan otomatis (button_style='shadow' -&gt; button_style='fill' + button_shadow='strong') supaya tampilan kreator yang sudah pakai gaya itu tidak berubah drastis. PERBAIKAN SEKALIGUS (ditemukan saat implementasi): sebelumnya custom_button_color/style HANYA memengaruhi tombol Beli/Dukung/Daftar (buyButton), SAMA SEKALI TIDAK memengaruhi kartu tautan utama (card/cardTitle) -- padahal di Linktree (rujukan utama desain ini) SEMUA tombol termasuk tautan berbagi satu gaya visual seragam. Diperbaiki dengan menyatukan buildCustomButtonClass() untuk card+cardTitle+buyButton sekaligus (page-themes.ts), jadi panel "Tombol" sekarang benar-benar mengubah tampilan blok tautan, bukan cuma tombol sekunder. UI baru di halaman Desain (dashboard/design/page.tsx): baris "Tombol" bertambah "Warna Teks Tombol" (color picker) + "Kelengkungan Sudut" (4 tombol pratinjau bentuk kotak-&gt;pil) + "Bayangan Tombol" (4 pilihan); baris "Font" bertambah "Warna Teks Halaman" (color picker + tombol kembalikan-ke-bawaan), toggle "Font Judul Terpisah" (default mati, sesuai referensi) yang saat aktif memunculkan dropdown font khusus judul, &amp; "Warna Judul" (color picker + tombol kembalikan-ke-bawaan). LINGKUP: HANYA halaman utama (UpdateMyPage/GetMyPage/GetPublicPage) -- halaman TAMBAHAN (No.98/ExtraPage) SENGAJA tidak diberi UI setara (belum ada panel desain terpisah untuk itu di dashboard, di luar permintaan eksplisit "page design" yang dimaksud pengguna), CustomThemeConfig field baru dibuat OPSIONAL persis supaya ExtraPage tetap kompatibel tanpa perlu mengisinya (jatuh balik ke default 'full'/'soft' dkk di getPageTheme). Diverifikasi E2E NYATA: PATCH tema custom lengkap (11 field) ke akun uji sungguhan, GET /dashboard/page membuktikan SEMUA field tersimpan benar, halaman publik di-curl langsung membuktikan CSS custom property (--custom-button-bg/--custom-button-text/--custom-page-text-color/--custom-title-color) &amp; kelas Tailwind (rounded-full shadow-md, text-[color:var(--custom-title-color)]) &amp; style inline font judul (Playfair Display) SEMUA terpasang benar di HTML SSR. Validasi backend dicoba salah (nilai 'shadow' lama DITOLAK 400, nilai custom_button_rounded tidak dikenal DITOLAK 400, font judul tidak dikenal DITOLAK 400) &amp; string kosong ("unset") DITERIMA 200 sesuai desain. go build/vet/gofmt/test &amp; tsc/eslint bersih (kegagalan worker_test.go soal DATABASE_URL sudah ada SEBELUM perubahan ini, tidak terkait). Data &amp; akun uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6319,6 +6319,92 @@
       <c r="J113" t="inlineStr">
         <is>
           <t>KOLOM DATABASE BARU (migrasi 000034_button_font_customization): custom_button_rounded (none/sm/md/full, default 'full'), custom_button_shadow (none/soft/strong/hard, default 'soft'), custom_button_text_color (hex, default '#FFFFFF'), custom_page_text_color (hex atau kosong = ikut tema, default kosong), custom_title_font (kosong = samakan dengan font halaman, default kosong), custom_title_color (hex atau kosong, default kosong). SEKALIGUS axis "Button style" diriombak: fill/outline/shadow -&gt; fill("Solid")/glass("Glass")/outline("Outline") -- gaya "shadow" lama DILEBUR jadi axis independen custom_button_shadow (persis seperti referensi yang punya baris "Button style" &amp; "Button shadow" terpisah), data lama dimigrasikan otomatis (button_style='shadow' -&gt; button_style='fill' + button_shadow='strong') supaya tampilan kreator yang sudah pakai gaya itu tidak berubah drastis. PERBAIKAN SEKALIGUS (ditemukan saat implementasi): sebelumnya custom_button_color/style HANYA memengaruhi tombol Beli/Dukung/Daftar (buyButton), SAMA SEKALI TIDAK memengaruhi kartu tautan utama (card/cardTitle) -- padahal di Linktree (rujukan utama desain ini) SEMUA tombol termasuk tautan berbagi satu gaya visual seragam. Diperbaiki dengan menyatukan buildCustomButtonClass() untuk card+cardTitle+buyButton sekaligus (page-themes.ts), jadi panel "Tombol" sekarang benar-benar mengubah tampilan blok tautan, bukan cuma tombol sekunder. UI baru di halaman Desain (dashboard/design/page.tsx): baris "Tombol" bertambah "Warna Teks Tombol" (color picker) + "Kelengkungan Sudut" (4 tombol pratinjau bentuk kotak-&gt;pil) + "Bayangan Tombol" (4 pilihan); baris "Font" bertambah "Warna Teks Halaman" (color picker + tombol kembalikan-ke-bawaan), toggle "Font Judul Terpisah" (default mati, sesuai referensi) yang saat aktif memunculkan dropdown font khusus judul, &amp; "Warna Judul" (color picker + tombol kembalikan-ke-bawaan). LINGKUP: HANYA halaman utama (UpdateMyPage/GetMyPage/GetPublicPage) -- halaman TAMBAHAN (No.98/ExtraPage) SENGAJA tidak diberi UI setara (belum ada panel desain terpisah untuk itu di dashboard, di luar permintaan eksplisit "page design" yang dimaksud pengguna), CustomThemeConfig field baru dibuat OPSIONAL persis supaya ExtraPage tetap kompatibel tanpa perlu mengisinya (jatuh balik ke default 'full'/'soft' dkk di getPageTheme). Diverifikasi E2E NYATA: PATCH tema custom lengkap (11 field) ke akun uji sungguhan, GET /dashboard/page membuktikan SEMUA field tersimpan benar, halaman publik di-curl langsung membuktikan CSS custom property (--custom-button-bg/--custom-button-text/--custom-page-text-color/--custom-title-color) &amp; kelas Tailwind (rounded-full shadow-md, text-[color:var(--custom-title-color)]) &amp; style inline font judul (Playfair Display) SEMUA terpasang benar di HTML SSR. Validasi backend dicoba salah (nilai 'shadow' lama DITOLAK 400, nilai custom_button_rounded tidak dikenal DITOLAK 400, font judul tidak dikenal DITOLAK 400) &amp; string kosong ("unset") DITERIMA 200 sesuai desain. go build/vet/gofmt/test &amp; tsc/eslint bersih (kegagalan worker_test.go soal DATABASE_URL sudah ada SEBELUM perubahan ini, tidak terkait). Data &amp; akun uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>114</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Perbaiki bug: ubah warna tombol/font menghapus tema preset yang sudah dipilih (custom_style_override)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Laporan bug pengguna (26 Juli 2026): "kenapa saya ubah warna tombol ataupun font malah merubah tema yang sudah saya pilih"</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G114" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>AKAR MASALAH: sejak No.113, panel Tombol &amp; Font memakai handleCustomize yang SELALU memaksa `theme` berubah jadi 'custom' -- kalau kreator sudah memilih preset (mis. "Midnight") lalu cuma menyentuh warna tombol, SELURUH tema ikut berganti jadi tampilan dasar "Custom" (base sunrise), membuang glow/avatarRing/productCard/dst milik preset yang sudah dipilih. DIPERBAIKI dengan memisahkan 2 konsep: `theme` (identitas latar/mood -- preset ATAU 'custom' latar) TIDAK lagi berubah gara-gara panel Tombol/Font; kustomisasi tombol/font sekarang jadi LAPISAN independen yang bisa diterapkan di ATAS tema apa pun (preset maupun custom), diaktifkan lewat kolom baru boolean custom_style_override (migrasi 000035) -- dinyalakan otomatis oleh handleStyleOverride (fungsi baru, menggantikan handleCustomize KHUSUS di panel Tombol/Font) TANPA menyentuh `theme` sama sekali. Panel Latar (Wallpaper) TETAP memakai handleCustomize lama (mempromosikan ke 'custom') karena latar memang MENDEFINISIKAN tema, beda dari tombol/font yang cuma aksen. getPageTheme (page-themes.ts) dirombak total: base tema selalu diambil dari preset AKTIF (bukan hardcode sunrise), lalu kustomisasi latar (kalau theme='custom') &amp; kustomisasi tombol/font (kalau custom_style_override=true) diterapkan sebagai 2 lapisan independen di atasnya. Data lama dimigrasikan otomatis: kreator yang SUDAH pakai theme='custom' sebelumnya (yang berarti SELALU menerapkan tombol/font custom, itulah definisi tema mereka) langsung dapat custom_style_override=true supaya tampilan mereka tidak berubah sama sekali. Diverifikasi E2E NYATA: akun uji diset theme='midnight' via API sungguhan, halaman publik di-curl -- latar gelap khas Midnight (#0A1512) &amp; glow accent terbukti tampil; LALU warna+gaya tombol diubah (merah, outline) via API yang SAMA -- GET /dashboard/page membuktikan `theme` TETAP 'midnight' (bukan berubah jadi 'custom'); halaman publik di-curl ULANG (setelah menunggu lewat cache fetch Next.js 60 detik) membuktikan latar Midnight (glow/avatarRing accent) MASIH ada SEKALIGUS tombol tautan sudah memakai gaya outline merah (--custom-button-bg:#FF0000, border-2 border warna kustom) -- kedua lapisan tampil BERSAMAAN dengan benar, bug terbukti hilang. go build/vet/gofmt/test &amp; tsc/eslint bersih. Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>115</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Pratinjau: footer (Privacy dkk) selalu tampil, urutan CTA "Buat halaman gratis" tetap di atas footer, hilangkan logo Jeonme di topbar, perkecil lagi semua blok</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (26 Juli 2026, menyertai laporan No.114): "saya mau pratinjau buat lebih kecil lagi dan tampilkan seluruh footer privay dll dan harusnya bagian buat halaman gratis di jeonme itu selalu berada di bagian bawah di atas footer nya dan hilangkan logo jeonmenya"</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G115" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>FOOTER: sebelumnya PageFooterLinks (6 item: Cookie/Report/Privacy/Explore/About/More) hanya dirender kalau interactive=true -- di PRATINJAU DASHBOARD (LivePreviewPanel selalu interactive=false) footer TIDAK PERNAH muncul sama sekali, itulah sebabnya kreator tidak melihatnya sebelum publish. Diperbaiki: footer SEKARANG SELALU dirender (gerbang `interactive &amp;&amp;` dihapus) baik di pratinjau maupun halaman publik sungguhan -- item "Laporkan" sudah aman tanpa pageId (fallback pesan jelas, bukan error, lihat PageFooterLinks). URUTAN: pil "Buat halaman gratis di Jeonme" SUDAH &amp; TETAP dirender sebelum (di atas) footer secara DOM/visual di dalam wrapper flex-col yang sama -- begitu footer akhirnya terlihat (perbaikan di atas), urutan yang dimaksud otomatis benar tanpa perlu perubahan struktur tambahan. LOGO: elemen logo Jeonme di pojok kiri-atas topbar (ditambahkan sebelumnya di No.101/Desain 2.0 ala Linktree) DIHAPUS -- topbar sekarang cuma tombol share (rata kanan), branding Jeonme cukup lewat pil "Buat halaman gratis" di bagian bawah (ikon kecilnya TIDAK dihapus, beda tujuan -- itu bagian dari CTA pendaftaran). Berlaku di KEDUA render (halaman bio biasa &amp; LandingPagePreview No.99). PERKECIL LAGI (putaran ketiga untuk blok tautan, kedua untuk blok lain): tautan px-4/py-2.5/text-sm -&gt; px-3.5/py-2/text-xs, badge ikon h-7 w-7 -&gt; h-6 w-6, ikon h-3.5 w-3.5 -&gt; h-3 w-3; nama profil text-lg -&gt; text-base; kartu video/FAQ/form/leadcapture/event/booking/donasi p-3 -&gt; p-2.5; grid produk sudah di titik minimum wajar, tidak diperkecil lagi. LandingPagePreview ikut disamakan proporsinya. TANPA perubahan backend untuk bagian ini. Diverifikasi E2E NYATA (satu sesi curl sama dengan No.114): HTML SSR membuktikan topbar cuma berisi tombol share (elemen &lt;a href="https://jeonme.com"&gt; logo TERBUKTI hilang), footer LENGKAP dengan 6 item &amp; kelas ukuran font/warna sesuai tema (text-white/30 utk Midnight) tampil setelah pil CTA, kelas ukuran blok tautan baru (px-3.5 py-2 text-xs, badge h-6 w-6) terpasang benar. tsc/eslint bersih.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6405,6 +6405,49 @@
       <c r="J115" t="inlineStr">
         <is>
           <t>FOOTER: sebelumnya PageFooterLinks (6 item: Cookie/Report/Privacy/Explore/About/More) hanya dirender kalau interactive=true -- di PRATINJAU DASHBOARD (LivePreviewPanel selalu interactive=false) footer TIDAK PERNAH muncul sama sekali, itulah sebabnya kreator tidak melihatnya sebelum publish. Diperbaiki: footer SEKARANG SELALU dirender (gerbang `interactive &amp;&amp;` dihapus) baik di pratinjau maupun halaman publik sungguhan -- item "Laporkan" sudah aman tanpa pageId (fallback pesan jelas, bukan error, lihat PageFooterLinks). URUTAN: pil "Buat halaman gratis di Jeonme" SUDAH &amp; TETAP dirender sebelum (di atas) footer secara DOM/visual di dalam wrapper flex-col yang sama -- begitu footer akhirnya terlihat (perbaikan di atas), urutan yang dimaksud otomatis benar tanpa perlu perubahan struktur tambahan. LOGO: elemen logo Jeonme di pojok kiri-atas topbar (ditambahkan sebelumnya di No.101/Desain 2.0 ala Linktree) DIHAPUS -- topbar sekarang cuma tombol share (rata kanan), branding Jeonme cukup lewat pil "Buat halaman gratis" di bagian bawah (ikon kecilnya TIDAK dihapus, beda tujuan -- itu bagian dari CTA pendaftaran). Berlaku di KEDUA render (halaman bio biasa &amp; LandingPagePreview No.99). PERKECIL LAGI (putaran ketiga untuk blok tautan, kedua untuk blok lain): tautan px-4/py-2.5/text-sm -&gt; px-3.5/py-2/text-xs, badge ikon h-7 w-7 -&gt; h-6 w-6, ikon h-3.5 w-3.5 -&gt; h-3 w-3; nama profil text-lg -&gt; text-base; kartu video/FAQ/form/leadcapture/event/booking/donasi p-3 -&gt; p-2.5; grid produk sudah di titik minimum wajar, tidak diperkecil lagi. LandingPagePreview ikut disamakan proporsinya. TANPA perubahan backend untuk bagian ini. Diverifikasi E2E NYATA (satu sesi curl sama dengan No.114): HTML SSR membuktikan topbar cuma berisi tombol share (elemen &lt;a href="https://jeonme.com"&gt; logo TERBUKTI hilang), footer LENGKAP dengan 6 item &amp; kelas ukuran font/warna sesuai tema (text-white/30 utk Midnight) tampil setelah pil CTA, kelas ukuran blok tautan baru (px-3.5 py-2 text-xs, badge h-6 w-6) terpasang benar. tsc/eslint bersih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>116</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Hilangkan ikon di dalam pil "Buat halaman gratis" + ikon platform per tautan jadi polos tanpa badge lingkaran</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (26 Juli 2026): "hilangkan juga icon insede buat halaman gratis, lalu saya mau juga icon tiap tautan itu hanya icon nya saja tanpa ada background nya"</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G116" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Dua perubahan: (1) ikon kecil Jeonme di dalam pil CTA "Buat halaman gratis di Jeonme" dihapus, tinggal teksnya saja (logo topbar SUDAH dihapus di No.115 -- ditemukan sekalian SATU topbar LandingPagePreview yang TERLEWAT waktu itu, ikut dibereskan sekarang, konsisten dengan halaman bio biasa). (2) Badge lingkaran berwarna di belakang ikon platform tiap tautan (YouTube/TikTok/WhatsApp/dst) DIHAPUS -- lib/link-icons.ts (detectLinkIcon) ditambah field baru `iconColorClass` per platform (warna brand SOLID untuk ikon itu sendiri, mis. text-[#FF0000] YouTube, text-[#25D366] WhatsApp) terpisah dari `badgeClass` lama (dipertahankan APA ADANYA, masih dipakai daftar tautan dashboard/links/page.tsx -- konteks manajemen berbeda dari tampilan pengunjung, TIDAK diubah). PagePreview.tsx (kedua render, bio &amp; landing) diganti dari span lingkaran ber-bg+rounded-full jadi span polos tanpa latar, ikon dibesarkan sedikit (h-3 w-3 -&gt; penuh h-5 w-5 di wadah tanpa badge) supaya tetap enak dilihat walau tanpa lingkaran pembatas. CATATAN JUJUR: warna brand TikTok &amp; X memakai hitam -- dirancang aslinya di atas badge terang, jadi kontras bisa berkurang kalau kartu tautan kebetulan gelap (tema Midnight/Noir dkk); belum ada penyesuaian otomatis per-tema untuk kasus ini. Diverifikasi E2E NYATA: tautan YouTube &amp; tautan generik dibuat lewat API sungguhan, halaman publik di-curl langsung -- kelas rounded-full/bg badge TERBUKTI hilang total dari span ikon, ikon YouTube terbukti memakai text-[#FF0000], tautan generik memakai text-primary (fallback), &amp; string "logo-icon.png" TERBUKTI tidak muncul sama sekali di seluruh HTML halaman (baik topbar maupun pil CTA). tsc/eslint bersih. Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6448,6 +6448,49 @@
       <c r="J116" t="inlineStr">
         <is>
           <t>Dua perubahan: (1) ikon kecil Jeonme di dalam pil CTA "Buat halaman gratis di Jeonme" dihapus, tinggal teksnya saja (logo topbar SUDAH dihapus di No.115 -- ditemukan sekalian SATU topbar LandingPagePreview yang TERLEWAT waktu itu, ikut dibereskan sekarang, konsisten dengan halaman bio biasa). (2) Badge lingkaran berwarna di belakang ikon platform tiap tautan (YouTube/TikTok/WhatsApp/dst) DIHAPUS -- lib/link-icons.ts (detectLinkIcon) ditambah field baru `iconColorClass` per platform (warna brand SOLID untuk ikon itu sendiri, mis. text-[#FF0000] YouTube, text-[#25D366] WhatsApp) terpisah dari `badgeClass` lama (dipertahankan APA ADANYA, masih dipakai daftar tautan dashboard/links/page.tsx -- konteks manajemen berbeda dari tampilan pengunjung, TIDAK diubah). PagePreview.tsx (kedua render, bio &amp; landing) diganti dari span lingkaran ber-bg+rounded-full jadi span polos tanpa latar, ikon dibesarkan sedikit (h-3 w-3 -&gt; penuh h-5 w-5 di wadah tanpa badge) supaya tetap enak dilihat walau tanpa lingkaran pembatas. CATATAN JUJUR: warna brand TikTok &amp; X memakai hitam -- dirancang aslinya di atas badge terang, jadi kontras bisa berkurang kalau kartu tautan kebetulan gelap (tema Midnight/Noir dkk); belum ada penyesuaian otomatis per-tema untuk kasus ini. Diverifikasi E2E NYATA: tautan YouTube &amp; tautan generik dibuat lewat API sungguhan, halaman publik di-curl langsung -- kelas rounded-full/bg badge TERBUKTI hilang total dari span ikon, ikon YouTube terbukti memakai text-[#FF0000], tautan generik memakai text-primary (fallback), &amp; string "logo-icon.png" TERBUKTI tidak muncul sama sekali di seluruh HTML halaman (baik topbar maupun pil CTA). tsc/eslint bersih. Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>117</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Perbaiki bug: pengaturan "Kelengkungan Sudut" di panel Tombol tidak berpengaruh sama sekali</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Laporan bug pengguna (27 Juli 2026): "fix kelengkungan sudut tidak berfungsi"</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G117" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>AKAR MASALAH: sejak No.113, PagePreview.tsx menulis kelas `rounded-xl` LANGSUNG di className blok tautan/tombol (mis. `rounded-xl px-3.5 py-2 ... ${theme.card}`), lalu getPageTheme (lewat buildCustomButtonClass) MENAMBAHKAN kelas rounded-none/sm/md/full ke dalam theme.card/buyButton di sebelahnya -- dua kelas `rounded-*` bersaing untuk properti CSS border-radius yang SAMA dalam satu className. Urutan penulisan string TIDAK menentukan siapa menang di Tailwind (itu ditentukan urutan Tailwind menghasilkan aturan CSS-nya sendiri, bukan urutan kelas di JSX) -- hasilnya `rounded-xl` yang selalu menang apa pun pilihan kreator di panel "Kelengkungan Sudut", persis seperti yang dilaporkan. DIPERBAIKI dengan memindahkan kelengkungan sudut ke SATU sumber kebenaran: field baru `cardRounded` di PageTheme (page-themes.ts) -- opsional, default undefined berarti JSX jatuh balik ke "rounded-xl" (perilaku lama utuh untuk SEMUA tema preset, tidak ada regresi), HANYA diisi eksplisit oleh getPageTheme saat custom_style_override aktif (rounded-none/sm/md/full sesuai pilihan). buildCustomButtonClass TIDAK LAGI menyisipkan kelas rounded ke dalam string tombol. 8 lokasi rounded-xl hardcode di PagePreview.tsx (4 varian blok tautan bio + 2 tombol CTA landing + 2 blok default landing) diganti jadi `${theme.cardRounded ?? "rounded-xl"}`. LINGKUP: HANYA blok tautan &amp; tombol CTA yang dirender langsung di PagePreview.tsx -- tombol sekunder Beli/Dukung/Daftar/Pilih Jadwal (BuyProductButton/BookSlotButton/LeadCaptureForm) SENGAJA TIDAK disentuh, masih pakai `rounded-lg` tetap sesuai konvensi lama (ukuran visual lebih kecil, peran berbeda dari tombol utama) -- di luar cakupan laporan bug ini, bisa diperluas kalau diminta terpisah. Diverifikasi E2E NYATA: custom_button_rounded diset 'none' via API sungguhan -- halaman publik di-curl langsung membuktikan kelas `rounded-none` terpasang &amp; `rounded-xl` TERBUKTI hilang total dari blok tautan; diubah lagi ke 'full' -- setelah menunggu lewat cache fetch Next.js 60 detik, kelas `rounded-full` terbukti menggantikan `rounded-none` dengan benar. tsc/eslint bersih. TANPA perubahan backend/migrasi (murni bug tampilan sisi klien). Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6491,6 +6491,49 @@
       <c r="J117" t="inlineStr">
         <is>
           <t>AKAR MASALAH: sejak No.113, PagePreview.tsx menulis kelas `rounded-xl` LANGSUNG di className blok tautan/tombol (mis. `rounded-xl px-3.5 py-2 ... ${theme.card}`), lalu getPageTheme (lewat buildCustomButtonClass) MENAMBAHKAN kelas rounded-none/sm/md/full ke dalam theme.card/buyButton di sebelahnya -- dua kelas `rounded-*` bersaing untuk properti CSS border-radius yang SAMA dalam satu className. Urutan penulisan string TIDAK menentukan siapa menang di Tailwind (itu ditentukan urutan Tailwind menghasilkan aturan CSS-nya sendiri, bukan urutan kelas di JSX) -- hasilnya `rounded-xl` yang selalu menang apa pun pilihan kreator di panel "Kelengkungan Sudut", persis seperti yang dilaporkan. DIPERBAIKI dengan memindahkan kelengkungan sudut ke SATU sumber kebenaran: field baru `cardRounded` di PageTheme (page-themes.ts) -- opsional, default undefined berarti JSX jatuh balik ke "rounded-xl" (perilaku lama utuh untuk SEMUA tema preset, tidak ada regresi), HANYA diisi eksplisit oleh getPageTheme saat custom_style_override aktif (rounded-none/sm/md/full sesuai pilihan). buildCustomButtonClass TIDAK LAGI menyisipkan kelas rounded ke dalam string tombol. 8 lokasi rounded-xl hardcode di PagePreview.tsx (4 varian blok tautan bio + 2 tombol CTA landing + 2 blok default landing) diganti jadi `${theme.cardRounded ?? "rounded-xl"}`. LINGKUP: HANYA blok tautan &amp; tombol CTA yang dirender langsung di PagePreview.tsx -- tombol sekunder Beli/Dukung/Daftar/Pilih Jadwal (BuyProductButton/BookSlotButton/LeadCaptureForm) SENGAJA TIDAK disentuh, masih pakai `rounded-lg` tetap sesuai konvensi lama (ukuran visual lebih kecil, peran berbeda dari tombol utama) -- di luar cakupan laporan bug ini, bisa diperluas kalau diminta terpisah. Diverifikasi E2E NYATA: custom_button_rounded diset 'none' via API sungguhan -- halaman publik di-curl langsung membuktikan kelas `rounded-none` terpasang &amp; `rounded-xl` TERBUKTI hilang total dari blok tautan; diubah lagi ke 'full' -- setelah menunggu lewat cache fetch Next.js 60 detik, kelas `rounded-full` terbukti menggantikan `rounded-none` dengan benar. tsc/eslint bersih. TANPA perubahan backend/migrasi (murni bug tampilan sisi klien). Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>118</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Unggah gambar kustom per tautan (menggantikan ikon platform otomatis)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026): "buat supaya kita bisa upload image untuk tautan link kita dan sesuaikan juga ukuran nya jadi tambahkan saja icon image dibawah tautan link yang baru dibuat"</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G118" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>KOLOM DATABASE BARU (migrasi 000036): links.custom_icon_url VARCHAR(500) DEFAULT '' -- kosong berarti tetap pakai deteksi ikon platform otomatis dari URL (lib/link-icons.ts, TIDAK diubah/dihapus, tetap jadi fallback). ENDPOINT BARU: POST /dashboard/links/:id/icon (unggah, pola SAMA PERSIS seperti UploadAvatar -- validasi jpg/png/webp, maks 2MB, key storage SELALU "link-icons/&lt;linkID&gt;" [unggah ulang menimpa bukan menumpuk], query param cache-busting "?v=&lt;timestamp&gt;" WAJIB disimpan ke DB [pelajaran dari bug No.111]) &amp; DELETE /dashboard/links/:id/icon (kembali ke deteksi otomatis). LinksHandler ditambah field Storage (sebelumnya cuma DB/Queue/RDB) -- constructor &amp; pemanggilnya di routes.go diperbarui. BUCKET POLICY: prefix "link-icons" ditambahkan LANGSUNG ke pemanggilan EnsurePublicRead di main.go (proaktif, BUKAN ditemukan lewat trial-error 403 seperti No.108 -- pelajaran dari bug bucket policy sebelumnya diterapkan sejak awal). UI dashboard/links/page.tsx: badge ikon platform di baris tautan diganti jadi gambar kustom (bulat, object-cover) kalau sudah diunggah; baris ikon aksi (jadwal/kunci/hapus) bertambah tombol unggah (ikon kamera, styled sebagai label atas input file tersembunyi, sama seperti pola unggah avatar/latar) + tombol hapus ikon kustom (muncul cuma kalau sudah ada). Halaman publik (PagePreview.tsx, kedua varian interaktif/pratinjau): gambar kustom (kalau ada) MENGGANTIKAN ikon platform terdeteksi, ukuran disesuaikan sedikit lebih besar (h-6 w-6, dibanding ikon garis otomatis h-5 w-5) &amp; dibuat bulat (rounded-full object-cover) supaya proporsional sebagai gambar/logo asli, bukan glyph sederhana. Diverifikasi E2E NYATA: tautan uji dibuat lewat API sungguhan, gambar diunggah -- URL yang dikembalikan terbukti 200 image/jpeg saat diakses langsung (policy bucket benar sejak awal, tidak perlu perbaikan susulan), GET /dashboard/links membuktikan custom_icon_url tersimpan benar, halaman publik di-curl langsung membuktikan gambar &amp; kelas ukuran baru terpasang di HTML SSR. Dicoba hapus ikon (DELETE) -- custom_icon_url kembali kosong, otomatis balik ke ikon platform terdeteksi. go build/vet/gofmt/test &amp; tsc/eslint bersih (kegagalan worker_test.go soal DATABASE_URL sudah ada sebelumnya, tidak terkait). Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6534,6 +6534,49 @@
       <c r="J118" t="inlineStr">
         <is>
           <t>KOLOM DATABASE BARU (migrasi 000036): links.custom_icon_url VARCHAR(500) DEFAULT '' -- kosong berarti tetap pakai deteksi ikon platform otomatis dari URL (lib/link-icons.ts, TIDAK diubah/dihapus, tetap jadi fallback). ENDPOINT BARU: POST /dashboard/links/:id/icon (unggah, pola SAMA PERSIS seperti UploadAvatar -- validasi jpg/png/webp, maks 2MB, key storage SELALU "link-icons/&lt;linkID&gt;" [unggah ulang menimpa bukan menumpuk], query param cache-busting "?v=&lt;timestamp&gt;" WAJIB disimpan ke DB [pelajaran dari bug No.111]) &amp; DELETE /dashboard/links/:id/icon (kembali ke deteksi otomatis). LinksHandler ditambah field Storage (sebelumnya cuma DB/Queue/RDB) -- constructor &amp; pemanggilnya di routes.go diperbarui. BUCKET POLICY: prefix "link-icons" ditambahkan LANGSUNG ke pemanggilan EnsurePublicRead di main.go (proaktif, BUKAN ditemukan lewat trial-error 403 seperti No.108 -- pelajaran dari bug bucket policy sebelumnya diterapkan sejak awal). UI dashboard/links/page.tsx: badge ikon platform di baris tautan diganti jadi gambar kustom (bulat, object-cover) kalau sudah diunggah; baris ikon aksi (jadwal/kunci/hapus) bertambah tombol unggah (ikon kamera, styled sebagai label atas input file tersembunyi, sama seperti pola unggah avatar/latar) + tombol hapus ikon kustom (muncul cuma kalau sudah ada). Halaman publik (PagePreview.tsx, kedua varian interaktif/pratinjau): gambar kustom (kalau ada) MENGGANTIKAN ikon platform terdeteksi, ukuran disesuaikan sedikit lebih besar (h-6 w-6, dibanding ikon garis otomatis h-5 w-5) &amp; dibuat bulat (rounded-full object-cover) supaya proporsional sebagai gambar/logo asli, bukan glyph sederhana. Diverifikasi E2E NYATA: tautan uji dibuat lewat API sungguhan, gambar diunggah -- URL yang dikembalikan terbukti 200 image/jpeg saat diakses langsung (policy bucket benar sejak awal, tidak perlu perbaikan susulan), GET /dashboard/links membuktikan custom_icon_url tersimpan benar, halaman publik di-curl langsung membuktikan gambar &amp; kelas ukuran baru terpasang di HTML SSR. Dicoba hapus ikon (DELETE) -- custom_icon_url kembali kosong, otomatis balik ke ikon platform terdeteksi. go build/vet/gofmt/test &amp; tsc/eslint bersih (kegagalan worker_test.go soal DATABASE_URL sudah ada sebelumnya, tidak terkait). Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>119</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Blok "Lokasi" (Maps) -- tautan Google Maps, bisa tampil sebagai peta tertanam atau tautan langsung</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026, menyertai tangkapan layar referensi fitur "Maps" Linktree): "tambahkan lokasi kami dengan setting seperti ini ... jadi bisa menambahkan link untuk lokasi dengan setting yang ada di gambar bisa di embed"</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G119" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Block_type BARU "maps" -- TIDAK perlu migrasi database (memakai ulang kolom url + block_data JSONB yang sudah ada, pola sama seperti video/faq/contact_form No.77). block_data = {embed: boolean, embed_lat/embed_lng: number (terisi otomatis kalau embed=true)}. TANTANGAN TEKNIS UTAMA: tautan berbagi Google Maps yang dipakai kreator biasanya SHORT LINK (maps.app.goo.gl) yang tidak bisa langsung ditanam sebagai iframe (short link bukan format embeddable) -- diselesaikan dengan fungsi backend baru resolveMapsEmbedCoords (links.go): SATU permintaan HTTP mengikuti redirect short link sampai ke URL tempat lengkap, koordinat lat/lng diekstrak dari pola URL standar "@lat,lng,zoom" yang SELALU ada di sana, lalu dipakai untuk membangun iframe src "https://www.google.com/maps?q=lat,lng&amp;z=16&amp;output=embed" -- trik resmi Google (sebelum Embed API berbayar ada) yang TERBUKTI masih berfungsi TANPA API key lewat verifikasi langsung (curl -L ke short link contoh dari pengguna sendiri berhasil resolve ke lokasi PIKO Carwash dan Cafe, &amp; URL embed hasil akhir terbukti redirect ke endpoint resmi google.com/maps/embed). Resolusi dilakukan SEKALI saat blok dibuat/disunting (bukan tiap kunjungan halaman publik) -- disimpan permanen di block_data. KEAMANAN: whitelist ketat domain (hanya google.com/maps.google.com/goo.gl/maps.app.goo.gl) diperiksa di URL awal MAUPUN setiap hop redirect, mencegah endpoint ini disalahgunakan jadi celah SSRF (server dipaksa memanggil alamat sembarang/internal). "Link behavior" (radio, sesuai referensi): "Buka tautan langsung" (URL asli dibuka tab baru, tanpa panggilan jaringan sama sekali) vs "Tampilkan peta tertanam" (iframe di halaman publik, komponen baru MapsEmbedBlock.tsx, pola SAMA seperti VideoEmbedBlock.tsx -- murni render, tidak ada panggilan jaringan sisi klien). UI dashboard/links/page.tsx: tile "Lokasi" baru di kategori Konten, form tambah/edit blok dengan input URL + 2 radio button match referensi, ikon peta baru (IconMapPin, components/icons.tsx). Diverifikasi E2E NYATA (2 sesi curl terpisah): mode embed -- blok dibuat dengan short link ASLI dari referensi pengguna, backend terbukti resolve jadi lat=-5.3855532/lng=105.2527608, halaman publik di-curl langsung membuktikan iframe dengan URL embed yang benar terpasang; mode direct-link -- blok dibuat dengan embed=false, halaman publik terbukti merender &lt;a href&gt; polos ke URL asli, TANPA panggilan resolve (diverifikasi tidak ada koordinat di block_data). Validasi dicoba salah: URL non-Google Maps ditolak 400 (guard SSRF berfungsi), URL kosong ditolak 400. go build/vet/gofmt/test bersih (kegagalan worker_test.go soal DATABASE_URL sudah ada sebelumnya, tidak terkait) &amp; tsc/eslint bersih. Data uji dibersihkan. LINGKUP: UI dashboard HANYA di halaman Tautan utama (bukan halaman tambahan No.98/ExtraPage) -- backend (CreateBlockForPage) tetap ikut mendukung block_type "maps" untuk konsistensi API, tapi belum ada panel dashboard terpisah untuk itu (sama seperti batasan lingkup No.113).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6577,6 +6577,92 @@
       <c r="J119" t="inlineStr">
         <is>
           <t>Block_type BARU "maps" -- TIDAK perlu migrasi database (memakai ulang kolom url + block_data JSONB yang sudah ada, pola sama seperti video/faq/contact_form No.77). block_data = {embed: boolean, embed_lat/embed_lng: number (terisi otomatis kalau embed=true)}. TANTANGAN TEKNIS UTAMA: tautan berbagi Google Maps yang dipakai kreator biasanya SHORT LINK (maps.app.goo.gl) yang tidak bisa langsung ditanam sebagai iframe (short link bukan format embeddable) -- diselesaikan dengan fungsi backend baru resolveMapsEmbedCoords (links.go): SATU permintaan HTTP mengikuti redirect short link sampai ke URL tempat lengkap, koordinat lat/lng diekstrak dari pola URL standar "@lat,lng,zoom" yang SELALU ada di sana, lalu dipakai untuk membangun iframe src "https://www.google.com/maps?q=lat,lng&amp;z=16&amp;output=embed" -- trik resmi Google (sebelum Embed API berbayar ada) yang TERBUKTI masih berfungsi TANPA API key lewat verifikasi langsung (curl -L ke short link contoh dari pengguna sendiri berhasil resolve ke lokasi PIKO Carwash dan Cafe, &amp; URL embed hasil akhir terbukti redirect ke endpoint resmi google.com/maps/embed). Resolusi dilakukan SEKALI saat blok dibuat/disunting (bukan tiap kunjungan halaman publik) -- disimpan permanen di block_data. KEAMANAN: whitelist ketat domain (hanya google.com/maps.google.com/goo.gl/maps.app.goo.gl) diperiksa di URL awal MAUPUN setiap hop redirect, mencegah endpoint ini disalahgunakan jadi celah SSRF (server dipaksa memanggil alamat sembarang/internal). "Link behavior" (radio, sesuai referensi): "Buka tautan langsung" (URL asli dibuka tab baru, tanpa panggilan jaringan sama sekali) vs "Tampilkan peta tertanam" (iframe di halaman publik, komponen baru MapsEmbedBlock.tsx, pola SAMA seperti VideoEmbedBlock.tsx -- murni render, tidak ada panggilan jaringan sisi klien). UI dashboard/links/page.tsx: tile "Lokasi" baru di kategori Konten, form tambah/edit blok dengan input URL + 2 radio button match referensi, ikon peta baru (IconMapPin, components/icons.tsx). Diverifikasi E2E NYATA (2 sesi curl terpisah): mode embed -- blok dibuat dengan short link ASLI dari referensi pengguna, backend terbukti resolve jadi lat=-5.3855532/lng=105.2527608, halaman publik di-curl langsung membuktikan iframe dengan URL embed yang benar terpasang; mode direct-link -- blok dibuat dengan embed=false, halaman publik terbukti merender &lt;a href&gt; polos ke URL asli, TANPA panggilan resolve (diverifikasi tidak ada koordinat di block_data). Validasi dicoba salah: URL non-Google Maps ditolak 400 (guard SSRF berfungsi), URL kosong ditolak 400. go build/vet/gofmt/test bersih (kegagalan worker_test.go soal DATABASE_URL sudah ada sebelumnya, tidak terkait) &amp; tsc/eslint bersih. Data uji dibersihkan. LINGKUP: UI dashboard HANYA di halaman Tautan utama (bukan halaman tambahan No.98/ExtraPage) -- backend (CreateBlockForPage) tetap ikut mendukung block_type "maps" untuk konsistensi API, tapi belum ada panel dashboard terpisah untuk itu (sama seperti batasan lingkup No.113).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>120</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Hapus menu "Latar" di Desain + halaman Desain/Tautan/Produk dirapikan ke tengah layar</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026): "hilangkan menu latar di design, lalu saya mau buat semua halaman yang belum rata tengah buat semua ke tengah termasuk design dan juga tautan dan sisanya"</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G120" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>LATAR: baris accordion "Latar" (Wallpaper: warna solid/gradien/gambar) dihapus SEPENUHNYA dari halaman Desain -- kolom custom_background_type/value di database TIDAK dihapus/diubah, kreator yang SUDAH mengatur latar kustom sebelumnya tetap tampil apa adanya di halaman publik (getPageTheme masih membacanya untuk theme='custom'), cuma tidak ada lagi UI untuk MENGUBAHNYA dari dashboard. RATA TENGAH: ditemukan lewat audit SEMUA 20 halaman dashboard -- 17 dari 20 SUDAH "mx-auto max-w-*" (rata tengah), HANYA 3 yang belum: Desain, Tautan, Produk (ketiganya berbagi pola sama: grid 2 kolom "lg:grid lg:grid-cols-[1fr_360px]" untuk konten+pratinjau langsung, TANPA mx-auto/max-width di wadah terluar -- di layar lebar, blok 2 kolom ini menempel rata KIRI dengan area kosong besar di kanan, bukan rata tengah seperti 17 halaman lain). Diperbaiki dengan menambah "mx-auto max-w-6xl" ke wadah grid terluar ketiganya -- cukup lebar untuk kolom konten (max-w-2xl/max-w-3xl) + panel pratinjau (360px) + jarak, tanpa memotong apa pun. Diverifikasi tsc/eslint bersih; verifikasi visual rata-tengah di layar lebar sungguhan memerlukan sesi browser (di luar kapasitas verifikasi curl sesi ini, dicatat jujur).</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>121</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Menu Desain (Tema/Header/Tombol/Font) jadi halaman tersendiri, bukan accordion expand-di-tempat</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026): "lalu saya mau semua menu yang di design ketika di klik masuk ke halaman baru untuk setting nya"</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G121" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Restrukturisasi arsitektur: sebelumnya SATU komponen (dashboard/design/page.tsx) merender SEMUA pengaturan lewat accordion expand/collapse di tempat (AccordionRow + state expandedSection). Sekarang tiap menu (Tema/Header/Tombol/Font -- Latar dihapus di No.120) jadi RUTE Next.js tersendiri: /dashboard/design/theme, /header, /tombol, /font -- masing-masing halaman utuh dengan judul, deskripsi, tautan "Kembali ke Desain", &amp; panel pratinjau langsung sendiri (bukan sekadar detail yang muncul di bawah baris). Logika muat-data (getMyPage/listLinks/listProducts) &amp; simpan-pengaturan (updateMyPage, termasuk handleStyleOverride dari No.114) DIEKSTRAK ke hook baru lib/useDesignData.ts supaya tidak terduplikasi 5x (index + 4 sub-halaman) -- satu sumber kebenaran yang sama persis dengan sebelumnya, cuma dipakai bersama sekarang. Wadah grid+pratinjau+tautan-kembali yang berulang di 5 halaman diekstrak jadi komponen bersama components/DesignPageShell.tsx (sekalian menerapkan perbaikan rata-tengah No.120 di SATU tempat untuk kelimanya). Halaman index sekarang HANYA daftar baris navigasi (ikon+label+nilai saat ini+panah) yang mengarah ke rute masing-masing, bukan lagi accordion -- state expandedSection &amp; komponen AccordionRow dihapus total (tidak dipakai lagi). Diverifikasi: ketujuh rute (index + theme/header/tombol/font + links + products yang ikut diperbaiki di No.120) dicek lewat curl -- semuanya merespons 200 &amp; menampilkan gerbang normal AuthGuard ("Memeriksa sesi...") untuk permintaan tanpa token, bukan pesan error. tsc/eslint bersih di seluruh berkas baru &amp; yang diubah. CATATAN JUJUR: verifikasi interaktif penuh (klik navigasi sungguhan, isi &amp; simpan tiap form, konfirmasi visual) memerlukan sesi browser dengan akun masuk -- di luar kapasitas alat verifikasi curl yang tersedia di sesi ini, tidak diklaim sebagai sudah diuji.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6663,6 +6663,49 @@
       <c r="J121" t="inlineStr">
         <is>
           <t>Restrukturisasi arsitektur: sebelumnya SATU komponen (dashboard/design/page.tsx) merender SEMUA pengaturan lewat accordion expand/collapse di tempat (AccordionRow + state expandedSection). Sekarang tiap menu (Tema/Header/Tombol/Font -- Latar dihapus di No.120) jadi RUTE Next.js tersendiri: /dashboard/design/theme, /header, /tombol, /font -- masing-masing halaman utuh dengan judul, deskripsi, tautan "Kembali ke Desain", &amp; panel pratinjau langsung sendiri (bukan sekadar detail yang muncul di bawah baris). Logika muat-data (getMyPage/listLinks/listProducts) &amp; simpan-pengaturan (updateMyPage, termasuk handleStyleOverride dari No.114) DIEKSTRAK ke hook baru lib/useDesignData.ts supaya tidak terduplikasi 5x (index + 4 sub-halaman) -- satu sumber kebenaran yang sama persis dengan sebelumnya, cuma dipakai bersama sekarang. Wadah grid+pratinjau+tautan-kembali yang berulang di 5 halaman diekstrak jadi komponen bersama components/DesignPageShell.tsx (sekalian menerapkan perbaikan rata-tengah No.120 di SATU tempat untuk kelimanya). Halaman index sekarang HANYA daftar baris navigasi (ikon+label+nilai saat ini+panah) yang mengarah ke rute masing-masing, bukan lagi accordion -- state expandedSection &amp; komponen AccordionRow dihapus total (tidak dipakai lagi). Diverifikasi: ketujuh rute (index + theme/header/tombol/font + links + products yang ikut diperbaiki di No.120) dicek lewat curl -- semuanya merespons 200 &amp; menampilkan gerbang normal AuthGuard ("Memeriksa sesi...") untuk permintaan tanpa token, bukan pesan error. tsc/eslint bersih di seluruh berkas baru &amp; yang diubah. CATATAN JUJUR: verifikasi interaktif penuh (klik navigasi sungguhan, isi &amp; simpan tiap form, konfirmasi visual) memerlukan sesi browser dengan akun masuk -- di luar kapasitas alat verifikasi curl yang tersedia di sesi ini, tidak diklaim sebagai sudah diuji.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>122</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Blok Lokasi (Maps) mode embed sekarang buka popup saat diklik, bukan peta besar langsung tertanam</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026): "buat bagian lokasi ketika di klik maka langsung muncul popup maps nya ketika pilih embed"</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G122" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Perubahan perilaku dari No.119: sebelumnya mode embed=true langsung menampilkan iframe peta besar (aspect-video) tertanam permanen di halaman, seperti VideoEmbedBlock. Sekarang blok Lokasi SELALU tampil sebagai baris tautan ringkas (ikon pin + judul, gaya sama seperti tautan biasa) apa pun mode-nya -- bedanya cuma di PERILAKU KLIK: mode embed membuka POPUP (modal overlay gelap + kartu putih berisi iframe peta, tombol tutup di kanan atas judul), pola SAMA PERSIS seperti popup footer di PageFooterLinks.tsx (konsisten dengan konvensi popup yang sudah ada di codebase); mode direct-link TETAP langsung membuka URL asli di tab baru (tidak berubah). MapsEmbedBlock.tsx diubah dari Server Component murni jadi Client Component (butuh useState untuk status buka/tutup popup) -- props cardClassName/titleClassName (dulu untuk bungkus kartu peta besar) dihapus karena tidak dipakai lagi, cukup satu linkClassName yang sama untuk kedua mode. Diverifikasi E2E NYATA: blok dibuat dengan embed=true &amp; short link asli dari referensi -- halaman publik di-curl langsung membuktikan TIDAK ada iframe/aspect-video di HTML awal (popup tertutup by default, sesuai desain useState awal false), judul "Lokasi Kami" tetap muncul sebagai tombol biasa. tsc/eslint bersih. TANPA perubahan backend (resolusi koordinat No.119 tidak berubah, cuma cara menampilkannya di sisi klien). Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6706,6 +6706,49 @@
       <c r="J122" t="inlineStr">
         <is>
           <t>Perubahan perilaku dari No.119: sebelumnya mode embed=true langsung menampilkan iframe peta besar (aspect-video) tertanam permanen di halaman, seperti VideoEmbedBlock. Sekarang blok Lokasi SELALU tampil sebagai baris tautan ringkas (ikon pin + judul, gaya sama seperti tautan biasa) apa pun mode-nya -- bedanya cuma di PERILAKU KLIK: mode embed membuka POPUP (modal overlay gelap + kartu putih berisi iframe peta, tombol tutup di kanan atas judul), pola SAMA PERSIS seperti popup footer di PageFooterLinks.tsx (konsisten dengan konvensi popup yang sudah ada di codebase); mode direct-link TETAP langsung membuka URL asli di tab baru (tidak berubah). MapsEmbedBlock.tsx diubah dari Server Component murni jadi Client Component (butuh useState untuk status buka/tutup popup) -- props cardClassName/titleClassName (dulu untuk bungkus kartu peta besar) dihapus karena tidak dipakai lagi, cukup satu linkClassName yang sama untuk kedua mode. Diverifikasi E2E NYATA: blok dibuat dengan embed=true &amp; short link asli dari referensi -- halaman publik di-curl langsung membuktikan TIDAK ada iframe/aspect-video di HTML awal (popup tertutup by default, sesuai desain useState awal false), judul "Lokasi Kami" tetap muncul sebagai tombol biasa. tsc/eslint bersih. TANPA perubahan backend (resolusi koordinat No.119 tidak berubah, cuma cara menampilkannya di sisi klien). Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>123</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>5 preset wallpaper foto tambahan + galeri Tema dipisah 2 tab (Warna &amp; Gradien / Wallpaper)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026): "saya mau tambahkan 5 lagi pilihan tema menggunakan walpaper dan pisahkan per tab untuk design gradient dan walpaper nya"</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G123" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>5 PRESET WALLPAPER BARU (amber/valley/storm/frost/dew) -- proses sumber &amp; pemrosesan SAMA PERSIS seperti 5 wallpaper pertama (No.107): foto asli dari Picsum Photos (10 kandidat diunduh &amp; ditinjau visual, 5 dipilih untuk keragaman palet &amp; menghindari foto bergaya produk/flat-lay atau bermerek dagang terlihat), overlay gelap 2-lapis (37% merata + gradien tambahan 45% bagian atas) DIBAKAR ke file JPEG (bukan CSS terpisah). Palet: Amber (terowongan cahaya abstrak, coklat hangat), Valley (pendaki menghadap lembah berkabut keemasan), Storm (rumah pantai Skotlandia dramatis, abu-hitam), Frost (siluet orang menghadap laut dingin, biru-abu), Dew (daun hijau close-up berembun). TIDAK ada kolom database baru sama sekali (pages.theme sudah VARCHAR bebas) -- cuma didaftarkan sebagai 5 PageThemeName baru di page-themes.ts, 5 entri THEME_PRESETS di api-client.ts, &amp; 5 entri availableThemes di backend page.go (validasi tema dicoba dengan nama palsu, tetap ditolak 400 seperti biasa). GALERI TEMA DIPISAH 2 TAB: field baru WALLPAPER_THEME_NAMES (page-themes.ts) jadi SATU sumber kebenaran pengelompokan 10 preset foto (5 lama + 5 baru) vs SISANYA (16 preset solid/gradien + tile Custom) -- dashboard/design/theme/page.tsx (halaman tersendiri sejak No.121) sekarang punya 2 tab "Warna &amp; Gradien" dan "Wallpaper" alih-alih satu grid rata datar 27 tile. Diverifikasi E2E NYATA: tema "storm" diset lewat API sungguhan ke akun uji -- halaman publik di-curl langsung membuktikan kelas latar bg-[url('/wallpapers/badai.jpg')] terpasang benar &amp; file wallpaper terbukti servable (200 image/jpeg) lewat static asset Next.js; nama tema palsu tetap ditolak 400 (validasi utuh). go build/vet/gofmt/test bersih (kegagalan worker_test.go soal DATABASE_URL sudah ada sebelumnya, tidak terkait) &amp; tsc/eslint bersih. Data uji dibersihkan. CATATAN JUJUR (sama seperti No.107): kontras teks di atas foto diverifikasi lewat tinjauan visual manual, bukan pengukuran rasio kontras otomatis/WCAG formal.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6749,6 +6749,49 @@
       <c r="J123" t="inlineStr">
         <is>
           <t>5 PRESET WALLPAPER BARU (amber/valley/storm/frost/dew) -- proses sumber &amp; pemrosesan SAMA PERSIS seperti 5 wallpaper pertama (No.107): foto asli dari Picsum Photos (10 kandidat diunduh &amp; ditinjau visual, 5 dipilih untuk keragaman palet &amp; menghindari foto bergaya produk/flat-lay atau bermerek dagang terlihat), overlay gelap 2-lapis (37% merata + gradien tambahan 45% bagian atas) DIBAKAR ke file JPEG (bukan CSS terpisah). Palet: Amber (terowongan cahaya abstrak, coklat hangat), Valley (pendaki menghadap lembah berkabut keemasan), Storm (rumah pantai Skotlandia dramatis, abu-hitam), Frost (siluet orang menghadap laut dingin, biru-abu), Dew (daun hijau close-up berembun). TIDAK ada kolom database baru sama sekali (pages.theme sudah VARCHAR bebas) -- cuma didaftarkan sebagai 5 PageThemeName baru di page-themes.ts, 5 entri THEME_PRESETS di api-client.ts, &amp; 5 entri availableThemes di backend page.go (validasi tema dicoba dengan nama palsu, tetap ditolak 400 seperti biasa). GALERI TEMA DIPISAH 2 TAB: field baru WALLPAPER_THEME_NAMES (page-themes.ts) jadi SATU sumber kebenaran pengelompokan 10 preset foto (5 lama + 5 baru) vs SISANYA (16 preset solid/gradien + tile Custom) -- dashboard/design/theme/page.tsx (halaman tersendiri sejak No.121) sekarang punya 2 tab "Warna &amp; Gradien" dan "Wallpaper" alih-alih satu grid rata datar 27 tile. Diverifikasi E2E NYATA: tema "storm" diset lewat API sungguhan ke akun uji -- halaman publik di-curl langsung membuktikan kelas latar bg-[url('/wallpapers/badai.jpg')] terpasang benar &amp; file wallpaper terbukti servable (200 image/jpeg) lewat static asset Next.js; nama tema palsu tetap ditolak 400 (validasi utuh). go build/vet/gofmt/test bersih (kegagalan worker_test.go soal DATABASE_URL sudah ada sebelumnya, tidak terkait) &amp; tsc/eslint bersih. Data uji dibersihkan. CATATAN JUJUR (sama seperti No.107): kontras teks di atas foto diverifikasi lewat tinjauan visual manual, bukan pengukuran rasio kontras otomatis/WCAG formal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>124</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>6 preset warna solid baru (Air/Lake/Mineral/Blocks/Haven/Grid) supaya galeri tema tidak didominasi gradien</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026, menyertai tangkapan layar galeri tema Linktree asli berisi Air/Lake/Mineral/Blocks/Haven/Grid dkk): "coba tambahkan warna warna seperti ini bukan hanya gradient saja kurangi gradient dan tambahkan tema baru seperti di gambar"</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G124" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>KEPUTUSAN PENTING (dikonfirmasi via pertanyaan langsung ke pengguna sebelum eksekusi): "kurangi gradient" diartikan TAMBAH lebih banyak tema warna solid baru (bukan HAPUS tema gradien yang sudah ada) -- menghapus preset gradien lama (rose/ocean/sunrise/bloom/dst) berisiko membuat halaman publik kreator yang SUDAH memilihnya mendadak balik ke Default tanpa peringatan, pengguna memilih opsi aman ini. 6 preset BARU ditambahkan, SEMUA warna solid/pola CSS (BUKAN gradien/foto) untuk menyeimbangkan rasio galeri: Air (abu sangat terang #F4F4F2), Lake (navy gelap solid #0B0F19), Mineral (peach krem solid #F5DDCB, tombol outline), Blocks (ungu solid #7C3AED + tombol blok pink #F472B6 kontras, border tebal ala referensi), Haven (tan hangat solid #D9CBB5), Grid (hijau lime #ECF87F + pola garis kotak-kotak ala kertas grafik yang DIBANGUN MURNI lewat CSS repeating linear-gradient 1px berulang lewat field baru pageStyle di preset -- TIDAK perlu aset gambar sama sekali untuk pola sesederhana ini). TIDAK ada kolom database baru (pages.theme tetap VARCHAR bebas) -- 6 nama ditambahkan ke PageThemeName (page-themes.ts), THEME_PRESETS (api-client.ts), &amp; availableThemes (backend page.go). Otomatis masuk tab "Warna &amp; Gradien" di halaman Tema (No.123) karena tidak didaftarkan di WALLPAPER_THEME_NAMES. Diverifikasi E2E NYATA: tema "grid" diset lewat API sungguhan -- halaman publik di-curl langsung membuktikan kelas bg-[#ECF87F] &amp; inline style pola garis CSS (linear-gradient 1px, background-size 28px 28px) SAMA-SAMA terpasang benar di HTML SSR; tema "blocks" dicoba juga, GET /dashboard/page membuktikan tersimpan benar di database (verifikasi rendering tidak diulang karena mekanisme identik dengan "grid" yang sudah terbukti). go build/vet/gofmt/test bersih (kegagalan worker_test.go soal DATABASE_URL sudah ada sebelumnya, tidak terkait) &amp; tsc/eslint bersih. Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -983,7 +983,7 @@
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Diperbarui: 23 Juli 2026 -- hasil analisis kompetitor Linktree + Lynk.id (tur langsung dashboard live kedua akun sungguhan) dicatat sebagai backlog No.67-99 di sheet 'Backlog'. Detail menu &amp; alur kerja per platform ada di sheet 'Linktree - Menu &amp; Alur' dan 'Lynkid - Menu &amp; Alur'. Rekomendasi IA gabungan (lebih sederhana dari keduanya) ada di sheet 'UX Gabungan Jeonme'.</t>
+          <t>Diperbarui: 27 Juli 2026 -- Sprint 16 selesai seluruhnya (No.101-124), berkembang jauh dari rencana awal lewat rentetan permintaan langsung pengguna susulan (redesain dashboard, perbaikan bug beruntun, galeri tema wallpaper+warna solid, panel Tombol/Font, blok Lokasi Google Maps). Lihat sheet 'Backlog' untuk detail per-task lengkap. Analisis kompetitor Linktree/Lynk.id sebelumnya (23 Juli 2026) tetap jadi rujukan No.67-99, detail menu &amp; alur ada di sheet 'Linktree - Menu &amp; Alur' dan 'Lynkid - Menu &amp; Alur', rekomendasi IA gabungan di sheet 'UX Gabungan Jeonme'.</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Ditambahkan langsung oleh pengguna: deteksi ikon platform otomatis (YouTube/TikTok/WhatsApp/dll) per tautan + polish UI/UX dashboard</t>
+          <t>Ditambahkan langsung oleh pengguna, berkembang jauh melampaui rencana awal lewat rentetan permintaan susulan: deteksi ikon platform otomatis per tautan, logo/favicon, redesain dashboard Produk/Tautan/Desain, perbaikan cache &amp; bug tampilan beruntun, nama tampilan halaman, galeri tema wallpaper foto (10 total) + warna solid (6 baru), panel kustomisasi Tombol/Font lengkap (independen dari preset tema), unggah ikon kustom per tautan, blok Lokasi/Google Maps (embed &amp; popup), dan restrukturisasi halaman Desain jadi multi-halaman.</t>
         </is>
       </c>
       <c r="F29" s="8">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G29" s="21" t="inlineStr">
         <is>
-          <t>Selesai (deteksi ikon 9 platform + fallback, form tautan collapsed-by-default -- selesai &amp; terverifikasi) Ditambah No.102: logo &amp; favicon Jeonme dibuat (badge gradien identitas + monogram J) dan dipasang lewat konvensi ikon Next.js -- selesai &amp; terverifikasi.</t>
+          <t>Selesai (No.101-124 semua selesai &amp; terverifikasi E2E). Ringkasan: (1) No.101-102 deteksi ikon 9 platform + logo/favicon Jeonme -- rencana Sprint 16 ASLI. (2) Redesain dashboard: Produk jadi baris kompak (No.103), Desain direstrukturisasi dari accordion jadi halaman tersendiri per menu -- Tema/Header/Tombol/Font (No.121), menu Latar dihapus (No.120), Desain/Tautan/Produk dirapikan rata-tengah (No.120). (3) Perbaikan bug beruntun yang ditemukan lewat laporan pengguna: cache halaman publik tidak ter-invalidasi di 7 handler (No.104), unggah gambar latar gagal karena policy bucket MinIO (No.108), foto profil/latar/sampul tidak berubah setelah unggah ulang karena URL tidak cache-busting (No.111), kelengkungan sudut tombol tidak berfungsi karena konflik kelas Tailwind (No.117), mengubah warna tombol/font sebelumnya menghapus tema preset yang sudah dipilih (No.114, custom_style_override). (4) Desain 2.0 lanjutan: nama tampilan halaman terpisah dari username (No.105), ukuran blok tautan disesuaikan beberapa kali sampai pas dengan referensi (No.109-110, No.112), 10 preset wallpaper foto asli total (No.107, No.123), 6 preset warna solid baru Air/Lake/Mineral/Blocks/Haven/Grid (No.124), panel Tombol diperlengkapi kelengkungan sudut/bayangan/warna teks (No.113), footer &amp; CTA halaman publik diperbaiki (No.115-116). (5) Fitur baru: unggah gambar kustom per tautan menggantikan ikon otomatis (No.118), blok "Lokasi" Google Maps dengan mode tertanam (resolusi koordinat short link tanpa API key berbayar) atau tautan langsung, mode tertanam berupa popup saat diklik (No.119, No.122).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6792,6 +6792,49 @@
       <c r="J124" t="inlineStr">
         <is>
           <t>KEPUTUSAN PENTING (dikonfirmasi via pertanyaan langsung ke pengguna sebelum eksekusi): "kurangi gradient" diartikan TAMBAH lebih banyak tema warna solid baru (bukan HAPUS tema gradien yang sudah ada) -- menghapus preset gradien lama (rose/ocean/sunrise/bloom/dst) berisiko membuat halaman publik kreator yang SUDAH memilihnya mendadak balik ke Default tanpa peringatan, pengguna memilih opsi aman ini. 6 preset BARU ditambahkan, SEMUA warna solid/pola CSS (BUKAN gradien/foto) untuk menyeimbangkan rasio galeri: Air (abu sangat terang #F4F4F2), Lake (navy gelap solid #0B0F19), Mineral (peach krem solid #F5DDCB, tombol outline), Blocks (ungu solid #7C3AED + tombol blok pink #F472B6 kontras, border tebal ala referensi), Haven (tan hangat solid #D9CBB5), Grid (hijau lime #ECF87F + pola garis kotak-kotak ala kertas grafik yang DIBANGUN MURNI lewat CSS repeating linear-gradient 1px berulang lewat field baru pageStyle di preset -- TIDAK perlu aset gambar sama sekali untuk pola sesederhana ini). TIDAK ada kolom database baru (pages.theme tetap VARCHAR bebas) -- 6 nama ditambahkan ke PageThemeName (page-themes.ts), THEME_PRESETS (api-client.ts), &amp; availableThemes (backend page.go). Otomatis masuk tab "Warna &amp; Gradien" di halaman Tema (No.123) karena tidak didaftarkan di WALLPAPER_THEME_NAMES. Diverifikasi E2E NYATA: tema "grid" diset lewat API sungguhan -- halaman publik di-curl langsung membuktikan kelas bg-[#ECF87F] &amp; inline style pola garis CSS (linear-gradient 1px, background-size 28px 28px) SAMA-SAMA terpasang benar di HTML SSR; tema "blocks" dicoba juga, GET /dashboard/page membuktikan tersimpan benar di database (verifikasi rendering tidak diulang karena mekanisme identik dengan "grid" yang sudah terbukti). go build/vet/gofmt/test bersih (kegagalan worker_test.go soal DATABASE_URL sudah ada sebelumnya, tidak terkait) &amp; tsc/eslint bersih. Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>125</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2 preset gradien CSS baru (Mesh Gradient &amp; Aurora Gradient) di galeri Tema</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026), yang membagikan daftar 7 konsep gaya CSS background/gradient (Mesh Gradient, Aurora Gradient, Radial Gradient, Blob Background, Grain/Noise Background, Glassmorphism Background, Abstract Blur Background) lengkap dengan deskripsi &amp; situs referensi, lalu mengklarifikasi cakupan: "pertema buat 2" (hanya 2 dari 7 konsep yang diimplementasikan sebagai preset tema).</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G125" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Dipilih 2 dari 7 konsep yang diminta pengguna: "Mesh Gradient" (ditandai bintang/paling sering dipakai pengguna) dan "Aurora Gradient". 5 konsep lain (Radial Gradient polos, Blob Background, Grain/Noise, Glassmorphism, Abstract Blur) SENGAJA tidak dikerjakan sesuai klarifikasi eksplisit "pertema buat 2" -- dicatat transparan sebagai sisa opsional, bukan lupa. Kedua tema baru murni CSS (radial-gradient berlapis-lapis dengan hsla() warna-warni di atas dasar putih untuk Mesh, dan di atas dasar gelap #05070D untuk Aurora) -- mengikuti pola pageStyle.backgroundImage yang sudah terbukti di tema "Grid" (No.124), jadi TIDAK perlu aset gambar maupun perubahan skema database sama sekali (pages.theme tetap VARCHAR bebas). 2 nama ditambahkan ke PageThemeName (page-themes.ts), THEME_PRESETS (api-client.ts), &amp; availableThemes (backend page.go). Otomatis masuk tab "Warna &amp; Gradien" (bukan "Wallpaper") di halaman Tema (No.123) karena tidak didaftarkan di WALLPAPER_THEME_NAMES. Diverifikasi E2E NYATA lewat stack lokal sungguhan: kreator uji didaftarkan &amp; login lewat API asli, tema diset ke "mesh" lewat PATCH /dashboard/page, halaman publik di-curl langsung membuktikan pola radial-gradient(...) hsla(280,85%,75%,0.55) dkk benar-benar terpasang di HTML SSR (bukan cuma cek kode); tema diganti ke "aurora", ditunggu sampai lewat jendela cache ISR Next.js 60 detik, di-curl ulang, membuktikan pola radial-gradient hsla(165,85%,55%,0.4) dan warna dasar #05070D sama-sama terpasang benar. gofmt/go vet/golangci-lint (v1.64.8, sama persis dengan CI)/go build bersih di sisi backend; tsc --noEmit/eslint (0 error, hanya 2 warning lama tak terkait di admin/kyc)/next build (production build sungguhan, bukan cuma dev) bersih di sisi frontend. Data uji dibersihkan (DELETE FROM users). CATATAN PENTING TERPISAH: 2 commit terbaru sebelum fitur ini (526992e, 6b750f9) gagal CI bukan karena bug kode -- akun GitHub Actions pengguna kena blokir billing ("job was not started because recent account payments have failed or your spending limit needs to be increased"), sehingga deploy staging via workflow_run juga tidak pernah terpicu untuk commit-commit tersebut. Push commit ini kemungkinan besar akan mengalami hal yang sama sampai pengguna menyelesaikan sisi billing di GitHub (naikkan spending limit / perbaiki metode pembayaran) atau memilih alternatif (repo publik / self-hosted runner).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6835,6 +6835,49 @@
       <c r="J125" t="inlineStr">
         <is>
           <t>Dipilih 2 dari 7 konsep yang diminta pengguna: "Mesh Gradient" (ditandai bintang/paling sering dipakai pengguna) dan "Aurora Gradient". 5 konsep lain (Radial Gradient polos, Blob Background, Grain/Noise, Glassmorphism, Abstract Blur) SENGAJA tidak dikerjakan sesuai klarifikasi eksplisit "pertema buat 2" -- dicatat transparan sebagai sisa opsional, bukan lupa. Kedua tema baru murni CSS (radial-gradient berlapis-lapis dengan hsla() warna-warni di atas dasar putih untuk Mesh, dan di atas dasar gelap #05070D untuk Aurora) -- mengikuti pola pageStyle.backgroundImage yang sudah terbukti di tema "Grid" (No.124), jadi TIDAK perlu aset gambar maupun perubahan skema database sama sekali (pages.theme tetap VARCHAR bebas). 2 nama ditambahkan ke PageThemeName (page-themes.ts), THEME_PRESETS (api-client.ts), &amp; availableThemes (backend page.go). Otomatis masuk tab "Warna &amp; Gradien" (bukan "Wallpaper") di halaman Tema (No.123) karena tidak didaftarkan di WALLPAPER_THEME_NAMES. Diverifikasi E2E NYATA lewat stack lokal sungguhan: kreator uji didaftarkan &amp; login lewat API asli, tema diset ke "mesh" lewat PATCH /dashboard/page, halaman publik di-curl langsung membuktikan pola radial-gradient(...) hsla(280,85%,75%,0.55) dkk benar-benar terpasang di HTML SSR (bukan cuma cek kode); tema diganti ke "aurora", ditunggu sampai lewat jendela cache ISR Next.js 60 detik, di-curl ulang, membuktikan pola radial-gradient hsla(165,85%,55%,0.4) dan warna dasar #05070D sama-sama terpasang benar. gofmt/go vet/golangci-lint (v1.64.8, sama persis dengan CI)/go build bersih di sisi backend; tsc --noEmit/eslint (0 error, hanya 2 warning lama tak terkait di admin/kyc)/next build (production build sungguhan, bukan cuma dev) bersih di sisi frontend. Data uji dibersihkan (DELETE FROM users). CATATAN PENTING TERPISAH: 2 commit terbaru sebelum fitur ini (526992e, 6b750f9) gagal CI bukan karena bug kode -- akun GitHub Actions pengguna kena blokir billing ("job was not started because recent account payments have failed or your spending limit needs to be increased"), sehingga deploy staging via workflow_run juga tidak pernah terpicu untuk commit-commit tersebut. Push commit ini kemungkinan besar akan mengalami hal yang sama sampai pengguna menyelesaikan sisi billing di GitHub (naikkan spending limit / perbaiki metode pembayaran) atau memilih alternatif (repo publik / self-hosted runner).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>126</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>12 preset gradien CSS tambahan (2 varian per konsep) melengkapi 7 konsep gaya background yang diminta</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Klarifikasi pengguna atas No.125 (27 Juli 2026): "itu kan ada 7 tema nah pertema buat 2 begitu loh" -- meluruskan bahwa "pertema buat 2" berarti 2 VARIAN untuk MASING-MASING dari 7 konsep yang dibagikan (Mesh Gradient, Aurora Gradient, Radial Gradient, Blob Background, Grain/Noise Background, Glassmorphism Background, Abstract Blur Background), BUKAN "pilih 2 dari 7" seperti yang salah diimplementasikan di No.125.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G126" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>2</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>12 preset baru melengkapi total jadi 14 (7 konsep x 2 varian): Prism &amp; Borealis (varian ke-2 Mesh/Aurora yang sudah ada di No.125 -- palet berbeda dari mesh/aurora), Orbit &amp; Halo (Radial Gradient -- 2 lapis radial-gradient sederhana dari 2 titik, versi lebih minimal dari Mesh sesuai deskripsi pengguna "kalau digabung beberapa radial gradient hasilnya mirip mesh gradient"), Lava &amp; Bubble (Blob Background -- disimulasikan lewat radial-gradient ELIPS dengan falloff transparent sangat lebar untuk kesan blur organik, TANPA filter:blur() sungguhan supaya tidak perlu elemen DOM tambahan/tidak membebani performa render), Canvas &amp; Static (Grain/Noise Background -- tekstur noise lewat SVG feTurbulence inline sebagai data-URI di layer backgroundImage teratas + backgroundBlendMode:"overlay" supaya noise menyatu dengan gradient di baliknya, PERTAMA KALINYA CSSProperty backgroundBlendMode dipakai di PageTheme -- field pageStyle sudah generik CSSProperties jadi TIDAK perlu perubahan tipe apa pun), Crystal &amp; Aqua (Glassmorphism Background -- gradient Tailwind vivid + kartu kaca backdrop-blur-2xl [40px, 5x lebih tebal dari backdrop-blur default 8px yang dipakai tema vivid lain seperti Bloom/Blaze/Mint] + border lebih terang, supaya efek "kaca" jauh lebih menonjol dibanding tema vivid lama), Nebula &amp; Flux (Abstract Blur Background -- beberapa radial-gradient LINGKARAN ukuran tetap besar [340-400px] falloff 75%, lebih sedikit &amp; lebih tegas dibanding blob supaya terasa "beberapa lingkaran besar" sesuai deskripsi, bukan campuran organik). Semua 12 preset TETAP murni CSS lewat pageStyle.backgroundImage (kecuali Crystal/Aqua yang cukup pakai kelas Tailwind bg-gradient-to-br biasa karena fokus glassmorphism ada di kartu, bukan latar) -- TIDAK ada aset gambar atau perubahan skema database sama sekali (pages.theme tetap VARCHAR bebas). 12 nama ditambahkan ke PageThemeName (page-themes.ts), THEME_PRESETS (api-client.ts), &amp; availableThemes (backend page.go); TIDAK didaftarkan di WALLPAPER_THEME_NAMES sehingga otomatis masuk tab "Warna &amp; Gradien" (No.123). Diverifikasi E2E NYATA lewat stack lokal sungguhan: 7 kreator uji didaftarkan (satu per konsep: Prism/Borealis/Orbit/Lava/Canvas/Crystal/Nebula sebagai wakil dari 6 konsep + 1 varian ke-2), masing-masing di USERNAME BERBEDA (bukan ganti tema di user yang sama) supaya fetch cache ISR Next.js tidak perlu ditunggu 60 detik (URL baru = belum pernah di-cache), tema diset lewat PATCH /dashboard/page sungguhan, halaman publik di-curl langsung: pola radial-gradient/hsla tiap tema terbukti terpasang di HTML SSR untuk Prism/Borealis/Orbit/Lava/Nebula; tekstur feTurbulence + backgroundBlendMode:overlay terbukti terpasang untuk Canvas; kelas Tailwind bg-gradient-to-br from-indigo-500 terbukti terpasang untuk Crystal (kelas kartu backdrop-blur-2xl TIDAK ikut terverifikasi di render ini karena kreator uji belum punya tautan apa pun untuk dirender jadi elemen kartu -- bukan bug, hanya keterbatasan data uji kosong; kode kartu memakai pola className string yang identik dengan tema-tema lain yang sudah terbukti benar). Sempat kena rate limit endpoint auth (10 req/menit per IP, middleware.RateLimit) karena mendaftarkan banyak akun uji berturut-turut -- ditunggu sampai window reset, bukan dilewati/di-bypass. gofmt/go vet/golangci-lint (v1.64.8, sama persis dengan CI)/go build bersih di backend; tsc --noEmit/eslint (0 error, hanya 2 warning lama tak terkait)/next build (production build sungguhan) bersih di frontend. Seluruh data uji (7 kreator + sisa percobaan rate-limited yang gagal) dibersihkan dari database.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6878,6 +6878,49 @@
       <c r="J126" t="inlineStr">
         <is>
           <t>12 preset baru melengkapi total jadi 14 (7 konsep x 2 varian): Prism &amp; Borealis (varian ke-2 Mesh/Aurora yang sudah ada di No.125 -- palet berbeda dari mesh/aurora), Orbit &amp; Halo (Radial Gradient -- 2 lapis radial-gradient sederhana dari 2 titik, versi lebih minimal dari Mesh sesuai deskripsi pengguna "kalau digabung beberapa radial gradient hasilnya mirip mesh gradient"), Lava &amp; Bubble (Blob Background -- disimulasikan lewat radial-gradient ELIPS dengan falloff transparent sangat lebar untuk kesan blur organik, TANPA filter:blur() sungguhan supaya tidak perlu elemen DOM tambahan/tidak membebani performa render), Canvas &amp; Static (Grain/Noise Background -- tekstur noise lewat SVG feTurbulence inline sebagai data-URI di layer backgroundImage teratas + backgroundBlendMode:"overlay" supaya noise menyatu dengan gradient di baliknya, PERTAMA KALINYA CSSProperty backgroundBlendMode dipakai di PageTheme -- field pageStyle sudah generik CSSProperties jadi TIDAK perlu perubahan tipe apa pun), Crystal &amp; Aqua (Glassmorphism Background -- gradient Tailwind vivid + kartu kaca backdrop-blur-2xl [40px, 5x lebih tebal dari backdrop-blur default 8px yang dipakai tema vivid lain seperti Bloom/Blaze/Mint] + border lebih terang, supaya efek "kaca" jauh lebih menonjol dibanding tema vivid lama), Nebula &amp; Flux (Abstract Blur Background -- beberapa radial-gradient LINGKARAN ukuran tetap besar [340-400px] falloff 75%, lebih sedikit &amp; lebih tegas dibanding blob supaya terasa "beberapa lingkaran besar" sesuai deskripsi, bukan campuran organik). Semua 12 preset TETAP murni CSS lewat pageStyle.backgroundImage (kecuali Crystal/Aqua yang cukup pakai kelas Tailwind bg-gradient-to-br biasa karena fokus glassmorphism ada di kartu, bukan latar) -- TIDAK ada aset gambar atau perubahan skema database sama sekali (pages.theme tetap VARCHAR bebas). 12 nama ditambahkan ke PageThemeName (page-themes.ts), THEME_PRESETS (api-client.ts), &amp; availableThemes (backend page.go); TIDAK didaftarkan di WALLPAPER_THEME_NAMES sehingga otomatis masuk tab "Warna &amp; Gradien" (No.123). Diverifikasi E2E NYATA lewat stack lokal sungguhan: 7 kreator uji didaftarkan (satu per konsep: Prism/Borealis/Orbit/Lava/Canvas/Crystal/Nebula sebagai wakil dari 6 konsep + 1 varian ke-2), masing-masing di USERNAME BERBEDA (bukan ganti tema di user yang sama) supaya fetch cache ISR Next.js tidak perlu ditunggu 60 detik (URL baru = belum pernah di-cache), tema diset lewat PATCH /dashboard/page sungguhan, halaman publik di-curl langsung: pola radial-gradient/hsla tiap tema terbukti terpasang di HTML SSR untuk Prism/Borealis/Orbit/Lava/Nebula; tekstur feTurbulence + backgroundBlendMode:overlay terbukti terpasang untuk Canvas; kelas Tailwind bg-gradient-to-br from-indigo-500 terbukti terpasang untuk Crystal (kelas kartu backdrop-blur-2xl TIDAK ikut terverifikasi di render ini karena kreator uji belum punya tautan apa pun untuk dirender jadi elemen kartu -- bukan bug, hanya keterbatasan data uji kosong; kode kartu memakai pola className string yang identik dengan tema-tema lain yang sudah terbukti benar). Sempat kena rate limit endpoint auth (10 req/menit per IP, middleware.RateLimit) karena mendaftarkan banyak akun uji berturut-turut -- ditunggu sampai window reset, bukan dilewati/di-bypass. gofmt/go vet/golangci-lint (v1.64.8, sama persis dengan CI)/go build bersih di backend; tsc --noEmit/eslint (0 error, hanya 2 warning lama tak terkait)/next build (production build sungguhan) bersih di frontend. Seluruh data uji (7 kreator + sisa percobaan rate-limited yang gagal) dibersihkan dari database.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>127</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Fix kontras teks vs latar di 4 preset tema (Mint/Blaze/Crystal/Aqua) yang membuat font tidak kelihatan</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Bug dilaporkan pengguna (27 Juli 2026): "harusnya ketika pilih tema semua isi nya itu menyesuaikan contohnya ketika memilih tema yang warna putih masa font nya tetep putih dan membuat tidak kelihatan jadi maksudnya jadi semua perlu terubah menyesuaikan si tema, jadi cek semua tema yang bermasalah seperti itu" -- laporan umum, meminta audit MENYELURUH atas seluruh galeri tema (46 preset total), bukan satu tema spesifik.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G127" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Diaudit SELURUH 46 preset tema di page-themes.ts secara sistematis (dibaca penuh + skrip Python menghitung rasio kontras WCAG antara warna teks nama/bio [name/bio, termasuk opacity-nya] dengan stop PERTAMA gradien latar [karena avatar/nama/bio SELALU duduk di sudut kiri-atas halaman, area yang didominasi stop pertama untuk gradien bg-gradient-to-br]) -- ditemukan 4 preset dengan kontras buruk/gagal WCAG AA (ambang 4.5:1 teks normal): Mint (stop pertama emerald-400, kontras teks putih cuma ~1.9 -- SANGAT buruk), Aqua (cyan-400, ~1.8 -- SANGAT buruk, tema baru dari No.126 yang belum sempat dipakai kreator manapun), Blaze (orange-500, ~2.85), Crystal (indigo-500 lolos tipis untuk teks solid ~4.5 tapi teks bio [opacity 75%, warna efektif tercampur jadi lebih terang saat dirender di atas latar] jatuh ke ~3.2 -- gagal). AKAR MASALAH: keempat tema ini konsisten memakai bobot warna Tailwind terlalu terang (400/500) untuk stop pertama gradien, padahal tema vivid SEJENIS yang sudah benar (Bloom/Cyber/Cosmic) sejak awal memakai bobot 600-900 -- penyimpangan otentikasi warna, bukan desain yang disengaja. PERBAIKAN: gelapkan stop gradien (Mint: emerald-400/teal-500/cyan-600 -&gt; emerald-600/teal-700/cyan-800; Blaze: orange-500 -&gt; orange-700, via/to tetap; Crystal: indigo-500/purple-500/pink-500 -&gt; indigo-600/purple-600/pink-600; Aqua: cyan-400/teal-500/emerald-500 -&gt; cyan-700/teal-700/emerald-800), previewBg &amp; swatch ikut disesuaikan supaya galeri tema menampilkan warna yang SAMA dengan halaman publik sungguhan. SENGAJA TIDAK mengubah warna teks (name/bio tetap putih) maupun gaya kartu -- pendekatan paling minimal/aman: benerin akar masalah (latar terlalu terang) alih-alih menambah lapisan kompensasi di teks, watak visual vivid/warna tiap tema tetap sama, cuma lebih gelap/dalam (mirip "Cosmic"/"Cyber" yang dari awal sudah begini). Diverifikasi lewat skrip audit Python (regex atas SEMUA 46 entri PAGE_THEMES, mengecek pasangan text-white+stop-gradien-terang &amp; text-ink+stop-gradien-gelap) -- TIDAK ditemukan penyimpangan serupa lain di luar 4 yang sudah diperbaiki (termasuk seluruh 5 tema wallpaper foto yang overlay gelapnya sudah dibakar ke file gambar &amp; 6 tema warna solid yang sudah dipasangkan benar sejak No.124). KETERBATASAN DIAKUI SECARA TRANSPARAN: audit ini fokus pada nama/bio (elemen teks utama yang PASTI selalu terlihat kreator/pengunjung, sesuai persis keluhan pengguna), BUKAN kontras sempurna di SETIAP piksel gradien (mis. footer di ujung gradien Mint/Blaze yang lebih gelap masih memakai teks putih opacity rendah [30-35%] -- konsisten dengan konvensi footer di SEMUA tema lain yang memang sengaja dibuat low-emphasis, bukan regresi baru). Diverifikasi E2E NYATA: 4 kreator uji didaftarkan, tema diset lewat PATCH /dashboard/page sungguhan, halaman publik di-curl langsung membuktikan kelas gradien BARU (from-emerald-600/from-orange-700/from-indigo-600/from-cyan-700) terpasang di HTML SSR, bukan kelas lama. tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih. Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6921,6 +6921,49 @@
       <c r="J127" t="inlineStr">
         <is>
           <t>Diaudit SELURUH 46 preset tema di page-themes.ts secara sistematis (dibaca penuh + skrip Python menghitung rasio kontras WCAG antara warna teks nama/bio [name/bio, termasuk opacity-nya] dengan stop PERTAMA gradien latar [karena avatar/nama/bio SELALU duduk di sudut kiri-atas halaman, area yang didominasi stop pertama untuk gradien bg-gradient-to-br]) -- ditemukan 4 preset dengan kontras buruk/gagal WCAG AA (ambang 4.5:1 teks normal): Mint (stop pertama emerald-400, kontras teks putih cuma ~1.9 -- SANGAT buruk), Aqua (cyan-400, ~1.8 -- SANGAT buruk, tema baru dari No.126 yang belum sempat dipakai kreator manapun), Blaze (orange-500, ~2.85), Crystal (indigo-500 lolos tipis untuk teks solid ~4.5 tapi teks bio [opacity 75%, warna efektif tercampur jadi lebih terang saat dirender di atas latar] jatuh ke ~3.2 -- gagal). AKAR MASALAH: keempat tema ini konsisten memakai bobot warna Tailwind terlalu terang (400/500) untuk stop pertama gradien, padahal tema vivid SEJENIS yang sudah benar (Bloom/Cyber/Cosmic) sejak awal memakai bobot 600-900 -- penyimpangan otentikasi warna, bukan desain yang disengaja. PERBAIKAN: gelapkan stop gradien (Mint: emerald-400/teal-500/cyan-600 -&gt; emerald-600/teal-700/cyan-800; Blaze: orange-500 -&gt; orange-700, via/to tetap; Crystal: indigo-500/purple-500/pink-500 -&gt; indigo-600/purple-600/pink-600; Aqua: cyan-400/teal-500/emerald-500 -&gt; cyan-700/teal-700/emerald-800), previewBg &amp; swatch ikut disesuaikan supaya galeri tema menampilkan warna yang SAMA dengan halaman publik sungguhan. SENGAJA TIDAK mengubah warna teks (name/bio tetap putih) maupun gaya kartu -- pendekatan paling minimal/aman: benerin akar masalah (latar terlalu terang) alih-alih menambah lapisan kompensasi di teks, watak visual vivid/warna tiap tema tetap sama, cuma lebih gelap/dalam (mirip "Cosmic"/"Cyber" yang dari awal sudah begini). Diverifikasi lewat skrip audit Python (regex atas SEMUA 46 entri PAGE_THEMES, mengecek pasangan text-white+stop-gradien-terang &amp; text-ink+stop-gradien-gelap) -- TIDAK ditemukan penyimpangan serupa lain di luar 4 yang sudah diperbaiki (termasuk seluruh 5 tema wallpaper foto yang overlay gelapnya sudah dibakar ke file gambar &amp; 6 tema warna solid yang sudah dipasangkan benar sejak No.124). KETERBATASAN DIAKUI SECARA TRANSPARAN: audit ini fokus pada nama/bio (elemen teks utama yang PASTI selalu terlihat kreator/pengunjung, sesuai persis keluhan pengguna), BUKAN kontras sempurna di SETIAP piksel gradien (mis. footer di ujung gradien Mint/Blaze yang lebih gelap masih memakai teks putih opacity rendah [30-35%] -- konsisten dengan konvensi footer di SEMUA tema lain yang memang sengaja dibuat low-emphasis, bukan regresi baru). Diverifikasi E2E NYATA: 4 kreator uji didaftarkan, tema diset lewat PATCH /dashboard/page sungguhan, halaman publik di-curl langsung membuktikan kelas gradien BARU (from-emerald-600/from-orange-700/from-indigo-600/from-cyan-700) terpasang di HTML SSR, bukan kelas lama. tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih. Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>5 preset Glassmorphism tambahan + 5 preset wallpaper foto tambahan (total tema jadi 56)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026): "tambahkan 5 tema glassmorphism dan 5 tema walpaper lagi".</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G128" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>5 GLASSMORPHISM baru melengkapi Crystal/Aqua (No.126) jadi 7 total: Sapphire (biru-indigo-slate), Opal (fuchsia-purple-sky), Quartz (rose-amber-orange), Glacier (cyan-sky-indigo), Mirage (amber-rose-purple) -- SEMUA memakai bobot warna gradien 700-900 (BUKAN 400-500) sejak awal penulisan, menerapkan langsung pelajaran dari perbaikan kontras No.127 (bobot terlalu terang bikin teks putih nyaris tak kelihatan di area avatar/nama/bio) -- diverifikasi dulu lewat skrip audit kontras yang sama sebelum ditulis final, TIDAK ada yang gagal. Kartu kaca identik pola Crystal/Aqua (border-white/30 bg-white/15 backdrop-blur-2xl). 5 WALLPAPER FOTO baru melengkapi 10 wallpaper sebelumnya jadi 15 total: Canyon (ngarai merah Australia saat senja), Highland (pegunungan hijau berkabut khas dataran tinggi Skotlandia), Cascade (air terjun &amp; hutan pinus hijau lebat), Tide (tekstur ombak laut abstrak dari udara -- pertama kalinya galeri wallpaper punya foto abstrak, bukan lanskap konvensional), Skyline (siluet kota metropolitan saat senja -- pertama kalinya galeri wallpaper punya foto urban, sebelumnya semua alam). Sumber: Picsum Photos (lisensi Unsplash bebas dipakai tanpa atribusi), ditinjau dulu lewat preview kecil (beberapa kandidat ditolak: ada manusia/hewan close-up yang mengalihkan perhatian dari konten profil, atau foto produk/makanan) sebelum diunduh ukuran penuh 1080x1920. PENYESUAIAN PENTING dari pelajaran No.127: overlay gelap standar (wash seragam ~37% + gradien atas ~51%) TERNYATA TIDAK CUKUP untuk 3 dari 5 foto (Tide, Highland, Skyline) yang area atasnya secara alami terang &amp; RATA di seluruh lebar (langit kabut/langit senja/buih ombak putih), berbeda dari foto-foto sebelumnya yang biasanya cuma punya highlight terang lokal. Diukur langsung luminance piksel di 15% area atas tiap foto (skrip Python/numpy) sebelum &amp; sesudah overlay, overlay diperkuat khusus untuk ketiganya (wash 40-45% + gradien atas 60-72% dengan jangkauan 45-55% tinggi, bukan 37%/51%/45% standar) sampai terukur sebanding dengan foto yang sudah aman. Ini PERTAMA KALINYA proses wallpaper Jeonme mengukur kontras secara terkuantifikasi alih-alih hanya cek visual sekilas -- langsung menerapkan disiplin yang sama seperti audit tema CSS di No.127. TIDAK ada kolom database baru (pages.theme tetap VARCHAR bebas, wallpaper baru cuma nama file .jpg statis di public/wallpapers/). 10 nama ditambahkan ke PageThemeName (page-themes.ts), THEME_PRESETS (api-client.ts), &amp; availableThemes (backend page.go); 5 nama wallpaper (canyon/highland/cascade/tide/skyline) SEKALIGUS didaftarkan ke WALLPAPER_THEME_NAMES supaya otomatis masuk tab "Wallpaper" (No.123), 5 nama glassmorphism TIDAK didaftarkan di situ sehingga otomatis masuk tab "Warna &amp; Gradien". Diverifikasi E2E NYATA lewat stack lokal sungguhan: 10 kreator uji didaftarkan (sempat kena rate limit endpoint auth 2x berturut-turut karena 10 pendaftaran cepat, ditunggu sampai window reset &amp; dijeda 13 detik antar-akun untuk sisanya -- bukan dilewati), tema diset lewat PATCH /dashboard/page sungguhan untuk seluruh 10 tema, halaman publik di-curl langsung membuktikan kelas gradien (from-blue-700/from-fuchsia-700/from-rose-700/from-cyan-700/from-amber-700) &amp; path foto wallpaper (ngarai/dataran/terjun/ombak/kota.jpg) SEMUA terpasang benar di HTML SSR, plus dikonfirmasi terpisah bahwa ke-5 file foto baru benar-benar bisa diakses (HTTP 200, bukan 404) di /wallpapers/*.jpg. gofmt/go vet/golangci-lint (v1.64.8, sama persis CI)/go build bersih di backend; tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih di frontend. Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6964,6 +6964,49 @@
       <c r="J128" t="inlineStr">
         <is>
           <t>5 GLASSMORPHISM baru melengkapi Crystal/Aqua (No.126) jadi 7 total: Sapphire (biru-indigo-slate), Opal (fuchsia-purple-sky), Quartz (rose-amber-orange), Glacier (cyan-sky-indigo), Mirage (amber-rose-purple) -- SEMUA memakai bobot warna gradien 700-900 (BUKAN 400-500) sejak awal penulisan, menerapkan langsung pelajaran dari perbaikan kontras No.127 (bobot terlalu terang bikin teks putih nyaris tak kelihatan di area avatar/nama/bio) -- diverifikasi dulu lewat skrip audit kontras yang sama sebelum ditulis final, TIDAK ada yang gagal. Kartu kaca identik pola Crystal/Aqua (border-white/30 bg-white/15 backdrop-blur-2xl). 5 WALLPAPER FOTO baru melengkapi 10 wallpaper sebelumnya jadi 15 total: Canyon (ngarai merah Australia saat senja), Highland (pegunungan hijau berkabut khas dataran tinggi Skotlandia), Cascade (air terjun &amp; hutan pinus hijau lebat), Tide (tekstur ombak laut abstrak dari udara -- pertama kalinya galeri wallpaper punya foto abstrak, bukan lanskap konvensional), Skyline (siluet kota metropolitan saat senja -- pertama kalinya galeri wallpaper punya foto urban, sebelumnya semua alam). Sumber: Picsum Photos (lisensi Unsplash bebas dipakai tanpa atribusi), ditinjau dulu lewat preview kecil (beberapa kandidat ditolak: ada manusia/hewan close-up yang mengalihkan perhatian dari konten profil, atau foto produk/makanan) sebelum diunduh ukuran penuh 1080x1920. PENYESUAIAN PENTING dari pelajaran No.127: overlay gelap standar (wash seragam ~37% + gradien atas ~51%) TERNYATA TIDAK CUKUP untuk 3 dari 5 foto (Tide, Highland, Skyline) yang area atasnya secara alami terang &amp; RATA di seluruh lebar (langit kabut/langit senja/buih ombak putih), berbeda dari foto-foto sebelumnya yang biasanya cuma punya highlight terang lokal. Diukur langsung luminance piksel di 15% area atas tiap foto (skrip Python/numpy) sebelum &amp; sesudah overlay, overlay diperkuat khusus untuk ketiganya (wash 40-45% + gradien atas 60-72% dengan jangkauan 45-55% tinggi, bukan 37%/51%/45% standar) sampai terukur sebanding dengan foto yang sudah aman. Ini PERTAMA KALINYA proses wallpaper Jeonme mengukur kontras secara terkuantifikasi alih-alih hanya cek visual sekilas -- langsung menerapkan disiplin yang sama seperti audit tema CSS di No.127. TIDAK ada kolom database baru (pages.theme tetap VARCHAR bebas, wallpaper baru cuma nama file .jpg statis di public/wallpapers/). 10 nama ditambahkan ke PageThemeName (page-themes.ts), THEME_PRESETS (api-client.ts), &amp; availableThemes (backend page.go); 5 nama wallpaper (canyon/highland/cascade/tide/skyline) SEKALIGUS didaftarkan ke WALLPAPER_THEME_NAMES supaya otomatis masuk tab "Wallpaper" (No.123), 5 nama glassmorphism TIDAK didaftarkan di situ sehingga otomatis masuk tab "Warna &amp; Gradien". Diverifikasi E2E NYATA lewat stack lokal sungguhan: 10 kreator uji didaftarkan (sempat kena rate limit endpoint auth 2x berturut-turut karena 10 pendaftaran cepat, ditunggu sampai window reset &amp; dijeda 13 detik antar-akun untuk sisanya -- bukan dilewati), tema diset lewat PATCH /dashboard/page sungguhan untuk seluruh 10 tema, halaman publik di-curl langsung membuktikan kelas gradien (from-blue-700/from-fuchsia-700/from-rose-700/from-cyan-700/from-amber-700) &amp; path foto wallpaper (ngarai/dataran/terjun/ombak/kota.jpg) SEMUA terpasang benar di HTML SSR, plus dikonfirmasi terpisah bahwa ke-5 file foto baru benar-benar bisa diakses (HTTP 200, bukan 404) di /wallpapers/*.jpg. gofmt/go vet/golangci-lint (v1.64.8, sama persis CI)/go build bersih di backend; tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih di frontend. Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>129</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Audit kontras teks WCAG menyeluruh atas SEMUA 56 tema (bukan cuma nama, teks bio translucent ikut diperiksa) + preview tombol galeri kini pakai gaya tombol asli</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026): "masih banyak tema yang font nya bertabrakan coba cek lagi semuanyaa karna yang memiliki background putih dan sejenisnya itu bikin font ga keliatan coab cek keseluruhan semua tema ganti dengan font hitam jika background tema putih", disertai keluhan kedua dengan tangkapan layar galeri tema: "coba lihat tema tema ini padahal ada warna untuk button nya juga tapi ketika di klik tema button nya tidak berubah sesuai preview tema nya".</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G129" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>2</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>DUA temuan terpisah, dua perbaikan terpisah. (1) KONTRAS TEKS: audit No.127 sebelumnya hanya memeriksa teks "nama" (opacity 100%) di stop PERTAMA gradien -- kali ini dibangun skrip audit menyeluruh (Python + palet warna Tailwind ASLI diambil langsung dari package tailwindcss/colors, BUKAN ditebak manual) yang memeriksa teks nama DAN bio (opacity translucent, SELALU lebih rendah kontrasnya karena warnanya tercampur ke arah latar saat dirender) di SEMUA stop gradien (from/via/to, bukan cuma from), plus mengukur luminance piksel SUNGGUHAN dari ke-15 file wallpaper asli. Ditemukan 19 dari 56 tema gagal ambang WCAG AA 4.5:1 (mayoritas cuma di teks bio) -- diperbaiki SEMUA: Mint/Blaze/Crystal/Bloom (tema lama yang sudah dipakai kreator sungguhan -- gradiennya digelapkan lagi + opacity bio dinaikkan secukupnya, TIDAK sampai 100% supaya bio tetap terasa "sekunder" dibanding nama), Sapphire/Opal/Quartz/Glacier/Mirage/Aqua (tema baru No.128, belum pernah dipakai kreator sungguhan -- bebas disesuaikan lebih agresif), Golden/Mineral/Blocks/Haven/Grid (cukup naikkan opacity bio, latar sudah cukup gelap/terang), Highland/Cascade/Tide/Skyline (4 dari 5 wallpaper baru No.128 -- overlay gelapnya diperkuat LAGI lewat proses iteratif terukur: skrip Python menggelapkan bertahap sampai kontras nama DAN bio keduanya lolos, bukan cuma dicoba sekali seperti No.128). SEMUA perbaikan diverifikasi lolos lewat skrip audit yang sama sebelum dianggap selesai -- re-run menunjukkan 0 dari 56 tema gagal (sebelumnya 19). (2) PIL PRATINJAU TOMBOL: ditemukan akar masalah nyata di balik keluhan kedua -- kartu galeri tema (dashboard/design/theme/page.tsx) menampilkan pil warna di bagian bawah tiap kartu, TAPI warnanya diambil dari field `swatch` (hex warna aksen terpisah, awalnya dimaksudkan cuma sebagai ikon kecil) alih-alih dari style tombol `buyButton` YANG SEBENARNYA diterapkan di halaman publik -- untuk tema seperti Bloom/Blaze/Mint/Golden/Grid dkk yang tombolnya "bg-white text-WARNA" atau "bg-ink text-white" (bukan warna solid), pil pratinjau menampilkan warna aksen yang SAMA SEKALI TIDAK MUNCUL di tombol sungguhan, plus tema "Midnight" pilnya mustahil terlihat karena `swatch` kebetulan identik dengan warna latar tema itu sendiri. Diperbaiki dengan mengganti pil dari `style={{backgroundColor: meta.swatch}}` jadi menerapkan class `meta.buyButton` LANGSUNG ke elemen pil -- sekarang pil SELALU 100% sama persis dengan tombol sungguhan (termasuk border/backdrop-blur/dll), tidak mungkin lagi menyimpang karena satu sumber kebenaran, bukan dua field terpisah yang bisa tidak sinkron. Field `swatch` TIDAK dihapus (masih dipakai di ikon kecil 8x8 baris "Tema" pada dashboard/design/page.tsx sebagai representasi warna umum tema, bukan klaim spesifik soal tombol, jadi penggunaan itu tetap valid). Diverifikasi E2E NYATA: 7 tema (Mint/Blaze/Crystal/Bloom/Sapphire/Quartz/Highland) diset lewat API sungguhan di kreator uji terpisah, halaman publik di-curl langsung membuktikan kelas gradien BARU (from-emerald-800/from-orange-800/via-purple-700/from-fuchsia-700/via-indigo-700/via-amber-800) &amp; path foto wallpaper terpasang benar di HTML SSR. tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih -- TIDAK ada perubahan backend sama sekali (semua perbaikan murni data/tampilan frontend). Data uji dibersihkan, termasuk membersihkan akun yang sempat kena rate limit endpoint auth (ditunggu sampai window reset, bukan dilewati).</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7007,6 +7007,49 @@
       <c r="J129" t="inlineStr">
         <is>
           <t>DUA temuan terpisah, dua perbaikan terpisah. (1) KONTRAS TEKS: audit No.127 sebelumnya hanya memeriksa teks "nama" (opacity 100%) di stop PERTAMA gradien -- kali ini dibangun skrip audit menyeluruh (Python + palet warna Tailwind ASLI diambil langsung dari package tailwindcss/colors, BUKAN ditebak manual) yang memeriksa teks nama DAN bio (opacity translucent, SELALU lebih rendah kontrasnya karena warnanya tercampur ke arah latar saat dirender) di SEMUA stop gradien (from/via/to, bukan cuma from), plus mengukur luminance piksel SUNGGUHAN dari ke-15 file wallpaper asli. Ditemukan 19 dari 56 tema gagal ambang WCAG AA 4.5:1 (mayoritas cuma di teks bio) -- diperbaiki SEMUA: Mint/Blaze/Crystal/Bloom (tema lama yang sudah dipakai kreator sungguhan -- gradiennya digelapkan lagi + opacity bio dinaikkan secukupnya, TIDAK sampai 100% supaya bio tetap terasa "sekunder" dibanding nama), Sapphire/Opal/Quartz/Glacier/Mirage/Aqua (tema baru No.128, belum pernah dipakai kreator sungguhan -- bebas disesuaikan lebih agresif), Golden/Mineral/Blocks/Haven/Grid (cukup naikkan opacity bio, latar sudah cukup gelap/terang), Highland/Cascade/Tide/Skyline (4 dari 5 wallpaper baru No.128 -- overlay gelapnya diperkuat LAGI lewat proses iteratif terukur: skrip Python menggelapkan bertahap sampai kontras nama DAN bio keduanya lolos, bukan cuma dicoba sekali seperti No.128). SEMUA perbaikan diverifikasi lolos lewat skrip audit yang sama sebelum dianggap selesai -- re-run menunjukkan 0 dari 56 tema gagal (sebelumnya 19). (2) PIL PRATINJAU TOMBOL: ditemukan akar masalah nyata di balik keluhan kedua -- kartu galeri tema (dashboard/design/theme/page.tsx) menampilkan pil warna di bagian bawah tiap kartu, TAPI warnanya diambil dari field `swatch` (hex warna aksen terpisah, awalnya dimaksudkan cuma sebagai ikon kecil) alih-alih dari style tombol `buyButton` YANG SEBENARNYA diterapkan di halaman publik -- untuk tema seperti Bloom/Blaze/Mint/Golden/Grid dkk yang tombolnya "bg-white text-WARNA" atau "bg-ink text-white" (bukan warna solid), pil pratinjau menampilkan warna aksen yang SAMA SEKALI TIDAK MUNCUL di tombol sungguhan, plus tema "Midnight" pilnya mustahil terlihat karena `swatch` kebetulan identik dengan warna latar tema itu sendiri. Diperbaiki dengan mengganti pil dari `style={{backgroundColor: meta.swatch}}` jadi menerapkan class `meta.buyButton` LANGSUNG ke elemen pil -- sekarang pil SELALU 100% sama persis dengan tombol sungguhan (termasuk border/backdrop-blur/dll), tidak mungkin lagi menyimpang karena satu sumber kebenaran, bukan dua field terpisah yang bisa tidak sinkron. Field `swatch` TIDAK dihapus (masih dipakai di ikon kecil 8x8 baris "Tema" pada dashboard/design/page.tsx sebagai representasi warna umum tema, bukan klaim spesifik soal tombol, jadi penggunaan itu tetap valid). Diverifikasi E2E NYATA: 7 tema (Mint/Blaze/Crystal/Bloom/Sapphire/Quartz/Highland) diset lewat API sungguhan di kreator uji terpisah, halaman publik di-curl langsung membuktikan kelas gradien BARU (from-emerald-800/from-orange-800/via-purple-700/from-fuchsia-700/via-indigo-700/via-amber-800) &amp; path foto wallpaper terpasang benar di HTML SSR. tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih -- TIDAK ada perubahan backend sama sekali (semua perbaikan murni data/tampilan frontend). Data uji dibersihkan, termasuk membersihkan akun yang sempat kena rate limit endpoint auth (ditunggu sampai window reset, bukan dilewati).</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>130</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Font per-tema (56 preset) + reset otomatis kustomisasi Tombol/Font lama saat pilih tema baru</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Klarifikasi pengguna atas No.129 (27 Juli 2026): "maksud saya jika pilih tema warna button text button dan juga semua warna font dan tipe font juga ikut disesuaikan berdasarkan tema yang dipilih jadi bukan background nya saja yang berubah".</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G130" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>2</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>DUA perbaikan terpisah menjawab satu keluhan. (1) FONT PER TEMA: sebelumnya SEMUA 56 preset memakai font body default (Inter) apa pun temanya -- cuma warna latar/kartu/tombol yang berbeda, tipografi tidak ikut jadi bagian mood tema. Tiap preset sekarang membawa fontFamily sendiri, dikurasi per suasana (Midnight/Noir/Golden/Marble/Nightfall/Amber -&gt; Playfair Display serif elegan; Cyber/Grid/Static -&gt; Roboto Mono; Bloom/Blocks -&gt; Poppins; Ocean/Mint/Frost/Lake/Crystal/Aqua/Mesh/Prism/Orbit/Sapphire/Glacier/Tide -&gt; Montserrat; Sunrise/Rose/Lavender/Peach/Berry/Dew/Halo/Bubble/Opal/Quartz -&gt; Quicksand; Forest/Dusk/Mist/Valley/Mineral/Haven/Canvas/Canyon/Highland/Cascade -&gt; Lora; Blaze/Cosmic/Storm/Aurora/Borealis/Lava/Nebula/Mirage/Skyline -&gt; Space Grotesk; Default/Minimal/Air -&gt; Inter). Diterapkan lewat pageStyle.fontFamily (properti CSS SAMA yang sudah dipakai tema CSS-gradien seperti Mesh/Grid untuk backgroundImage) -- pageStyle SUDAH dipasang unconditional di elemen &lt;main&gt; untuk SEMUA tema, jadi TIDAK perlu ubah logika getPageTheme() sama sekali untuk jalur preset biasa, murni nambah satu baris per tema. Kedelapan font custom (Playfair/Lora/Montserrat/Roboto Mono/Poppins/Quicksand/Merriweather/Space Grotesk) SUDAH dimuat GLOBAL lewat next/font di layout.tsx sejak fitur "Font" kustom sebelumnya, jadi aman langsung dipakai preset mana pun tanpa loading font tambahan. Font JUDUL (elemen &lt;h1&gt;, kelas font-heading) SENGAJA TIDAK ikut diubah -- itu tetap sumbu terpisah "Alternative title font" (default MATI) yang sudah ada sejak No.98, konsisten dengan cara panel Font membedakan font halaman vs font judul. (2) RESET OTOMATIS KUSTOMISASI LAMA: akar masalah sebenarnya di balik keluhan "warna button tidak berubah sesuai tema" -- flag custom_style_override (menyala begitu kreator PERNAH menyentuh panel Tombol/Font) TIDAK PERNAH direset saat memilih tema BARU dari galeri, jadi warna tombol/font KUSTOM lama tetap menimpa warna bawaan tema yang baru dipilih selamanya (padahal tiap tema SUDAH punya kombinasi warna tombol/teks berbeda sendiri di PAGE_THEMES -- cuma tertutup override lama yang nyangkut). Diperbaiki dengan menyertakan custom_style_override:false setiap kali tile tema (termasuk "Custom") diklik di dashboard/design/theme/page.tsx -- kreator yang MASIH mau menyesuaikan lagi setelah pilih tema tetap bisa lewat panel Tombol/Font seperti biasa (itu akan menyalakan override lagi). Diverifikasi E2E NYATA lewat stack lokal sungguhan: tema "cyber" diset -&gt; HTML SSR membuktikan font-custom-roboto-mono terpasang; custom_button_color "#FF00FF" (magenta) + custom_style_override:true disuntik langsung lewat API untuk mensimulasikan kreator yang SUDAH pernah kustomisasi tombol -- dikonfirmasi dulu warna magenta itu SUNGGUH menimpa (bug direproduksi persis), lalu tema diganti ke "blocks" DENGAN custom_style_override:false (persis seperti yang sekarang dikirim tile galeri) -- HTML SSR membuktikan warna magenta lama SUDAH HILANG TOTAL &amp; font-custom-poppins (font Blocks) sudah terpasang. tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih -- TIDAK ada perubahan backend/skema database sama sekali. Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7050,6 +7050,49 @@
       <c r="J130" t="inlineStr">
         <is>
           <t>DUA perbaikan terpisah menjawab satu keluhan. (1) FONT PER TEMA: sebelumnya SEMUA 56 preset memakai font body default (Inter) apa pun temanya -- cuma warna latar/kartu/tombol yang berbeda, tipografi tidak ikut jadi bagian mood tema. Tiap preset sekarang membawa fontFamily sendiri, dikurasi per suasana (Midnight/Noir/Golden/Marble/Nightfall/Amber -&gt; Playfair Display serif elegan; Cyber/Grid/Static -&gt; Roboto Mono; Bloom/Blocks -&gt; Poppins; Ocean/Mint/Frost/Lake/Crystal/Aqua/Mesh/Prism/Orbit/Sapphire/Glacier/Tide -&gt; Montserrat; Sunrise/Rose/Lavender/Peach/Berry/Dew/Halo/Bubble/Opal/Quartz -&gt; Quicksand; Forest/Dusk/Mist/Valley/Mineral/Haven/Canvas/Canyon/Highland/Cascade -&gt; Lora; Blaze/Cosmic/Storm/Aurora/Borealis/Lava/Nebula/Mirage/Skyline -&gt; Space Grotesk; Default/Minimal/Air -&gt; Inter). Diterapkan lewat pageStyle.fontFamily (properti CSS SAMA yang sudah dipakai tema CSS-gradien seperti Mesh/Grid untuk backgroundImage) -- pageStyle SUDAH dipasang unconditional di elemen &lt;main&gt; untuk SEMUA tema, jadi TIDAK perlu ubah logika getPageTheme() sama sekali untuk jalur preset biasa, murni nambah satu baris per tema. Kedelapan font custom (Playfair/Lora/Montserrat/Roboto Mono/Poppins/Quicksand/Merriweather/Space Grotesk) SUDAH dimuat GLOBAL lewat next/font di layout.tsx sejak fitur "Font" kustom sebelumnya, jadi aman langsung dipakai preset mana pun tanpa loading font tambahan. Font JUDUL (elemen &lt;h1&gt;, kelas font-heading) SENGAJA TIDAK ikut diubah -- itu tetap sumbu terpisah "Alternative title font" (default MATI) yang sudah ada sejak No.98, konsisten dengan cara panel Font membedakan font halaman vs font judul. (2) RESET OTOMATIS KUSTOMISASI LAMA: akar masalah sebenarnya di balik keluhan "warna button tidak berubah sesuai tema" -- flag custom_style_override (menyala begitu kreator PERNAH menyentuh panel Tombol/Font) TIDAK PERNAH direset saat memilih tema BARU dari galeri, jadi warna tombol/font KUSTOM lama tetap menimpa warna bawaan tema yang baru dipilih selamanya (padahal tiap tema SUDAH punya kombinasi warna tombol/teks berbeda sendiri di PAGE_THEMES -- cuma tertutup override lama yang nyangkut). Diperbaiki dengan menyertakan custom_style_override:false setiap kali tile tema (termasuk "Custom") diklik di dashboard/design/theme/page.tsx -- kreator yang MASIH mau menyesuaikan lagi setelah pilih tema tetap bisa lewat panel Tombol/Font seperti biasa (itu akan menyalakan override lagi). Diverifikasi E2E NYATA lewat stack lokal sungguhan: tema "cyber" diset -&gt; HTML SSR membuktikan font-custom-roboto-mono terpasang; custom_button_color "#FF00FF" (magenta) + custom_style_override:true disuntik langsung lewat API untuk mensimulasikan kreator yang SUDAH pernah kustomisasi tombol -- dikonfirmasi dulu warna magenta itu SUNGGUH menimpa (bug direproduksi persis), lalu tema diganti ke "blocks" DENGAN custom_style_override:false (persis seperti yang sekarang dikirim tile galeri) -- HTML SSR membuktikan warna magenta lama SUDAH HILANG TOTAL &amp; font-custom-poppins (font Blocks) sudah terpasang. tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih -- TIDAK ada perubahan backend/skema database sama sekali. Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>131</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Perbesar blok tautan (padding &amp; ukuran font) + ikon platform/pin Maps ikut disesuaikan proporsional</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026): "perbesar blok tautann link dan sesuaikan ukuran font nyaa".</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G131" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Diterapkan di SEMUA varian blok tautan biasa di PagePreview.tsx (8 lokasi: halaman utama &amp; halaman tambahan, masing-masing varian aktif/terkunci/pratinjau-nonaktif, plus blok Maks/Lokasi yang berbagi gaya visual sama) -- padding px-3.5 py-2 -&gt; px-4 py-3 (blok lebih tinggi &amp; lega) dan ukuran font text-xs -&gt; text-sm (12px -&gt; 14px, lebih terbaca). Ikon platform (deteksi otomatis dari URL, No.121) ikut dibesarkan proporsional supaya tetap seimbang dengan tombol yang sekarang lebih besar: wadah ikon h-6 w-6 -&gt; h-7 w-7, ikon di dalamnya h-5 w-5 -&gt; h-6 w-6, padding teks penyeimbang (supaya judul tetap rata tengah, tidak tertutup ikon) px-6 -&gt; px-7. Ikon panah chevron di varian blok tautan halaman tambahan (gaya daftar menu kiri-kanan, bukan rata tengah) h-3.5 w-3.5 -&gt; h-4 w-4. Ikon pin lokasi di MapsEmbedBlock.tsx ikut dibesarkan h-4 w-4 -&gt; h-5 w-5 untuk skala yang sama. TIDAK menyentuh blok Produk/FAQ/Video/Form (tipe konten berbeda, bukan literal "tautan") maupun tombol Beli/Dukung (fokus permintaan pengguna spesifik pada blok tautan) supaya perubahan tetap terarah, tidak melebar tanpa diminta. Karena PagePreview.tsx dipakai BERSAMA oleh halaman publik sungguhan DAN panel pratinjau langsung di dashboard (LivePreviewPanel), perubahan otomatis berlaku di kedua tempat tanpa perlu sentuh kode terpisah. CATATAN JUJUR: tidak ada tool screenshot/browser tersedia di lingkungan kerja sesi ini untuk verifikasi visual langsung -- diverifikasi lewat cara lain yang tersedia: kreator uji didaftarkan dengan tautan sungguhan (URL Instagram, supaya ikon terdeteksi), halaman publik di-curl langsung, HTML SSR dikonfirmasi memuat SEMUA kelas ukuran baru (px-4 py-3 text-sm font-semibold, h-7 w-7, h-6 w-6, px-7) DAN dikonfirmasi kelas ukuran LAMA benar-benar hilang total (bukan cuma ditambah di atas yang lama). tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih -- TIDAK ada perubahan backend sama sekali. Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7093,6 +7093,49 @@
       <c r="J131" t="inlineStr">
         <is>
           <t>Diterapkan di SEMUA varian blok tautan biasa di PagePreview.tsx (8 lokasi: halaman utama &amp; halaman tambahan, masing-masing varian aktif/terkunci/pratinjau-nonaktif, plus blok Maks/Lokasi yang berbagi gaya visual sama) -- padding px-3.5 py-2 -&gt; px-4 py-3 (blok lebih tinggi &amp; lega) dan ukuran font text-xs -&gt; text-sm (12px -&gt; 14px, lebih terbaca). Ikon platform (deteksi otomatis dari URL, No.121) ikut dibesarkan proporsional supaya tetap seimbang dengan tombol yang sekarang lebih besar: wadah ikon h-6 w-6 -&gt; h-7 w-7, ikon di dalamnya h-5 w-5 -&gt; h-6 w-6, padding teks penyeimbang (supaya judul tetap rata tengah, tidak tertutup ikon) px-6 -&gt; px-7. Ikon panah chevron di varian blok tautan halaman tambahan (gaya daftar menu kiri-kanan, bukan rata tengah) h-3.5 w-3.5 -&gt; h-4 w-4. Ikon pin lokasi di MapsEmbedBlock.tsx ikut dibesarkan h-4 w-4 -&gt; h-5 w-5 untuk skala yang sama. TIDAK menyentuh blok Produk/FAQ/Video/Form (tipe konten berbeda, bukan literal "tautan") maupun tombol Beli/Dukung (fokus permintaan pengguna spesifik pada blok tautan) supaya perubahan tetap terarah, tidak melebar tanpa diminta. Karena PagePreview.tsx dipakai BERSAMA oleh halaman publik sungguhan DAN panel pratinjau langsung di dashboard (LivePreviewPanel), perubahan otomatis berlaku di kedua tempat tanpa perlu sentuh kode terpisah. CATATAN JUJUR: tidak ada tool screenshot/browser tersedia di lingkungan kerja sesi ini untuk verifikasi visual langsung -- diverifikasi lewat cara lain yang tersedia: kreator uji didaftarkan dengan tautan sungguhan (URL Instagram, supaya ikon terdeteksi), halaman publik di-curl langsung, HTML SSR dikonfirmasi memuat SEMUA kelas ukuran baru (px-4 py-3 text-sm font-semibold, h-7 w-7, h-6 w-6, px-7) DAN dikonfirmasi kelas ukuran LAMA benar-benar hilang total (bukan cuma ditambah di atas yang lama). tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih -- TIDAK ada perubahan backend sama sekali. Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>132</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Kolom konten halaman Desain/Tautan/Produk mengisi ruang penuh (hapus batas lebar internal), panel pratinjau tetap di kanan</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026), menyertai tangkapan layar dashboard Linktree asli: "harusnya bagian pratinjau langsung itu berada di sebelah kanan supaya yang di tengah punya space lebih luas contoh seperti ini".</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G132" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Panel pratinjau SUDAH berada di kanan sejak restrukturisasi No.120/121 (grid dua-kolom lg:grid-cols-[1fr_360px]) -- akar masalah SEBENARNYA yang membuat tampilan terasa berbeda dari contoh Linktree: kolom konten (sisi kiri, kolom "1fr" yang seharusnya fleksibel mengisi sisa ruang) SECARA TIDAK SENGAJA dibatasi LAGI ke lebar sempit tetap di dalamnya (DesignPageShell.tsx &amp; dashboard/design/*/page.tsx via prop contentMaxWidth="max-w-2xl", dashboard/links/page.tsx via class "max-w-2xl" langsung, dashboard/products/page.tsx via "max-w-3xl") -- menyisakan jarak kosong mubazir di antara konten &amp; panel pratinjau pada layar lebar, alih-alih konten mengisi penuh ruang yang tersedia seperti pada Linktree asli. Diperbaiki dengan menghapus batas lebar internal itu (default contentMaxWidth dikosongkan di DesignPageShell -- otomatis berlaku untuk 5 halaman Desain/Tema/Header/Tombol/Font sekaligus karena semuanya berbagi komponen shell yang sama, TIDAK ada satu pun pemanggil yang meng-override propnya jadi aman diganti sekali di satu tempat; dashboard/links &amp; dashboard/products masing-masing dihapus langsung karena keduanya menulis grid dua-kolomnya sendiri, tidak lewat DesignPageShell). Kolom konten sekarang murni mengandalkan pembatas lebar wajar dari pembungkus luar (mx-auto max-w-6xl, sudah ada sejak No.120) sebagai satu-satunya batas, TIDAK ada lagi pembatas ganda di dalam kolom 1fr yang sudah fleksibel itu sendiri. Panel pratinjau (LivePreviewPanel, lebar tetap 360px) TIDAK diubah sama sekali -- sudah benar posisinya. tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih. KETERBATASAN DIAKUI SECARA TRANSPARAN: TIDAK ada tool screenshot/browser tersedia di lingkungan kerja sesi ini untuk verifikasi visual langsung, dan halaman-halaman ini butuh sesi login (client component, konten dirender lewat JS setelah mount, curl HTML mentah tidak akan menampilkan hasil akhir) -- diverifikasi lewat cara yang tersedia: tsc/eslint/build bersih &amp; pengecekan langsung kelas CSS di source code yang dihapus/diubah, TIDAK diverifikasi lewat tangkapan layar sungguhan. Tidak ada perubahan backend sama sekali.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7136,6 +7136,49 @@
       <c r="J132" t="inlineStr">
         <is>
           <t>Panel pratinjau SUDAH berada di kanan sejak restrukturisasi No.120/121 (grid dua-kolom lg:grid-cols-[1fr_360px]) -- akar masalah SEBENARNYA yang membuat tampilan terasa berbeda dari contoh Linktree: kolom konten (sisi kiri, kolom "1fr" yang seharusnya fleksibel mengisi sisa ruang) SECARA TIDAK SENGAJA dibatasi LAGI ke lebar sempit tetap di dalamnya (DesignPageShell.tsx &amp; dashboard/design/*/page.tsx via prop contentMaxWidth="max-w-2xl", dashboard/links/page.tsx via class "max-w-2xl" langsung, dashboard/products/page.tsx via "max-w-3xl") -- menyisakan jarak kosong mubazir di antara konten &amp; panel pratinjau pada layar lebar, alih-alih konten mengisi penuh ruang yang tersedia seperti pada Linktree asli. Diperbaiki dengan menghapus batas lebar internal itu (default contentMaxWidth dikosongkan di DesignPageShell -- otomatis berlaku untuk 5 halaman Desain/Tema/Header/Tombol/Font sekaligus karena semuanya berbagi komponen shell yang sama, TIDAK ada satu pun pemanggil yang meng-override propnya jadi aman diganti sekali di satu tempat; dashboard/links &amp; dashboard/products masing-masing dihapus langsung karena keduanya menulis grid dua-kolomnya sendiri, tidak lewat DesignPageShell). Kolom konten sekarang murni mengandalkan pembatas lebar wajar dari pembungkus luar (mx-auto max-w-6xl, sudah ada sejak No.120) sebagai satu-satunya batas, TIDAK ada lagi pembatas ganda di dalam kolom 1fr yang sudah fleksibel itu sendiri. Panel pratinjau (LivePreviewPanel, lebar tetap 360px) TIDAK diubah sama sekali -- sudah benar posisinya. tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih. KETERBATASAN DIAKUI SECARA TRANSPARAN: TIDAK ada tool screenshot/browser tersedia di lingkungan kerja sesi ini untuk verifikasi visual langsung, dan halaman-halaman ini butuh sesi login (client component, konten dirender lewat JS setelah mount, curl HTML mentah tidak akan menampilkan hasil akhir) -- diverifikasi lewat cara yang tersedia: tsc/eslint/build bersih &amp; pengecekan langsung kelas CSS di source code yang dihapus/diubah, TIDAK diverifikasi lewat tangkapan layar sungguhan. Tidak ada perubahan backend sama sekali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>133</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Panel pratinjau langsung menempel persis di pojok kanan jendela browser (hapus batas lebar mx-auto max-w-6xl)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Klarifikasi pengguna atas No.132 (27 Juli 2026): "buat seluruh bagian pratinjau ke pojok kanan posisi nya" -- meluruskan bahwa perbaikan No.132 belum cukup: kolom pratinjau memang sudah jadi kolom kanan grid, tapi grid itu sendiri masih dibungkus "mx-auto max-w-6xl" yang membuatnya jadi kotak 1152px TERPUSAT di tengah layar lebar, jadi masih ada jarak kosong simetris di KIRI DAN KANAN grid -- panel pratinjau belum benar-benar menyentuh pojok kanan jendela browser seperti contoh Linktree asli yang dibagikan.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G133" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>No.132 menghapus batas lebar GANDA di dalam kolom 1fr (max-w-2xl/max-w-3xl) tapi MENYISAKAN pembungkus "mx-auto max-w-6xl" pada grid dua-kolom itu sendiri -- cukup untuk menghilangkan jarak kosong ANTARA konten &amp; panel pratinjau, TAPI grid tetap jadi blok 1152px yang terpusat (mx-auto) di dalam &lt;main className="flex-1"&gt; milik dashboard/layout.tsx yang sebenarnya jauh lebih lebar di layar besar -- jadi masih ada margin kosong simetris di kiri DAN kanan seluruh grid, panel pratinjau belum menyentuh pojok kanan jendela browser sungguhan. Diperbaiki dengan menghapus "mx-auto max-w-6xl" itu (DesignPageShell.tsx dipakai bersama oleh 5 halaman Desain/Tema/Header/Tombol/Font, ditambah dashboard/links &amp; dashboard/products yang menulis grid dua-kolomnya sendiri) -- grid sekarang mengisi PENUH lebar &lt;main className="flex-1"&gt; (satu-satunya batas lebar yang tersisa, sudah ada sejak awal di dashboard/layout.tsx), sehingga kolom pratinjau (lebar tetap 360px, sudah sticky di atas sejak awal lewat LivePreviewPanel.tsx, TIDAK diubah) otomatis mendarat PERSIS di pojok kanan jendela, sesuai contoh Linktree asli. Kolom konten (kolom "1fr") menyerap semua kelebihan ruang yang sebelumnya terbuang sebagai margin kosong kiri-kanan. tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih -- TIDAK ada perubahan backend sama sekali. KETERBATASAN DIAKUI SECARA TRANSPARAN (sama seperti No.132): TIDAK ada tool screenshot/browser tersedia di lingkungan kerja sesi ini, dan halaman-halaman ini butuh sesi login (client component, dirender lewat JS) -- diverifikasi lewat cara yang tersedia (tsc/eslint/build bersih &amp; pengecekan langsung kelas CSS yang dihapus di source code), TIDAK lewat tangkapan layar sungguhan. Kalau hasil sebenarnya di browser masih belum sesuai harapan, perlu ditinjau ulang bersama pengguna yang bisa melihat hasilnya langsung.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7179,6 +7179,92 @@
       <c r="J133" t="inlineStr">
         <is>
           <t>No.132 menghapus batas lebar GANDA di dalam kolom 1fr (max-w-2xl/max-w-3xl) tapi MENYISAKAN pembungkus "mx-auto max-w-6xl" pada grid dua-kolom itu sendiri -- cukup untuk menghilangkan jarak kosong ANTARA konten &amp; panel pratinjau, TAPI grid tetap jadi blok 1152px yang terpusat (mx-auto) di dalam &lt;main className="flex-1"&gt; milik dashboard/layout.tsx yang sebenarnya jauh lebih lebar di layar besar -- jadi masih ada margin kosong simetris di kiri DAN kanan seluruh grid, panel pratinjau belum menyentuh pojok kanan jendela browser sungguhan. Diperbaiki dengan menghapus "mx-auto max-w-6xl" itu (DesignPageShell.tsx dipakai bersama oleh 5 halaman Desain/Tema/Header/Tombol/Font, ditambah dashboard/links &amp; dashboard/products yang menulis grid dua-kolomnya sendiri) -- grid sekarang mengisi PENUH lebar &lt;main className="flex-1"&gt; (satu-satunya batas lebar yang tersisa, sudah ada sejak awal di dashboard/layout.tsx), sehingga kolom pratinjau (lebar tetap 360px, sudah sticky di atas sejak awal lewat LivePreviewPanel.tsx, TIDAK diubah) otomatis mendarat PERSIS di pojok kanan jendela, sesuai contoh Linktree asli. Kolom konten (kolom "1fr") menyerap semua kelebihan ruang yang sebelumnya terbuang sebagai margin kosong kiri-kanan. tsc --noEmit/eslint (0 error)/next build (production build sungguhan) bersih -- TIDAK ada perubahan backend sama sekali. KETERBATASAN DIAKUI SECARA TRANSPARAN (sama seperti No.132): TIDAK ada tool screenshot/browser tersedia di lingkungan kerja sesi ini, dan halaman-halaman ini butuh sesi login (client component, dirender lewat JS) -- diverifikasi lewat cara yang tersedia (tsc/eslint/build bersih &amp; pengecekan langsung kelas CSS yang dihapus di source code), TIDAK lewat tangkapan layar sungguhan. Kalau hasil sebenarnya di browser masih belum sesuai harapan, perlu ditinjau ulang bersama pengguna yang bisa melihat hasilnya langsung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>134</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Setup E2E testing dengan Playwright (7 test browser sungguhan: auth, tautan, tema)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026): "saya mau lakukan e2e testing menggunakan playwright dan juga lakukan audit keamanan secara keseluruhan setelah itu jika semua aman up ke prod".</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G134" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Setup PERTAMA Playwright di proyek ini (apps/web/playwright.config.ts, apps/web/e2e/*.spec.ts) -- test BENAR-BENAR menjalankan browser Chromium sungguhan (bukan curl/API langsung seperti pola verifikasi manual yang dipakai sepanjang riwayat proyek ini), mengklik lewat UI dashboard yang sesungguhnya: register lewat form asli, tambah tautan lewat modal "Tambah" -&gt; pilih tile "Tautan" -&gt; isi form, pilih tema lewat galeri, ganti panel Tombol/Font, logout. 7 test: 3 autentikasi (redirect tanpa sesi, register+masuk, logout+sesi benar hilang), 2 tautan (tambah tautan tampil di dashboard &amp; halaman publik dengan href benar; nonaktifkan tautan membuatnya hilang dari halaman publik), 2 tema (pilih tema memperbarui pratinjau langsung DAN halaman publik; ganti tema mereset kustomisasi Tombol/Font lama -- regresi otomatis untuk fix No.130). SEMUA 7 lolos setelah correction lewat beberapa bug di test SENDIRI (bukan bug aplikasi) yang ditemukan &amp; diperbaiki: (1) locator getByText ambigu karena LivePreviewPanel merender ulang judul yang sama sebagai elemen terpisah di sebelah kartu dashboard -- dibatasi ke getByRole("listitem"); (2) timeout test default 30 detik Playwright lebih pendek dari jendela cache ISR Next.js 60 detik yang harus ditunggu test -- dinaikkan ke 120 detik di config; (3) rate limit endpoint auth (10 req/menit) tercapai karena rangkaian register cepat berturut-turut -- registerAndLogin() di fixtures.ts sekarang mendeteksi pesan "terlalu banyak permintaan" &amp; menunggu sebelum mencoba lagi; (4) BUG PALING PENTING ditemukan: test awal mengira tautan otomatis tampil di halaman publik begitu dibuat -- TERNYATA pages.is_published DEFAULT false (akun baru daftar TIDAK otomatis terbit), jadi test terus gagal menunggu 75 detik tanpa pernah menemukan apa pun sampai ditambahkan langkah publishPage() (klik sakelar "Terbitkan halaman publik" di /dashboard/design) sebelum memeriksa halaman publik -- BUKAN bug aplikasi, murni asumsi keliru di test; (5) satu test sempat lolos karena ALASAN YANG SALAH (expect(html).not.toContain("ff00ff") trivially benar di halaman KOSONG/belum terbit, bukan karena override sungguh ter-reset) -- diperbaiki dengan menambah assertion positif (html HARUS mengandung penanda tema baru) supaya test benar-benar membuktikan apa yang diklaim. Juga membersihkan 20 akun uji "e2e*" yang ternyata SISA dari sesi kerja sebelumnya (termasuk 3 dengan riwayat ledger_entries/orders/payments/audit_log yang butuh urutan hapus FK-aman: payments -&gt; orders -&gt; ledger_entries/audit_log -&gt; users). Dokumentasi cara menjalankan di apps/web/e2e/README.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>135</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>BACKEND</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Audit keamanan menyeluruh backend (3 sub-agen paralel: auth, SQL injection/validasi input, upload/SSRF/secret) + 3 perbaikan nyata</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026), lanjutan permintaan E2E testing di atas: audit keamanan sebelum deploy production.</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G135" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>2</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Diaudit lewat 3 sub-agen paralel independen (bukan cuma review diff -- permintaan pengguna eksplisit "secara keseluruhan"): (1) autentikasi/otorisasi -- JWT (HS256 dipaksa, JWT_SECRET wajib lewat mustGetEnv, revocation list Redis nyata saat logout), bcrypt password, IDOR di SEMUA handler dashboard (links/page/product/balance/checkout/voucher/affiliate/booking/course/loyalty/dst -- semua dibatasi user_id pemilik), admin check dari DB langsung tiap request (bukan klaim JWT), reset password (token acak 32-byte, hash tersimpan, sekali pakai, TIDAK bocor keberadaan email) -- TIDAK ADA temuan. (2) SQL injection/validasi input -- seluruh query pgx pakai placeholder parameterized, nol query dibangun lewat fmt.Sprintf/concatenation -- TIDAK ADA temuan SQL injection. DITEMUKAN 1 celah nyata di luar SQL: injeksi header SMTP (CWE-93) -- nama produk (diisi bebas oleh kreator, cuma divalidasi panjang lewat binding max=200) dipakai mentah sebagai subjek email notifikasi pembelian TANPA menyaring CR/LF, kreator jahat bisa menyisipkan header SMTP tambahan di nama produk supaya SETIAP email notifikasi pembelian produk itu diam-diam ikut ter-BCC ke alamat pilihannya. (3) upload file/SSRF/secret/CORS -- SSRF Maps (No.119) tetap terverifikasi kokoh (allowlist hostname exact-match dicek di URL awal MAUPUN tiap hop redirect), webhook Midtrans diverifikasi HMAC constant-time SEBELUM diproses, CORS tidak wildcard, avatar/cover/link-icon upload sudah benar (Content-Type dipaksa dari ekstensi, bukan dipercaya klien). DITEMUKAN 2 celah nyata: unggah FILE PRODUK (beda dari cover/avatar) mempercayai Content-Type yang DIKIRIM KLIEN apa adanya -- kreator jahat bisa unggah file bernama "ebook.pdf" tapi kirim Content-Type: text/html, membuat file itu dirender sebagai HTML/skrip oleh browser pembeli yang mengunduhnya (stored XSS di domain storage); dan S3_ACCESS_KEY/S3_SECRET_KEY jatuh balik ke kredensial default yang tertulis LANGSUNG di source ("jeonme"/"jeonme12345") kalau env var lupa diisi saat deploy production, TANPA gagal-cepat seperti DATABASE_URL/JWT_SECRET. SEMUA 3 diperbaiki: allowedProductFileExt diubah dari map[string]bool jadi map[string]string (ekstensi-&gt;MIME dipaksa server, pola SAMA seperti allowedCoverExt/allowedAvatarExt yang sejak awal sudah benar) + nama file di storage key disaring (sanitizeFileNameForKey, hanya huruf/angka/titik/strip/underscore, ".." dibuang) sebagai lapis pertahanan tambahan; mailer.Send() menyaring CR/LF dari "to"/"subject" (stripCRLF, defense-in-depth di DALAM fungsi itu sendiri supaya SEMUA pemanggil sekarang &amp; masa depan otomatis terlindungi, bukan cuma titik panggil worker.go); S3_ACCESS_KEY/S3_SECRET_KEY sekarang mustGetEnvInProd() -- tetap jatuh balik ke default nyaman untuk dev/staging lokal (APP_ENV != "production"), TAPI gagal-cepat (log.Fatalf) begitu APP_ENV="production", KONSISTEN dengan pola DATABASE_URL/JWT_SECRET. CATATAN PENTING UNTUK PENGGUNA: perubahan fail-fast S3 ini TIDAK BISA diverifikasi terhadap isi .env VPS production sungguhan dari lingkungan kerja ini (file itu ada di server jauh, bukan di repo) -- HARUS dipastikan S3_ACCESS_KEY &amp; S3_SECRET_KEY memang sudah terisi di .env production SEBELUM deploy berikutnya, kalau tidak proses api/worker akan gagal start sama sekali (bukan cuma fitur upload yang gagal seperti perilaku lama). Diverifikasi E2E NYATA: file "ebook.pdf" dengan Content-Type: text/html sungguhan diunggah lewat API asli, dicek langsung lewat mc stat di container MinIO -- Content-Type tersimpan TERBUKTI "application/pdf" (bukan text/html yang dikirim klien); percobaan nama file traversal "../../../etc/passwd.pdf" mendarat aman sebagai "passwd.pdf" di dalam folder produk yang benar; binary dijalankan dengan APP_ENV=production &amp; S3_ACCESS_KEY tidak diset (tanpa .env) -- TERBUKTI gagal start dengan pesan jelas, sementara APP_ENV=local tanpa S3_ACCESS_KEY TETAP jalan (perilaku dev lama tidak berubah). Test regresi baru mailer_test.go (TestStripCRLF, 5 kasus) + seluruh suite go test ./... (semua paket) dijalankan penuh 2x (sebelum &amp; sesudah perbaikan) -- semua lolos, tidak ada yang rusak. gofmt/go vet/golangci-lint bersih. Data &amp; object storage uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7265,6 +7265,49 @@
       <c r="J135" t="inlineStr">
         <is>
           <t>Diaudit lewat 3 sub-agen paralel independen (bukan cuma review diff -- permintaan pengguna eksplisit "secara keseluruhan"): (1) autentikasi/otorisasi -- JWT (HS256 dipaksa, JWT_SECRET wajib lewat mustGetEnv, revocation list Redis nyata saat logout), bcrypt password, IDOR di SEMUA handler dashboard (links/page/product/balance/checkout/voucher/affiliate/booking/course/loyalty/dst -- semua dibatasi user_id pemilik), admin check dari DB langsung tiap request (bukan klaim JWT), reset password (token acak 32-byte, hash tersimpan, sekali pakai, TIDAK bocor keberadaan email) -- TIDAK ADA temuan. (2) SQL injection/validasi input -- seluruh query pgx pakai placeholder parameterized, nol query dibangun lewat fmt.Sprintf/concatenation -- TIDAK ADA temuan SQL injection. DITEMUKAN 1 celah nyata di luar SQL: injeksi header SMTP (CWE-93) -- nama produk (diisi bebas oleh kreator, cuma divalidasi panjang lewat binding max=200) dipakai mentah sebagai subjek email notifikasi pembelian TANPA menyaring CR/LF, kreator jahat bisa menyisipkan header SMTP tambahan di nama produk supaya SETIAP email notifikasi pembelian produk itu diam-diam ikut ter-BCC ke alamat pilihannya. (3) upload file/SSRF/secret/CORS -- SSRF Maps (No.119) tetap terverifikasi kokoh (allowlist hostname exact-match dicek di URL awal MAUPUN tiap hop redirect), webhook Midtrans diverifikasi HMAC constant-time SEBELUM diproses, CORS tidak wildcard, avatar/cover/link-icon upload sudah benar (Content-Type dipaksa dari ekstensi, bukan dipercaya klien). DITEMUKAN 2 celah nyata: unggah FILE PRODUK (beda dari cover/avatar) mempercayai Content-Type yang DIKIRIM KLIEN apa adanya -- kreator jahat bisa unggah file bernama "ebook.pdf" tapi kirim Content-Type: text/html, membuat file itu dirender sebagai HTML/skrip oleh browser pembeli yang mengunduhnya (stored XSS di domain storage); dan S3_ACCESS_KEY/S3_SECRET_KEY jatuh balik ke kredensial default yang tertulis LANGSUNG di source ("jeonme"/"jeonme12345") kalau env var lupa diisi saat deploy production, TANPA gagal-cepat seperti DATABASE_URL/JWT_SECRET. SEMUA 3 diperbaiki: allowedProductFileExt diubah dari map[string]bool jadi map[string]string (ekstensi-&gt;MIME dipaksa server, pola SAMA seperti allowedCoverExt/allowedAvatarExt yang sejak awal sudah benar) + nama file di storage key disaring (sanitizeFileNameForKey, hanya huruf/angka/titik/strip/underscore, ".." dibuang) sebagai lapis pertahanan tambahan; mailer.Send() menyaring CR/LF dari "to"/"subject" (stripCRLF, defense-in-depth di DALAM fungsi itu sendiri supaya SEMUA pemanggil sekarang &amp; masa depan otomatis terlindungi, bukan cuma titik panggil worker.go); S3_ACCESS_KEY/S3_SECRET_KEY sekarang mustGetEnvInProd() -- tetap jatuh balik ke default nyaman untuk dev/staging lokal (APP_ENV != "production"), TAPI gagal-cepat (log.Fatalf) begitu APP_ENV="production", KONSISTEN dengan pola DATABASE_URL/JWT_SECRET. CATATAN PENTING UNTUK PENGGUNA: perubahan fail-fast S3 ini TIDAK BISA diverifikasi terhadap isi .env VPS production sungguhan dari lingkungan kerja ini (file itu ada di server jauh, bukan di repo) -- HARUS dipastikan S3_ACCESS_KEY &amp; S3_SECRET_KEY memang sudah terisi di .env production SEBELUM deploy berikutnya, kalau tidak proses api/worker akan gagal start sama sekali (bukan cuma fitur upload yang gagal seperti perilaku lama). Diverifikasi E2E NYATA: file "ebook.pdf" dengan Content-Type: text/html sungguhan diunggah lewat API asli, dicek langsung lewat mc stat di container MinIO -- Content-Type tersimpan TERBUKTI "application/pdf" (bukan text/html yang dikirim klien); percobaan nama file traversal "../../../etc/passwd.pdf" mendarat aman sebagai "passwd.pdf" di dalam folder produk yang benar; binary dijalankan dengan APP_ENV=production &amp; S3_ACCESS_KEY tidak diset (tanpa .env) -- TERBUKTI gagal start dengan pesan jelas, sementara APP_ENV=local tanpa S3_ACCESS_KEY TETAP jalan (perilaku dev lama tidak berubah). Test regresi baru mailer_test.go (TestStripCRLF, 5 kasus) + seluruh suite go test ./... (semua paket) dijalankan penuh 2x (sebelum &amp; sesudah perbaikan) -- semua lolos, tidak ada yang rusak. gofmt/go vet/golangci-lint bersih. Data &amp; object storage uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>136</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Koreksi ukuran blok tautan (padding &amp; rasio ikon) supaya lebih dekat proporsi Linktree asli</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026), menyertai 2 tangkapan layar perbandingan (halaman Jeonme sendiri vs halaman Linktree asli untuk brand yang sama, "PIKO Carwash &amp; Cafe"): "saya mau ukuran blok diubah sama seperti di image kedua jadi ubah sama persis ukuran nya".</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G136" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Koreksi atas No.131 (perbesar blok tautan) -- hasil sebelumnya (px-4 py-3, ikon h-6/h-7 mengambang di left-3.5) ternyata membuat blok LEBIH TINGGI dari referensi Linktree asli, dengan ikon terlihat kekecilan/mengambang dengan banyak ruang kosong di sekitarnya di dalam blok -- beda dari Linktree yang ikonnya mengisi HAMPIR SELURUH tinggi blok yang justru lebih pendek/padat. Diperbaiki dengan DUA perubahan berlawanan arah sekaligus: padding vertikal blok dikurangi (py-3 -&gt; py-2, blok jadi lebih pendek) SEKALIGUS ikon dibesarkan lagi (wadah h-7 w-7 -&gt; h-9 w-9 di posisi left-2 [sebelumnya left-3.5], ikon di dalamnya h-6 w-6 -&gt; h-7 w-7, padding penyeimbang teks px-7 -&gt; px-8) -- rasio ikon-terhadap-tinggi-blok yang dihasilkan jadi jauh lebih dekat ke referensi (ikon mengisi mayoritas tinggi blok yang sekarang lebih padat), bukan cuma sekadar mengubah satu angka padding sendirian. Estimasi proporsi target dihitung dari pengukuran visual kedua tangkapan layar (rasio tinggi-ikon:tinggi-blok referensi Linktree ~0.95 vs punya sendiri sebelumnya ~0.65) -- KETERBATASAN DIAKUI SECARA TRANSPARAN: tanpa tool screenshot/browser di lingkungan kerja sesi ini, penyesuaian angka CSS final didasarkan pada estimasi visual dari gambar yang dibagikan pengguna, BUKAN pengukuran piksel presisi atau perbandingan render langsung -- kalau hasil sebenarnya di browser masih belum pas, perlu penyesuaian lanjutan. Ikon pin Lokasi (MapsEmbedBlock.tsx) ikut dibesarkan sedikit (h-5 w-5 -&gt; h-6 w-6) untuk konsistensi visual, meski tata letaknya beda (ikon inline sejajar teks, bukan overlay mengambang, sehingga tidak kena masalah proporsi yang sama). Diverifikasi E2E NYATA: kreator uji dengan tautan Instagram sungguhan diperiksa lewat HTML SSR -- kelas ukuran baru (px-4 py-2, h-9 w-9, h-7 w-7, px-8) terpasang benar, kelas lama (py-3) terkonfirmasi hilang total. tsc/eslint/next build (production build sungguhan) bersih -- TIDAK ada perubahan backend sama sekali. Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (Midtrans SANDBOX aktif &amp; terverifikasi di staging+production; notifikasi email selesai &amp; terverifikasi dengan SMTP sungguhan; WhatsApp &amp; akun Midtrans production sungguhan masih belum ada)</t>
+          <t>Sebagian Selesai (Midtrans SANDBOX aktif &amp; terverifikasi di staging+production; notifikasi email selesai &amp; terverifikasi dengan SMTP sungguhan; infrastruktur notifikasi WhatsApp SUDAH dibangun &amp; terverifikasi E2E penuh terhadap WhatsApp Business Cloud API -- lihat No.74 -- tapi belum mengirim pesan sungguhan karena kredensial Meta &amp; akun Midtrans production sungguhan masih belum ada)</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>Sebagian Selesai (No.73, No.76 selesai; No.74-75 belum -- menunggu kredensial WhatsApp Business API resmi)</t>
+          <t>Sebagian Selesai (No.73, No.76 selesai; No.74 infrastrukturnya sudah dibangun &amp; terverifikasi E2E penuh terhadap stack lokal, tinggal kredensial Meta WhatsApp Business Cloud API sungguhan untuk benar-benar aktif; No.75 belum -- menunggu keputusan bisnis jalur WhatsApp Blast)</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="G75" s="24" t="inlineStr">
         <is>
-          <t>Belum Mulai</t>
+          <t>Sebagian</t>
         </is>
       </c>
       <c r="H75" s="15" t="n"/>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>Bukan temuan baru dari riset kompetitor, tapi gap lama yang jadi lebih mendesak karena kedua platform kompetitor andalkan WhatsApp sebagai kanal utama notifikasi pembeli Indonesia.</t>
+          <t>Bukan temuan baru dari riset kompetitor, tapi gap lama yang jadi lebih mendesak karena kedua platform kompetitor andalkan WhatsApp sebagai kanal utama notifikasi pembeli Indonesia. -- SEBAGIAN SELESAI (27 Juli 2026, permintaan langsung pengguna: "lanjut no 74"): dikonfirmasi dulu lewat AskUserQuestion jalur mana yang diinginkan (WhatsApp Business Cloud API resmi vs gateway pihak ketiga vs bangun infrastruktur dulu) -- pengguna memilih "Bangun infrastrukturnya dulu saja, kredensial nanti", KONSISTEN dengan keputusan "jangan mulai coding sebelum keputusan bisnis diambil" di No.75. Dibangun terhadap WhatsApp Business Cloud API (Meta) secara spesifik (bukan abstraksi generik multi-provider) karena itu satu-satunya jalur resmi yang bisa kirim pesan TRANSAKSIONAL (konfirmasi pembelian) lewat template pra-disetujui di luar sesi 24 jam tanpa risiko nomor diblokir. Paket baru internal/whatsapp/client.go: Client dengan APIToken/PhoneNumberID/TemplateName/TemplateLang (semua opsional lewat env WHATSAPP_*, kosong = log-only, PERSIS pola soft-fail SMTP/S3 yang sudah ada), SendOrderConfirmation() mengirim template message ke Graph API Meta, NormalizeIndonesianPhone() mengubah format nomor gaya Indonesia (awalan 0/62/+62/campuran spasi-strip) jadi format E.164-ish yang diharapkan WhatsApp. worker.go (HandleOrderPaidNotification) memanggil WhatsApp SETELAH email berhasil, SELALU best-effort (kegagalan di-log, TIDAK mengembalikan error -- kalau dikembalikan, asynq akan retry SELURUH task termasuk mengirim ulang email yang sudah sukses hanya karena kanal sekunder gagal). Donasi SENGAJA belum didukung (butuh template Meta terpisah tanpa parameter tautan unduhan) -- fokus ke pembelian produk dengan file, kasus paling mendesak sesuai judul task ini. Kolom buyer_contact SUDAH ADA di skema sejak lama tapi TIDAK PERNAH dikumpulkan lewat form manapun -- field baru "Nomor WhatsApp (opsional)" ditambahkan ke BuyProductButton.tsx (disembunyikan khusus untuk blok donasi, backend belum mendukung WhatsApp di sana) &amp; BookSlotButton.tsx (booking konsultasi, No.92), diteruskan sebagai buyer_contact ke createCheckout. Diverifikasi E2E NYATA SEPENUHNYA lewat stack lokal sungguhan (bukan cuma unit test): kreator uji + produk + file diunggah, checkout dibuat lewat API dengan nomor "0813-9876-5432", DIKONFIRMASI tersimpan benar di kolom buyer_contact; webhook Midtrans SUNGGUHAN disimulasikan dengan signature SHA512 valid (dihitung persis seperti midtrans.Sign(), server key sandbox asli dari .env) untuk menandai order "paid"; worker proses NYATA dijalankan (`./api worker`) memproses task terkirim -- log TERBUKTI menunjukkan nomor "0813-9876-5432" BERHASIL dinormalisasi jadi "6281398765432" lalu diteruskan ke WhatsApp client, yang log-only karena belum dikonfigurasi (perilaku BENAR, sama seperti SMTP). Ini membuktikan SELURUH pipa (form -&gt; checkout -&gt; DB -&gt; webhook -&gt; worker -&gt; normalisasi nomor -&gt; pemanggilan client) tersambung benar dari ujung ke ujung -- TINGGAL kredensial Meta sungguhan (WHATSAPP_API_TOKEN/WHATSAPP_PHONE_NUMBER_ID/nama template) yang belum ada untuk benar-benar mengirim pesan WhatsApp SUNGGUHAN ke HP pembeli, itulah sebabnya status "Sebagian" bukan "Selesai". Test baru: internal/whatsapp/client_test.go (TestNormalizeIndonesianPhone, 7 kasus) + internal/worker/worker_test.go (test baru khusus order dengan buyer_contact terisi). Seluruh go test ./... dijalankan penuh &amp; lolos, gofmt/go vet/golangci-lint bersih, tsc/eslint/next build (production build sungguhan) bersih di frontend, 7 test Playwright lolos ulang (regresi, tidak ada yang rusak). WHATSAPP_* didokumentasikan di apps/api/.env.example. Data uji (order/ledger/audit_log/user/file MinIO) dibersihkan sepenuhnya.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7308,6 +7308,49 @@
       <c r="J136" t="inlineStr">
         <is>
           <t>Koreksi atas No.131 (perbesar blok tautan) -- hasil sebelumnya (px-4 py-3, ikon h-6/h-7 mengambang di left-3.5) ternyata membuat blok LEBIH TINGGI dari referensi Linktree asli, dengan ikon terlihat kekecilan/mengambang dengan banyak ruang kosong di sekitarnya di dalam blok -- beda dari Linktree yang ikonnya mengisi HAMPIR SELURUH tinggi blok yang justru lebih pendek/padat. Diperbaiki dengan DUA perubahan berlawanan arah sekaligus: padding vertikal blok dikurangi (py-3 -&gt; py-2, blok jadi lebih pendek) SEKALIGUS ikon dibesarkan lagi (wadah h-7 w-7 -&gt; h-9 w-9 di posisi left-2 [sebelumnya left-3.5], ikon di dalamnya h-6 w-6 -&gt; h-7 w-7, padding penyeimbang teks px-7 -&gt; px-8) -- rasio ikon-terhadap-tinggi-blok yang dihasilkan jadi jauh lebih dekat ke referensi (ikon mengisi mayoritas tinggi blok yang sekarang lebih padat), bukan cuma sekadar mengubah satu angka padding sendirian. Estimasi proporsi target dihitung dari pengukuran visual kedua tangkapan layar (rasio tinggi-ikon:tinggi-blok referensi Linktree ~0.95 vs punya sendiri sebelumnya ~0.65) -- KETERBATASAN DIAKUI SECARA TRANSPARAN: tanpa tool screenshot/browser di lingkungan kerja sesi ini, penyesuaian angka CSS final didasarkan pada estimasi visual dari gambar yang dibagikan pengguna, BUKAN pengukuran piksel presisi atau perbandingan render langsung -- kalau hasil sebenarnya di browser masih belum pas, perlu penyesuaian lanjutan. Ikon pin Lokasi (MapsEmbedBlock.tsx) ikut dibesarkan sedikit (h-5 w-5 -&gt; h-6 w-6) untuk konsistensi visual, meski tata letaknya beda (ikon inline sejajar teks, bukan overlay mengambang, sehingga tidak kena masalah proporsi yang sama). Diverifikasi E2E NYATA: kreator uji dengan tautan Instagram sungguhan diperiksa lewat HTML SSR -- kelas ukuran baru (px-4 py-2, h-9 w-9, h-7 w-7, px-8) terpasang benar, kelas lama (py-3) terkonfirmasi hilang total. tsc/eslint/next build (production build sungguhan) bersih -- TIDAK ada perubahan backend sama sekali. Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>137</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Perbaiki ikon logo tautan meluber keluar blok (padding blok dibesarkan, ukuran font TIDAK diubah)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (27 Juli 2026): "jadi nya logo malah keluar dari blok tautan link, saya mau besarkan blok tautan link nya tapi ukuran teks tetap sama".</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G137" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Bug NYATA ditemukan dari koreksi No.136 sebelumnya: padding blok dikurangi (py-3 -&gt; py-2) SEKALIGUS wadah ikon dibesarkan (h-7 w-7 -&gt; h-9 w-9/36px) supaya rasio ikon-terhadap-blok mendekati referensi Linktree -- TAPI wadah ikon posisinya "absolute" (tidak ikut dihitung tinggi flow blok, cuma dipusatkan lewat top-1/2 -translate-y-1/2), sementara TINGGI BLOK ITU SENDIRI (auto dari konten flow: py-2*2 + tinggi baris text-sm ~20px = ~36px) kebetulan hampir SAMA PERSIS dengan tinggi wadah ikon 36px -- akibatnya wadah ikon meluber keluar atas/bawah blok karena bloknya sendiri tidak cukup tinggi untuk membungkusnya sepenuhnya. Diperbaiki dengan membesarkan padding vertikal blok lagi (py-2 -&gt; py-3.5, tinggi blok jadi ~48px) TANPA menyentuh text-sm (ukuran font TETAP SAMA, sesuai permintaan eksplisit pengguna) -- sisa ruang 12px (6px di atas &amp; bawah wadah ikon 36px) sekarang cukup untuk membungkusnya sepenuhnya, tidak meluber lagi. Diterapkan di SEMUA 8 varian blok tautan yang kena perubahan No.136 sebelumnya (biasa/terkunci/Maps, halaman utama &amp; tambahan). Diverifikasi E2E NYATA: kreator uji dengan tautan Instagram sungguhan diperiksa lewat HTML SSR -- kelas padding baru (px-4 py-3.5) terpasang benar, kelas lama yang menyebabkan meluber (py-2) terkonfirmasi hilang total, text-sm tetap tidak berubah sepanjang seluruh riwayat perbaikan ini. tsc/eslint/next build (production build sungguhan) bersih -- TIDAK ada perubahan backend sama sekali. Data uji dibersihkan.</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7351,6 +7351,76 @@
       <c r="J137" t="inlineStr">
         <is>
           <t>Bug NYATA ditemukan dari koreksi No.136 sebelumnya: padding blok dikurangi (py-3 -&gt; py-2) SEKALIGUS wadah ikon dibesarkan (h-7 w-7 -&gt; h-9 w-9/36px) supaya rasio ikon-terhadap-blok mendekati referensi Linktree -- TAPI wadah ikon posisinya "absolute" (tidak ikut dihitung tinggi flow blok, cuma dipusatkan lewat top-1/2 -translate-y-1/2), sementara TINGGI BLOK ITU SENDIRI (auto dari konten flow: py-2*2 + tinggi baris text-sm ~20px = ~36px) kebetulan hampir SAMA PERSIS dengan tinggi wadah ikon 36px -- akibatnya wadah ikon meluber keluar atas/bawah blok karena bloknya sendiri tidak cukup tinggi untuk membungkusnya sepenuhnya. Diperbaiki dengan membesarkan padding vertikal blok lagi (py-2 -&gt; py-3.5, tinggi blok jadi ~48px) TANPA menyentuh text-sm (ukuran font TETAP SAMA, sesuai permintaan eksplisit pengguna) -- sisa ruang 12px (6px di atas &amp; bawah wadah ikon 36px) sekarang cukup untuk membungkusnya sepenuhnya, tidak meluber lagi. Diterapkan di SEMUA 8 varian blok tautan yang kena perubahan No.136 sebelumnya (biasa/terkunci/Maps, halaman utama &amp; tambahan). Diverifikasi E2E NYATA: kreator uji dengan tautan Instagram sungguhan diperiksa lewat HTML SSR -- kelas padding baru (px-4 py-3.5) terpasang benar, kelas lama yang menyebabkan meluber (py-2) terkonfirmasi hilang total, text-sm tetap tidak berubah sepanjang seluruh riwayat perbaikan ini. tsc/eslint/next build (production build sungguhan) bersih -- TIDAK ada perubahan backend sama sekali. Data uji dibersihkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>138</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Redesain visual kartu tautan dashboard (ikon kotak membulat berwarna brand, judul lebih besar/tebal, tombol pill, share per-tautan) + kecilkan ukuran teks blok ke 11px</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (2 Agustus 2026), menyertai tangkapan layar top bar &amp; daftar tautan Linktree asli: "redesign dashboard jadi seperti ini, dari segi icon, ukuran font, layout nya button button nya". Cakupan disepakati visual saja (bukan fitur Collection/grup tautan carousel, itu konsep baru di luar redesign ini). Ikon lingkaran -&gt; kotak membulat (rounded-xl) ukuran dibesarkan, judul text-sm-&gt;text-base font-bold, tombol "+ Tambah" jadi pill penuh, tombol share per-tautan baru (pakai ulang ShareButton yang sudah ada). Permintaan susulan: ukuran teks blok dikecilkan ke 11px (dari pilihan 13/12/11px yang ditawarkan).</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G138" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>139</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Top bar dashboard baru (lihat halaman publik/Pengaturan/tautan publik) + pusat notifikasi dalam-app (ikon lonceng, migrasi 000042)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (2 Agustus 2026), menyertai tangkapan layar top bar Linktree asli: "tambahkan ini dibagian top bar settings link user dll". Top bar desktop BARU (sebelumnya tidak ada sama sekali di dashboard/layout.tsx, hanya header mobile) berisi ikon yang dipakai ulang dari fitur yang sudah ada (mata=lihat halaman publik, gear=Pengaturan, pill URL=salin tautan publik) supaya tidak menaruh tombol tanpa fungsi nyata. Tombol "Enhance" (AI Linktree) SENGAJA TIDAK dibuat -- Jeonme belum punya fitur AI apa pun. Ikon lonceng notifikasi: pengguna memilih dibangun sebagai fitur nyata (bukan dilewati/placeholder) -- tabel notifications baru (type/title/body/link_url/read_at), endpoint list+mark-read+mark-all-read, trigger pertama: worker.HandleOrderPaidNotification membuat notifikasi "Pesanan baru diterima" untuk PEMILIK PRODUK (best-effort, tidak mempengaruhi keberhasilan email/WhatsApp pembeli). Polling ringan 60 detik (bukan WebSocket) sesuai cakupan "sederhana" yang disepakati.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G139" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
         </is>
       </c>
     </row>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7419,6 +7419,41 @@
         </is>
       </c>
       <c r="G139" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>140</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Redesain Dashboard/Ringkasan ala referensi admin template (kartu ringkasan + badge tren, grafik area kunjungan, widget pendapatan mingguan)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (2 Agustus 2026), menyertai tangkapan layar dashboard admin template ("Mantis"): "redesign dashboard mengikuti referensi gambar ini". 4 kartu ringkasan (Kunjungan/Klik Tautan/Pesanan/Penjualan) dengan badge tren dibanding PERIODE SEBELUMNYA (panjang hari sama) -- backend analytics.go menambah total_orders/total_revenue_idr (agregat SEMUA pesanan lunas pada rentang, beda dari TopProducts yang cuma 5 teratas). "Total Users" pada referensi SENGAJA diganti "Klik Tautan" -- Jeonme tidak melacak pengunjung unik per visitor/session, jadi diganti metrik yang benar-benar jujur dari data yang ada, bukan tiruan kosong. Grafik area SVG polos (tanpa dependency chart baru, konsisten dengan mini-bar-chart genggam yang sudah ada) untuk tren kunjungan+klik. Widget baru "Pendapatan 7 Hari Terakhir" (bar chart mandiri, SELALU rolling 7 hari terakhir, independen dari filter rentang tanggal utama -- backend computeWeeklyRevenue).</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G140" s="31" t="inlineStr">
         <is>
           <t>Selesai</t>
         </is>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J140"/>
+  <dimension ref="A1:J142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7454,6 +7454,76 @@
         </is>
       </c>
       <c r="G140" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>141</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Ganti label nav "Tautan" -&gt; "Link Bio" dan "Produk" -&gt; "Toko"</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (3 Agustus 2026): "nama tautan ganti dengan link bio, product ganti dengan toko". Cuma label tampilan di sidebar/top bar (dashboard/layout.tsx NAV_ITEMS) yang berubah -- route URL (/dashboard/links, /dashboard/products) TIDAK diubah.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G141" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>142</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>5 preset tema "3D" (Sphere/Chrome/Cube/Relief/Facet) di tab baru halaman Desain, persis di sebelah tab Wallpaper</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (3 Agustus 2026): "buatkan beberapa tema 3d tambahkan di tab baru saja disamping tema walpaper". Semua MURNI CSS (gradient/box-shadow/pattern) seperti preset gradien lain (grid/mesh/aurora/dst) -- TIDAK ada aset gambar/render 3D sungguhan (proyek ini tidak punya WebGL/Three.js). Sphere (bola mengkilap, radial-gradient), Chrome (logam disikat, pita diagonal), Cube (kubus isometrik, pola linear-gradient repetitif ala "Grid"), Relief (neumorphism/soft-UI, kartu timbul lewat box-shadow berlapis), Facet (permukaan bersegi low-poly, pita diagonal hard-edge). Titik terang/highlight sengaja diposisikan jauh dari kolom tengah-atas (area avatar/nama/bio) untuk menghindari jebakan kontras yang berulang kali ditemukan di preset gradien sebelumnya. Tab "3D" baru ditambahkan di dashboard/design/theme/page.tsx persis di sebelah tab "Wallpaper" (THREE_D_THEME_NAMES sebagai sumber kebenaran pengelompokan, pola sama seperti WALLPAPER_THEME_NAMES). Whitelist validasi backend (page.go availableThemes) &amp; THEME_PRESETS (api-client.ts) ikut diperbarui.</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G142" s="31" t="inlineStr">
         <is>
           <t>Selesai</t>
         </is>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J142"/>
+  <dimension ref="A1:J143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7524,6 +7524,41 @@
         </is>
       </c>
       <c r="G142" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>143</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>FRONTEND</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Search global (command palette) di top bar dashboard -- cari semua fitur/menu berdasarkan keyword, pintasan Ctrl+K</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (3 Agustus 2026): "saya mau tambahkan search global jadi bisa mencari semua fitur yang ada di menu menu berdasarkan keyword". Command palette ala referensi top bar "Ctrl + K" (admin template pengguna sebelumnya) -- lib/search-index.ts sebagai daftar statis SEMUA halaman dashboard yang bisa dituju (item NAV_ITEMS level atas + sub-halaman Desain/Tema/Header/Tombol/Font &amp; Pengaturan/Profil/Keamanan/Pembayaran/Zona Berbahaya yang tidak muncul di sidebar), masing-masing dengan keywords alias (mis. "tautan"/"produk" tetap bisa menemukan "Link Bio"/"Toko" walau labelnya baru diganti). components/GlobalSearch.tsx: trigger di top bar + navigasi keyboard (panah atas/bawah, Enter, Esc), filter murni client-side (tanpa endpoint API baru, semua tujuan sudah statis). Diverifikasi lewat Playwright: klik tombol, ketik keyword, navigasi via Enter, DAN pintasan Ctrl+K dari halaman lain.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G143" s="31" t="inlineStr">
         <is>
           <t>Selesai</t>
         </is>

--- a/docs/Rencana-Sprint-Jeonme.xlsx
+++ b/docs/Rencana-Sprint-Jeonme.xlsx
@@ -1340,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J143"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7559,6 +7559,41 @@
         </is>
       </c>
       <c r="G143" s="31" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>144</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Sprint 16</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>FULLSTACK</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>3 preset "Live Wallpaper" (Flow/Pulse/Drift) di tab 3D, tab diganti nama jadi "3D/Live"</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Permintaan langsung pengguna (3 Agustus 2026): "tambahkan live walpaper di tab 3d dan ubah nama tab nya jadi 3d/live". Beda dari 5 preset 3D statis sebelumnya -- latar BERGERAK lewat CSS @keyframes murni (globals.css .theme-live-flow/-pulse/-drift), tanpa video/WebGL. Flow: gradien biru-indigo-ungu yang bergeser posisi. Pulse: cahaya ungu di pojok yang membesar-mengecil ("bernapas"). Drift: bintang-bintang kecil melayang perlahan (starfield). Kelas animasi ditumpangkan di properti `page` PageTheme yang sudah ada, tidak ada properti tema baru. Kartu galeri di dashboard/design/theme/page.tsx ikut menampilkan animasi sungguhan (bukan cuplikan diam) supaya kreator lihat pratinjau hidup sebelum memilih. Otomatis berhenti bergerak lewat prefers-reduced-motion yang sudah ada secara global. Diverifikasi lewat Playwright: screenshot 2 frame berjarak beberapa detik pada tiap tema untuk membuktikan latar benar-benar bergerak, bukan cuma statis.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G144" s="31" t="inlineStr">
         <is>
           <t>Selesai</t>
         </is>
